--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C4A9F1C-6E30-4BD5-B831-C02C8CD6A569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00CF85DE-F2BB-49F5-BB9D-374819A9978B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1F1A6BF-F341-4931-AE03-14F7AB521259}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{542074E4-56A8-43BD-A6C0-5B3F26D05838}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1630,7 +1630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C3B866-B74E-4F11-A50D-3BF1C261FDF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5479951-E0F7-4195-ACD6-D493E5D48CB5}">
   <dimension ref="B3:R292"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00CF85DE-F2BB-49F5-BB9D-374819A9978B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F65469-C98E-47B6-993B-4EBBB8706CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{542074E4-56A8-43BD-A6C0-5B3F26D05838}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CCD32770-07C0-46D1-AE1E-E5ABDE2BCFD4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -359,154 +359,154 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -371.0 km- way/160201298-330;way/170832455-275</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- way/160201298-330;way/172887193-330</t>
-  </si>
-  <si>
-    <t>grid link -238.0 km- way/223939702-220;way/87853100-330</t>
-  </si>
-  <si>
-    <t>grid link -10.0 km- AU104-220;way/89180086-220</t>
-  </si>
-  <si>
-    <t>grid link -285.0 km- way/64943050-500;way/89180086-220</t>
-  </si>
-  <si>
-    <t>grid link -145.0 km- way/312550977-500;way/89180086-220</t>
-  </si>
-  <si>
-    <t>grid link -223.0 km- way/169794711-220;way/89180086-220</t>
-  </si>
-  <si>
-    <t>grid link -537.0 km- way/169416665-220;way/169794711-220</t>
-  </si>
-  <si>
-    <t>grid link -364.0 km- AU104-220;way/169794711-220</t>
-  </si>
-  <si>
-    <t>grid link -102.0 km- way/171486427-275;way/432510474-275</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- way/119995150-275;way/171486427-275</t>
-  </si>
-  <si>
-    <t>grid link -152.0 km- way/121646942-275;way/171486427-275</t>
-  </si>
-  <si>
-    <t>grid link -365.0 km- way/169794711-220;way/830928846-220</t>
-  </si>
-  <si>
-    <t>grid link -120.0 km- way/170709510-275;way/172887193-330</t>
-  </si>
-  <si>
-    <t>grid link -150.0 km- way/171728751-275;way/432510474-275</t>
-  </si>
-  <si>
-    <t>grid link -36.0 km- way/119995150-275;way/171486427-275</t>
-  </si>
-  <si>
-    <t>grid link -222.0 km- way/119995150-275;way/432510474-275</t>
-  </si>
-  <si>
-    <t>grid link -361.0 km- way/119995150-275;way/170709510-275</t>
-  </si>
-  <si>
-    <t>grid link -250.0 km- way/655511604-330;way/925410265-330</t>
-  </si>
-  <si>
-    <t>grid link -294.0 km- AU73-330;way/160201298-330</t>
-  </si>
-  <si>
-    <t>grid link -255.0 km- AU73-330;way/169408193-330</t>
-  </si>
-  <si>
-    <t>grid link -249.0 km- way/171744075-275;way/196583889-275</t>
-  </si>
-  <si>
-    <t>grid link -201.0 km- way/169416665-220;way/172231145-330</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- way/164764363-275;way/164775125-275</t>
-  </si>
-  <si>
-    <t>grid link -100.0 km- way/170709510-275;way/171728751-275</t>
-  </si>
-  <si>
-    <t>grid link -254.0 km- way/337655870-220;way/583492111-220</t>
-  </si>
-  <si>
-    <t>grid link -398.0 km- AU51-220;way/223939702-220</t>
-  </si>
-  <si>
-    <t>grid link -278.0 km- way/169408193-330;way/925410265-330</t>
-  </si>
-  <si>
-    <t>grid link -489.0 km- way/174875093-330;way/64943050-500</t>
-  </si>
-  <si>
-    <t>grid link -223.0 km- way/166113109-275;way/171486427-275</t>
-  </si>
-  <si>
-    <t>grid link -68.0 km- way/121646942-275;way/166113109-275</t>
-  </si>
-  <si>
-    <t>grid link -87.0 km- way/174441055-220;way/88191017-220</t>
-  </si>
-  <si>
-    <t>grid link -421.0 km- way/172362099-275;way/312550977-500</t>
-  </si>
-  <si>
-    <t>grid link -109.0 km- AU57-330;way/87853100-330</t>
-  </si>
-  <si>
-    <t>grid link -589.0 km- way/164775125-275;way/169794711-220</t>
-  </si>
-  <si>
-    <t>grid link -187.0 km- way/164775125-275;way/172362099-275</t>
-  </si>
-  <si>
-    <t>grid link -228.0 km- way/480009927-500;way/570175005-220</t>
-  </si>
-  <si>
-    <t>grid link -47.0 km- way/570175005-220;way/64943050-500</t>
-  </si>
-  <si>
-    <t>grid link -199.0 km- way/480009927-500;way/64943050-500</t>
-  </si>
-  <si>
-    <t>grid link -71.0 km- way/166113109-275;way/171744075-275</t>
-  </si>
-  <si>
-    <t>grid link -407.0 km- AU73-330;way/925410265-330</t>
-  </si>
-  <si>
-    <t>grid link -126.0 km- way/170709510-275;way/170832455-275</t>
-  </si>
-  <si>
-    <t>grid link -109.0 km- way/170709510-275;way/172887193-330</t>
-  </si>
-  <si>
-    <t>grid link -41.0 km- way/170709510-275;way/550221344-275</t>
-  </si>
-  <si>
-    <t>grid link -85.0 km- way/337655870-220;way/583506664-220</t>
-  </si>
-  <si>
-    <t>grid link -337.0 km- way/208359871-330;way/655511604-330</t>
-  </si>
-  <si>
-    <t>grid link -175.0 km- way/174875093-330;way/208359871-330</t>
-  </si>
-  <si>
-    <t>grid link -102.0 km- way/172231145-330;way/174875093-330</t>
-  </si>
-  <si>
-    <t>grid link -138.0 km- way/172231145-330;way/208359871-330</t>
-  </si>
-  <si>
-    <t>grid link -114.0 km- AU57-330;way/950049612-330</t>
+    <t>grid link -371.0 km- way/160201298-330;way/170832455-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- way/160201298-330;way/172887193-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -238.0 km- way/223939702-220;way/87853100-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -10.0 km- AU104-220;way/89180086-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -285.0 km- way/64943050-500;way/89180086-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -145.0 km- way/312550977-500;way/89180086-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -223.0 km- way/169794711-220;way/89180086-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -537.0 km- way/169416665-220;way/169794711-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -364.0 km- AU104-220;way/169794711-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -102.0 km- way/171486427-275;way/432510474-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- way/119995150-275;way/171486427-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -152.0 km- way/121646942-275;way/171486427-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -365.0 km- way/169794711-220;way/830928846-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -120.0 km- way/170709510-275;way/172887193-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -150.0 km- way/171728751-275;way/432510474-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -36.0 km- way/119995150-275;way/171486427-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -222.0 km- way/119995150-275;way/432510474-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -361.0 km- way/119995150-275;way/170709510-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -250.0 km- way/655511604-330;way/925410265-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -294.0 km- AU73-330;way/160201298-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -255.0 km- AU73-330;way/169408193-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -249.0 km- way/171744075-275;way/196583889-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -201.0 km- way/169416665-220;way/172231145-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- way/164764363-275;way/164775125-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -100.0 km- way/170709510-275;way/171728751-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -254.0 km- way/337655870-220;way/583492111-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -398.0 km- AU51-220;way/223939702-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -278.0 km- way/169408193-330;way/925410265-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -489.0 km- way/174875093-330;way/64943050-500 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -223.0 km- way/166113109-275;way/171486427-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -68.0 km- way/121646942-275;way/166113109-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -87.0 km- way/174441055-220;way/88191017-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -421.0 km- way/172362099-275;way/312550977-500 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -109.0 km- AU57-330;way/87853100-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -589.0 km- way/164775125-275;way/169794711-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -187.0 km- way/164775125-275;way/172362099-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -228.0 km- way/480009927-500;way/570175005-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -47.0 km- way/570175005-220;way/64943050-500 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -199.0 km- way/480009927-500;way/64943050-500 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -71.0 km- way/166113109-275;way/171744075-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -407.0 km- AU73-330;way/925410265-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -126.0 km- way/170709510-275;way/170832455-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -109.0 km- way/170709510-275;way/172887193-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -41.0 km- way/170709510-275;way/550221344-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -85.0 km- way/337655870-220;way/583506664-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -337.0 km- way/208359871-330;way/655511604-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -175.0 km- way/174875093-330;way/208359871-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -102.0 km- way/172231145-330;way/174875093-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -138.0 km- way/172231145-330;way/208359871-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -114.0 km- AU57-330;way/950049612-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>~commodity_geo</t>
@@ -1630,7 +1630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5479951-E0F7-4195-ACD6-D493E5D48CB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D89C7E-1E35-40F0-8566-BCDE4CD587EE}">
   <dimension ref="B3:R292"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F65469-C98E-47B6-993B-4EBBB8706CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83AC07DE-7B7B-44F4-875A-BA5858414505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CCD32770-07C0-46D1-AE1E-E5ABDE2BCFD4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CCA1F90A-DCE5-40F5-946B-941B1E819CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="416">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -74,10 +74,10 @@
     <t>e_Armidale_AUS</t>
   </si>
   <si>
-    <t>e_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>g_Armidale_AUS-Blackwall_AUS</t>
+    <t>e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>g_Armidale_AUS-Brisbane_AUS</t>
   </si>
   <si>
     <t>B</t>
@@ -227,6 +227,12 @@
     <t>g_Davenport_AUS-Robertstown_AUS</t>
   </si>
   <si>
+    <t>e_Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>g_Dubbo_AUS-MountPiper_AUS</t>
+  </si>
+  <si>
     <t>g_GinGin_AUS-Tarong_AUS</t>
   </si>
   <si>
@@ -245,6 +251,15 @@
     <t>g_Merredin_AUS-Kalgoorlie_AUS</t>
   </si>
   <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>g_Morawa_AUS-Yandin_AUS</t>
+  </si>
+  <si>
     <t>g_MountPiper_AUS-SydneyWest_AUS</t>
   </si>
   <si>
@@ -284,6 +299,12 @@
     <t>g_Perth_AUS-Australind_AUS</t>
   </si>
   <si>
+    <t>e_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>g_PortHedland_AUS-Karratha_AUS</t>
+  </si>
+  <si>
     <t>g_Robertstown_AUS-Balranald_AUS</t>
   </si>
   <si>
@@ -311,7 +332,7 @@
     <t>g_SydneyWest_AUS-CentralCoast_AUS</t>
   </si>
   <si>
-    <t>g_Tarong_AUS-Blackwall_AUS</t>
+    <t>g_Tarong_AUS-Brisbane_AUS</t>
   </si>
   <si>
     <t>g_Tarong_AUS-BulliCreek_AUS</t>
@@ -344,9 +365,6 @@
     <t>g_Wagga_AUS-UpperTumut_AUS</t>
   </si>
   <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
     <t>g_Yandin_AUS-Perth_AUS</t>
   </si>
   <si>
@@ -359,7 +377,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -371.0 km- way/160201298-330;way/170832455-275 (thermal x 0.7 N-1)</t>
+    <t>grid link -371.0 km- way/160201298-330;way/172587651-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>grid link -90.0 km- way/160201298-330;way/172887193-330 (thermal x 0.7 N-1)</t>
@@ -431,6 +449,9 @@
     <t>grid link -94.0 km- way/164764363-275;way/164775125-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -249.0 km- way/169406848-330;way/169408193-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -100.0 km- way/170709510-275;way/171728751-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -440,6 +461,9 @@
     <t>grid link -398.0 km- AU51-220;way/223939702-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -118.0 km- way/583513574-330;way/950049612-330 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -278.0 km- way/169408193-330;way/925410265-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -461,6 +485,9 @@
     <t>grid link -109.0 km- AU57-330;way/87853100-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -303.0 km- AU3-220;way/583492111-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -589.0 km- way/164775125-275;way/169794711-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -482,7 +509,7 @@
     <t>grid link -407.0 km- AU73-330;way/925410265-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>grid link -126.0 km- way/170709510-275;way/170832455-275 (thermal x 0.7 N-1)</t>
+    <t>grid link -126.0 km- way/170709510-275;way/172587651-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>grid link -109.0 km- way/170709510-275;way/172887193-330 (thermal x 0.7 N-1)</t>
@@ -1630,8 +1657,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D89C7E-1E35-40F0-8566-BCDE4CD587EE}">
-  <dimension ref="B3:R292"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A6817A-36C9-40B7-A5F2-87927B98DCFE}">
+  <dimension ref="B3:R295"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1639,10 +1666,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="O3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -1668,22 +1695,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="O4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="P4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="R4" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -1712,10 +1739,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -1753,7 +1780,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O6" t="s">
         <v>10</v>
@@ -1794,7 +1821,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="O7" t="s">
         <v>16</v>
@@ -1835,7 +1862,7 @@
         <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="O8" t="s">
         <v>19</v>
@@ -1876,7 +1903,7 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O9" t="s">
         <v>26</v>
@@ -1917,19 +1944,19 @@
         <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="O10" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="P10" t="s">
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>152.78594479220749</v>
+        <v>150.48716060704265</v>
       </c>
       <c r="R10">
-        <v>-27.541324760522063</v>
+        <v>-23.537233256213721</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -1958,19 +1985,19 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>150.48716060704265</v>
+        <v>152.95633561497641</v>
       </c>
       <c r="R11">
-        <v>-23.537233256213721</v>
+        <v>-27.732264407857119</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -1999,7 +2026,7 @@
         <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>36</v>
@@ -2040,7 +2067,7 @@
         <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="O13" t="s">
         <v>38</v>
@@ -2081,7 +2108,7 @@
         <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s">
         <v>14</v>
@@ -2122,7 +2149,7 @@
         <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="O15" t="s">
         <v>32</v>
@@ -2163,7 +2190,7 @@
         <v>37</v>
       </c>
       <c r="L16" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -2204,7 +2231,7 @@
         <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="O17" t="s">
         <v>47</v>
@@ -2245,7 +2272,7 @@
         <v>41</v>
       </c>
       <c r="L18" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O18" t="s">
         <v>50</v>
@@ -2286,7 +2313,7 @@
         <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O19" t="s">
         <v>54</v>
@@ -2327,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="L20" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="O20" t="s">
         <v>28</v>
@@ -2368,7 +2395,7 @@
         <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="O21" t="s">
         <v>59</v>
@@ -2409,19 +2436,19 @@
         <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O22" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>151.81952564800682</v>
+        <v>148.9632109591046</v>
       </c>
       <c r="R22">
-        <v>-24.90133538944163</v>
+        <v>-32.527168433245279</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2450,19 +2477,19 @@
         <v>49</v>
       </c>
       <c r="L23" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="O23" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>146.42885495857578</v>
+        <v>151.81952564800682</v>
       </c>
       <c r="R23">
-        <v>-38.281663652861432</v>
+        <v>-24.90133538944163</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2491,19 +2518,19 @@
         <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="O24" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>142.28083100000038</v>
+        <v>146.42885495857578</v>
       </c>
       <c r="R24">
-        <v>-36.721698083045936</v>
+        <v>-38.281663652861432</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2532,19 +2559,19 @@
         <v>53</v>
       </c>
       <c r="L25" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O25" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>121.42358390000004</v>
+        <v>142.28083100000038</v>
       </c>
       <c r="R25">
-        <v>-30.781882477049411</v>
+        <v>-36.721698083045936</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
@@ -2573,19 +2600,19 @@
         <v>56</v>
       </c>
       <c r="L26" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="O26" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>116.74275233957847</v>
+        <v>121.42358390000004</v>
       </c>
       <c r="R26">
-        <v>-20.762601878195927</v>
+        <v>-30.781882477049411</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -2614,19 +2641,19 @@
         <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O27" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>118.22746058460694</v>
+        <v>116.74275233957847</v>
       </c>
       <c r="R27">
-        <v>-31.539704529422323</v>
+        <v>-20.762601878195927</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
@@ -2655,19 +2682,19 @@
         <v>61</v>
       </c>
       <c r="L28" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="O28" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>150.02574011758799</v>
+        <v>118.22746058460694</v>
       </c>
       <c r="R28">
-        <v>-33.363653242312999</v>
+        <v>-31.539704529422323</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
@@ -2681,34 +2708,34 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="O29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>148.144166863903</v>
+        <v>116.7594477898767</v>
       </c>
       <c r="R29">
-        <v>-36.225604818390735</v>
+        <v>-29.187814184805315</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
@@ -2722,34 +2749,34 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" t="s">
         <v>64</v>
-      </c>
-      <c r="G30" t="s">
-        <v>65</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L30" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="O30" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>148.68315461202329</v>
+        <v>150.02574011758799</v>
       </c>
       <c r="R30">
-        <v>-21.63132000917609</v>
+        <v>-33.363653242312999</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
@@ -2763,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
@@ -2778,7 +2805,7 @@
         <v>67</v>
       </c>
       <c r="L31" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="O31" t="s">
         <v>74</v>
@@ -2787,10 +2814,10 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>146.98953647822455</v>
+        <v>148.144166863903</v>
       </c>
       <c r="R31">
-        <v>-41.7876715671242</v>
+        <v>-36.225604818390735</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
@@ -2804,34 +2831,34 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L32" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="O32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>138.71215621124384</v>
+        <v>148.68315461202329</v>
       </c>
       <c r="R32">
-        <v>-34.7354348842319</v>
+        <v>-21.63132000917609</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.45">
@@ -2845,22 +2872,22 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L33" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="O33" t="s">
         <v>79</v>
@@ -2869,10 +2896,10 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>115.84737549921022</v>
+        <v>146.98953647822455</v>
       </c>
       <c r="R33">
-        <v>-32.189392578269448</v>
+        <v>-41.7876715671242</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.45">
@@ -2886,34 +2913,34 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L34" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O34" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>139.12683826085333</v>
+        <v>138.71215621124384</v>
       </c>
       <c r="R34">
-        <v>-33.956428790142837</v>
+        <v>-34.7354348842319</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.45">
@@ -2927,34 +2954,34 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L35" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P35" t="s">
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>145.22587842608721</v>
+        <v>115.84737549921022</v>
       </c>
       <c r="R35">
-        <v>-37.929945191522378</v>
+        <v>-32.189392578269448</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.45">
@@ -2968,34 +2995,34 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L36" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O36" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>146.30697121829795</v>
+        <v>118.54463160000005</v>
       </c>
       <c r="R36">
-        <v>-41.33568787101467</v>
+        <v>-20.432074971605672</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.45">
@@ -3009,10 +3036,10 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
         <v>78</v>
@@ -3024,19 +3051,19 @@
         <v>78</v>
       </c>
       <c r="L37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O37" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>145.07540407639536</v>
+        <v>139.12683826085333</v>
       </c>
       <c r="R37">
-        <v>-37.645174301346643</v>
+        <v>-33.956428790142837</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.45">
@@ -3053,31 +3080,31 @@
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="O38" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>147.7754061331616</v>
+        <v>145.22587842608721</v>
       </c>
       <c r="R38">
-        <v>-20.499447155592211</v>
+        <v>-37.929945191522378</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.45">
@@ -3091,34 +3118,34 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O39" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="P39" t="s">
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>150.82867670028497</v>
+        <v>146.30697121829795</v>
       </c>
       <c r="R39">
-        <v>-33.815823161761138</v>
+        <v>-41.33568787101467</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.45">
@@ -3132,34 +3159,34 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="O40" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="P40" t="s">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>151.90657331394655</v>
+        <v>145.07540407639536</v>
       </c>
       <c r="R40">
-        <v>-26.786815702260583</v>
+        <v>-37.645174301346643</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.45">
@@ -3173,34 +3200,34 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L41" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="O41" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="P41" t="s">
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>142.18101587735953</v>
+        <v>147.7754061331616</v>
       </c>
       <c r="R41">
-        <v>-38.17911060837443</v>
+        <v>-20.499447155592211</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.45">
@@ -3214,34 +3241,34 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L42" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="O42" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P42" t="s">
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>117.77622337735301</v>
+        <v>150.82867670028497</v>
       </c>
       <c r="R42">
-        <v>-22.73480648494872</v>
+        <v>-33.815823161761138</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.45">
@@ -3255,34 +3282,34 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L43" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="O43" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="P43" t="s">
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>148.38595135487864</v>
+        <v>151.90657331394655</v>
       </c>
       <c r="R43">
-        <v>-35.91111863050287</v>
+        <v>-26.786815702260583</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.45">
@@ -3296,34 +3323,34 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L44" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O44" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="P44" t="s">
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>147.39393085110601</v>
+        <v>142.18101587735953</v>
       </c>
       <c r="R44">
-        <v>-35.200406760019412</v>
+        <v>-38.17911060837443</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.45">
@@ -3337,34 +3364,34 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L45" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O45" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>149.76896533906228</v>
+        <v>117.77622337735301</v>
       </c>
       <c r="R45">
-        <v>-26.268566355497121</v>
+        <v>-22.73480648494872</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.45">
@@ -3378,34 +3405,34 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="O46" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>115.53508832785479</v>
+        <v>148.38595135487864</v>
       </c>
       <c r="R46">
-        <v>-30.767640414252401</v>
+        <v>-35.91111863050287</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.45">
@@ -3419,34 +3446,34 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L47" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="O47" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="P47" t="s">
         <v>8</v>
       </c>
       <c r="Q47">
-        <v>126.87543483120088</v>
+        <v>147.39393085110601</v>
       </c>
       <c r="R47">
-        <v>-31.570835856427525</v>
+        <v>-35.200406760019412</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.45">
@@ -3460,34 +3487,34 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L48" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O48" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="P48" t="s">
         <v>8</v>
       </c>
       <c r="Q48">
-        <v>138.68088035579376</v>
+        <v>149.76896533906228</v>
       </c>
       <c r="R48">
-        <v>-33.050322280935085</v>
+        <v>-26.268566355497121</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.45">
@@ -3501,34 +3528,34 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O49" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="P49" t="s">
         <v>8</v>
       </c>
       <c r="Q49">
-        <v>133.78757460034689</v>
+        <v>115.53508832785479</v>
       </c>
       <c r="R49">
-        <v>-31.537820769156081</v>
+        <v>-30.767640414252401</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.45">
@@ -3542,34 +3569,34 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O50" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
       </c>
       <c r="Q50">
-        <v>138.41823350812663</v>
+        <v>126.87543483120088</v>
       </c>
       <c r="R50">
-        <v>-35.501951363966938</v>
+        <v>-31.570835856427525</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.45">
@@ -3583,34 +3610,34 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L51" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="O51" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>132.10100769152496</v>
+        <v>138.68088035579376</v>
       </c>
       <c r="R51">
-        <v>-25.49357352256672</v>
+        <v>-33.050322280935085</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.45">
@@ -3624,34 +3651,34 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G52" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O52" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
       </c>
       <c r="Q52">
-        <v>133.70279525625577</v>
+        <v>133.78757460034689</v>
       </c>
       <c r="R52">
-        <v>-28.066746287936159</v>
+        <v>-31.537820769156081</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.45">
@@ -3665,34 +3692,34 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="F53" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="G53" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="O53" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>131.34409440196771</v>
+        <v>138.41823350812663</v>
       </c>
       <c r="R53">
-        <v>-28.04146789637413</v>
+        <v>-35.501951363966938</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3706,3365 +3733,3488 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G54" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L54" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="O54" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
+        <v>132.10100769152496</v>
+      </c>
+      <c r="R54">
+        <v>-25.49357352256672</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" t="s">
+        <v>106</v>
+      </c>
+      <c r="L55" t="s">
+        <v>162</v>
+      </c>
+      <c r="O55" t="s">
+        <v>175</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>133.70279525625577</v>
+      </c>
+      <c r="R55">
+        <v>-28.066746287936159</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F56" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" t="s">
+        <v>107</v>
+      </c>
+      <c r="H56" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" t="s">
+        <v>107</v>
+      </c>
+      <c r="L56" t="s">
+        <v>163</v>
+      </c>
+      <c r="O56" t="s">
+        <v>176</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>131.34409440196771</v>
+      </c>
+      <c r="R56">
+        <v>-28.04146789637413</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" t="s">
+        <v>108</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" t="s">
+        <v>164</v>
+      </c>
+      <c r="O57" t="s">
+        <v>177</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
         <v>130.63850148412087</v>
       </c>
-      <c r="R54">
+      <c r="R57">
         <v>-30.151673533026507</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O55" t="s">
-        <v>169</v>
-      </c>
-      <c r="P55" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q55">
-        <v>136.6543963226575</v>
-      </c>
-      <c r="R55">
-        <v>-30.346236863934219</v>
-      </c>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O56" t="s">
-        <v>170</v>
-      </c>
-      <c r="P56" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q56">
-        <v>134.69581248525074</v>
-      </c>
-      <c r="R56">
-        <v>-30.730748793905519</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O57" t="s">
-        <v>171</v>
-      </c>
-      <c r="P57" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q57">
-        <v>135.42179448527094</v>
-      </c>
-      <c r="R57">
-        <v>-24.023047149503736</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O58" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>130.86103071723457</v>
+        <v>136.6543963226575</v>
       </c>
       <c r="R58">
-        <v>-22.595450439397052</v>
+        <v>-30.346236863934219</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O59" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>140.73446817308161</v>
+        <v>134.69581248525074</v>
       </c>
       <c r="R59">
-        <v>-31.100522794087091</v>
+        <v>-30.730748793905519</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O60" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>136.74960353581776</v>
+        <v>135.42179448527094</v>
       </c>
       <c r="R60">
-        <v>-28.096813504185462</v>
+        <v>-24.023047149503736</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O61" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>138.55276692913932</v>
+        <v>130.86103071723457</v>
       </c>
       <c r="R61">
-        <v>-26.886442670709371</v>
+        <v>-22.595450439397052</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O62" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>134.09893869430459</v>
+        <v>140.73446817308161</v>
       </c>
       <c r="R62">
-        <v>-12.767605192826451</v>
+        <v>-31.100522794087091</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O63" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>136.25707133560488</v>
+        <v>136.74960353581776</v>
       </c>
       <c r="R63">
-        <v>-16.639117165833714</v>
+        <v>-28.096813504185462</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O64" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>140.33047031611449</v>
+        <v>138.55276692913932</v>
       </c>
       <c r="R64">
-        <v>-19.270168976498251</v>
+        <v>-26.886442670709371</v>
       </c>
     </row>
     <row r="65" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O65" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>131.02821227078974</v>
+        <v>134.09893869430459</v>
       </c>
       <c r="R65">
-        <v>-20.288555696485421</v>
+        <v>-12.767605192826451</v>
       </c>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O66" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>132.9773260478994</v>
+        <v>136.25707133560488</v>
       </c>
       <c r="R66">
-        <v>-19.134632003477144</v>
+        <v>-16.639117165833714</v>
       </c>
     </row>
     <row r="67" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O67" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>133.08033774630167</v>
+        <v>140.33047031611449</v>
       </c>
       <c r="R67">
-        <v>-17.232170442209615</v>
+        <v>-19.270168976498251</v>
       </c>
     </row>
     <row r="68" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O68" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>130.07387926508619</v>
+        <v>131.02821227078974</v>
       </c>
       <c r="R68">
-        <v>-15.90683731540358</v>
+        <v>-20.288555696485421</v>
       </c>
     </row>
     <row r="69" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O69" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>131.44822420859035</v>
+        <v>132.9773260478994</v>
       </c>
       <c r="R69">
-        <v>-12.82434425746715</v>
+        <v>-19.134632003477144</v>
       </c>
     </row>
     <row r="70" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O70" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>144.06475345158557</v>
+        <v>133.08033774630167</v>
       </c>
       <c r="R70">
-        <v>-14.918328674842474</v>
+        <v>-17.232170442209615</v>
       </c>
     </row>
     <row r="71" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O71" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>142.83587016468007</v>
+        <v>130.07387926508619</v>
       </c>
       <c r="R71">
-        <v>-12.686216555715513</v>
+        <v>-15.90683731540358</v>
       </c>
     </row>
     <row r="72" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O72" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>142.40851942403145</v>
+        <v>131.44822420859035</v>
       </c>
       <c r="R72">
-        <v>-18.491878095825161</v>
+        <v>-12.82434425746715</v>
       </c>
     </row>
     <row r="73" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O73" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>145.31671437316541</v>
+        <v>144.06475345158557</v>
       </c>
       <c r="R73">
-        <v>-19.409940321761617</v>
+        <v>-14.918328674842474</v>
       </c>
     </row>
     <row r="74" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O74" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>143.2193142021186</v>
+        <v>142.83587016468007</v>
       </c>
       <c r="R74">
-        <v>-21.577252989404748</v>
+        <v>-12.686216555715513</v>
       </c>
     </row>
     <row r="75" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O75" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>141.13298709337377</v>
+        <v>142.40851942403145</v>
       </c>
       <c r="R75">
-        <v>-22.375086663489547</v>
+        <v>-18.491878095825161</v>
       </c>
     </row>
     <row r="76" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O76" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>138.88894971874203</v>
+        <v>145.31671437316541</v>
       </c>
       <c r="R76">
-        <v>-24.087766437384666</v>
+        <v>-19.409940321761617</v>
       </c>
     </row>
     <row r="77" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O77" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>136.76817822772392</v>
+        <v>143.2193142021186</v>
       </c>
       <c r="R77">
-        <v>-19.38668521985424</v>
+        <v>-21.577252989404748</v>
       </c>
     </row>
     <row r="78" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O78" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>136.4508348496494</v>
+        <v>141.13298709337377</v>
       </c>
       <c r="R78">
-        <v>-21.384730246760789</v>
+        <v>-22.375086663489547</v>
       </c>
     </row>
     <row r="79" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O79" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>127.74686025752874</v>
+        <v>138.88894971874203</v>
       </c>
       <c r="R79">
-        <v>-16.305787203948107</v>
+        <v>-24.087766437384666</v>
       </c>
     </row>
     <row r="80" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O80" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>127.14468786066958</v>
+        <v>136.76817822772392</v>
       </c>
       <c r="R80">
-        <v>-21.316826063663147</v>
+        <v>-19.38668521985424</v>
       </c>
     </row>
     <row r="81" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O81" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>128.03124895889869</v>
+        <v>136.4508348496494</v>
       </c>
       <c r="R81">
-        <v>-19.504849900358565</v>
+        <v>-21.384730246760789</v>
       </c>
     </row>
     <row r="82" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O82" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>124.30097588195656</v>
+        <v>127.74686025752874</v>
       </c>
       <c r="R82">
-        <v>-19.646611890372487</v>
+        <v>-16.305787203948107</v>
       </c>
     </row>
     <row r="83" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O83" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>125.44646700631158</v>
+        <v>127.14468786066958</v>
       </c>
       <c r="R83">
-        <v>-18.034517000819385</v>
+        <v>-21.316826063663147</v>
       </c>
     </row>
     <row r="84" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O84" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>119.8792314384001</v>
+        <v>128.03124895889869</v>
       </c>
       <c r="R84">
-        <v>-26.943751576747506</v>
+        <v>-19.504849900358565</v>
       </c>
     </row>
     <row r="85" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O85" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>123.91849872196477</v>
+        <v>124.30097588195656</v>
       </c>
       <c r="R85">
-        <v>-28.596430984362627</v>
+        <v>-19.646611890372487</v>
       </c>
     </row>
     <row r="86" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O86" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>120.83347096461442</v>
+        <v>125.44646700631158</v>
       </c>
       <c r="R86">
-        <v>-28.749113003071905</v>
+        <v>-18.034517000819385</v>
       </c>
     </row>
     <row r="87" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O87" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>127.45396257591824</v>
+        <v>119.8792314384001</v>
       </c>
       <c r="R87">
-        <v>-29.710182852828943</v>
+        <v>-26.943751576747506</v>
       </c>
     </row>
     <row r="88" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O88" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>125.2634274064108</v>
+        <v>123.91849872196477</v>
       </c>
       <c r="R88">
-        <v>-30.48444119537271</v>
+        <v>-28.596430984362627</v>
       </c>
     </row>
     <row r="89" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O89" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P89" t="s">
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>124.60722906157319</v>
+        <v>120.83347096461442</v>
       </c>
       <c r="R89">
-        <v>-31.80277872120627</v>
+        <v>-28.749113003071905</v>
       </c>
     </row>
     <row r="90" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>122.14641208564728</v>
+        <v>127.45396257591824</v>
       </c>
       <c r="R90">
-        <v>-30.486367305495254</v>
+        <v>-29.710182852828943</v>
       </c>
     </row>
     <row r="91" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>126.75981019754011</v>
+        <v>125.2634274064108</v>
       </c>
       <c r="R91">
-        <v>-23.110892098770499</v>
+        <v>-30.48444119537271</v>
       </c>
     </row>
     <row r="92" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>125.01398345772546</v>
+        <v>124.60722906157319</v>
       </c>
       <c r="R92">
-        <v>-26.67735817029363</v>
+        <v>-31.80277872120627</v>
       </c>
     </row>
     <row r="93" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>127.5392725342796</v>
+        <v>122.14641208564728</v>
       </c>
       <c r="R93">
-        <v>-26.043555904293484</v>
+        <v>-30.486367305495254</v>
       </c>
     </row>
     <row r="94" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>121.1112351491342</v>
+        <v>126.75981019754011</v>
       </c>
       <c r="R94">
-        <v>-24.976935367502929</v>
+        <v>-23.110892098770499</v>
       </c>
     </row>
     <row r="95" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>123.32635134509788</v>
+        <v>125.01398345772546</v>
       </c>
       <c r="R95">
-        <v>-23.526051244043099</v>
+        <v>-26.67735817029363</v>
       </c>
     </row>
     <row r="96" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O96" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="P96" t="s">
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>121.92904804994386</v>
+        <v>127.5392725342796</v>
       </c>
       <c r="R96">
-        <v>-20.812639760955228</v>
+        <v>-26.043555904293484</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O97" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="P97" t="s">
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>119.16208753086686</v>
+        <v>121.1112351491342</v>
       </c>
       <c r="R97">
-        <v>-21.695504082474919</v>
+        <v>-24.976935367502929</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O98" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="P98" t="s">
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>117.41731439882852</v>
+        <v>123.32635134509788</v>
       </c>
       <c r="R98">
-        <v>-24.068771928108724</v>
+        <v>-23.526051244043099</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O99" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="P99" t="s">
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>149.05199661054391</v>
+        <v>121.92904804994386</v>
       </c>
       <c r="R99">
-        <v>-37.002032630466068</v>
+        <v>-20.812639760955228</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O100" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="P100" t="s">
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>148.65352254441521</v>
+        <v>119.16208753086686</v>
       </c>
       <c r="R100">
-        <v>-34.439834706959083</v>
+        <v>-21.695504082474919</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O101" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="P101" t="s">
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>145.73081872404185</v>
+        <v>117.41731439882852</v>
       </c>
       <c r="R101">
-        <v>-35.085374523771193</v>
+        <v>-24.068771928108724</v>
       </c>
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O102" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P102" t="s">
         <v>8</v>
       </c>
       <c r="Q102">
-        <v>147.56216804451495</v>
+        <v>149.05199661054391</v>
       </c>
       <c r="R102">
-        <v>-35.99216254102295</v>
+        <v>-37.002032630466068</v>
       </c>
     </row>
     <row r="103" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O103" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="P103" t="s">
         <v>8</v>
       </c>
       <c r="Q103">
-        <v>142.90804330239868</v>
+        <v>148.65352254441521</v>
       </c>
       <c r="R103">
-        <v>-33.141361171375287</v>
+        <v>-34.439834706959083</v>
       </c>
     </row>
     <row r="104" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O104" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="P104" t="s">
         <v>8</v>
       </c>
       <c r="Q104">
-        <v>143.83516136861633</v>
+        <v>145.73081872404185</v>
       </c>
       <c r="R104">
-        <v>-34.872998231421811</v>
+        <v>-35.085374523771193</v>
       </c>
     </row>
     <row r="105" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O105" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P105" t="s">
         <v>8</v>
       </c>
       <c r="Q105">
-        <v>145.52740655459939</v>
+        <v>147.56216804451495</v>
       </c>
       <c r="R105">
-        <v>-36.621932253037947</v>
+        <v>-35.99216254102295</v>
       </c>
     </row>
     <row r="106" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O106" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="P106" t="s">
         <v>8</v>
       </c>
       <c r="Q106">
-        <v>146.92390427712806</v>
+        <v>142.90804330239868</v>
       </c>
       <c r="R106">
-        <v>-38.141004719968016</v>
+        <v>-33.141361171375287</v>
       </c>
     </row>
     <row r="107" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O107" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P107" t="s">
         <v>8</v>
       </c>
       <c r="Q107">
-        <v>145.30589191019487</v>
+        <v>143.83516136861633</v>
       </c>
       <c r="R107">
-        <v>-38.106686018724361</v>
+        <v>-34.872998231421811</v>
       </c>
     </row>
     <row r="108" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O108" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="P108" t="s">
         <v>8</v>
       </c>
       <c r="Q108">
-        <v>141.9946318567072</v>
+        <v>145.52740655459939</v>
       </c>
       <c r="R108">
-        <v>-37.361011760610033</v>
+        <v>-36.621932253037947</v>
       </c>
     </row>
     <row r="109" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O109" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P109" t="s">
         <v>8</v>
       </c>
       <c r="Q109">
-        <v>142.82534027744816</v>
+        <v>146.92390427712806</v>
       </c>
       <c r="R109">
-        <v>-38.177452919514529</v>
+        <v>-38.141004719968016</v>
       </c>
     </row>
     <row r="110" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O110" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="P110" t="s">
         <v>8</v>
       </c>
       <c r="Q110">
-        <v>140.4901558842385</v>
+        <v>145.30589191019487</v>
       </c>
       <c r="R110">
-        <v>-35.674441574858221</v>
+        <v>-38.106686018724361</v>
       </c>
     </row>
     <row r="111" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O111" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P111" t="s">
         <v>8</v>
       </c>
       <c r="Q111">
-        <v>140.48912208275175</v>
+        <v>141.9946318567072</v>
       </c>
       <c r="R111">
-        <v>-37.060205851775557</v>
+        <v>-37.361011760610033</v>
       </c>
     </row>
     <row r="112" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O112" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="P112" t="s">
         <v>8</v>
       </c>
       <c r="Q112">
-        <v>145.36174013178348</v>
+        <v>142.82534027744816</v>
       </c>
       <c r="R112">
-        <v>-40.954878234189231</v>
+        <v>-38.177452919514529</v>
       </c>
     </row>
     <row r="113" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O113" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P113" t="s">
         <v>8</v>
       </c>
       <c r="Q113">
-        <v>147.73975425579624</v>
+        <v>140.4901558842385</v>
       </c>
       <c r="R113">
-        <v>-41.160834609417009</v>
+        <v>-35.674441574858221</v>
       </c>
     </row>
     <row r="114" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O114" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="P114" t="s">
         <v>8</v>
       </c>
       <c r="Q114">
-        <v>147.36591370809563</v>
+        <v>140.48912208275175</v>
       </c>
       <c r="R114">
-        <v>-42.210138412085627</v>
+        <v>-37.060205851775557</v>
       </c>
     </row>
     <row r="115" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O115" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P115" t="s">
         <v>8</v>
       </c>
       <c r="Q115">
-        <v>122.55812845579398</v>
+        <v>145.36174013178348</v>
       </c>
       <c r="R115">
-        <v>-33.332763044697707</v>
+        <v>-40.954878234189231</v>
       </c>
     </row>
     <row r="116" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
       </c>
       <c r="Q116">
-        <v>120.86799171391893</v>
+        <v>147.73975425579624</v>
       </c>
       <c r="R116">
-        <v>-32.593875240972459</v>
+        <v>-41.160834609417009</v>
       </c>
     </row>
     <row r="117" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
       </c>
       <c r="Q117">
-        <v>116.03100720882161</v>
+        <v>147.36591370809563</v>
       </c>
       <c r="R117">
-        <v>-34.127034311484337</v>
+        <v>-42.210138412085627</v>
       </c>
     </row>
     <row r="118" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
       </c>
       <c r="Q118">
-        <v>118.0751068059126</v>
+        <v>122.55812845579398</v>
       </c>
       <c r="R118">
-        <v>-34.615466066232315</v>
+        <v>-33.332763044697707</v>
       </c>
     </row>
     <row r="119" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
       </c>
       <c r="Q119">
-        <v>116.65659464654038</v>
+        <v>120.86799171391893</v>
       </c>
       <c r="R119">
-        <v>-27.007695799781629</v>
+        <v>-32.593875240972459</v>
       </c>
     </row>
     <row r="120" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
       </c>
       <c r="Q120">
-        <v>115.14238021324108</v>
+        <v>116.03100720882161</v>
       </c>
       <c r="R120">
-        <v>-24.697893127946649</v>
+        <v>-34.127034311484337</v>
       </c>
     </row>
     <row r="121" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
       </c>
       <c r="Q121">
-        <v>115.68722214682816</v>
+        <v>118.0751068059126</v>
       </c>
       <c r="R121">
-        <v>-28.167441697824167</v>
+        <v>-34.615466066232315</v>
       </c>
     </row>
     <row r="122" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
       </c>
       <c r="Q122">
-        <v>115.90421239972798</v>
+        <v>116.65659464654038</v>
       </c>
       <c r="R122">
-        <v>-31.444882640740847</v>
+        <v>-27.007695799781629</v>
       </c>
     </row>
     <row r="123" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
       </c>
       <c r="Q123">
-        <v>118.59104261535464</v>
+        <v>115.14238021324108</v>
       </c>
       <c r="R123">
-        <v>-29.285502942557969</v>
+        <v>-24.697893127946649</v>
       </c>
     </row>
     <row r="124" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
       </c>
       <c r="Q124">
-        <v>118.39673279724994</v>
+        <v>115.68722214682816</v>
       </c>
       <c r="R124">
-        <v>-30.752758698157304</v>
+        <v>-28.167441697824167</v>
       </c>
     </row>
     <row r="125" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
       </c>
       <c r="Q125">
-        <v>150.93934717708817</v>
+        <v>115.90421239972798</v>
       </c>
       <c r="R125">
-        <v>-24.76727518444596</v>
+        <v>-31.444882640740847</v>
       </c>
     </row>
     <row r="126" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
       </c>
       <c r="Q126">
-        <v>148.23171019375965</v>
+        <v>118.59104261535464</v>
       </c>
       <c r="R126">
-        <v>-20.970084429509942</v>
+        <v>-29.285502942557969</v>
       </c>
     </row>
     <row r="127" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
       </c>
       <c r="Q127">
-        <v>147.06350485205559</v>
+        <v>118.39673279724994</v>
       </c>
       <c r="R127">
-        <v>-21.81503719825152</v>
+        <v>-30.752758698157304</v>
       </c>
     </row>
     <row r="128" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
       </c>
       <c r="Q128">
-        <v>151.88900228121577</v>
+        <v>150.93934717708817</v>
       </c>
       <c r="R128">
-        <v>-28.426665025009203</v>
+        <v>-24.76727518444596</v>
       </c>
     </row>
     <row r="129" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
       </c>
       <c r="Q129">
-        <v>149.22438062186285</v>
+        <v>148.23171019375965</v>
       </c>
       <c r="R129">
-        <v>-27.235374901982532</v>
+        <v>-20.970084429509942</v>
       </c>
     </row>
     <row r="130" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
       </c>
       <c r="Q130">
-        <v>147.76330434123716</v>
+        <v>147.06350485205559</v>
       </c>
       <c r="R130">
-        <v>-28.17719003058987</v>
+        <v>-21.81503719825152</v>
       </c>
     </row>
     <row r="131" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
       </c>
       <c r="Q131">
-        <v>149.43559238340944</v>
+        <v>151.88900228121577</v>
       </c>
       <c r="R131">
-        <v>-25.53208894708445</v>
+        <v>-28.426665025009203</v>
       </c>
     </row>
     <row r="132" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
       </c>
       <c r="Q132">
-        <v>146.46677109095083</v>
+        <v>149.22438062186285</v>
       </c>
       <c r="R132">
-        <v>-23.265870692651252</v>
+        <v>-27.235374901982532</v>
       </c>
     </row>
     <row r="133" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
       </c>
       <c r="Q133">
-        <v>146.2530408921524</v>
+        <v>147.76330434123716</v>
       </c>
       <c r="R133">
-        <v>-24.912836419118246</v>
+        <v>-28.17719003058987</v>
       </c>
     </row>
     <row r="134" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
       </c>
       <c r="Q134">
-        <v>150.77513759786697</v>
+        <v>149.43559238340944</v>
       </c>
       <c r="R134">
-        <v>-33.927321285914829</v>
+        <v>-25.53208894708445</v>
       </c>
     </row>
     <row r="135" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O135" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P135" t="s">
         <v>8</v>
       </c>
       <c r="Q135">
-        <v>149.63395959889763</v>
+        <v>146.46677109095083</v>
       </c>
       <c r="R135">
-        <v>-34.446112622440367</v>
+        <v>-23.265870692651252</v>
       </c>
     </row>
     <row r="136" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O136" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="P136" t="s">
         <v>8</v>
       </c>
       <c r="Q136">
-        <v>151.9510333951863</v>
+        <v>146.2530408921524</v>
       </c>
       <c r="R136">
-        <v>-31.610779267089288</v>
+        <v>-24.912836419118246</v>
       </c>
     </row>
     <row r="137" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O137" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P137" t="s">
         <v>8</v>
       </c>
       <c r="Q137">
-        <v>150.64279122684428</v>
+        <v>150.77513759786697</v>
       </c>
       <c r="R137">
-        <v>-30.329307192442041</v>
+        <v>-33.927321285914829</v>
       </c>
     </row>
     <row r="138" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O138" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="P138" t="s">
         <v>8</v>
       </c>
       <c r="Q138">
-        <v>142.69665953395346</v>
+        <v>149.63395959889763</v>
       </c>
       <c r="R138">
-        <v>-28.42615104088356</v>
+        <v>-34.446112622440367</v>
       </c>
     </row>
     <row r="139" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O139" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P139" t="s">
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>145.17717767511434</v>
+        <v>151.9510333951863</v>
       </c>
       <c r="R139">
-        <v>-28.240292440619939</v>
+        <v>-31.610779267089288</v>
       </c>
     </row>
     <row r="140" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O140" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P140" t="s">
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>143.59071424731289</v>
+        <v>150.64279122684428</v>
       </c>
       <c r="R140">
-        <v>-25.934310769926011</v>
+        <v>-30.329307192442041</v>
       </c>
     </row>
     <row r="141" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
       </c>
       <c r="Q141">
-        <v>147.73996892366085</v>
+        <v>142.69665953395346</v>
       </c>
       <c r="R141">
-        <v>-30.460324370284951</v>
+        <v>-28.42615104088356</v>
       </c>
     </row>
     <row r="142" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
       </c>
       <c r="Q142">
-        <v>145.08028680507692</v>
+        <v>145.17717767511434</v>
       </c>
       <c r="R142">
-        <v>-33.42596416811471</v>
+        <v>-28.240292440619939</v>
       </c>
     </row>
     <row r="143" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
       </c>
       <c r="Q143">
-        <v>144.10689207891647</v>
+        <v>143.59071424731289</v>
       </c>
       <c r="R143">
-        <v>-31.011320891898983</v>
+        <v>-25.934310769926011</v>
       </c>
     </row>
     <row r="144" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
       </c>
       <c r="Q144">
-        <v>119.9126561006962</v>
+        <v>147.73996892366085</v>
       </c>
       <c r="R144">
-        <v>-18.762930736574628</v>
+        <v>-30.460324370284951</v>
       </c>
     </row>
     <row r="145" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
       </c>
       <c r="Q145">
-        <v>118.04505668609308</v>
+        <v>145.08028680507692</v>
       </c>
       <c r="R145">
-        <v>-18.943711458300104</v>
+        <v>-33.42596416811471</v>
       </c>
     </row>
     <row r="146" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
       </c>
       <c r="Q146">
-        <v>119.47741098585524</v>
+        <v>144.10689207891647</v>
       </c>
       <c r="R146">
-        <v>-17.341576901661309</v>
+        <v>-31.011320891898983</v>
       </c>
     </row>
     <row r="147" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
       </c>
       <c r="Q147">
-        <v>120.7699066609067</v>
+        <v>119.9126561006962</v>
       </c>
       <c r="R147">
-        <v>-16.701861452529982</v>
+        <v>-18.762930736574628</v>
       </c>
     </row>
     <row r="148" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
       </c>
       <c r="Q148">
-        <v>120.92507981057096</v>
+        <v>118.04505668609308</v>
       </c>
       <c r="R148">
-        <v>-17.89119788373922</v>
+        <v>-18.943711458300104</v>
       </c>
     </row>
     <row r="149" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>148.32310486365299</v>
+        <v>119.47741098585524</v>
       </c>
       <c r="R149">
-        <v>-38.317649436280313</v>
+        <v>-17.341576901661309</v>
       </c>
     </row>
     <row r="150" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>149.91427469508412</v>
+        <v>120.7699066609067</v>
       </c>
       <c r="R150">
-        <v>-37.666954901440938</v>
+        <v>-16.701861452529982</v>
       </c>
     </row>
     <row r="151" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>148.2380581815757</v>
+        <v>120.92507981057096</v>
       </c>
       <c r="R151">
-        <v>-42.385662374939223</v>
+        <v>-17.89119788373922</v>
       </c>
     </row>
     <row r="152" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
       </c>
       <c r="Q152">
-        <v>145.49022483115897</v>
+        <v>148.32310486365299</v>
       </c>
       <c r="R152">
-        <v>-43.009861490614647</v>
+        <v>-38.317649436280313</v>
       </c>
     </row>
     <row r="153" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O153" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P153" t="s">
         <v>8</v>
       </c>
       <c r="Q153">
-        <v>141.65592107949502</v>
+        <v>149.91427469508412</v>
       </c>
       <c r="R153">
-        <v>-38.521010458884057</v>
+        <v>-37.666954901440938</v>
       </c>
     </row>
     <row r="154" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O154" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P154" t="s">
         <v>8</v>
       </c>
       <c r="Q154">
-        <v>144.55763782706819</v>
+        <v>148.2380581815757</v>
       </c>
       <c r="R154">
-        <v>-38.513951467094387</v>
+        <v>-42.385662374939223</v>
       </c>
     </row>
     <row r="155" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
       </c>
       <c r="Q155">
-        <v>144.77326716667514</v>
+        <v>145.49022483115897</v>
       </c>
       <c r="R155">
-        <v>-39.715987878044587</v>
+        <v>-43.009861490614647</v>
       </c>
     </row>
     <row r="156" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O156" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="P156" t="s">
         <v>8</v>
       </c>
       <c r="Q156">
-        <v>147.27289869429097</v>
+        <v>141.65592107949502</v>
       </c>
       <c r="R156">
-        <v>-39.835742995149893</v>
+        <v>-38.521010458884057</v>
       </c>
     </row>
     <row r="157" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O157" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P157" t="s">
         <v>8</v>
       </c>
       <c r="Q157">
-        <v>125.93096074584602</v>
+        <v>144.55763782706819</v>
       </c>
       <c r="R157">
-        <v>-33.361274423793468</v>
+        <v>-38.513951467094387</v>
       </c>
     </row>
     <row r="158" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O158" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P158" t="s">
         <v>8</v>
       </c>
       <c r="Q158">
-        <v>123.37535402247092</v>
+        <v>144.77326716667514</v>
       </c>
       <c r="R158">
-        <v>-34.303485688836098</v>
+        <v>-39.715987878044587</v>
       </c>
     </row>
     <row r="159" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O159" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P159" t="s">
         <v>8</v>
       </c>
       <c r="Q159">
-        <v>114.7947165340852</v>
+        <v>147.27289869429097</v>
       </c>
       <c r="R159">
-        <v>-32.54438600940842</v>
+        <v>-39.835742995149893</v>
       </c>
     </row>
     <row r="160" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O160" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="P160" t="s">
         <v>8</v>
       </c>
       <c r="Q160">
-        <v>115.63509693996244</v>
+        <v>125.93096074584602</v>
       </c>
       <c r="R160">
-        <v>-34.956218827910511</v>
+        <v>-33.361274423793468</v>
       </c>
     </row>
     <row r="161" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O161" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P161" t="s">
         <v>8</v>
       </c>
       <c r="Q161">
-        <v>119.9072235311796</v>
+        <v>123.37535402247092</v>
       </c>
       <c r="R161">
-        <v>-34.597269389279965</v>
+        <v>-34.303485688836098</v>
       </c>
     </row>
     <row r="162" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O162" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="P162" t="s">
         <v>8</v>
       </c>
       <c r="Q162">
-        <v>137.78035397071665</v>
+        <v>114.7947165340852</v>
       </c>
       <c r="R162">
-        <v>-32.819241490786624</v>
+        <v>-32.54438600940842</v>
       </c>
     </row>
     <row r="163" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O163" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P163" t="s">
         <v>8</v>
       </c>
       <c r="Q163">
-        <v>137.20967407247699</v>
+        <v>115.63509693996244</v>
       </c>
       <c r="R163">
-        <v>-36.223304540952505</v>
+        <v>-34.956218827910511</v>
       </c>
     </row>
     <row r="164" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O164" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="P164" t="s">
         <v>8</v>
       </c>
       <c r="Q164">
-        <v>129.134450023667</v>
+        <v>119.9072235311796</v>
       </c>
       <c r="R164">
-        <v>-32.909253032721082</v>
+        <v>-34.597269389279965</v>
       </c>
     </row>
     <row r="165" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O165" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P165" t="s">
         <v>8</v>
       </c>
       <c r="Q165">
-        <v>132.03627064460872</v>
+        <v>137.78035397071665</v>
       </c>
       <c r="R165">
-        <v>-33.087877243811086</v>
+        <v>-32.819241490786624</v>
       </c>
     </row>
     <row r="166" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O166" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="P166" t="s">
         <v>8</v>
       </c>
       <c r="Q166">
-        <v>133.90646814672945</v>
+        <v>137.20967407247699</v>
       </c>
       <c r="R166">
-        <v>-34.666650757457681</v>
+        <v>-36.223304540952505</v>
       </c>
     </row>
     <row r="167" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O167" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P167" t="s">
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>133.91848973168982</v>
+        <v>129.134450023667</v>
       </c>
       <c r="R167">
-        <v>-33.290709632176373</v>
+        <v>-32.909253032721082</v>
       </c>
     </row>
     <row r="168" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O168" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="P168" t="s">
         <v>8</v>
       </c>
       <c r="Q168">
-        <v>113.74486915277508</v>
+        <v>132.03627064460872</v>
       </c>
       <c r="R168">
-        <v>-28.996828120045929</v>
+        <v>-33.087877243811086</v>
       </c>
     </row>
     <row r="169" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O169" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P169" t="s">
         <v>8</v>
       </c>
       <c r="Q169">
-        <v>112.74359053980096</v>
+        <v>133.90646814672945</v>
       </c>
       <c r="R169">
-        <v>-26.772426753633201</v>
+        <v>-34.666650757457681</v>
       </c>
     </row>
     <row r="170" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O170" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P170" t="s">
         <v>8</v>
       </c>
       <c r="Q170">
-        <v>112.63415325098336</v>
+        <v>133.91848973168982</v>
       </c>
       <c r="R170">
-        <v>-24.422167043715746</v>
+        <v>-33.290709632176373</v>
       </c>
     </row>
     <row r="171" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O171" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P171" t="s">
         <v>8</v>
       </c>
       <c r="Q171">
-        <v>113.73544067893422</v>
+        <v>113.74486915277508</v>
       </c>
       <c r="R171">
-        <v>-21.706116736523096</v>
+        <v>-28.996828120045929</v>
       </c>
     </row>
     <row r="172" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O172" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="P172" t="s">
         <v>8</v>
       </c>
       <c r="Q172">
-        <v>116.10746995541636</v>
+        <v>112.74359053980096</v>
       </c>
       <c r="R172">
-        <v>-19.480023550066459</v>
+        <v>-26.772426753633201</v>
       </c>
     </row>
     <row r="173" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O173" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P173" t="s">
         <v>8</v>
       </c>
       <c r="Q173">
-        <v>114.68862040279514</v>
+        <v>112.63415325098336</v>
       </c>
       <c r="R173">
-        <v>-20.711484124597217</v>
+        <v>-24.422167043715746</v>
       </c>
     </row>
     <row r="174" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O174" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="P174" t="s">
         <v>8</v>
       </c>
       <c r="Q174">
-        <v>153.46075007326399</v>
+        <v>113.73544067893422</v>
       </c>
       <c r="R174">
-        <v>-25.64608975222702</v>
+        <v>-21.706116736523096</v>
       </c>
     </row>
     <row r="175" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O175" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P175" t="s">
         <v>8</v>
       </c>
       <c r="Q175">
-        <v>159.20482777269496</v>
+        <v>116.10746995541636</v>
       </c>
       <c r="R175">
-        <v>-31.490532239940517</v>
+        <v>-19.480023550066459</v>
       </c>
     </row>
     <row r="176" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O176" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="P176" t="s">
         <v>8</v>
       </c>
       <c r="Q176">
-        <v>153.68674355709717</v>
+        <v>114.68862040279514</v>
       </c>
       <c r="R176">
-        <v>-27.494239414331563</v>
+        <v>-20.711484124597217</v>
       </c>
     </row>
     <row r="177" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O177" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P177" t="s">
         <v>8</v>
       </c>
       <c r="Q177">
-        <v>151.35627784832863</v>
+        <v>153.46075007326399</v>
       </c>
       <c r="R177">
-        <v>-34.275360972593546</v>
+        <v>-25.64608975222702</v>
       </c>
     </row>
     <row r="178" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O178" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="P178" t="s">
         <v>8</v>
       </c>
       <c r="Q178">
-        <v>153.55763832618015</v>
+        <v>159.20482777269496</v>
       </c>
       <c r="R178">
-        <v>-29.527372673957174</v>
+        <v>-31.490532239940517</v>
       </c>
     </row>
     <row r="179" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O179" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P179" t="s">
         <v>8</v>
       </c>
       <c r="Q179">
-        <v>152.90565408954197</v>
+        <v>153.68674355709717</v>
       </c>
       <c r="R179">
-        <v>-32.160506789513327</v>
+        <v>-27.494239414331563</v>
       </c>
     </row>
     <row r="180" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O180" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="P180" t="s">
         <v>8</v>
       </c>
       <c r="Q180">
-        <v>123.6209360771076</v>
+        <v>151.35627784832863</v>
       </c>
       <c r="R180">
-        <v>-12.313250418759196</v>
+        <v>-34.275360972593546</v>
       </c>
     </row>
     <row r="181" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O181" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P181" t="s">
         <v>8</v>
       </c>
       <c r="Q181">
-        <v>127.28982693164365</v>
+        <v>153.55763832618015</v>
       </c>
       <c r="R181">
-        <v>-13.447264969718235</v>
+        <v>-29.527372673957174</v>
       </c>
     </row>
     <row r="182" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O182" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="P182" t="s">
         <v>8</v>
       </c>
       <c r="Q182">
-        <v>137.9274007467076</v>
+        <v>152.90565408954197</v>
       </c>
       <c r="R182">
-        <v>-13.53904439343483</v>
+        <v>-32.160506789513327</v>
       </c>
     </row>
     <row r="183" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O183" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P183" t="s">
         <v>8</v>
       </c>
       <c r="Q183">
-        <v>138.7835300980004</v>
+        <v>123.6209360771076</v>
       </c>
       <c r="R183">
-        <v>-14.99287485410888</v>
+        <v>-12.313250418759196</v>
       </c>
     </row>
     <row r="184" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O184" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="P184" t="s">
         <v>8</v>
       </c>
       <c r="Q184">
-        <v>140.70260155913493</v>
+        <v>127.28982693164365</v>
       </c>
       <c r="R184">
-        <v>-11.977657398671996</v>
+        <v>-13.447264969718235</v>
       </c>
     </row>
     <row r="185" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O185" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P185" t="s">
         <v>8</v>
       </c>
       <c r="Q185">
-        <v>140.0512616860895</v>
+        <v>137.9274007467076</v>
       </c>
       <c r="R185">
-        <v>-13.649234810616214</v>
+        <v>-13.53904439343483</v>
       </c>
     </row>
     <row r="186" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O186" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="P186" t="s">
         <v>8</v>
       </c>
       <c r="Q186">
-        <v>135.53232690608246</v>
+        <v>138.7835300980004</v>
       </c>
       <c r="R186">
-        <v>-10.058412830277735</v>
+        <v>-14.99287485410888</v>
       </c>
     </row>
     <row r="187" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O187" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P187" t="s">
         <v>8</v>
       </c>
       <c r="Q187">
-        <v>138.02236339770641</v>
+        <v>140.70260155913493</v>
       </c>
       <c r="R187">
-        <v>-11.457551359089519</v>
+        <v>-11.977657398671996</v>
       </c>
     </row>
     <row r="188" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O188" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="P188" t="s">
         <v>8</v>
       </c>
       <c r="Q188">
-        <v>129.80616836492629</v>
+        <v>140.0512616860895</v>
       </c>
       <c r="R188">
-        <v>-10.099829044183595</v>
+        <v>-13.649234810616214</v>
       </c>
     </row>
     <row r="189" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O189" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P189" t="s">
         <v>8</v>
       </c>
       <c r="Q189">
-        <v>132.27258092622665</v>
+        <v>135.53232690608246</v>
       </c>
       <c r="R189">
-        <v>-10.034977983480973</v>
+        <v>-10.058412830277735</v>
       </c>
     </row>
     <row r="190" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O190" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="P190" t="s">
         <v>8</v>
       </c>
       <c r="Q190">
-        <v>152.45277308531408</v>
+        <v>138.02236339770641</v>
       </c>
       <c r="R190">
-        <v>-22.783968088520972</v>
+        <v>-11.457551359089519</v>
       </c>
     </row>
     <row r="191" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O191" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P191" t="s">
         <v>8</v>
       </c>
       <c r="Q191">
-        <v>152.48347016037607</v>
+        <v>129.80616836492629</v>
       </c>
       <c r="R191">
-        <v>-20.980492993694121</v>
+        <v>-10.099829044183595</v>
       </c>
     </row>
     <row r="192" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O192" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="P192" t="s">
         <v>8</v>
       </c>
       <c r="Q192">
-        <v>144.36177021993478</v>
+        <v>132.27258092622665</v>
       </c>
       <c r="R192">
-        <v>-9.9641044817147968</v>
+        <v>-10.034977983480973</v>
       </c>
     </row>
     <row r="193" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O193" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P193" t="s">
         <v>8</v>
       </c>
       <c r="Q193">
-        <v>144.12580128857698</v>
+        <v>152.45277308531408</v>
       </c>
       <c r="R193">
-        <v>-12.160973985632396</v>
+        <v>-22.783968088520972</v>
       </c>
     </row>
     <row r="194" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O194" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="P194" t="s">
         <v>8</v>
       </c>
       <c r="Q194">
-        <v>149.93800636445266</v>
+        <v>152.48347016037607</v>
       </c>
       <c r="R194">
-        <v>-16.926232109956484</v>
+        <v>-20.980492993694121</v>
       </c>
     </row>
     <row r="195" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O195" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P195" t="s">
         <v>8</v>
       </c>
       <c r="Q195">
-        <v>149.09136985948658</v>
+        <v>144.36177021993478</v>
       </c>
       <c r="R195">
-        <v>-19.056413284503343</v>
+        <v>-9.9641044817147968</v>
       </c>
     </row>
     <row r="196" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O196" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P196" t="s">
         <v>8</v>
       </c>
       <c r="Q196">
-        <v>143.90359456668338</v>
+        <v>144.12580128857698</v>
       </c>
       <c r="R196">
-        <v>-16.424523984767728</v>
+        <v>-12.160973985632396</v>
       </c>
     </row>
     <row r="197" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O197" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P197" t="s">
         <v>8</v>
       </c>
       <c r="Q197">
-        <v>143.22470052438001</v>
+        <v>149.93800636445266</v>
       </c>
       <c r="R197">
-        <v>-13.468602452715691</v>
+        <v>-16.926232109956484</v>
       </c>
     </row>
     <row r="198" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O198" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="P198" t="s">
         <v>8</v>
       </c>
       <c r="Q198">
-        <v>143.90529016295486</v>
+        <v>149.09136985948658</v>
       </c>
       <c r="R198">
-        <v>-18.480560456616804</v>
+        <v>-19.056413284503343</v>
       </c>
     </row>
     <row r="199" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O199" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P199" t="s">
         <v>8</v>
       </c>
       <c r="Q199">
-        <v>141.91280510410783</v>
+        <v>143.90359456668338</v>
       </c>
       <c r="R199">
-        <v>-14.267874545971546</v>
+        <v>-16.424523984767728</v>
       </c>
     </row>
     <row r="200" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O200" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="P200" t="s">
         <v>8</v>
       </c>
       <c r="Q200">
-        <v>147.94674742269942</v>
+        <v>143.22470052438001</v>
       </c>
       <c r="R200">
-        <v>-20.402760450148971</v>
+        <v>-13.468602452715691</v>
       </c>
     </row>
     <row r="201" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O201" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P201" t="s">
         <v>8</v>
       </c>
       <c r="Q201">
-        <v>144.07788557941856</v>
+        <v>143.90529016295486</v>
       </c>
       <c r="R201">
-        <v>-21.717575465917388</v>
+        <v>-18.480560456616804</v>
       </c>
     </row>
     <row r="202" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O202" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P202" t="s">
         <v>8</v>
       </c>
       <c r="Q202">
-        <v>145.9443079211926</v>
+        <v>141.91280510410783</v>
       </c>
       <c r="R202">
-        <v>-20.239947228052181</v>
+        <v>-14.267874545971546</v>
       </c>
     </row>
     <row r="203" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O203" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P203" t="s">
         <v>8</v>
       </c>
       <c r="Q203">
-        <v>147.65166753303404</v>
+        <v>147.94674742269942</v>
       </c>
       <c r="R203">
-        <v>-22.848790085185165</v>
+        <v>-20.402760450148971</v>
       </c>
     </row>
     <row r="204" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O204" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="P204" t="s">
         <v>8</v>
       </c>
       <c r="Q204">
-        <v>142.11939483808513</v>
+        <v>144.07788557941856</v>
       </c>
       <c r="R204">
-        <v>-20.287585477957197</v>
+        <v>-21.717575465917388</v>
       </c>
     </row>
     <row r="205" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O205" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P205" t="s">
         <v>8</v>
       </c>
       <c r="Q205">
-        <v>142.30082021143733</v>
+        <v>145.9443079211926</v>
       </c>
       <c r="R205">
-        <v>-18.402066295276651</v>
+        <v>-20.239947228052181</v>
       </c>
     </row>
     <row r="206" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O206" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P206" t="s">
         <v>8</v>
       </c>
       <c r="Q206">
-        <v>139.9406845355177</v>
+        <v>147.65166753303404</v>
       </c>
       <c r="R206">
-        <v>-18.592001825958096</v>
+        <v>-22.848790085185165</v>
       </c>
     </row>
     <row r="207" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O207" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P207" t="s">
         <v>8</v>
       </c>
       <c r="Q207">
-        <v>136.52844938766063</v>
+        <v>142.11939483808513</v>
       </c>
       <c r="R207">
-        <v>-16.923318022496602</v>
+        <v>-20.287585477957197</v>
       </c>
     </row>
     <row r="208" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O208" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P208" t="s">
         <v>8</v>
       </c>
       <c r="Q208">
-        <v>138.01439622256723</v>
+        <v>142.30082021143733</v>
       </c>
       <c r="R208">
-        <v>-19.947965320150729</v>
+        <v>-18.402066295276651</v>
       </c>
     </row>
     <row r="209" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O209" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P209" t="s">
         <v>8</v>
       </c>
       <c r="Q209">
-        <v>135.46557003772165</v>
+        <v>139.9406845355177</v>
       </c>
       <c r="R209">
-        <v>-18.416233482486358</v>
+        <v>-18.592001825958096</v>
       </c>
     </row>
     <row r="210" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O210" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="P210" t="s">
         <v>8</v>
       </c>
       <c r="Q210">
-        <v>134.79283929397783</v>
+        <v>136.52844938766063</v>
       </c>
       <c r="R210">
-        <v>-20.732600676782639</v>
+        <v>-16.923318022496602</v>
       </c>
     </row>
     <row r="211" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O211" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P211" t="s">
         <v>8</v>
       </c>
       <c r="Q211">
-        <v>136.52758085947576</v>
+        <v>138.01439622256723</v>
       </c>
       <c r="R211">
-        <v>-22.021539553207361</v>
+        <v>-19.947965320150729</v>
       </c>
     </row>
     <row r="212" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O212" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="P212" t="s">
         <v>8</v>
       </c>
       <c r="Q212">
-        <v>127.98414541606536</v>
+        <v>135.46557003772165</v>
       </c>
       <c r="R212">
-        <v>-20.935762467407532</v>
+        <v>-18.416233482486358</v>
       </c>
     </row>
     <row r="213" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O213" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P213" t="s">
         <v>8</v>
       </c>
       <c r="Q213">
-        <v>126.75721806702428</v>
+        <v>134.79283929397783</v>
       </c>
       <c r="R213">
-        <v>-19.535728093615841</v>
+        <v>-20.732600676782639</v>
       </c>
     </row>
     <row r="214" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O214" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="P214" t="s">
         <v>8</v>
       </c>
       <c r="Q214">
-        <v>131.0185841389347</v>
+        <v>136.52758085947576</v>
       </c>
       <c r="R214">
-        <v>-20.991416477707151</v>
+        <v>-22.021539553207361</v>
       </c>
     </row>
     <row r="215" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O215" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P215" t="s">
         <v>8</v>
       </c>
       <c r="Q215">
-        <v>132.36508456813664</v>
+        <v>127.98414541606536</v>
       </c>
       <c r="R215">
-        <v>-18.910342658765423</v>
+        <v>-20.935762467407532</v>
       </c>
     </row>
     <row r="216" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O216" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="P216" t="s">
         <v>8</v>
       </c>
       <c r="Q216">
-        <v>134.77431748659325</v>
+        <v>126.75721806702428</v>
       </c>
       <c r="R216">
-        <v>-15.537965116102958</v>
+        <v>-19.535728093615841</v>
       </c>
     </row>
     <row r="217" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O217" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P217" t="s">
         <v>8</v>
       </c>
       <c r="Q217">
-        <v>134.41284432791551</v>
+        <v>131.0185841389347</v>
       </c>
       <c r="R217">
-        <v>-12.119621907128884</v>
+        <v>-20.991416477707151</v>
       </c>
     </row>
     <row r="218" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O218" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="P218" t="s">
         <v>8</v>
       </c>
       <c r="Q218">
-        <v>135.69256848725669</v>
+        <v>132.36508456813664</v>
       </c>
       <c r="R218">
-        <v>-13.664146166265898</v>
+        <v>-18.910342658765423</v>
       </c>
     </row>
     <row r="219" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O219" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P219" t="s">
         <v>8</v>
       </c>
       <c r="Q219">
-        <v>131.62113689763146</v>
+        <v>134.77431748659325</v>
       </c>
       <c r="R219">
-        <v>-12.894653149909704</v>
+        <v>-15.537965116102958</v>
       </c>
     </row>
     <row r="220" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O220" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="P220" t="s">
         <v>8</v>
       </c>
       <c r="Q220">
-        <v>132.48892524469898</v>
+        <v>134.41284432791551</v>
       </c>
       <c r="R220">
-        <v>-13.907083618728224</v>
+        <v>-12.119621907128884</v>
       </c>
     </row>
     <row r="221" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O221" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P221" t="s">
         <v>8</v>
       </c>
       <c r="Q221">
-        <v>125.8255204059364</v>
+        <v>135.69256848725669</v>
       </c>
       <c r="R221">
-        <v>-17.70421688591648</v>
+        <v>-13.664146166265898</v>
       </c>
     </row>
     <row r="222" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O222" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="P222" t="s">
         <v>8</v>
       </c>
       <c r="Q222">
-        <v>127.53869595671664</v>
+        <v>131.62113689763146</v>
       </c>
       <c r="R222">
-        <v>-15.425735818899312</v>
+        <v>-12.894653149909704</v>
       </c>
     </row>
     <row r="223" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O223" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P223" t="s">
         <v>8</v>
       </c>
       <c r="Q223">
-        <v>132.08986312355745</v>
+        <v>132.48892524469898</v>
       </c>
       <c r="R223">
-        <v>-16.935964240758963</v>
+        <v>-13.907083618728224</v>
       </c>
     </row>
     <row r="224" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O224" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="P224" t="s">
         <v>8</v>
       </c>
       <c r="Q224">
-        <v>127.9753364052041</v>
+        <v>125.8255204059364</v>
       </c>
       <c r="R224">
-        <v>-17.004321685535825</v>
+        <v>-17.70421688591648</v>
       </c>
     </row>
     <row r="225" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O225" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="P225" t="s">
         <v>8</v>
       </c>
       <c r="Q225">
-        <v>146.86282244839464</v>
+        <v>127.53869595671664</v>
       </c>
       <c r="R225">
-        <v>-37.676684149628869</v>
+        <v>-15.425735818899312</v>
       </c>
     </row>
     <row r="226" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O226" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="P226" t="s">
         <v>8</v>
       </c>
       <c r="Q226">
-        <v>149.04105094255826</v>
+        <v>132.08986312355745</v>
       </c>
       <c r="R226">
-        <v>-36.144059038515685</v>
+        <v>-16.935964240758963</v>
       </c>
     </row>
     <row r="227" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O227" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="P227" t="s">
         <v>8</v>
       </c>
       <c r="Q227">
-        <v>147.20822379338119</v>
+        <v>127.9753364052041</v>
       </c>
       <c r="R227">
-        <v>-42.133338684243697</v>
+        <v>-17.004321685535825</v>
       </c>
     </row>
     <row r="228" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O228" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="P228" t="s">
         <v>8</v>
       </c>
       <c r="Q228">
-        <v>145.87076740617448</v>
+        <v>146.86282244839464</v>
       </c>
       <c r="R228">
-        <v>-38.482407313362081</v>
+        <v>-37.676684149628869</v>
       </c>
     </row>
     <row r="229" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O229" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="P229" t="s">
         <v>8</v>
       </c>
       <c r="Q229">
-        <v>141.59885822344779</v>
+        <v>149.04105094255826</v>
       </c>
       <c r="R229">
-        <v>-37.194161249481041</v>
+        <v>-36.144059038515685</v>
       </c>
     </row>
     <row r="230" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O230" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="P230" t="s">
         <v>8</v>
       </c>
       <c r="Q230">
-        <v>136.47849302130328</v>
+        <v>147.20822379338119</v>
       </c>
       <c r="R230">
-        <v>-32.689973080235788</v>
+        <v>-42.133338684243697</v>
       </c>
     </row>
     <row r="231" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O231" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P231" t="s">
         <v>8</v>
       </c>
       <c r="Q231">
-        <v>143.02654384684817</v>
+        <v>145.87076740617448</v>
       </c>
       <c r="R231">
-        <v>-32.045131116301349</v>
+        <v>-38.482407313362081</v>
       </c>
     </row>
     <row r="232" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O232" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="P232" t="s">
         <v>8</v>
       </c>
       <c r="Q232">
-        <v>144.49127087303509</v>
+        <v>141.59885822344779</v>
       </c>
       <c r="R232">
-        <v>-34.862419802160197</v>
+        <v>-37.194161249481041</v>
       </c>
     </row>
     <row r="233" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O233" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P233" t="s">
         <v>8</v>
       </c>
       <c r="Q233">
-        <v>140.56642796401263</v>
+        <v>136.47849302130328</v>
       </c>
       <c r="R233">
-        <v>-33.052401492209839</v>
+        <v>-32.689973080235788</v>
       </c>
     </row>
     <row r="234" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O234" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="P234" t="s">
         <v>8</v>
       </c>
       <c r="Q234">
-        <v>140.00081023529913</v>
+        <v>143.02654384684817</v>
       </c>
       <c r="R234">
-        <v>-31.408285546713287</v>
+        <v>-32.045131116301349</v>
       </c>
     </row>
     <row r="235" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O235" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P235" t="s">
         <v>8</v>
       </c>
       <c r="Q235">
-        <v>137.08711551887083</v>
+        <v>144.49127087303509</v>
       </c>
       <c r="R235">
-        <v>-31.014904189409062</v>
+        <v>-34.862419802160197</v>
       </c>
     </row>
     <row r="236" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O236" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="P236" t="s">
         <v>8</v>
       </c>
       <c r="Q236">
-        <v>145.51452797003827</v>
+        <v>140.56642796401263</v>
       </c>
       <c r="R236">
-        <v>-24.435784713644757</v>
+        <v>-33.052401492209839</v>
       </c>
     </row>
     <row r="237" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O237" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P237" t="s">
         <v>8</v>
       </c>
       <c r="Q237">
-        <v>140.02638596197502</v>
+        <v>140.00081023529913</v>
       </c>
       <c r="R237">
-        <v>-24.142642750494868</v>
+        <v>-31.408285546713287</v>
       </c>
     </row>
     <row r="238" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O238" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="P238" t="s">
         <v>8</v>
       </c>
       <c r="Q238">
-        <v>141.87331622694285</v>
+        <v>137.08711551887083</v>
       </c>
       <c r="R238">
-        <v>-22.59801335237621</v>
+        <v>-31.014904189409062</v>
       </c>
     </row>
     <row r="239" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O239" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P239" t="s">
         <v>8</v>
       </c>
       <c r="Q239">
-        <v>134.39885944606516</v>
+        <v>145.51452797003827</v>
       </c>
       <c r="R239">
-        <v>-24.79923061036914</v>
+        <v>-24.435784713644757</v>
       </c>
     </row>
     <row r="240" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O240" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="P240" t="s">
         <v>8</v>
       </c>
       <c r="Q240">
-        <v>137.32322652242817</v>
+        <v>140.02638596197502</v>
       </c>
       <c r="R240">
-        <v>-24.727021000667804</v>
+        <v>-24.142642750494868</v>
       </c>
     </row>
     <row r="241" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O241" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P241" t="s">
         <v>8</v>
       </c>
       <c r="Q241">
-        <v>143.17631246690607</v>
+        <v>141.87331622694285</v>
       </c>
       <c r="R241">
-        <v>-26.284316493363157</v>
+        <v>-22.59801335237621</v>
       </c>
     </row>
     <row r="242" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O242" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="P242" t="s">
         <v>8</v>
       </c>
       <c r="Q242">
-        <v>141.05568117271642</v>
+        <v>134.39885944606516</v>
       </c>
       <c r="R242">
-        <v>-27.058724077525344</v>
+        <v>-24.79923061036914</v>
       </c>
     </row>
     <row r="243" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O243" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P243" t="s">
         <v>8</v>
       </c>
       <c r="Q243">
-        <v>131.51442733918063</v>
+        <v>137.32322652242817</v>
       </c>
       <c r="R243">
-        <v>-28.368760408286018</v>
+        <v>-24.727021000667804</v>
       </c>
     </row>
     <row r="244" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O244" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="P244" t="s">
         <v>8</v>
       </c>
       <c r="Q244">
-        <v>134.32283850489063</v>
+        <v>143.17631246690607</v>
       </c>
       <c r="R244">
-        <v>-30.621921725356888</v>
+        <v>-26.284316493363157</v>
       </c>
     </row>
     <row r="245" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O245" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="P245" t="s">
         <v>8</v>
       </c>
       <c r="Q245">
-        <v>130.77152772622495</v>
+        <v>141.05568117271642</v>
       </c>
       <c r="R245">
-        <v>-30.635030423097369</v>
+        <v>-27.058724077525344</v>
       </c>
     </row>
     <row r="246" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O246" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="P246" t="s">
         <v>8</v>
       </c>
       <c r="Q246">
-        <v>140.72984435371333</v>
+        <v>131.51442733918063</v>
       </c>
       <c r="R246">
-        <v>-29.40377609579539</v>
+        <v>-28.368760408286018</v>
       </c>
     </row>
     <row r="247" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O247" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P247" t="s">
         <v>8</v>
       </c>
       <c r="Q247">
-        <v>134.66612187113373</v>
+        <v>134.32283850489063</v>
       </c>
       <c r="R247">
-        <v>-28.15690116839572</v>
+        <v>-30.621921725356888</v>
       </c>
     </row>
     <row r="248" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O248" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="P248" t="s">
         <v>8</v>
       </c>
       <c r="Q248">
-        <v>136.77228252752337</v>
+        <v>130.77152772622495</v>
       </c>
       <c r="R248">
-        <v>-27.541992457451759</v>
+        <v>-30.635030423097369</v>
       </c>
     </row>
     <row r="249" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O249" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="P249" t="s">
         <v>8</v>
       </c>
       <c r="Q249">
-        <v>149.35779146912768</v>
+        <v>140.72984435371333</v>
       </c>
       <c r="R249">
-        <v>-26.300868571942431</v>
+        <v>-29.40377609579539</v>
       </c>
     </row>
     <row r="250" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O250" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="P250" t="s">
         <v>8</v>
       </c>
       <c r="Q250">
-        <v>148.14237478588089</v>
+        <v>134.66612187113373</v>
       </c>
       <c r="R250">
-        <v>-27.600157486042235</v>
+        <v>-28.15690116839572</v>
       </c>
     </row>
     <row r="251" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O251" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="P251" t="s">
         <v>8</v>
       </c>
       <c r="Q251">
-        <v>152.12642849359025</v>
+        <v>136.77228252752337</v>
       </c>
       <c r="R251">
-        <v>-28.3347891959374</v>
+        <v>-27.541992457451759</v>
       </c>
     </row>
     <row r="252" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O252" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="P252" t="s">
         <v>8</v>
       </c>
       <c r="Q252">
-        <v>153.10456995993425</v>
+        <v>149.35779146912768</v>
       </c>
       <c r="R252">
-        <v>-28.752190756768822</v>
+        <v>-26.300868571942431</v>
       </c>
     </row>
     <row r="253" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O253" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P253" t="s">
         <v>8</v>
       </c>
       <c r="Q253">
-        <v>150.05391578943551</v>
+        <v>148.14237478588089</v>
       </c>
       <c r="R253">
-        <v>-24.982613757086916</v>
+        <v>-27.600157486042235</v>
       </c>
     </row>
     <row r="254" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O254" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="P254" t="s">
         <v>8</v>
       </c>
       <c r="Q254">
-        <v>151.79277925052281</v>
+        <v>152.12642849359025</v>
       </c>
       <c r="R254">
-        <v>-25.038955284229257</v>
+        <v>-28.3347891959374</v>
       </c>
     </row>
     <row r="255" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O255" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="P255" t="s">
         <v>8</v>
       </c>
       <c r="Q255">
-        <v>151.94448277205771</v>
+        <v>153.10456995993425</v>
       </c>
       <c r="R255">
-        <v>-30.648097888639381</v>
+        <v>-28.752190756768822</v>
       </c>
     </row>
     <row r="256" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O256" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="P256" t="s">
         <v>8</v>
       </c>
       <c r="Q256">
-        <v>150.2541462946395</v>
+        <v>150.05391578943551</v>
       </c>
       <c r="R256">
-        <v>-31.530311559255505</v>
+        <v>-24.982613757086916</v>
       </c>
     </row>
     <row r="257" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O257" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="P257" t="s">
         <v>8</v>
       </c>
       <c r="Q257">
-        <v>149.62090042212768</v>
+        <v>151.79277925052281</v>
       </c>
       <c r="R257">
-        <v>-34.29495419383332</v>
+        <v>-25.038955284229257</v>
       </c>
     </row>
     <row r="258" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O258" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="P258" t="s">
         <v>8</v>
       </c>
       <c r="Q258">
-        <v>152.83763455688668</v>
+        <v>151.94448277205771</v>
       </c>
       <c r="R258">
-        <v>-30.889034568147331</v>
+        <v>-30.648097888639381</v>
       </c>
     </row>
     <row r="259" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O259" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="P259" t="s">
         <v>8</v>
       </c>
       <c r="Q259">
-        <v>151.67802522839008</v>
+        <v>150.2541462946395</v>
       </c>
       <c r="R259">
-        <v>-32.897248213926524</v>
+        <v>-31.530311559255505</v>
       </c>
     </row>
     <row r="260" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O260" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="P260" t="s">
         <v>8</v>
       </c>
       <c r="Q260">
-        <v>144.77318477184815</v>
+        <v>149.62090042212768</v>
       </c>
       <c r="R260">
-        <v>-30.102696294151649</v>
+        <v>-34.29495419383332</v>
       </c>
     </row>
     <row r="261" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O261" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P261" t="s">
         <v>8</v>
       </c>
       <c r="Q261">
-        <v>146.63244669472485</v>
+        <v>152.83763455688668</v>
       </c>
       <c r="R261">
-        <v>-28.772135899285555</v>
+        <v>-30.889034568147331</v>
       </c>
     </row>
     <row r="262" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O262" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="P262" t="s">
         <v>8</v>
       </c>
       <c r="Q262">
-        <v>145.27438207575517</v>
+        <v>151.67802522839008</v>
       </c>
       <c r="R262">
-        <v>-33.717668107285725</v>
+        <v>-32.897248213926524</v>
       </c>
     </row>
     <row r="263" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O263" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="P263" t="s">
         <v>8</v>
       </c>
       <c r="Q263">
-        <v>147.93972516999915</v>
+        <v>144.77318477184815</v>
       </c>
       <c r="R263">
-        <v>-32.762336355038023</v>
+        <v>-30.102696294151649</v>
       </c>
     </row>
     <row r="264" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O264" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="P264" t="s">
         <v>8</v>
       </c>
       <c r="Q264">
-        <v>115.97456492850932</v>
+        <v>146.63244669472485</v>
       </c>
       <c r="R264">
-        <v>-27.306192795280872</v>
+        <v>-28.772135899285555</v>
       </c>
     </row>
     <row r="265" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O265" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="P265" t="s">
         <v>8</v>
       </c>
       <c r="Q265">
-        <v>118.30697028240009</v>
+        <v>145.27438207575517</v>
       </c>
       <c r="R265">
-        <v>-27.961249059143668</v>
+        <v>-33.717668107285725</v>
       </c>
     </row>
     <row r="266" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O266" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="P266" t="s">
         <v>8</v>
       </c>
       <c r="Q266">
-        <v>116.84344906931088</v>
+        <v>147.93972516999915</v>
       </c>
       <c r="R266">
-        <v>-29.109751296776803</v>
+        <v>-32.762336355038023</v>
       </c>
     </row>
     <row r="267" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O267" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="P267" t="s">
         <v>8</v>
       </c>
       <c r="Q267">
-        <v>127.92921064711308</v>
+        <v>115.97456492850932</v>
       </c>
       <c r="R267">
-        <v>-27.965189577949349</v>
+        <v>-27.306192795280872</v>
       </c>
     </row>
     <row r="268" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O268" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="P268" t="s">
         <v>8</v>
       </c>
       <c r="Q268">
-        <v>124.48324861064027</v>
+        <v>118.30697028240009</v>
       </c>
       <c r="R268">
-        <v>-28.350204599948327</v>
+        <v>-27.961249059143668</v>
       </c>
     </row>
     <row r="269" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O269" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="P269" t="s">
         <v>8</v>
       </c>
       <c r="Q269">
-        <v>121.30598072890582</v>
+        <v>116.84344906931088</v>
       </c>
       <c r="R269">
-        <v>-28.309618557173209</v>
+        <v>-29.109751296776803</v>
       </c>
     </row>
     <row r="270" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O270" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="P270" t="s">
         <v>8</v>
       </c>
       <c r="Q270">
-        <v>124.46777334471824</v>
+        <v>127.92921064711308</v>
       </c>
       <c r="R270">
-        <v>-32.105240034383613</v>
+        <v>-27.965189577949349</v>
       </c>
     </row>
     <row r="271" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O271" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="P271" t="s">
         <v>8</v>
       </c>
       <c r="Q271">
-        <v>124.4931229496114</v>
+        <v>124.48324861064027</v>
       </c>
       <c r="R271">
-        <v>-30.717946569059819</v>
+        <v>-28.350204599948327</v>
       </c>
     </row>
     <row r="272" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O272" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="P272" t="s">
         <v>8</v>
       </c>
       <c r="Q272">
-        <v>127.0895269072734</v>
+        <v>121.30598072890582</v>
       </c>
       <c r="R272">
-        <v>-30.529227185974907</v>
+        <v>-28.309618557173209</v>
       </c>
     </row>
     <row r="273" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O273" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="P273" t="s">
         <v>8</v>
       </c>
       <c r="Q273">
-        <v>118.05603838350194</v>
+        <v>124.46777334471824</v>
       </c>
       <c r="R273">
-        <v>-34.353314155008022</v>
+        <v>-32.105240034383613</v>
       </c>
     </row>
     <row r="274" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O274" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="P274" t="s">
         <v>8</v>
       </c>
       <c r="Q274">
-        <v>116.48599270419892</v>
+        <v>124.4931229496114</v>
       </c>
       <c r="R274">
-        <v>-31.735226030591157</v>
+        <v>-30.717946569059819</v>
       </c>
     </row>
     <row r="275" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O275" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="P275" t="s">
         <v>8</v>
       </c>
       <c r="Q275">
-        <v>121.35823120776448</v>
+        <v>127.0895269072734</v>
       </c>
       <c r="R275">
-        <v>-30.231203300821271</v>
+        <v>-30.529227185974907</v>
       </c>
     </row>
     <row r="276" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O276" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="P276" t="s">
         <v>8</v>
       </c>
       <c r="Q276">
-        <v>120.98810738452003</v>
+        <v>118.05603838350194</v>
       </c>
       <c r="R276">
-        <v>-31.912666666511377</v>
+        <v>-34.353314155008022</v>
       </c>
     </row>
     <row r="277" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O277" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P277" t="s">
         <v>8</v>
       </c>
       <c r="Q277">
-        <v>121.40365316346715</v>
+        <v>116.48599270419892</v>
       </c>
       <c r="R277">
-        <v>-23.38749660972239</v>
+        <v>-31.735226030591157</v>
       </c>
     </row>
     <row r="278" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O278" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="P278" t="s">
         <v>8</v>
       </c>
       <c r="Q278">
-        <v>120.78862262071124</v>
+        <v>121.35823120776448</v>
       </c>
       <c r="R278">
-        <v>-25.85084559145124</v>
+        <v>-30.231203300821271</v>
       </c>
     </row>
     <row r="279" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O279" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="P279" t="s">
         <v>8</v>
       </c>
       <c r="Q279">
-        <v>124.92644854307436</v>
+        <v>120.98810738452003</v>
       </c>
       <c r="R279">
-        <v>-24.488649236868213</v>
+        <v>-31.912666666511377</v>
       </c>
     </row>
     <row r="280" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O280" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="P280" t="s">
         <v>8</v>
       </c>
       <c r="Q280">
-        <v>125.40253143865678</v>
+        <v>121.40365316346715</v>
       </c>
       <c r="R280">
-        <v>-26.39599312341414</v>
+        <v>-23.38749660972239</v>
       </c>
     </row>
     <row r="281" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O281" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P281" t="s">
         <v>8</v>
       </c>
       <c r="Q281">
-        <v>127.83407424972432</v>
+        <v>120.78862262071124</v>
       </c>
       <c r="R281">
-        <v>-23.326148026767665</v>
+        <v>-25.85084559145124</v>
       </c>
     </row>
     <row r="282" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O282" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="P282" t="s">
         <v>8</v>
       </c>
       <c r="Q282">
-        <v>125.11073457612062</v>
+        <v>124.92644854307436</v>
       </c>
       <c r="R282">
-        <v>-22.060062802137889</v>
+        <v>-24.488649236868213</v>
       </c>
     </row>
     <row r="283" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O283" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="P283" t="s">
         <v>8</v>
       </c>
       <c r="Q283">
-        <v>130.77987585880484</v>
+        <v>125.40253143865678</v>
       </c>
       <c r="R283">
-        <v>-23.6520771510862</v>
+        <v>-26.39599312341414</v>
       </c>
     </row>
     <row r="284" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O284" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="P284" t="s">
         <v>8</v>
       </c>
       <c r="Q284">
-        <v>129.76000532797065</v>
+        <v>127.83407424972432</v>
       </c>
       <c r="R284">
-        <v>-25.751442172745637</v>
+        <v>-23.326148026767665</v>
       </c>
     </row>
     <row r="285" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O285" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="P285" t="s">
         <v>8</v>
       </c>
       <c r="Q285">
-        <v>121.19680097154732</v>
+        <v>125.11073457612062</v>
       </c>
       <c r="R285">
-        <v>-20.824241557837841</v>
+        <v>-22.060062802137889</v>
       </c>
     </row>
     <row r="286" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O286" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="P286" t="s">
         <v>8</v>
       </c>
       <c r="Q286">
-        <v>123.82322757098922</v>
+        <v>130.77987585880484</v>
       </c>
       <c r="R286">
-        <v>-17.471436176410265</v>
+        <v>-23.6520771510862</v>
       </c>
     </row>
     <row r="287" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O287" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="P287" t="s">
         <v>8</v>
       </c>
       <c r="Q287">
-        <v>123.74790786027596</v>
+        <v>129.76000532797065</v>
       </c>
       <c r="R287">
-        <v>-19.213785896290247</v>
+        <v>-25.751442172745637</v>
       </c>
     </row>
     <row r="288" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O288" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="P288" t="s">
         <v>8</v>
       </c>
       <c r="Q288">
-        <v>117.42275836968288</v>
+        <v>121.19680097154732</v>
       </c>
       <c r="R288">
-        <v>-21.144003963089126</v>
+        <v>-20.824241557837841</v>
       </c>
     </row>
     <row r="289" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O289" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="P289" t="s">
         <v>8</v>
       </c>
       <c r="Q289">
-        <v>117.89666131220254</v>
+        <v>123.82322757098922</v>
       </c>
       <c r="R289">
-        <v>-23.720298383817479</v>
+        <v>-17.471436176410265</v>
       </c>
     </row>
     <row r="290" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O290" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P290" t="s">
         <v>8</v>
       </c>
       <c r="Q290">
-        <v>116.20239512475231</v>
+        <v>123.74790786027596</v>
       </c>
       <c r="R290">
-        <v>-25.347887721648856</v>
+        <v>-19.213785896290247</v>
       </c>
     </row>
     <row r="291" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O291" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="P291" t="s">
         <v>8</v>
       </c>
       <c r="Q291">
-        <v>115.38939990331832</v>
+        <v>117.42275836968288</v>
       </c>
       <c r="R291">
-        <v>-22.518290090128978</v>
+        <v>-21.144003963089126</v>
       </c>
     </row>
     <row r="292" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O292" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P292" t="s">
         <v>8</v>
       </c>
       <c r="Q292">
+        <v>117.89666131220254</v>
+      </c>
+      <c r="R292">
+        <v>-23.720298383817479</v>
+      </c>
+    </row>
+    <row r="293" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O293" t="s">
+        <v>413</v>
+      </c>
+      <c r="P293" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q293">
+        <v>116.20239512475231</v>
+      </c>
+      <c r="R293">
+        <v>-25.347887721648856</v>
+      </c>
+    </row>
+    <row r="294" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O294" t="s">
+        <v>414</v>
+      </c>
+      <c r="P294" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q294">
+        <v>115.38939990331832</v>
+      </c>
+      <c r="R294">
+        <v>-22.518290090128978</v>
+      </c>
+    </row>
+    <row r="295" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O295" t="s">
+        <v>415</v>
+      </c>
+      <c r="P295" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q295">
         <v>114.29262158861788</v>
       </c>
-      <c r="R292">
+      <c r="R295">
         <v>-24.397642917030851</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83AC07DE-7B7B-44F4-875A-BA5858414505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAE26AE5-1B53-49FF-B3DC-680BA728D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CCA1F90A-DCE5-40F5-946B-941B1E819CFD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D875987-C0C4-4376-955C-2C928307D689}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1657,7 +1657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A6817A-36C9-40B7-A5F2-87927B98DCFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495C8880-8258-4789-9FFE-BC1B756F414B}">
   <dimension ref="B3:R295"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAE26AE5-1B53-49FF-B3DC-680BA728D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AFDD7C5-0405-45F1-8224-4A0E23801E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D875987-C0C4-4376-955C-2C928307D689}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F39D64EB-BF91-4BE4-B25E-2D1D19EC4433}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="413">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -227,12 +227,6 @@
     <t>g_Davenport_AUS-Robertstown_AUS</t>
   </si>
   <si>
-    <t>e_Dubbo_AUS</t>
-  </si>
-  <si>
-    <t>g_Dubbo_AUS-MountPiper_AUS</t>
-  </si>
-  <si>
     <t>g_GinGin_AUS-Tarong_AUS</t>
   </si>
   <si>
@@ -447,9 +441,6 @@
   </si>
   <si>
     <t>grid link -94.0 km- way/164764363-275;way/164775125-275 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
-    <t>grid link -249.0 km- way/169406848-330;way/169408193-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>grid link -100.0 km- way/170709510-275;way/171728751-275 (thermal x 0.7 N-1)</t>
@@ -1657,8 +1648,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495C8880-8258-4789-9FFE-BC1B756F414B}">
-  <dimension ref="B3:R295"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399521CA-0D9D-4B40-9D16-E55576119735}">
+  <dimension ref="B3:R294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1666,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -1695,22 +1686,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" t="s">
         <v>166</v>
-      </c>
-      <c r="P4" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -1739,10 +1730,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -1780,7 +1771,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O6" t="s">
         <v>10</v>
@@ -1821,7 +1812,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="O7" t="s">
         <v>16</v>
@@ -1862,7 +1853,7 @@
         <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O8" t="s">
         <v>19</v>
@@ -1903,7 +1894,7 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O9" t="s">
         <v>26</v>
@@ -1944,7 +1935,7 @@
         <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
         <v>31</v>
@@ -1985,7 +1976,7 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O11" t="s">
         <v>11</v>
@@ -2026,7 +2017,7 @@
         <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O12" t="s">
         <v>36</v>
@@ -2067,7 +2058,7 @@
         <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="O13" t="s">
         <v>38</v>
@@ -2108,7 +2099,7 @@
         <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
         <v>14</v>
@@ -2149,7 +2140,7 @@
         <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O15" t="s">
         <v>32</v>
@@ -2190,7 +2181,7 @@
         <v>37</v>
       </c>
       <c r="L16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O16" t="s">
         <v>34</v>
@@ -2231,7 +2222,7 @@
         <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O17" t="s">
         <v>47</v>
@@ -2272,7 +2263,7 @@
         <v>41</v>
       </c>
       <c r="L18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O18" t="s">
         <v>50</v>
@@ -2313,7 +2304,7 @@
         <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O19" t="s">
         <v>54</v>
@@ -2354,7 +2345,7 @@
         <v>44</v>
       </c>
       <c r="L20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="O20" t="s">
         <v>28</v>
@@ -2395,7 +2386,7 @@
         <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O21" t="s">
         <v>59</v>
@@ -2436,19 +2427,19 @@
         <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O22" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>148.9632109591046</v>
+        <v>151.81952564800682</v>
       </c>
       <c r="R22">
-        <v>-32.527168433245279</v>
+        <v>-24.90133538944163</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2477,19 +2468,19 @@
         <v>49</v>
       </c>
       <c r="L23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O23" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>151.81952564800682</v>
+        <v>146.42885495857578</v>
       </c>
       <c r="R23">
-        <v>-24.90133538944163</v>
+        <v>-38.281663652861432</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2518,19 +2509,19 @@
         <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O24" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>146.42885495857578</v>
+        <v>142.28083100000038</v>
       </c>
       <c r="R24">
-        <v>-38.281663652861432</v>
+        <v>-36.721698083045936</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2559,19 +2550,19 @@
         <v>53</v>
       </c>
       <c r="L25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O25" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>142.28083100000038</v>
+        <v>121.42358390000004</v>
       </c>
       <c r="R25">
-        <v>-36.721698083045936</v>
+        <v>-30.781882477049411</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
@@ -2600,19 +2591,19 @@
         <v>56</v>
       </c>
       <c r="L26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O26" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>121.42358390000004</v>
+        <v>116.74275233957847</v>
       </c>
       <c r="R26">
-        <v>-30.781882477049411</v>
+        <v>-20.762601878195927</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -2641,19 +2632,19 @@
         <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O27" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>116.74275233957847</v>
+        <v>118.22746058460694</v>
       </c>
       <c r="R27">
-        <v>-20.762601878195927</v>
+        <v>-31.539704529422323</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
@@ -2682,19 +2673,19 @@
         <v>61</v>
       </c>
       <c r="L28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O28" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>118.22746058460694</v>
+        <v>116.7594477898767</v>
       </c>
       <c r="R28">
-        <v>-31.539704529422323</v>
+        <v>-29.187814184805315</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
@@ -2708,34 +2699,34 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" t="s">
         <v>62</v>
-      </c>
-      <c r="F29" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" t="s">
-        <v>63</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O29" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>116.7594477898767</v>
+        <v>150.02574011758799</v>
       </c>
       <c r="R29">
-        <v>-29.187814184805315</v>
+        <v>-33.363653242312999</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
@@ -2749,34 +2740,34 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O30" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>150.02574011758799</v>
+        <v>148.144166863903</v>
       </c>
       <c r="R30">
-        <v>-33.363653242312999</v>
+        <v>-36.225604818390735</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
@@ -2790,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
@@ -2805,7 +2796,7 @@
         <v>67</v>
       </c>
       <c r="L31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O31" t="s">
         <v>74</v>
@@ -2814,10 +2805,10 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>148.144166863903</v>
+        <v>148.68315461202329</v>
       </c>
       <c r="R31">
-        <v>-36.225604818390735</v>
+        <v>-21.63132000917609</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
@@ -2831,34 +2822,34 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>148.68315461202329</v>
+        <v>146.98953647822455</v>
       </c>
       <c r="R32">
-        <v>-21.63132000917609</v>
+        <v>-41.7876715671242</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.45">
@@ -2872,34 +2863,34 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" t="s">
         <v>71</v>
-      </c>
-      <c r="G33" t="s">
-        <v>72</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L33" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>146.98953647822455</v>
+        <v>138.71215621124384</v>
       </c>
       <c r="R33">
-        <v>-41.7876715671242</v>
+        <v>-34.7354348842319</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.45">
@@ -2913,10 +2904,10 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
         <v>73</v>
@@ -2928,7 +2919,7 @@
         <v>73</v>
       </c>
       <c r="L34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O34" t="s">
         <v>82</v>
@@ -2937,10 +2928,10 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>138.71215621124384</v>
+        <v>115.84737549921022</v>
       </c>
       <c r="R34">
-        <v>-34.7354348842319</v>
+        <v>-32.189392578269448</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.45">
@@ -2957,7 +2948,7 @@
         <v>74</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
         <v>75</v>
@@ -2969,7 +2960,7 @@
         <v>75</v>
       </c>
       <c r="L35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O35" t="s">
         <v>84</v>
@@ -2978,10 +2969,10 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>115.84737549921022</v>
+        <v>118.54463160000005</v>
       </c>
       <c r="R35">
-        <v>-32.189392578269448</v>
+        <v>-20.432074971605672</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.45">
@@ -2995,34 +2986,34 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s">
         <v>76</v>
-      </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" t="s">
-        <v>77</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L36" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O36" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>118.54463160000005</v>
+        <v>139.12683826085333</v>
       </c>
       <c r="R36">
-        <v>-20.432074971605672</v>
+        <v>-33.956428790142837</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.45">
@@ -3036,34 +3027,34 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O37" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>139.12683826085333</v>
+        <v>145.22587842608721</v>
       </c>
       <c r="R37">
-        <v>-33.956428790142837</v>
+        <v>-37.929945191522378</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.45">
@@ -3077,10 +3068,10 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
         <v>81</v>
@@ -3092,19 +3083,19 @@
         <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O38" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>145.22587842608721</v>
+        <v>146.30697121829795</v>
       </c>
       <c r="R38">
-        <v>-37.929945191522378</v>
+        <v>-41.33568787101467</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.45">
@@ -3121,7 +3112,7 @@
         <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
         <v>83</v>
@@ -3133,19 +3124,19 @@
         <v>83</v>
       </c>
       <c r="L39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O39" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="P39" t="s">
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>146.30697121829795</v>
+        <v>145.07540407639536</v>
       </c>
       <c r="R39">
-        <v>-41.33568787101467</v>
+        <v>-37.645174301346643</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.45">
@@ -3162,7 +3153,7 @@
         <v>84</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G40" t="s">
         <v>85</v>
@@ -3174,19 +3165,19 @@
         <v>85</v>
       </c>
       <c r="L40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O40" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="P40" t="s">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>145.07540407639536</v>
+        <v>147.7754061331616</v>
       </c>
       <c r="R40">
-        <v>-37.645174301346643</v>
+        <v>-20.499447155592211</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.45">
@@ -3200,34 +3191,34 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" t="s">
         <v>86</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41" t="s">
-        <v>87</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O41" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="P41" t="s">
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>147.7754061331616</v>
+        <v>150.82867670028497</v>
       </c>
       <c r="R41">
-        <v>-20.499447155592211</v>
+        <v>-33.815823161761138</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.45">
@@ -3244,31 +3235,31 @@
         <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="O42" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P42" t="s">
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>150.82867670028497</v>
+        <v>151.90657331394655</v>
       </c>
       <c r="R42">
-        <v>-33.815823161761138</v>
+        <v>-26.786815702260583</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.45">
@@ -3282,34 +3273,34 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O43" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P43" t="s">
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>151.90657331394655</v>
+        <v>142.18101587735953</v>
       </c>
       <c r="R43">
-        <v>-26.786815702260583</v>
+        <v>-38.17911060837443</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.45">
@@ -3323,34 +3314,34 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
         <v>91</v>
-      </c>
-      <c r="G44" t="s">
-        <v>92</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O44" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="P44" t="s">
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>142.18101587735953</v>
+        <v>117.77622337735301</v>
       </c>
       <c r="R44">
-        <v>-38.17911060837443</v>
+        <v>-22.73480648494872</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.45">
@@ -3364,34 +3355,34 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O45" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>117.77622337735301</v>
+        <v>148.38595135487864</v>
       </c>
       <c r="R45">
-        <v>-22.73480648494872</v>
+        <v>-35.91111863050287</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.45">
@@ -3405,34 +3396,34 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O46" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>148.38595135487864</v>
+        <v>147.39393085110601</v>
       </c>
       <c r="R46">
-        <v>-35.91111863050287</v>
+        <v>-35.200406760019412</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.45">
@@ -3446,34 +3437,34 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O47" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="P47" t="s">
         <v>8</v>
       </c>
       <c r="Q47">
-        <v>147.39393085110601</v>
+        <v>149.76896533906228</v>
       </c>
       <c r="R47">
-        <v>-35.200406760019412</v>
+        <v>-26.268566355497121</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.45">
@@ -3487,34 +3478,34 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L48" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O48" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="P48" t="s">
         <v>8</v>
       </c>
       <c r="Q48">
-        <v>149.76896533906228</v>
+        <v>115.53508832785479</v>
       </c>
       <c r="R48">
-        <v>-26.268566355497121</v>
+        <v>-30.767640414252401</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.45">
@@ -3531,31 +3522,31 @@
         <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O49" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="P49" t="s">
         <v>8</v>
       </c>
       <c r="Q49">
-        <v>115.53508832785479</v>
+        <v>126.87543483120088</v>
       </c>
       <c r="R49">
-        <v>-30.767640414252401</v>
+        <v>-31.570835856427525</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.45">
@@ -3572,7 +3563,7 @@
         <v>40</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
         <v>98</v>
@@ -3584,19 +3575,19 @@
         <v>98</v>
       </c>
       <c r="L50" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O50" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
       </c>
       <c r="Q50">
-        <v>126.87543483120088</v>
+        <v>138.68088035579376</v>
       </c>
       <c r="R50">
-        <v>-31.570835856427525</v>
+        <v>-33.050322280935085</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.45">
@@ -3610,7 +3601,7 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
         <v>99</v>
@@ -3625,19 +3616,19 @@
         <v>100</v>
       </c>
       <c r="L51" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O51" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>138.68088035579376</v>
+        <v>133.78757460034689</v>
       </c>
       <c r="R51">
-        <v>-33.050322280935085</v>
+        <v>-31.537820769156081</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.45">
@@ -3651,10 +3642,10 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s">
         <v>102</v>
@@ -3666,19 +3657,19 @@
         <v>102</v>
       </c>
       <c r="L52" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
       </c>
       <c r="Q52">
-        <v>133.78757460034689</v>
+        <v>138.41823350812663</v>
       </c>
       <c r="R52">
-        <v>-31.537820769156081</v>
+        <v>-35.501951363966938</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.45">
@@ -3692,34 +3683,34 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F53" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" t="s">
         <v>103</v>
-      </c>
-      <c r="F53" t="s">
-        <v>47</v>
-      </c>
-      <c r="G53" t="s">
-        <v>104</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>138.41823350812663</v>
+        <v>132.10100769152496</v>
       </c>
       <c r="R53">
-        <v>-35.501951363966938</v>
+        <v>-25.49357352256672</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3733,34 +3724,34 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="F54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L54" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O54" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>132.10100769152496</v>
+        <v>133.70279525625577</v>
       </c>
       <c r="R54">
-        <v>-25.49357352256672</v>
+        <v>-28.066746287936159</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -3777,31 +3768,31 @@
         <v>57</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O55" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>133.70279525625577</v>
+        <v>131.34409440196771</v>
       </c>
       <c r="R55">
-        <v>-28.066746287936159</v>
+        <v>-28.04146789637413</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.45">
@@ -3815,3406 +3806,3365 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F56" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L56" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O56" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P56" t="s">
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>131.34409440196771</v>
+        <v>130.63850148412087</v>
       </c>
       <c r="R56">
-        <v>-28.04146789637413</v>
+        <v>-30.151673533026507</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>71</v>
-      </c>
-      <c r="F57" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" t="s">
-        <v>108</v>
-      </c>
-      <c r="H57" t="s">
-        <v>13</v>
-      </c>
-      <c r="K57" t="s">
-        <v>108</v>
-      </c>
-      <c r="L57" t="s">
-        <v>164</v>
-      </c>
       <c r="O57" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P57" t="s">
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>130.63850148412087</v>
+        <v>136.6543963226575</v>
       </c>
       <c r="R57">
-        <v>-30.151673533026507</v>
+        <v>-30.346236863934219</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O58" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>136.6543963226575</v>
+        <v>134.69581248525074</v>
       </c>
       <c r="R58">
-        <v>-30.346236863934219</v>
+        <v>-30.730748793905519</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O59" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>134.69581248525074</v>
+        <v>135.42179448527094</v>
       </c>
       <c r="R59">
-        <v>-30.730748793905519</v>
+        <v>-24.023047149503736</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O60" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>135.42179448527094</v>
+        <v>130.86103071723457</v>
       </c>
       <c r="R60">
-        <v>-24.023047149503736</v>
+        <v>-22.595450439397052</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O61" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>130.86103071723457</v>
+        <v>140.73446817308161</v>
       </c>
       <c r="R61">
-        <v>-22.595450439397052</v>
+        <v>-31.100522794087091</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O62" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>140.73446817308161</v>
+        <v>136.74960353581776</v>
       </c>
       <c r="R62">
-        <v>-31.100522794087091</v>
+        <v>-28.096813504185462</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>136.74960353581776</v>
+        <v>138.55276692913932</v>
       </c>
       <c r="R63">
-        <v>-28.096813504185462</v>
+        <v>-26.886442670709371</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O64" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>138.55276692913932</v>
+        <v>134.09893869430459</v>
       </c>
       <c r="R64">
-        <v>-26.886442670709371</v>
+        <v>-12.767605192826451</v>
       </c>
     </row>
     <row r="65" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O65" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>134.09893869430459</v>
+        <v>136.25707133560488</v>
       </c>
       <c r="R65">
-        <v>-12.767605192826451</v>
+        <v>-16.639117165833714</v>
       </c>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O66" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>136.25707133560488</v>
+        <v>140.33047031611449</v>
       </c>
       <c r="R66">
-        <v>-16.639117165833714</v>
+        <v>-19.270168976498251</v>
       </c>
     </row>
     <row r="67" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O67" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>140.33047031611449</v>
+        <v>131.02821227078974</v>
       </c>
       <c r="R67">
-        <v>-19.270168976498251</v>
+        <v>-20.288555696485421</v>
       </c>
     </row>
     <row r="68" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>131.02821227078974</v>
+        <v>132.9773260478994</v>
       </c>
       <c r="R68">
-        <v>-20.288555696485421</v>
+        <v>-19.134632003477144</v>
       </c>
     </row>
     <row r="69" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O69" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>132.9773260478994</v>
+        <v>133.08033774630167</v>
       </c>
       <c r="R69">
-        <v>-19.134632003477144</v>
+        <v>-17.232170442209615</v>
       </c>
     </row>
     <row r="70" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O70" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>133.08033774630167</v>
+        <v>130.07387926508619</v>
       </c>
       <c r="R70">
-        <v>-17.232170442209615</v>
+        <v>-15.90683731540358</v>
       </c>
     </row>
     <row r="71" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O71" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>130.07387926508619</v>
+        <v>131.44822420859035</v>
       </c>
       <c r="R71">
-        <v>-15.90683731540358</v>
+        <v>-12.82434425746715</v>
       </c>
     </row>
     <row r="72" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O72" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>131.44822420859035</v>
+        <v>144.06475345158557</v>
       </c>
       <c r="R72">
-        <v>-12.82434425746715</v>
+        <v>-14.918328674842474</v>
       </c>
     </row>
     <row r="73" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O73" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>144.06475345158557</v>
+        <v>142.83587016468007</v>
       </c>
       <c r="R73">
-        <v>-14.918328674842474</v>
+        <v>-12.686216555715513</v>
       </c>
     </row>
     <row r="74" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O74" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>142.83587016468007</v>
+        <v>142.40851942403145</v>
       </c>
       <c r="R74">
-        <v>-12.686216555715513</v>
+        <v>-18.491878095825161</v>
       </c>
     </row>
     <row r="75" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O75" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>142.40851942403145</v>
+        <v>145.31671437316541</v>
       </c>
       <c r="R75">
-        <v>-18.491878095825161</v>
+        <v>-19.409940321761617</v>
       </c>
     </row>
     <row r="76" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O76" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>145.31671437316541</v>
+        <v>143.2193142021186</v>
       </c>
       <c r="R76">
-        <v>-19.409940321761617</v>
+        <v>-21.577252989404748</v>
       </c>
     </row>
     <row r="77" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O77" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>143.2193142021186</v>
+        <v>141.13298709337377</v>
       </c>
       <c r="R77">
-        <v>-21.577252989404748</v>
+        <v>-22.375086663489547</v>
       </c>
     </row>
     <row r="78" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O78" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>141.13298709337377</v>
+        <v>138.88894971874203</v>
       </c>
       <c r="R78">
-        <v>-22.375086663489547</v>
+        <v>-24.087766437384666</v>
       </c>
     </row>
     <row r="79" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O79" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>138.88894971874203</v>
+        <v>136.76817822772392</v>
       </c>
       <c r="R79">
-        <v>-24.087766437384666</v>
+        <v>-19.38668521985424</v>
       </c>
     </row>
     <row r="80" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O80" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>136.76817822772392</v>
+        <v>136.4508348496494</v>
       </c>
       <c r="R80">
-        <v>-19.38668521985424</v>
+        <v>-21.384730246760789</v>
       </c>
     </row>
     <row r="81" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O81" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>136.4508348496494</v>
+        <v>127.74686025752874</v>
       </c>
       <c r="R81">
-        <v>-21.384730246760789</v>
+        <v>-16.305787203948107</v>
       </c>
     </row>
     <row r="82" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O82" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>127.74686025752874</v>
+        <v>127.14468786066958</v>
       </c>
       <c r="R82">
-        <v>-16.305787203948107</v>
+        <v>-21.316826063663147</v>
       </c>
     </row>
     <row r="83" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O83" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>127.14468786066958</v>
+        <v>128.03124895889869</v>
       </c>
       <c r="R83">
-        <v>-21.316826063663147</v>
+        <v>-19.504849900358565</v>
       </c>
     </row>
     <row r="84" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O84" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>128.03124895889869</v>
+        <v>124.30097588195656</v>
       </c>
       <c r="R84">
-        <v>-19.504849900358565</v>
+        <v>-19.646611890372487</v>
       </c>
     </row>
     <row r="85" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O85" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>124.30097588195656</v>
+        <v>125.44646700631158</v>
       </c>
       <c r="R85">
-        <v>-19.646611890372487</v>
+        <v>-18.034517000819385</v>
       </c>
     </row>
     <row r="86" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O86" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>125.44646700631158</v>
+        <v>119.8792314384001</v>
       </c>
       <c r="R86">
-        <v>-18.034517000819385</v>
+        <v>-26.943751576747506</v>
       </c>
     </row>
     <row r="87" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O87" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>119.8792314384001</v>
+        <v>123.91849872196477</v>
       </c>
       <c r="R87">
-        <v>-26.943751576747506</v>
+        <v>-28.596430984362627</v>
       </c>
     </row>
     <row r="88" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O88" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>123.91849872196477</v>
+        <v>120.83347096461442</v>
       </c>
       <c r="R88">
-        <v>-28.596430984362627</v>
+        <v>-28.749113003071905</v>
       </c>
     </row>
     <row r="89" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O89" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P89" t="s">
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>120.83347096461442</v>
+        <v>127.45396257591824</v>
       </c>
       <c r="R89">
-        <v>-28.749113003071905</v>
+        <v>-29.710182852828943</v>
       </c>
     </row>
     <row r="90" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>127.45396257591824</v>
+        <v>125.2634274064108</v>
       </c>
       <c r="R90">
-        <v>-29.710182852828943</v>
+        <v>-30.48444119537271</v>
       </c>
     </row>
     <row r="91" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>125.2634274064108</v>
+        <v>124.60722906157319</v>
       </c>
       <c r="R91">
-        <v>-30.48444119537271</v>
+        <v>-31.80277872120627</v>
       </c>
     </row>
     <row r="92" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>124.60722906157319</v>
+        <v>122.14641208564728</v>
       </c>
       <c r="R92">
-        <v>-31.80277872120627</v>
+        <v>-30.486367305495254</v>
       </c>
     </row>
     <row r="93" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>122.14641208564728</v>
+        <v>126.75981019754011</v>
       </c>
       <c r="R93">
-        <v>-30.486367305495254</v>
+        <v>-23.110892098770499</v>
       </c>
     </row>
     <row r="94" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>126.75981019754011</v>
+        <v>125.01398345772546</v>
       </c>
       <c r="R94">
-        <v>-23.110892098770499</v>
+        <v>-26.67735817029363</v>
       </c>
     </row>
     <row r="95" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>125.01398345772546</v>
+        <v>127.5392725342796</v>
       </c>
       <c r="R95">
-        <v>-26.67735817029363</v>
+        <v>-26.043555904293484</v>
       </c>
     </row>
     <row r="96" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O96" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P96" t="s">
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>127.5392725342796</v>
+        <v>121.1112351491342</v>
       </c>
       <c r="R96">
-        <v>-26.043555904293484</v>
+        <v>-24.976935367502929</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P97" t="s">
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>121.1112351491342</v>
+        <v>123.32635134509788</v>
       </c>
       <c r="R97">
-        <v>-24.976935367502929</v>
+        <v>-23.526051244043099</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O98" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P98" t="s">
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>123.32635134509788</v>
+        <v>121.92904804994386</v>
       </c>
       <c r="R98">
-        <v>-23.526051244043099</v>
+        <v>-20.812639760955228</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O99" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P99" t="s">
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>121.92904804994386</v>
+        <v>119.16208753086686</v>
       </c>
       <c r="R99">
-        <v>-20.812639760955228</v>
+        <v>-21.695504082474919</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O100" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P100" t="s">
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>119.16208753086686</v>
+        <v>117.41731439882852</v>
       </c>
       <c r="R100">
-        <v>-21.695504082474919</v>
+        <v>-24.068771928108724</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O101" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P101" t="s">
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>117.41731439882852</v>
+        <v>149.05199661054391</v>
       </c>
       <c r="R101">
-        <v>-24.068771928108724</v>
+        <v>-37.002032630466068</v>
       </c>
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O102" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P102" t="s">
         <v>8</v>
       </c>
       <c r="Q102">
-        <v>149.05199661054391</v>
+        <v>148.65352254441521</v>
       </c>
       <c r="R102">
-        <v>-37.002032630466068</v>
+        <v>-34.439834706959083</v>
       </c>
     </row>
     <row r="103" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O103" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P103" t="s">
         <v>8</v>
       </c>
       <c r="Q103">
-        <v>148.65352254441521</v>
+        <v>145.73081872404185</v>
       </c>
       <c r="R103">
-        <v>-34.439834706959083</v>
+        <v>-35.085374523771193</v>
       </c>
     </row>
     <row r="104" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O104" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P104" t="s">
         <v>8</v>
       </c>
       <c r="Q104">
-        <v>145.73081872404185</v>
+        <v>147.56216804451495</v>
       </c>
       <c r="R104">
-        <v>-35.085374523771193</v>
+        <v>-35.99216254102295</v>
       </c>
     </row>
     <row r="105" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O105" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P105" t="s">
         <v>8</v>
       </c>
       <c r="Q105">
-        <v>147.56216804451495</v>
+        <v>142.90804330239868</v>
       </c>
       <c r="R105">
-        <v>-35.99216254102295</v>
+        <v>-33.141361171375287</v>
       </c>
     </row>
     <row r="106" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O106" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P106" t="s">
         <v>8</v>
       </c>
       <c r="Q106">
-        <v>142.90804330239868</v>
+        <v>143.83516136861633</v>
       </c>
       <c r="R106">
-        <v>-33.141361171375287</v>
+        <v>-34.872998231421811</v>
       </c>
     </row>
     <row r="107" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O107" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P107" t="s">
         <v>8</v>
       </c>
       <c r="Q107">
-        <v>143.83516136861633</v>
+        <v>145.52740655459939</v>
       </c>
       <c r="R107">
-        <v>-34.872998231421811</v>
+        <v>-36.621932253037947</v>
       </c>
     </row>
     <row r="108" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O108" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P108" t="s">
         <v>8</v>
       </c>
       <c r="Q108">
-        <v>145.52740655459939</v>
+        <v>146.92390427712806</v>
       </c>
       <c r="R108">
-        <v>-36.621932253037947</v>
+        <v>-38.141004719968016</v>
       </c>
     </row>
     <row r="109" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O109" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P109" t="s">
         <v>8</v>
       </c>
       <c r="Q109">
-        <v>146.92390427712806</v>
+        <v>145.30589191019487</v>
       </c>
       <c r="R109">
-        <v>-38.141004719968016</v>
+        <v>-38.106686018724361</v>
       </c>
     </row>
     <row r="110" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O110" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P110" t="s">
         <v>8</v>
       </c>
       <c r="Q110">
-        <v>145.30589191019487</v>
+        <v>141.9946318567072</v>
       </c>
       <c r="R110">
-        <v>-38.106686018724361</v>
+        <v>-37.361011760610033</v>
       </c>
     </row>
     <row r="111" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O111" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P111" t="s">
         <v>8</v>
       </c>
       <c r="Q111">
-        <v>141.9946318567072</v>
+        <v>142.82534027744816</v>
       </c>
       <c r="R111">
-        <v>-37.361011760610033</v>
+        <v>-38.177452919514529</v>
       </c>
     </row>
     <row r="112" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O112" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P112" t="s">
         <v>8</v>
       </c>
       <c r="Q112">
-        <v>142.82534027744816</v>
+        <v>140.4901558842385</v>
       </c>
       <c r="R112">
-        <v>-38.177452919514529</v>
+        <v>-35.674441574858221</v>
       </c>
     </row>
     <row r="113" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O113" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P113" t="s">
         <v>8</v>
       </c>
       <c r="Q113">
-        <v>140.4901558842385</v>
+        <v>140.48912208275175</v>
       </c>
       <c r="R113">
-        <v>-35.674441574858221</v>
+        <v>-37.060205851775557</v>
       </c>
     </row>
     <row r="114" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O114" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P114" t="s">
         <v>8</v>
       </c>
       <c r="Q114">
-        <v>140.48912208275175</v>
+        <v>145.36174013178348</v>
       </c>
       <c r="R114">
-        <v>-37.060205851775557</v>
+        <v>-40.954878234189231</v>
       </c>
     </row>
     <row r="115" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O115" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P115" t="s">
         <v>8</v>
       </c>
       <c r="Q115">
-        <v>145.36174013178348</v>
+        <v>147.73975425579624</v>
       </c>
       <c r="R115">
-        <v>-40.954878234189231</v>
+        <v>-41.160834609417009</v>
       </c>
     </row>
     <row r="116" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
       </c>
       <c r="Q116">
-        <v>147.73975425579624</v>
+        <v>147.36591370809563</v>
       </c>
       <c r="R116">
-        <v>-41.160834609417009</v>
+        <v>-42.210138412085627</v>
       </c>
     </row>
     <row r="117" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
       </c>
       <c r="Q117">
-        <v>147.36591370809563</v>
+        <v>122.55812845579398</v>
       </c>
       <c r="R117">
-        <v>-42.210138412085627</v>
+        <v>-33.332763044697707</v>
       </c>
     </row>
     <row r="118" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
       </c>
       <c r="Q118">
-        <v>122.55812845579398</v>
+        <v>120.86799171391893</v>
       </c>
       <c r="R118">
-        <v>-33.332763044697707</v>
+        <v>-32.593875240972459</v>
       </c>
     </row>
     <row r="119" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
       </c>
       <c r="Q119">
-        <v>120.86799171391893</v>
+        <v>116.03100720882161</v>
       </c>
       <c r="R119">
-        <v>-32.593875240972459</v>
+        <v>-34.127034311484337</v>
       </c>
     </row>
     <row r="120" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
       </c>
       <c r="Q120">
-        <v>116.03100720882161</v>
+        <v>118.0751068059126</v>
       </c>
       <c r="R120">
-        <v>-34.127034311484337</v>
+        <v>-34.615466066232315</v>
       </c>
     </row>
     <row r="121" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
       </c>
       <c r="Q121">
-        <v>118.0751068059126</v>
+        <v>116.65659464654038</v>
       </c>
       <c r="R121">
-        <v>-34.615466066232315</v>
+        <v>-27.007695799781629</v>
       </c>
     </row>
     <row r="122" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
       </c>
       <c r="Q122">
-        <v>116.65659464654038</v>
+        <v>115.14238021324108</v>
       </c>
       <c r="R122">
-        <v>-27.007695799781629</v>
+        <v>-24.697893127946649</v>
       </c>
     </row>
     <row r="123" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
       </c>
       <c r="Q123">
-        <v>115.14238021324108</v>
+        <v>115.68722214682816</v>
       </c>
       <c r="R123">
-        <v>-24.697893127946649</v>
+        <v>-28.167441697824167</v>
       </c>
     </row>
     <row r="124" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
       </c>
       <c r="Q124">
-        <v>115.68722214682816</v>
+        <v>115.90421239972798</v>
       </c>
       <c r="R124">
-        <v>-28.167441697824167</v>
+        <v>-31.444882640740847</v>
       </c>
     </row>
     <row r="125" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
       </c>
       <c r="Q125">
-        <v>115.90421239972798</v>
+        <v>118.59104261535464</v>
       </c>
       <c r="R125">
-        <v>-31.444882640740847</v>
+        <v>-29.285502942557969</v>
       </c>
     </row>
     <row r="126" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
       </c>
       <c r="Q126">
-        <v>118.59104261535464</v>
+        <v>118.39673279724994</v>
       </c>
       <c r="R126">
-        <v>-29.285502942557969</v>
+        <v>-30.752758698157304</v>
       </c>
     </row>
     <row r="127" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
       </c>
       <c r="Q127">
-        <v>118.39673279724994</v>
+        <v>150.93934717708817</v>
       </c>
       <c r="R127">
-        <v>-30.752758698157304</v>
+        <v>-24.76727518444596</v>
       </c>
     </row>
     <row r="128" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
       </c>
       <c r="Q128">
-        <v>150.93934717708817</v>
+        <v>148.23171019375965</v>
       </c>
       <c r="R128">
-        <v>-24.76727518444596</v>
+        <v>-20.970084429509942</v>
       </c>
     </row>
     <row r="129" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
       </c>
       <c r="Q129">
-        <v>148.23171019375965</v>
+        <v>147.06350485205559</v>
       </c>
       <c r="R129">
-        <v>-20.970084429509942</v>
+        <v>-21.81503719825152</v>
       </c>
     </row>
     <row r="130" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
       </c>
       <c r="Q130">
-        <v>147.06350485205559</v>
+        <v>151.88900228121577</v>
       </c>
       <c r="R130">
-        <v>-21.81503719825152</v>
+        <v>-28.426665025009203</v>
       </c>
     </row>
     <row r="131" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
       </c>
       <c r="Q131">
-        <v>151.88900228121577</v>
+        <v>149.22438062186285</v>
       </c>
       <c r="R131">
-        <v>-28.426665025009203</v>
+        <v>-27.235374901982532</v>
       </c>
     </row>
     <row r="132" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
       </c>
       <c r="Q132">
-        <v>149.22438062186285</v>
+        <v>147.76330434123716</v>
       </c>
       <c r="R132">
-        <v>-27.235374901982532</v>
+        <v>-28.17719003058987</v>
       </c>
     </row>
     <row r="133" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
       </c>
       <c r="Q133">
-        <v>147.76330434123716</v>
+        <v>149.43559238340944</v>
       </c>
       <c r="R133">
-        <v>-28.17719003058987</v>
+        <v>-25.53208894708445</v>
       </c>
     </row>
     <row r="134" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
       </c>
       <c r="Q134">
-        <v>149.43559238340944</v>
+        <v>146.46677109095083</v>
       </c>
       <c r="R134">
-        <v>-25.53208894708445</v>
+        <v>-23.265870692651252</v>
       </c>
     </row>
     <row r="135" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O135" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P135" t="s">
         <v>8</v>
       </c>
       <c r="Q135">
-        <v>146.46677109095083</v>
+        <v>146.2530408921524</v>
       </c>
       <c r="R135">
-        <v>-23.265870692651252</v>
+        <v>-24.912836419118246</v>
       </c>
     </row>
     <row r="136" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O136" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P136" t="s">
         <v>8</v>
       </c>
       <c r="Q136">
-        <v>146.2530408921524</v>
+        <v>150.77513759786697</v>
       </c>
       <c r="R136">
-        <v>-24.912836419118246</v>
+        <v>-33.927321285914829</v>
       </c>
     </row>
     <row r="137" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O137" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P137" t="s">
         <v>8</v>
       </c>
       <c r="Q137">
-        <v>150.77513759786697</v>
+        <v>149.63395959889763</v>
       </c>
       <c r="R137">
-        <v>-33.927321285914829</v>
+        <v>-34.446112622440367</v>
       </c>
     </row>
     <row r="138" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O138" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P138" t="s">
         <v>8</v>
       </c>
       <c r="Q138">
-        <v>149.63395959889763</v>
+        <v>151.9510333951863</v>
       </c>
       <c r="R138">
-        <v>-34.446112622440367</v>
+        <v>-31.610779267089288</v>
       </c>
     </row>
     <row r="139" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O139" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P139" t="s">
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>151.9510333951863</v>
+        <v>150.64279122684428</v>
       </c>
       <c r="R139">
-        <v>-31.610779267089288</v>
+        <v>-30.329307192442041</v>
       </c>
     </row>
     <row r="140" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O140" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P140" t="s">
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>150.64279122684428</v>
+        <v>142.69665953395346</v>
       </c>
       <c r="R140">
-        <v>-30.329307192442041</v>
+        <v>-28.42615104088356</v>
       </c>
     </row>
     <row r="141" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
       </c>
       <c r="Q141">
-        <v>142.69665953395346</v>
+        <v>145.17717767511434</v>
       </c>
       <c r="R141">
-        <v>-28.42615104088356</v>
+        <v>-28.240292440619939</v>
       </c>
     </row>
     <row r="142" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
       </c>
       <c r="Q142">
-        <v>145.17717767511434</v>
+        <v>143.59071424731289</v>
       </c>
       <c r="R142">
-        <v>-28.240292440619939</v>
+        <v>-25.934310769926011</v>
       </c>
     </row>
     <row r="143" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
       </c>
       <c r="Q143">
-        <v>143.59071424731289</v>
+        <v>147.73996892366085</v>
       </c>
       <c r="R143">
-        <v>-25.934310769926011</v>
+        <v>-30.460324370284951</v>
       </c>
     </row>
     <row r="144" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
       </c>
       <c r="Q144">
-        <v>147.73996892366085</v>
+        <v>145.08028680507692</v>
       </c>
       <c r="R144">
-        <v>-30.460324370284951</v>
+        <v>-33.42596416811471</v>
       </c>
     </row>
     <row r="145" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
       </c>
       <c r="Q145">
-        <v>145.08028680507692</v>
+        <v>144.10689207891647</v>
       </c>
       <c r="R145">
-        <v>-33.42596416811471</v>
+        <v>-31.011320891898983</v>
       </c>
     </row>
     <row r="146" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
       </c>
       <c r="Q146">
-        <v>144.10689207891647</v>
+        <v>119.9126561006962</v>
       </c>
       <c r="R146">
-        <v>-31.011320891898983</v>
+        <v>-18.762930736574628</v>
       </c>
     </row>
     <row r="147" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
       </c>
       <c r="Q147">
-        <v>119.9126561006962</v>
+        <v>118.04505668609308</v>
       </c>
       <c r="R147">
-        <v>-18.762930736574628</v>
+        <v>-18.943711458300104</v>
       </c>
     </row>
     <row r="148" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
       </c>
       <c r="Q148">
-        <v>118.04505668609308</v>
+        <v>119.47741098585524</v>
       </c>
       <c r="R148">
-        <v>-18.943711458300104</v>
+        <v>-17.341576901661309</v>
       </c>
     </row>
     <row r="149" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>119.47741098585524</v>
+        <v>120.7699066609067</v>
       </c>
       <c r="R149">
-        <v>-17.341576901661309</v>
+        <v>-16.701861452529982</v>
       </c>
     </row>
     <row r="150" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>120.7699066609067</v>
+        <v>120.92507981057096</v>
       </c>
       <c r="R150">
-        <v>-16.701861452529982</v>
+        <v>-17.89119788373922</v>
       </c>
     </row>
     <row r="151" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>120.92507981057096</v>
+        <v>148.32310486365299</v>
       </c>
       <c r="R151">
-        <v>-17.89119788373922</v>
+        <v>-38.317649436280313</v>
       </c>
     </row>
     <row r="152" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
       </c>
       <c r="Q152">
-        <v>148.32310486365299</v>
+        <v>149.91427469508412</v>
       </c>
       <c r="R152">
-        <v>-38.317649436280313</v>
+        <v>-37.666954901440938</v>
       </c>
     </row>
     <row r="153" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O153" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P153" t="s">
         <v>8</v>
       </c>
       <c r="Q153">
-        <v>149.91427469508412</v>
+        <v>148.2380581815757</v>
       </c>
       <c r="R153">
-        <v>-37.666954901440938</v>
+        <v>-42.385662374939223</v>
       </c>
     </row>
     <row r="154" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O154" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P154" t="s">
         <v>8</v>
       </c>
       <c r="Q154">
-        <v>148.2380581815757</v>
+        <v>145.49022483115897</v>
       </c>
       <c r="R154">
-        <v>-42.385662374939223</v>
+        <v>-43.009861490614647</v>
       </c>
     </row>
     <row r="155" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
       </c>
       <c r="Q155">
-        <v>145.49022483115897</v>
+        <v>141.65592107949502</v>
       </c>
       <c r="R155">
-        <v>-43.009861490614647</v>
+        <v>-38.521010458884057</v>
       </c>
     </row>
     <row r="156" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O156" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P156" t="s">
         <v>8</v>
       </c>
       <c r="Q156">
-        <v>141.65592107949502</v>
+        <v>144.55763782706819</v>
       </c>
       <c r="R156">
-        <v>-38.521010458884057</v>
+        <v>-38.513951467094387</v>
       </c>
     </row>
     <row r="157" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O157" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P157" t="s">
         <v>8</v>
       </c>
       <c r="Q157">
-        <v>144.55763782706819</v>
+        <v>144.77326716667514</v>
       </c>
       <c r="R157">
-        <v>-38.513951467094387</v>
+        <v>-39.715987878044587</v>
       </c>
     </row>
     <row r="158" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O158" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P158" t="s">
         <v>8</v>
       </c>
       <c r="Q158">
-        <v>144.77326716667514</v>
+        <v>147.27289869429097</v>
       </c>
       <c r="R158">
-        <v>-39.715987878044587</v>
+        <v>-39.835742995149893</v>
       </c>
     </row>
     <row r="159" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O159" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P159" t="s">
         <v>8</v>
       </c>
       <c r="Q159">
-        <v>147.27289869429097</v>
+        <v>125.93096074584602</v>
       </c>
       <c r="R159">
-        <v>-39.835742995149893</v>
+        <v>-33.361274423793468</v>
       </c>
     </row>
     <row r="160" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O160" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P160" t="s">
         <v>8</v>
       </c>
       <c r="Q160">
-        <v>125.93096074584602</v>
+        <v>123.37535402247092</v>
       </c>
       <c r="R160">
-        <v>-33.361274423793468</v>
+        <v>-34.303485688836098</v>
       </c>
     </row>
     <row r="161" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O161" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P161" t="s">
         <v>8</v>
       </c>
       <c r="Q161">
-        <v>123.37535402247092</v>
+        <v>114.7947165340852</v>
       </c>
       <c r="R161">
-        <v>-34.303485688836098</v>
+        <v>-32.54438600940842</v>
       </c>
     </row>
     <row r="162" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O162" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P162" t="s">
         <v>8</v>
       </c>
       <c r="Q162">
-        <v>114.7947165340852</v>
+        <v>115.63509693996244</v>
       </c>
       <c r="R162">
-        <v>-32.54438600940842</v>
+        <v>-34.956218827910511</v>
       </c>
     </row>
     <row r="163" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O163" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P163" t="s">
         <v>8</v>
       </c>
       <c r="Q163">
-        <v>115.63509693996244</v>
+        <v>119.9072235311796</v>
       </c>
       <c r="R163">
-        <v>-34.956218827910511</v>
+        <v>-34.597269389279965</v>
       </c>
     </row>
     <row r="164" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O164" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P164" t="s">
         <v>8</v>
       </c>
       <c r="Q164">
-        <v>119.9072235311796</v>
+        <v>137.78035397071665</v>
       </c>
       <c r="R164">
-        <v>-34.597269389279965</v>
+        <v>-32.819241490786624</v>
       </c>
     </row>
     <row r="165" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O165" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P165" t="s">
         <v>8</v>
       </c>
       <c r="Q165">
-        <v>137.78035397071665</v>
+        <v>137.20967407247699</v>
       </c>
       <c r="R165">
-        <v>-32.819241490786624</v>
+        <v>-36.223304540952505</v>
       </c>
     </row>
     <row r="166" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O166" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P166" t="s">
         <v>8</v>
       </c>
       <c r="Q166">
-        <v>137.20967407247699</v>
+        <v>129.134450023667</v>
       </c>
       <c r="R166">
-        <v>-36.223304540952505</v>
+        <v>-32.909253032721082</v>
       </c>
     </row>
     <row r="167" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O167" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P167" t="s">
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>129.134450023667</v>
+        <v>132.03627064460872</v>
       </c>
       <c r="R167">
-        <v>-32.909253032721082</v>
+        <v>-33.087877243811086</v>
       </c>
     </row>
     <row r="168" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O168" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P168" t="s">
         <v>8</v>
       </c>
       <c r="Q168">
-        <v>132.03627064460872</v>
+        <v>133.90646814672945</v>
       </c>
       <c r="R168">
-        <v>-33.087877243811086</v>
+        <v>-34.666650757457681</v>
       </c>
     </row>
     <row r="169" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O169" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P169" t="s">
         <v>8</v>
       </c>
       <c r="Q169">
-        <v>133.90646814672945</v>
+        <v>133.91848973168982</v>
       </c>
       <c r="R169">
-        <v>-34.666650757457681</v>
+        <v>-33.290709632176373</v>
       </c>
     </row>
     <row r="170" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O170" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P170" t="s">
         <v>8</v>
       </c>
       <c r="Q170">
-        <v>133.91848973168982</v>
+        <v>113.74486915277508</v>
       </c>
       <c r="R170">
-        <v>-33.290709632176373</v>
+        <v>-28.996828120045929</v>
       </c>
     </row>
     <row r="171" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O171" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P171" t="s">
         <v>8</v>
       </c>
       <c r="Q171">
-        <v>113.74486915277508</v>
+        <v>112.74359053980096</v>
       </c>
       <c r="R171">
-        <v>-28.996828120045929</v>
+        <v>-26.772426753633201</v>
       </c>
     </row>
     <row r="172" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O172" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P172" t="s">
         <v>8</v>
       </c>
       <c r="Q172">
-        <v>112.74359053980096</v>
+        <v>112.63415325098336</v>
       </c>
       <c r="R172">
-        <v>-26.772426753633201</v>
+        <v>-24.422167043715746</v>
       </c>
     </row>
     <row r="173" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O173" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P173" t="s">
         <v>8</v>
       </c>
       <c r="Q173">
-        <v>112.63415325098336</v>
+        <v>113.73544067893422</v>
       </c>
       <c r="R173">
-        <v>-24.422167043715746</v>
+        <v>-21.706116736523096</v>
       </c>
     </row>
     <row r="174" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O174" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P174" t="s">
         <v>8</v>
       </c>
       <c r="Q174">
-        <v>113.73544067893422</v>
+        <v>116.10746995541636</v>
       </c>
       <c r="R174">
-        <v>-21.706116736523096</v>
+        <v>-19.480023550066459</v>
       </c>
     </row>
     <row r="175" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O175" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P175" t="s">
         <v>8</v>
       </c>
       <c r="Q175">
-        <v>116.10746995541636</v>
+        <v>114.68862040279514</v>
       </c>
       <c r="R175">
-        <v>-19.480023550066459</v>
+        <v>-20.711484124597217</v>
       </c>
     </row>
     <row r="176" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O176" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P176" t="s">
         <v>8</v>
       </c>
       <c r="Q176">
-        <v>114.68862040279514</v>
+        <v>153.46075007326399</v>
       </c>
       <c r="R176">
-        <v>-20.711484124597217</v>
+        <v>-25.64608975222702</v>
       </c>
     </row>
     <row r="177" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O177" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P177" t="s">
         <v>8</v>
       </c>
       <c r="Q177">
-        <v>153.46075007326399</v>
+        <v>159.20482777269496</v>
       </c>
       <c r="R177">
-        <v>-25.64608975222702</v>
+        <v>-31.490532239940517</v>
       </c>
     </row>
     <row r="178" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O178" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P178" t="s">
         <v>8</v>
       </c>
       <c r="Q178">
-        <v>159.20482777269496</v>
+        <v>153.68674355709717</v>
       </c>
       <c r="R178">
-        <v>-31.490532239940517</v>
+        <v>-27.494239414331563</v>
       </c>
     </row>
     <row r="179" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O179" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P179" t="s">
         <v>8</v>
       </c>
       <c r="Q179">
-        <v>153.68674355709717</v>
+        <v>151.35627784832863</v>
       </c>
       <c r="R179">
-        <v>-27.494239414331563</v>
+        <v>-34.275360972593546</v>
       </c>
     </row>
     <row r="180" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O180" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P180" t="s">
         <v>8</v>
       </c>
       <c r="Q180">
-        <v>151.35627784832863</v>
+        <v>153.55763832618015</v>
       </c>
       <c r="R180">
-        <v>-34.275360972593546</v>
+        <v>-29.527372673957174</v>
       </c>
     </row>
     <row r="181" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O181" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P181" t="s">
         <v>8</v>
       </c>
       <c r="Q181">
-        <v>153.55763832618015</v>
+        <v>152.90565408954197</v>
       </c>
       <c r="R181">
-        <v>-29.527372673957174</v>
+        <v>-32.160506789513327</v>
       </c>
     </row>
     <row r="182" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O182" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P182" t="s">
         <v>8</v>
       </c>
       <c r="Q182">
-        <v>152.90565408954197</v>
+        <v>123.6209360771076</v>
       </c>
       <c r="R182">
-        <v>-32.160506789513327</v>
+        <v>-12.313250418759196</v>
       </c>
     </row>
     <row r="183" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O183" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P183" t="s">
         <v>8</v>
       </c>
       <c r="Q183">
-        <v>123.6209360771076</v>
+        <v>127.28982693164365</v>
       </c>
       <c r="R183">
-        <v>-12.313250418759196</v>
+        <v>-13.447264969718235</v>
       </c>
     </row>
     <row r="184" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O184" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P184" t="s">
         <v>8</v>
       </c>
       <c r="Q184">
-        <v>127.28982693164365</v>
+        <v>137.9274007467076</v>
       </c>
       <c r="R184">
-        <v>-13.447264969718235</v>
+        <v>-13.53904439343483</v>
       </c>
     </row>
     <row r="185" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O185" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P185" t="s">
         <v>8</v>
       </c>
       <c r="Q185">
-        <v>137.9274007467076</v>
+        <v>138.7835300980004</v>
       </c>
       <c r="R185">
-        <v>-13.53904439343483</v>
+        <v>-14.99287485410888</v>
       </c>
     </row>
     <row r="186" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O186" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P186" t="s">
         <v>8</v>
       </c>
       <c r="Q186">
-        <v>138.7835300980004</v>
+        <v>140.70260155913493</v>
       </c>
       <c r="R186">
-        <v>-14.99287485410888</v>
+        <v>-11.977657398671996</v>
       </c>
     </row>
     <row r="187" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O187" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P187" t="s">
         <v>8</v>
       </c>
       <c r="Q187">
-        <v>140.70260155913493</v>
+        <v>140.0512616860895</v>
       </c>
       <c r="R187">
-        <v>-11.977657398671996</v>
+        <v>-13.649234810616214</v>
       </c>
     </row>
     <row r="188" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O188" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P188" t="s">
         <v>8</v>
       </c>
       <c r="Q188">
-        <v>140.0512616860895</v>
+        <v>135.53232690608246</v>
       </c>
       <c r="R188">
-        <v>-13.649234810616214</v>
+        <v>-10.058412830277735</v>
       </c>
     </row>
     <row r="189" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O189" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P189" t="s">
         <v>8</v>
       </c>
       <c r="Q189">
-        <v>135.53232690608246</v>
+        <v>138.02236339770641</v>
       </c>
       <c r="R189">
-        <v>-10.058412830277735</v>
+        <v>-11.457551359089519</v>
       </c>
     </row>
     <row r="190" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O190" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P190" t="s">
         <v>8</v>
       </c>
       <c r="Q190">
-        <v>138.02236339770641</v>
+        <v>129.80616836492629</v>
       </c>
       <c r="R190">
-        <v>-11.457551359089519</v>
+        <v>-10.099829044183595</v>
       </c>
     </row>
     <row r="191" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O191" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P191" t="s">
         <v>8</v>
       </c>
       <c r="Q191">
-        <v>129.80616836492629</v>
+        <v>132.27258092622665</v>
       </c>
       <c r="R191">
-        <v>-10.099829044183595</v>
+        <v>-10.034977983480973</v>
       </c>
     </row>
     <row r="192" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O192" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P192" t="s">
         <v>8</v>
       </c>
       <c r="Q192">
-        <v>132.27258092622665</v>
+        <v>152.45277308531408</v>
       </c>
       <c r="R192">
-        <v>-10.034977983480973</v>
+        <v>-22.783968088520972</v>
       </c>
     </row>
     <row r="193" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O193" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P193" t="s">
         <v>8</v>
       </c>
       <c r="Q193">
-        <v>152.45277308531408</v>
+        <v>152.48347016037607</v>
       </c>
       <c r="R193">
-        <v>-22.783968088520972</v>
+        <v>-20.980492993694121</v>
       </c>
     </row>
     <row r="194" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O194" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P194" t="s">
         <v>8</v>
       </c>
       <c r="Q194">
-        <v>152.48347016037607</v>
+        <v>144.36177021993478</v>
       </c>
       <c r="R194">
-        <v>-20.980492993694121</v>
+        <v>-9.9641044817147968</v>
       </c>
     </row>
     <row r="195" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O195" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P195" t="s">
         <v>8</v>
       </c>
       <c r="Q195">
-        <v>144.36177021993478</v>
+        <v>144.12580128857698</v>
       </c>
       <c r="R195">
-        <v>-9.9641044817147968</v>
+        <v>-12.160973985632396</v>
       </c>
     </row>
     <row r="196" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O196" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P196" t="s">
         <v>8</v>
       </c>
       <c r="Q196">
-        <v>144.12580128857698</v>
+        <v>149.93800636445266</v>
       </c>
       <c r="R196">
-        <v>-12.160973985632396</v>
+        <v>-16.926232109956484</v>
       </c>
     </row>
     <row r="197" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O197" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="P197" t="s">
         <v>8</v>
       </c>
       <c r="Q197">
-        <v>149.93800636445266</v>
+        <v>149.09136985948658</v>
       </c>
       <c r="R197">
-        <v>-16.926232109956484</v>
+        <v>-19.056413284503343</v>
       </c>
     </row>
     <row r="198" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O198" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P198" t="s">
         <v>8</v>
       </c>
       <c r="Q198">
-        <v>149.09136985948658</v>
+        <v>143.90359456668338</v>
       </c>
       <c r="R198">
-        <v>-19.056413284503343</v>
+        <v>-16.424523984767728</v>
       </c>
     </row>
     <row r="199" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O199" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="P199" t="s">
         <v>8</v>
       </c>
       <c r="Q199">
-        <v>143.90359456668338</v>
+        <v>143.22470052438001</v>
       </c>
       <c r="R199">
-        <v>-16.424523984767728</v>
+        <v>-13.468602452715691</v>
       </c>
     </row>
     <row r="200" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O200" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P200" t="s">
         <v>8</v>
       </c>
       <c r="Q200">
-        <v>143.22470052438001</v>
+        <v>143.90529016295486</v>
       </c>
       <c r="R200">
-        <v>-13.468602452715691</v>
+        <v>-18.480560456616804</v>
       </c>
     </row>
     <row r="201" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O201" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P201" t="s">
         <v>8</v>
       </c>
       <c r="Q201">
-        <v>143.90529016295486</v>
+        <v>141.91280510410783</v>
       </c>
       <c r="R201">
-        <v>-18.480560456616804</v>
+        <v>-14.267874545971546</v>
       </c>
     </row>
     <row r="202" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O202" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P202" t="s">
         <v>8</v>
       </c>
       <c r="Q202">
-        <v>141.91280510410783</v>
+        <v>147.94674742269942</v>
       </c>
       <c r="R202">
-        <v>-14.267874545971546</v>
+        <v>-20.402760450148971</v>
       </c>
     </row>
     <row r="203" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O203" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P203" t="s">
         <v>8</v>
       </c>
       <c r="Q203">
-        <v>147.94674742269942</v>
+        <v>144.07788557941856</v>
       </c>
       <c r="R203">
-        <v>-20.402760450148971</v>
+        <v>-21.717575465917388</v>
       </c>
     </row>
     <row r="204" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O204" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P204" t="s">
         <v>8</v>
       </c>
       <c r="Q204">
-        <v>144.07788557941856</v>
+        <v>145.9443079211926</v>
       </c>
       <c r="R204">
-        <v>-21.717575465917388</v>
+        <v>-20.239947228052181</v>
       </c>
     </row>
     <row r="205" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O205" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P205" t="s">
         <v>8</v>
       </c>
       <c r="Q205">
-        <v>145.9443079211926</v>
+        <v>147.65166753303404</v>
       </c>
       <c r="R205">
-        <v>-20.239947228052181</v>
+        <v>-22.848790085185165</v>
       </c>
     </row>
     <row r="206" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O206" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P206" t="s">
         <v>8</v>
       </c>
       <c r="Q206">
-        <v>147.65166753303404</v>
+        <v>142.11939483808513</v>
       </c>
       <c r="R206">
-        <v>-22.848790085185165</v>
+        <v>-20.287585477957197</v>
       </c>
     </row>
     <row r="207" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O207" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="P207" t="s">
         <v>8</v>
       </c>
       <c r="Q207">
-        <v>142.11939483808513</v>
+        <v>142.30082021143733</v>
       </c>
       <c r="R207">
-        <v>-20.287585477957197</v>
+        <v>-18.402066295276651</v>
       </c>
     </row>
     <row r="208" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O208" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P208" t="s">
         <v>8</v>
       </c>
       <c r="Q208">
-        <v>142.30082021143733</v>
+        <v>139.9406845355177</v>
       </c>
       <c r="R208">
-        <v>-18.402066295276651</v>
+        <v>-18.592001825958096</v>
       </c>
     </row>
     <row r="209" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O209" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P209" t="s">
         <v>8</v>
       </c>
       <c r="Q209">
-        <v>139.9406845355177</v>
+        <v>136.52844938766063</v>
       </c>
       <c r="R209">
-        <v>-18.592001825958096</v>
+        <v>-16.923318022496602</v>
       </c>
     </row>
     <row r="210" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O210" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P210" t="s">
         <v>8</v>
       </c>
       <c r="Q210">
-        <v>136.52844938766063</v>
+        <v>138.01439622256723</v>
       </c>
       <c r="R210">
-        <v>-16.923318022496602</v>
+        <v>-19.947965320150729</v>
       </c>
     </row>
     <row r="211" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O211" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P211" t="s">
         <v>8</v>
       </c>
       <c r="Q211">
-        <v>138.01439622256723</v>
+        <v>135.46557003772165</v>
       </c>
       <c r="R211">
-        <v>-19.947965320150729</v>
+        <v>-18.416233482486358</v>
       </c>
     </row>
     <row r="212" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O212" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P212" t="s">
         <v>8</v>
       </c>
       <c r="Q212">
-        <v>135.46557003772165</v>
+        <v>134.79283929397783</v>
       </c>
       <c r="R212">
-        <v>-18.416233482486358</v>
+        <v>-20.732600676782639</v>
       </c>
     </row>
     <row r="213" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O213" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="P213" t="s">
         <v>8</v>
       </c>
       <c r="Q213">
-        <v>134.79283929397783</v>
+        <v>136.52758085947576</v>
       </c>
       <c r="R213">
-        <v>-20.732600676782639</v>
+        <v>-22.021539553207361</v>
       </c>
     </row>
     <row r="214" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O214" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P214" t="s">
         <v>8</v>
       </c>
       <c r="Q214">
-        <v>136.52758085947576</v>
+        <v>127.98414541606536</v>
       </c>
       <c r="R214">
-        <v>-22.021539553207361</v>
+        <v>-20.935762467407532</v>
       </c>
     </row>
     <row r="215" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O215" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P215" t="s">
         <v>8</v>
       </c>
       <c r="Q215">
-        <v>127.98414541606536</v>
+        <v>126.75721806702428</v>
       </c>
       <c r="R215">
-        <v>-20.935762467407532</v>
+        <v>-19.535728093615841</v>
       </c>
     </row>
     <row r="216" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O216" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P216" t="s">
         <v>8</v>
       </c>
       <c r="Q216">
-        <v>126.75721806702428</v>
+        <v>131.0185841389347</v>
       </c>
       <c r="R216">
-        <v>-19.535728093615841</v>
+        <v>-20.991416477707151</v>
       </c>
     </row>
     <row r="217" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O217" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P217" t="s">
         <v>8</v>
       </c>
       <c r="Q217">
-        <v>131.0185841389347</v>
+        <v>132.36508456813664</v>
       </c>
       <c r="R217">
-        <v>-20.991416477707151</v>
+        <v>-18.910342658765423</v>
       </c>
     </row>
     <row r="218" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O218" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P218" t="s">
         <v>8</v>
       </c>
       <c r="Q218">
-        <v>132.36508456813664</v>
+        <v>134.77431748659325</v>
       </c>
       <c r="R218">
-        <v>-18.910342658765423</v>
+        <v>-15.537965116102958</v>
       </c>
     </row>
     <row r="219" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O219" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P219" t="s">
         <v>8</v>
       </c>
       <c r="Q219">
-        <v>134.77431748659325</v>
+        <v>134.41284432791551</v>
       </c>
       <c r="R219">
-        <v>-15.537965116102958</v>
+        <v>-12.119621907128884</v>
       </c>
     </row>
     <row r="220" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O220" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P220" t="s">
         <v>8</v>
       </c>
       <c r="Q220">
-        <v>134.41284432791551</v>
+        <v>135.69256848725669</v>
       </c>
       <c r="R220">
-        <v>-12.119621907128884</v>
+        <v>-13.664146166265898</v>
       </c>
     </row>
     <row r="221" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O221" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P221" t="s">
         <v>8</v>
       </c>
       <c r="Q221">
-        <v>135.69256848725669</v>
+        <v>131.62113689763146</v>
       </c>
       <c r="R221">
-        <v>-13.664146166265898</v>
+        <v>-12.894653149909704</v>
       </c>
     </row>
     <row r="222" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O222" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P222" t="s">
         <v>8</v>
       </c>
       <c r="Q222">
-        <v>131.62113689763146</v>
+        <v>132.48892524469898</v>
       </c>
       <c r="R222">
-        <v>-12.894653149909704</v>
+        <v>-13.907083618728224</v>
       </c>
     </row>
     <row r="223" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O223" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P223" t="s">
         <v>8</v>
       </c>
       <c r="Q223">
-        <v>132.48892524469898</v>
+        <v>125.8255204059364</v>
       </c>
       <c r="R223">
-        <v>-13.907083618728224</v>
+        <v>-17.70421688591648</v>
       </c>
     </row>
     <row r="224" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O224" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P224" t="s">
         <v>8</v>
       </c>
       <c r="Q224">
-        <v>125.8255204059364</v>
+        <v>127.53869595671664</v>
       </c>
       <c r="R224">
-        <v>-17.70421688591648</v>
+        <v>-15.425735818899312</v>
       </c>
     </row>
     <row r="225" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O225" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P225" t="s">
         <v>8</v>
       </c>
       <c r="Q225">
-        <v>127.53869595671664</v>
+        <v>132.08986312355745</v>
       </c>
       <c r="R225">
-        <v>-15.425735818899312</v>
+        <v>-16.935964240758963</v>
       </c>
     </row>
     <row r="226" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O226" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P226" t="s">
         <v>8</v>
       </c>
       <c r="Q226">
-        <v>132.08986312355745</v>
+        <v>127.9753364052041</v>
       </c>
       <c r="R226">
-        <v>-16.935964240758963</v>
+        <v>-17.004321685535825</v>
       </c>
     </row>
     <row r="227" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O227" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P227" t="s">
         <v>8</v>
       </c>
       <c r="Q227">
-        <v>127.9753364052041</v>
+        <v>146.86282244839464</v>
       </c>
       <c r="R227">
-        <v>-17.004321685535825</v>
+        <v>-37.676684149628869</v>
       </c>
     </row>
     <row r="228" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O228" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P228" t="s">
         <v>8</v>
       </c>
       <c r="Q228">
-        <v>146.86282244839464</v>
+        <v>149.04105094255826</v>
       </c>
       <c r="R228">
-        <v>-37.676684149628869</v>
+        <v>-36.144059038515685</v>
       </c>
     </row>
     <row r="229" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O229" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P229" t="s">
         <v>8</v>
       </c>
       <c r="Q229">
-        <v>149.04105094255826</v>
+        <v>147.20822379338119</v>
       </c>
       <c r="R229">
-        <v>-36.144059038515685</v>
+        <v>-42.133338684243697</v>
       </c>
     </row>
     <row r="230" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O230" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P230" t="s">
         <v>8</v>
       </c>
       <c r="Q230">
-        <v>147.20822379338119</v>
+        <v>145.87076740617448</v>
       </c>
       <c r="R230">
-        <v>-42.133338684243697</v>
+        <v>-38.482407313362081</v>
       </c>
     </row>
     <row r="231" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O231" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P231" t="s">
         <v>8</v>
       </c>
       <c r="Q231">
-        <v>145.87076740617448</v>
+        <v>141.59885822344779</v>
       </c>
       <c r="R231">
-        <v>-38.482407313362081</v>
+        <v>-37.194161249481041</v>
       </c>
     </row>
     <row r="232" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O232" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P232" t="s">
         <v>8</v>
       </c>
       <c r="Q232">
-        <v>141.59885822344779</v>
+        <v>136.47849302130328</v>
       </c>
       <c r="R232">
-        <v>-37.194161249481041</v>
+        <v>-32.689973080235788</v>
       </c>
     </row>
     <row r="233" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O233" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P233" t="s">
         <v>8</v>
       </c>
       <c r="Q233">
-        <v>136.47849302130328</v>
+        <v>143.02654384684817</v>
       </c>
       <c r="R233">
-        <v>-32.689973080235788</v>
+        <v>-32.045131116301349</v>
       </c>
     </row>
     <row r="234" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O234" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P234" t="s">
         <v>8</v>
       </c>
       <c r="Q234">
-        <v>143.02654384684817</v>
+        <v>144.49127087303509</v>
       </c>
       <c r="R234">
-        <v>-32.045131116301349</v>
+        <v>-34.862419802160197</v>
       </c>
     </row>
     <row r="235" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O235" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="P235" t="s">
         <v>8</v>
       </c>
       <c r="Q235">
-        <v>144.49127087303509</v>
+        <v>140.56642796401263</v>
       </c>
       <c r="R235">
-        <v>-34.862419802160197</v>
+        <v>-33.052401492209839</v>
       </c>
     </row>
     <row r="236" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O236" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P236" t="s">
         <v>8</v>
       </c>
       <c r="Q236">
-        <v>140.56642796401263</v>
+        <v>140.00081023529913</v>
       </c>
       <c r="R236">
-        <v>-33.052401492209839</v>
+        <v>-31.408285546713287</v>
       </c>
     </row>
     <row r="237" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O237" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P237" t="s">
         <v>8</v>
       </c>
       <c r="Q237">
-        <v>140.00081023529913</v>
+        <v>137.08711551887083</v>
       </c>
       <c r="R237">
-        <v>-31.408285546713287</v>
+        <v>-31.014904189409062</v>
       </c>
     </row>
     <row r="238" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O238" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P238" t="s">
         <v>8</v>
       </c>
       <c r="Q238">
-        <v>137.08711551887083</v>
+        <v>145.51452797003827</v>
       </c>
       <c r="R238">
-        <v>-31.014904189409062</v>
+        <v>-24.435784713644757</v>
       </c>
     </row>
     <row r="239" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O239" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P239" t="s">
         <v>8</v>
       </c>
       <c r="Q239">
-        <v>145.51452797003827</v>
+        <v>140.02638596197502</v>
       </c>
       <c r="R239">
-        <v>-24.435784713644757</v>
+        <v>-24.142642750494868</v>
       </c>
     </row>
     <row r="240" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O240" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P240" t="s">
         <v>8</v>
       </c>
       <c r="Q240">
-        <v>140.02638596197502</v>
+        <v>141.87331622694285</v>
       </c>
       <c r="R240">
-        <v>-24.142642750494868</v>
+        <v>-22.59801335237621</v>
       </c>
     </row>
     <row r="241" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O241" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P241" t="s">
         <v>8</v>
       </c>
       <c r="Q241">
-        <v>141.87331622694285</v>
+        <v>134.39885944606516</v>
       </c>
       <c r="R241">
-        <v>-22.59801335237621</v>
+        <v>-24.79923061036914</v>
       </c>
     </row>
     <row r="242" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O242" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P242" t="s">
         <v>8</v>
       </c>
       <c r="Q242">
-        <v>134.39885944606516</v>
+        <v>137.32322652242817</v>
       </c>
       <c r="R242">
-        <v>-24.79923061036914</v>
+        <v>-24.727021000667804</v>
       </c>
     </row>
     <row r="243" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O243" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P243" t="s">
         <v>8</v>
       </c>
       <c r="Q243">
-        <v>137.32322652242817</v>
+        <v>143.17631246690607</v>
       </c>
       <c r="R243">
-        <v>-24.727021000667804</v>
+        <v>-26.284316493363157</v>
       </c>
     </row>
     <row r="244" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O244" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P244" t="s">
         <v>8</v>
       </c>
       <c r="Q244">
-        <v>143.17631246690607</v>
+        <v>141.05568117271642</v>
       </c>
       <c r="R244">
-        <v>-26.284316493363157</v>
+        <v>-27.058724077525344</v>
       </c>
     </row>
     <row r="245" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O245" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P245" t="s">
         <v>8</v>
       </c>
       <c r="Q245">
-        <v>141.05568117271642</v>
+        <v>131.51442733918063</v>
       </c>
       <c r="R245">
-        <v>-27.058724077525344</v>
+        <v>-28.368760408286018</v>
       </c>
     </row>
     <row r="246" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O246" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P246" t="s">
         <v>8</v>
       </c>
       <c r="Q246">
-        <v>131.51442733918063</v>
+        <v>134.32283850489063</v>
       </c>
       <c r="R246">
-        <v>-28.368760408286018</v>
+        <v>-30.621921725356888</v>
       </c>
     </row>
     <row r="247" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O247" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P247" t="s">
         <v>8</v>
       </c>
       <c r="Q247">
-        <v>134.32283850489063</v>
+        <v>130.77152772622495</v>
       </c>
       <c r="R247">
-        <v>-30.621921725356888</v>
+        <v>-30.635030423097369</v>
       </c>
     </row>
     <row r="248" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O248" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P248" t="s">
         <v>8</v>
       </c>
       <c r="Q248">
-        <v>130.77152772622495</v>
+        <v>140.72984435371333</v>
       </c>
       <c r="R248">
-        <v>-30.635030423097369</v>
+        <v>-29.40377609579539</v>
       </c>
     </row>
     <row r="249" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O249" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P249" t="s">
         <v>8</v>
       </c>
       <c r="Q249">
-        <v>140.72984435371333</v>
+        <v>134.66612187113373</v>
       </c>
       <c r="R249">
-        <v>-29.40377609579539</v>
+        <v>-28.15690116839572</v>
       </c>
     </row>
     <row r="250" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O250" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P250" t="s">
         <v>8</v>
       </c>
       <c r="Q250">
-        <v>134.66612187113373</v>
+        <v>136.77228252752337</v>
       </c>
       <c r="R250">
-        <v>-28.15690116839572</v>
+        <v>-27.541992457451759</v>
       </c>
     </row>
     <row r="251" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O251" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P251" t="s">
         <v>8</v>
       </c>
       <c r="Q251">
-        <v>136.77228252752337</v>
+        <v>149.35779146912768</v>
       </c>
       <c r="R251">
-        <v>-27.541992457451759</v>
+        <v>-26.300868571942431</v>
       </c>
     </row>
     <row r="252" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O252" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P252" t="s">
         <v>8</v>
       </c>
       <c r="Q252">
-        <v>149.35779146912768</v>
+        <v>148.14237478588089</v>
       </c>
       <c r="R252">
-        <v>-26.300868571942431</v>
+        <v>-27.600157486042235</v>
       </c>
     </row>
     <row r="253" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O253" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P253" t="s">
         <v>8</v>
       </c>
       <c r="Q253">
-        <v>148.14237478588089</v>
+        <v>152.12642849359025</v>
       </c>
       <c r="R253">
-        <v>-27.600157486042235</v>
+        <v>-28.3347891959374</v>
       </c>
     </row>
     <row r="254" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O254" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P254" t="s">
         <v>8</v>
       </c>
       <c r="Q254">
-        <v>152.12642849359025</v>
+        <v>153.10456995993425</v>
       </c>
       <c r="R254">
-        <v>-28.3347891959374</v>
+        <v>-28.752190756768822</v>
       </c>
     </row>
     <row r="255" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O255" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="P255" t="s">
         <v>8</v>
       </c>
       <c r="Q255">
-        <v>153.10456995993425</v>
+        <v>150.05391578943551</v>
       </c>
       <c r="R255">
-        <v>-28.752190756768822</v>
+        <v>-24.982613757086916</v>
       </c>
     </row>
     <row r="256" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O256" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P256" t="s">
         <v>8</v>
       </c>
       <c r="Q256">
-        <v>150.05391578943551</v>
+        <v>151.79277925052281</v>
       </c>
       <c r="R256">
-        <v>-24.982613757086916</v>
+        <v>-25.038955284229257</v>
       </c>
     </row>
     <row r="257" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O257" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P257" t="s">
         <v>8</v>
       </c>
       <c r="Q257">
-        <v>151.79277925052281</v>
+        <v>151.94448277205771</v>
       </c>
       <c r="R257">
-        <v>-25.038955284229257</v>
+        <v>-30.648097888639381</v>
       </c>
     </row>
     <row r="258" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O258" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P258" t="s">
         <v>8</v>
       </c>
       <c r="Q258">
-        <v>151.94448277205771</v>
+        <v>150.2541462946395</v>
       </c>
       <c r="R258">
-        <v>-30.648097888639381</v>
+        <v>-31.530311559255505</v>
       </c>
     </row>
     <row r="259" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O259" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P259" t="s">
         <v>8</v>
       </c>
       <c r="Q259">
-        <v>150.2541462946395</v>
+        <v>149.62090042212768</v>
       </c>
       <c r="R259">
-        <v>-31.530311559255505</v>
+        <v>-34.29495419383332</v>
       </c>
     </row>
     <row r="260" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O260" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P260" t="s">
         <v>8</v>
       </c>
       <c r="Q260">
-        <v>149.62090042212768</v>
+        <v>152.83763455688668</v>
       </c>
       <c r="R260">
-        <v>-34.29495419383332</v>
+        <v>-30.889034568147331</v>
       </c>
     </row>
     <row r="261" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O261" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P261" t="s">
         <v>8</v>
       </c>
       <c r="Q261">
-        <v>152.83763455688668</v>
+        <v>151.67802522839008</v>
       </c>
       <c r="R261">
-        <v>-30.889034568147331</v>
+        <v>-32.897248213926524</v>
       </c>
     </row>
     <row r="262" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O262" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P262" t="s">
         <v>8</v>
       </c>
       <c r="Q262">
-        <v>151.67802522839008</v>
+        <v>144.77318477184815</v>
       </c>
       <c r="R262">
-        <v>-32.897248213926524</v>
+        <v>-30.102696294151649</v>
       </c>
     </row>
     <row r="263" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O263" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P263" t="s">
         <v>8</v>
       </c>
       <c r="Q263">
-        <v>144.77318477184815</v>
+        <v>146.63244669472485</v>
       </c>
       <c r="R263">
-        <v>-30.102696294151649</v>
+        <v>-28.772135899285555</v>
       </c>
     </row>
     <row r="264" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O264" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P264" t="s">
         <v>8</v>
       </c>
       <c r="Q264">
-        <v>146.63244669472485</v>
+        <v>145.27438207575517</v>
       </c>
       <c r="R264">
-        <v>-28.772135899285555</v>
+        <v>-33.717668107285725</v>
       </c>
     </row>
     <row r="265" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O265" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P265" t="s">
         <v>8</v>
       </c>
       <c r="Q265">
-        <v>145.27438207575517</v>
+        <v>147.93972516999915</v>
       </c>
       <c r="R265">
-        <v>-33.717668107285725</v>
+        <v>-32.762336355038023</v>
       </c>
     </row>
     <row r="266" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O266" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P266" t="s">
         <v>8</v>
       </c>
       <c r="Q266">
-        <v>147.93972516999915</v>
+        <v>115.97456492850932</v>
       </c>
       <c r="R266">
-        <v>-32.762336355038023</v>
+        <v>-27.306192795280872</v>
       </c>
     </row>
     <row r="267" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O267" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P267" t="s">
         <v>8</v>
       </c>
       <c r="Q267">
-        <v>115.97456492850932</v>
+        <v>118.30697028240009</v>
       </c>
       <c r="R267">
-        <v>-27.306192795280872</v>
+        <v>-27.961249059143668</v>
       </c>
     </row>
     <row r="268" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O268" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P268" t="s">
         <v>8</v>
       </c>
       <c r="Q268">
-        <v>118.30697028240009</v>
+        <v>116.84344906931088</v>
       </c>
       <c r="R268">
-        <v>-27.961249059143668</v>
+        <v>-29.109751296776803</v>
       </c>
     </row>
     <row r="269" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O269" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P269" t="s">
         <v>8</v>
       </c>
       <c r="Q269">
-        <v>116.84344906931088</v>
+        <v>127.92921064711308</v>
       </c>
       <c r="R269">
-        <v>-29.109751296776803</v>
+        <v>-27.965189577949349</v>
       </c>
     </row>
     <row r="270" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O270" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P270" t="s">
         <v>8</v>
       </c>
       <c r="Q270">
-        <v>127.92921064711308</v>
+        <v>124.48324861064027</v>
       </c>
       <c r="R270">
-        <v>-27.965189577949349</v>
+        <v>-28.350204599948327</v>
       </c>
     </row>
     <row r="271" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O271" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P271" t="s">
         <v>8</v>
       </c>
       <c r="Q271">
-        <v>124.48324861064027</v>
+        <v>121.30598072890582</v>
       </c>
       <c r="R271">
-        <v>-28.350204599948327</v>
+        <v>-28.309618557173209</v>
       </c>
     </row>
     <row r="272" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O272" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P272" t="s">
         <v>8</v>
       </c>
       <c r="Q272">
-        <v>121.30598072890582</v>
+        <v>124.46777334471824</v>
       </c>
       <c r="R272">
-        <v>-28.309618557173209</v>
+        <v>-32.105240034383613</v>
       </c>
     </row>
     <row r="273" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O273" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P273" t="s">
         <v>8</v>
       </c>
       <c r="Q273">
-        <v>124.46777334471824</v>
+        <v>124.4931229496114</v>
       </c>
       <c r="R273">
-        <v>-32.105240034383613</v>
+        <v>-30.717946569059819</v>
       </c>
     </row>
     <row r="274" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O274" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P274" t="s">
         <v>8</v>
       </c>
       <c r="Q274">
-        <v>124.4931229496114</v>
+        <v>127.0895269072734</v>
       </c>
       <c r="R274">
-        <v>-30.717946569059819</v>
+        <v>-30.529227185974907</v>
       </c>
     </row>
     <row r="275" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O275" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="P275" t="s">
         <v>8</v>
       </c>
       <c r="Q275">
-        <v>127.0895269072734</v>
+        <v>118.05603838350194</v>
       </c>
       <c r="R275">
-        <v>-30.529227185974907</v>
+        <v>-34.353314155008022</v>
       </c>
     </row>
     <row r="276" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O276" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P276" t="s">
         <v>8</v>
       </c>
       <c r="Q276">
-        <v>118.05603838350194</v>
+        <v>116.48599270419892</v>
       </c>
       <c r="R276">
-        <v>-34.353314155008022</v>
+        <v>-31.735226030591157</v>
       </c>
     </row>
     <row r="277" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O277" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P277" t="s">
         <v>8</v>
       </c>
       <c r="Q277">
-        <v>116.48599270419892</v>
+        <v>121.35823120776448</v>
       </c>
       <c r="R277">
-        <v>-31.735226030591157</v>
+        <v>-30.231203300821271</v>
       </c>
     </row>
     <row r="278" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O278" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P278" t="s">
         <v>8</v>
       </c>
       <c r="Q278">
-        <v>121.35823120776448</v>
+        <v>120.98810738452003</v>
       </c>
       <c r="R278">
-        <v>-30.231203300821271</v>
+        <v>-31.912666666511377</v>
       </c>
     </row>
     <row r="279" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O279" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P279" t="s">
         <v>8</v>
       </c>
       <c r="Q279">
-        <v>120.98810738452003</v>
+        <v>121.40365316346715</v>
       </c>
       <c r="R279">
-        <v>-31.912666666511377</v>
+        <v>-23.38749660972239</v>
       </c>
     </row>
     <row r="280" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O280" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P280" t="s">
         <v>8</v>
       </c>
       <c r="Q280">
-        <v>121.40365316346715</v>
+        <v>120.78862262071124</v>
       </c>
       <c r="R280">
-        <v>-23.38749660972239</v>
+        <v>-25.85084559145124</v>
       </c>
     </row>
     <row r="281" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O281" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P281" t="s">
         <v>8</v>
       </c>
       <c r="Q281">
-        <v>120.78862262071124</v>
+        <v>124.92644854307436</v>
       </c>
       <c r="R281">
-        <v>-25.85084559145124</v>
+        <v>-24.488649236868213</v>
       </c>
     </row>
     <row r="282" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O282" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P282" t="s">
         <v>8</v>
       </c>
       <c r="Q282">
-        <v>124.92644854307436</v>
+        <v>125.40253143865678</v>
       </c>
       <c r="R282">
-        <v>-24.488649236868213</v>
+        <v>-26.39599312341414</v>
       </c>
     </row>
     <row r="283" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O283" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P283" t="s">
         <v>8</v>
       </c>
       <c r="Q283">
-        <v>125.40253143865678</v>
+        <v>127.83407424972432</v>
       </c>
       <c r="R283">
-        <v>-26.39599312341414</v>
+        <v>-23.326148026767665</v>
       </c>
     </row>
     <row r="284" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O284" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P284" t="s">
         <v>8</v>
       </c>
       <c r="Q284">
-        <v>127.83407424972432</v>
+        <v>125.11073457612062</v>
       </c>
       <c r="R284">
-        <v>-23.326148026767665</v>
+        <v>-22.060062802137889</v>
       </c>
     </row>
     <row r="285" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O285" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P285" t="s">
         <v>8</v>
       </c>
       <c r="Q285">
-        <v>125.11073457612062</v>
+        <v>130.77987585880484</v>
       </c>
       <c r="R285">
-        <v>-22.060062802137889</v>
+        <v>-23.6520771510862</v>
       </c>
     </row>
     <row r="286" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O286" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P286" t="s">
         <v>8</v>
       </c>
       <c r="Q286">
-        <v>130.77987585880484</v>
+        <v>129.76000532797065</v>
       </c>
       <c r="R286">
-        <v>-23.6520771510862</v>
+        <v>-25.751442172745637</v>
       </c>
     </row>
     <row r="287" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O287" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P287" t="s">
         <v>8</v>
       </c>
       <c r="Q287">
-        <v>129.76000532797065</v>
+        <v>121.19680097154732</v>
       </c>
       <c r="R287">
-        <v>-25.751442172745637</v>
+        <v>-20.824241557837841</v>
       </c>
     </row>
     <row r="288" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O288" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P288" t="s">
         <v>8</v>
       </c>
       <c r="Q288">
-        <v>121.19680097154732</v>
+        <v>123.82322757098922</v>
       </c>
       <c r="R288">
-        <v>-20.824241557837841</v>
+        <v>-17.471436176410265</v>
       </c>
     </row>
     <row r="289" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O289" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="P289" t="s">
         <v>8</v>
       </c>
       <c r="Q289">
-        <v>123.82322757098922</v>
+        <v>123.74790786027596</v>
       </c>
       <c r="R289">
-        <v>-17.471436176410265</v>
+        <v>-19.213785896290247</v>
       </c>
     </row>
     <row r="290" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O290" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P290" t="s">
         <v>8</v>
       </c>
       <c r="Q290">
-        <v>123.74790786027596</v>
+        <v>117.42275836968288</v>
       </c>
       <c r="R290">
-        <v>-19.213785896290247</v>
+        <v>-21.144003963089126</v>
       </c>
     </row>
     <row r="291" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O291" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P291" t="s">
         <v>8</v>
       </c>
       <c r="Q291">
-        <v>117.42275836968288</v>
+        <v>117.89666131220254</v>
       </c>
       <c r="R291">
-        <v>-21.144003963089126</v>
+        <v>-23.720298383817479</v>
       </c>
     </row>
     <row r="292" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O292" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P292" t="s">
         <v>8</v>
       </c>
       <c r="Q292">
-        <v>117.89666131220254</v>
+        <v>116.20239512475231</v>
       </c>
       <c r="R292">
-        <v>-23.720298383817479</v>
+        <v>-25.347887721648856</v>
       </c>
     </row>
     <row r="293" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O293" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P293" t="s">
         <v>8</v>
       </c>
       <c r="Q293">
-        <v>116.20239512475231</v>
+        <v>115.38939990331832</v>
       </c>
       <c r="R293">
-        <v>-25.347887721648856</v>
+        <v>-22.518290090128978</v>
       </c>
     </row>
     <row r="294" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O294" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P294" t="s">
         <v>8</v>
       </c>
       <c r="Q294">
-        <v>115.38939990331832</v>
+        <v>114.29262158861788</v>
       </c>
       <c r="R294">
-        <v>-22.518290090128978</v>
-      </c>
-    </row>
-    <row r="295" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O295" t="s">
-        <v>415</v>
-      </c>
-      <c r="P295" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q295">
-        <v>114.29262158861788</v>
-      </c>
-      <c r="R295">
         <v>-24.397642917030851</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AFDD7C5-0405-45F1-8224-4A0E23801E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E799660-8DFE-4EF2-8F24-F751E5DE7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F39D64EB-BF91-4BE4-B25E-2D1D19EC4433}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FC849403-00A2-4456-8646-3D8DBEAC1D6F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1648,7 +1648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399521CA-0D9D-4B40-9D16-E55576119735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D526CB-501F-4F64-AC03-6C64D4ACC54B}">
   <dimension ref="B3:R294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E799660-8DFE-4EF2-8F24-F751E5DE7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03FD8880-DB40-4082-B770-4765C7B0EC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FC849403-00A2-4456-8646-3D8DBEAC1D6F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{65CDBFCA-0BF4-4A78-9585-9147E1A87EF2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1648,7 +1648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D526CB-501F-4F64-AC03-6C64D4ACC54B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CBE14C-7D75-4A82-B23C-903DEE33F72D}">
   <dimension ref="B3:R294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03FD8880-DB40-4082-B770-4765C7B0EC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05B38BD7-F9F3-4497-AF0D-6937B774A8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{65CDBFCA-0BF4-4A78-9585-9147E1A87EF2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3EBA9A0-17D7-42CD-BE39-5272F0764C25}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="421">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -71,6 +71,24 @@
     <t>ELC</t>
   </si>
   <si>
+    <t>e_AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
+    <t>e_Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>g_AUS42p8S146p2E_AUS-Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>e_Sheffield_AUS</t>
+  </si>
+  <si>
+    <t>g_AUS42p8S146p2E_AUS-Sheffield_AUS</t>
+  </si>
+  <si>
     <t>e_Armidale_AUS</t>
   </si>
   <si>
@@ -80,9 +98,6 @@
     <t>g_Armidale_AUS-Brisbane_AUS</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>e_BulliCreek_AUS</t>
   </si>
   <si>
@@ -272,10 +287,10 @@
     <t>g_Nebo_AUS-Broadsound_AUS</t>
   </si>
   <si>
-    <t>e_Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Sheffield_AUS</t>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
   </si>
   <si>
     <t>g_Palmerston_AUS-Sheffield_AUS</t>
@@ -371,6 +386,12 @@
     <t>description</t>
   </si>
   <si>
+    <t>grid link -122.0 km- AU149-220;way/174441055-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -131.0 km- AU149-220;way/88191017-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -371.0 km- way/160201298-330;way/172587651-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -465,6 +486,9 @@
   </si>
   <si>
     <t>grid link -68.0 km- way/121646942-275;way/166113109-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -123.0 km- way/164764363-275;way/185835127-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>grid link -87.0 km- way/174441055-220;way/88191017-220 (thermal x 0.7 N-1)</t>
@@ -1648,8 +1672,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97CBE14C-7D75-4A82-B23C-903DEE33F72D}">
-  <dimension ref="B3:R294"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BF4525-D81A-4AEB-B1E7-225B3B7ACA9A}">
+  <dimension ref="B3:R296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1657,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -1686,22 +1710,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="P4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="Q4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="R4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -1730,10 +1754,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -1771,7 +1795,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="O6" t="s">
         <v>10</v>
@@ -1780,10 +1804,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>151.71319760744726</v>
+        <v>146.17591077698933</v>
       </c>
       <c r="R6">
-        <v>-30.532100853424872</v>
+        <v>-42.848328268142403</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
@@ -1812,7 +1836,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="O7" t="s">
         <v>16</v>
@@ -1821,10 +1845,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>116.2758549871163</v>
+        <v>151.71319760744726</v>
       </c>
       <c r="R7">
-        <v>-33.318012556546421</v>
+        <v>-30.532100853424872</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
@@ -1838,34 +1862,34 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s">
+        <v>118</v>
+      </c>
+      <c r="O8" t="s">
         <v>21</v>
       </c>
-      <c r="L8" t="s">
-        <v>113</v>
-      </c>
-      <c r="O8" t="s">
-        <v>19</v>
-      </c>
       <c r="P8" t="s">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>143.92108294719912</v>
+        <v>116.2758549871163</v>
       </c>
       <c r="R8">
-        <v>-37.567537497399123</v>
+        <v>-33.318012556546421</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
@@ -1879,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -1894,19 +1918,19 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>143.5251594037239</v>
+        <v>143.92108294719912</v>
       </c>
       <c r="R9">
-        <v>-34.775720926588463</v>
+        <v>-37.567537497399123</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
@@ -1920,22 +1944,22 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O10" t="s">
         <v>31</v>
@@ -1944,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>150.48716060704265</v>
+        <v>143.5251594037239</v>
       </c>
       <c r="R10">
-        <v>-23.537233256213721</v>
+        <v>-34.775720926588463</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -1961,34 +1985,34 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>152.95633561497641</v>
+        <v>150.48716060704265</v>
       </c>
       <c r="R11">
-        <v>-27.732264407857119</v>
+        <v>-23.537233256213721</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -2002,34 +2026,34 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O12" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>149.40404924290272</v>
+        <v>152.95633561497641</v>
       </c>
       <c r="R12">
-        <v>-22.820756210209289</v>
+        <v>-27.732264407857119</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
@@ -2043,34 +2067,34 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>141.41917764116005</v>
+        <v>149.40404924290272</v>
       </c>
       <c r="R13">
-        <v>-31.986353168692315</v>
+        <v>-22.820756210209289</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.45">
@@ -2087,31 +2111,31 @@
         <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>150.84329384341081</v>
+        <v>141.41917764116005</v>
       </c>
       <c r="R14">
-        <v>-27.920986820196017</v>
+        <v>-31.986353168692315</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
@@ -2128,7 +2152,7 @@
         <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
         <v>35</v>
@@ -2140,19 +2164,19 @@
         <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>151.19284847613793</v>
+        <v>150.84329384341081</v>
       </c>
       <c r="R15">
-        <v>-23.856194719487281</v>
+        <v>-27.920986820196017</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -2169,31 +2193,31 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" t="s">
+        <v>126</v>
+      </c>
+      <c r="O16" t="s">
         <v>37</v>
       </c>
-      <c r="L16" t="s">
-        <v>121</v>
-      </c>
-      <c r="O16" t="s">
-        <v>34</v>
-      </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>150.62709905075124</v>
+        <v>151.19284847613793</v>
       </c>
       <c r="R16">
-        <v>-24.342461230294287</v>
+        <v>-23.856194719487281</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -2207,34 +2231,34 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" t="s">
+        <v>127</v>
+      </c>
+      <c r="O17" t="s">
         <v>39</v>
       </c>
-      <c r="L17" t="s">
-        <v>122</v>
-      </c>
-      <c r="O17" t="s">
-        <v>47</v>
-      </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>148.90388563970319</v>
+        <v>150.62709905075124</v>
       </c>
       <c r="R17">
-        <v>-34.862594637477081</v>
+        <v>-24.342461230294287</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -2248,34 +2272,34 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>151.49237495717287</v>
+        <v>148.90388563970319</v>
       </c>
       <c r="R18">
-        <v>-33.052074884026759</v>
+        <v>-34.862594637477081</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
@@ -2289,34 +2313,34 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L19" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="O19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>145.52658139950708</v>
+        <v>151.49237495717287</v>
       </c>
       <c r="R19">
-        <v>-17.800806029919851</v>
+        <v>-33.052074884026759</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">
@@ -2330,34 +2354,34 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O20" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>146.03429268958672</v>
+        <v>145.52658139950708</v>
       </c>
       <c r="R20">
-        <v>-34.648775935550987</v>
+        <v>-17.800806029919851</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.45">
@@ -2371,34 +2395,34 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="O21" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>137.8128974128341</v>
+        <v>146.03429268958672</v>
       </c>
       <c r="R21">
-        <v>-32.536269144315668</v>
+        <v>-34.648775935550987</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.45">
@@ -2412,34 +2436,34 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O22" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>151.81952564800682</v>
+        <v>137.8128974128341</v>
       </c>
       <c r="R22">
-        <v>-24.90133538944163</v>
+        <v>-32.536269144315668</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2453,34 +2477,34 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="O23" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>146.42885495857578</v>
+        <v>151.81952564800682</v>
       </c>
       <c r="R23">
-        <v>-38.281663652861432</v>
+        <v>-24.90133538944163</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2494,10 +2518,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -2509,19 +2533,19 @@
         <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="O24" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>142.28083100000038</v>
+        <v>146.42885495857578</v>
       </c>
       <c r="R24">
-        <v>-36.721698083045936</v>
+        <v>-38.281663652861432</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2535,34 +2559,34 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="O25" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>121.42358390000004</v>
+        <v>142.28083100000038</v>
       </c>
       <c r="R25">
-        <v>-30.781882477049411</v>
+        <v>-36.721698083045936</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
@@ -2576,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
         <v>56</v>
@@ -2591,19 +2615,19 @@
         <v>56</v>
       </c>
       <c r="L26" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="O26" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>116.74275233957847</v>
+        <v>121.42358390000004</v>
       </c>
       <c r="R26">
-        <v>-20.762601878195927</v>
+        <v>-30.781882477049411</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -2617,7 +2641,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
         <v>57</v>
@@ -2632,19 +2656,19 @@
         <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O27" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>118.22746058460694</v>
+        <v>116.74275233957847</v>
       </c>
       <c r="R27">
-        <v>-31.539704529422323</v>
+        <v>-20.762601878195927</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
@@ -2673,19 +2697,19 @@
         <v>61</v>
       </c>
       <c r="L28" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="O28" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>116.7594477898767</v>
+        <v>118.22746058460694</v>
       </c>
       <c r="R28">
-        <v>-29.187814184805315</v>
+        <v>-31.539704529422323</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
@@ -2699,34 +2723,34 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>150.02574011758799</v>
+        <v>116.7594477898767</v>
       </c>
       <c r="R29">
-        <v>-33.363653242312999</v>
+        <v>-29.187814184805315</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
@@ -2740,34 +2764,34 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L30" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="O30" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>148.144166863903</v>
+        <v>150.02574011758799</v>
       </c>
       <c r="R30">
-        <v>-36.225604818390735</v>
+        <v>-33.363653242312999</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
@@ -2781,10 +2805,10 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
         <v>67</v>
@@ -2796,19 +2820,19 @@
         <v>67</v>
       </c>
       <c r="L31" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="O31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P31" t="s">
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>148.68315461202329</v>
+        <v>148.144166863903</v>
       </c>
       <c r="R31">
-        <v>-21.63132000917609</v>
+        <v>-36.225604818390735</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
@@ -2837,19 +2861,19 @@
         <v>70</v>
       </c>
       <c r="L32" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>146.98953647822455</v>
+        <v>148.68315461202329</v>
       </c>
       <c r="R32">
-        <v>-41.7876715671242</v>
+        <v>-21.63132000917609</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.45">
@@ -2863,34 +2887,34 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L33" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="O33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>138.71215621124384</v>
+        <v>136.86041214033099</v>
       </c>
       <c r="R33">
-        <v>-34.7354348842319</v>
+        <v>-30.449226158779943</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.45">
@@ -2904,34 +2928,34 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L34" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="O34" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>115.84737549921022</v>
+        <v>146.98953647822455</v>
       </c>
       <c r="R34">
-        <v>-32.189392578269448</v>
+        <v>-41.7876715671242</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.45">
@@ -2945,34 +2969,34 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L35" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P35" t="s">
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>118.54463160000005</v>
+        <v>138.71215621124384</v>
       </c>
       <c r="R35">
-        <v>-20.432074971605672</v>
+        <v>-34.7354348842319</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.45">
@@ -2986,34 +3010,34 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="O36" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>139.12683826085333</v>
+        <v>115.84737549921022</v>
       </c>
       <c r="R36">
-        <v>-33.956428790142837</v>
+        <v>-32.189392578269448</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.45">
@@ -3027,34 +3051,34 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L37" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="O37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>145.22587842608721</v>
+        <v>118.54463160000005</v>
       </c>
       <c r="R37">
-        <v>-37.929945191522378</v>
+        <v>-20.432074971605672</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.45">
@@ -3068,10 +3092,10 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G38" t="s">
         <v>81</v>
@@ -3083,19 +3107,19 @@
         <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O38" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>146.30697121829795</v>
+        <v>139.12683826085333</v>
       </c>
       <c r="R38">
-        <v>-41.33568787101467</v>
+        <v>-33.956428790142837</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.45">
@@ -3112,7 +3136,7 @@
         <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
         <v>83</v>
@@ -3124,19 +3148,19 @@
         <v>83</v>
       </c>
       <c r="L39" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="O39" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="P39" t="s">
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>145.07540407639536</v>
+        <v>145.22587842608721</v>
       </c>
       <c r="R39">
-        <v>-37.645174301346643</v>
+        <v>-37.929945191522378</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.45">
@@ -3150,34 +3174,34 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
         <v>84</v>
-      </c>
-      <c r="F40" t="s">
-        <v>63</v>
-      </c>
-      <c r="G40" t="s">
-        <v>85</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L40" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="O40" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="P40" t="s">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>147.7754061331616</v>
+        <v>146.30697121829795</v>
       </c>
       <c r="R40">
-        <v>-20.499447155592211</v>
+        <v>-41.33568787101467</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.45">
@@ -3191,10 +3215,10 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G41" t="s">
         <v>86</v>
@@ -3206,19 +3230,19 @@
         <v>86</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="O41" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="P41" t="s">
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>150.82867670028497</v>
+        <v>145.07540407639536</v>
       </c>
       <c r="R41">
-        <v>-33.815823161761138</v>
+        <v>-37.645174301346643</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.45">
@@ -3232,34 +3256,34 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L42" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="O42" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P42" t="s">
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>151.90657331394655</v>
+        <v>147.7754061331616</v>
       </c>
       <c r="R42">
-        <v>-26.786815702260583</v>
+        <v>-20.499447155592211</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.45">
@@ -3273,10 +3297,10 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G43" t="s">
         <v>90</v>
@@ -3288,19 +3312,19 @@
         <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O43" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="P43" t="s">
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>142.18101587735953</v>
+        <v>150.82867670028497</v>
       </c>
       <c r="R43">
-        <v>-38.17911060837443</v>
+        <v>-33.815823161761138</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.45">
@@ -3314,10 +3338,10 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
         <v>91</v>
@@ -3329,19 +3353,19 @@
         <v>91</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O44" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="P44" t="s">
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>117.77622337735301</v>
+        <v>151.90657331394655</v>
       </c>
       <c r="R44">
-        <v>-22.73480648494872</v>
+        <v>-26.786815702260583</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.45">
@@ -3355,10 +3379,10 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s">
         <v>92</v>
@@ -3370,19 +3394,19 @@
         <v>92</v>
       </c>
       <c r="L45" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="O45" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>148.38595135487864</v>
+        <v>142.18101587735953</v>
       </c>
       <c r="R45">
-        <v>-35.91111863050287</v>
+        <v>-38.17911060837443</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.45">
@@ -3396,34 +3420,34 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L46" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="O46" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>147.39393085110601</v>
+        <v>117.77622337735301</v>
       </c>
       <c r="R46">
-        <v>-35.200406760019412</v>
+        <v>-22.73480648494872</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.45">
@@ -3437,34 +3461,34 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L47" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O47" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="P47" t="s">
         <v>8</v>
       </c>
       <c r="Q47">
-        <v>149.76896533906228</v>
+        <v>148.38595135487864</v>
       </c>
       <c r="R47">
-        <v>-26.268566355497121</v>
+        <v>-35.91111863050287</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.45">
@@ -3478,34 +3502,34 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L48" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O48" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="P48" t="s">
         <v>8</v>
       </c>
       <c r="Q48">
-        <v>115.53508832785479</v>
+        <v>147.39393085110601</v>
       </c>
       <c r="R48">
-        <v>-30.767640414252401</v>
+        <v>-35.200406760019412</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.45">
@@ -3519,34 +3543,34 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="O49" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="P49" t="s">
         <v>8</v>
       </c>
       <c r="Q49">
-        <v>126.87543483120088</v>
+        <v>149.76896533906228</v>
       </c>
       <c r="R49">
-        <v>-31.570835856427525</v>
+        <v>-26.268566355497121</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.45">
@@ -3560,34 +3584,34 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="G50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L50" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="O50" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
       </c>
       <c r="Q50">
-        <v>138.68088035579376</v>
+        <v>115.53508832785479</v>
       </c>
       <c r="R50">
-        <v>-33.050322280935085</v>
+        <v>-30.767640414252401</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.45">
@@ -3601,10 +3625,10 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
         <v>100</v>
@@ -3616,19 +3640,19 @@
         <v>100</v>
       </c>
       <c r="L51" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="O51" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>133.78757460034689</v>
+        <v>150.70992497038807</v>
       </c>
       <c r="R51">
-        <v>-31.537820769156081</v>
+        <v>-34.147467956805272</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.45">
@@ -3642,34 +3666,34 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" t="s">
         <v>101</v>
-      </c>
-      <c r="F52" t="s">
-        <v>47</v>
-      </c>
-      <c r="G52" t="s">
-        <v>102</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="O52" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
       </c>
       <c r="Q52">
-        <v>138.41823350812663</v>
+        <v>145.06309545865503</v>
       </c>
       <c r="R52">
-        <v>-35.501951363966938</v>
+        <v>-36.83533638167507</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.45">
@@ -3683,10 +3707,10 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="G53" t="s">
         <v>103</v>
@@ -3698,19 +3722,19 @@
         <v>103</v>
       </c>
       <c r="L53" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="O53" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>132.10100769152496</v>
+        <v>117.35009498174544</v>
       </c>
       <c r="R53">
-        <v>-25.49357352256672</v>
+        <v>-34.633289924628762</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3724,34 +3748,34 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F54" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="G54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L54" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="O54" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>133.70279525625577</v>
+        <v>145.74672600476077</v>
       </c>
       <c r="R54">
-        <v>-28.066746287936159</v>
+        <v>-41.239472398304343</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -3765,34 +3789,34 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="G55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="O55" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>131.34409440196771</v>
+        <v>143.55638576867557</v>
       </c>
       <c r="R55">
-        <v>-28.04146789637413</v>
+        <v>-37.465189354544776</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.45">
@@ -3806,3366 +3830,3475 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
       </c>
       <c r="K56" t="s">
+        <v>108</v>
+      </c>
+      <c r="L56" t="s">
+        <v>166</v>
+      </c>
+      <c r="O56" t="s">
+        <v>180</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>150.05896747449162</v>
+      </c>
+      <c r="R56">
+        <v>-24.58894897576948</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" t="s">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s">
+        <v>109</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" t="s">
+        <v>109</v>
+      </c>
+      <c r="L57" t="s">
+        <v>167</v>
+      </c>
+      <c r="O57" t="s">
+        <v>181</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>147.35227485485339</v>
+      </c>
+      <c r="R57">
+        <v>-23.8370612107902</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" t="s">
         <v>106</v>
       </c>
-      <c r="L56" t="s">
-        <v>161</v>
-      </c>
-      <c r="O56" t="s">
-        <v>174</v>
-      </c>
-      <c r="P56" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q56">
-        <v>130.63850148412087</v>
-      </c>
-      <c r="R56">
-        <v>-30.151673533026507</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O57" t="s">
-        <v>175</v>
-      </c>
-      <c r="P57" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q57">
-        <v>136.6543963226575</v>
-      </c>
-      <c r="R57">
-        <v>-30.346236863934219</v>
-      </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="G58" t="s">
+        <v>110</v>
+      </c>
+      <c r="H58" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" t="s">
+        <v>110</v>
+      </c>
+      <c r="L58" t="s">
+        <v>168</v>
+      </c>
       <c r="O58" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>134.69581248525074</v>
+        <v>150.70172534099848</v>
       </c>
       <c r="R58">
-        <v>-30.730748793905519</v>
+        <v>-30.507071736111641</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s">
+        <v>87</v>
+      </c>
+      <c r="G59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H59" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" t="s">
+        <v>111</v>
+      </c>
+      <c r="L59" t="s">
+        <v>169</v>
+      </c>
       <c r="O59" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>135.42179448527094</v>
+        <v>135.66607044264202</v>
       </c>
       <c r="R59">
-        <v>-24.023047149503736</v>
+        <v>-33.218506405773972</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O60" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>130.86103071723457</v>
+        <v>138.02203212366797</v>
       </c>
       <c r="R60">
-        <v>-22.595450439397052</v>
+        <v>-31.939913984234508</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O61" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>140.73446817308161</v>
+        <v>139.86385810415234</v>
       </c>
       <c r="R61">
-        <v>-31.100522794087091</v>
+        <v>-33.257596019081056</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O62" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>136.74960353581776</v>
+        <v>145.55549987114685</v>
       </c>
       <c r="R62">
-        <v>-28.096813504185462</v>
+        <v>-23.758848518091867</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O63" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>138.55276692913932</v>
+        <v>148.23176617237627</v>
       </c>
       <c r="R63">
-        <v>-26.886442670709371</v>
+        <v>-31.648362130602383</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O64" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>134.09893869430459</v>
+        <v>145.64492309820076</v>
       </c>
       <c r="R64">
-        <v>-12.767605192826451</v>
+        <v>-31.400551816060769</v>
       </c>
     </row>
     <row r="65" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O65" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>136.25707133560488</v>
+        <v>145.08659035415462</v>
       </c>
       <c r="R65">
-        <v>-16.639117165833714</v>
+        <v>-34.137093062271134</v>
       </c>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O66" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>140.33047031611449</v>
+        <v>143.66575959932467</v>
       </c>
       <c r="R66">
-        <v>-19.270168976498251</v>
+        <v>-33.62388010001915</v>
       </c>
     </row>
     <row r="67" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O67" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>131.02821227078974</v>
+        <v>151.59594681987377</v>
       </c>
       <c r="R67">
-        <v>-20.288555696485421</v>
+        <v>-26.369630010973268</v>
       </c>
     </row>
     <row r="68" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O68" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>132.9773260478994</v>
+        <v>150.15732905181272</v>
       </c>
       <c r="R68">
-        <v>-19.134632003477144</v>
+        <v>-23.706875486581438</v>
       </c>
     </row>
     <row r="69" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O69" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>133.08033774630167</v>
+        <v>151.4718066142166</v>
       </c>
       <c r="R69">
-        <v>-17.232170442209615</v>
+        <v>-25.411178903352639</v>
       </c>
     </row>
     <row r="70" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O70" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>130.07387926508619</v>
+        <v>146.43171849829355</v>
       </c>
       <c r="R70">
-        <v>-15.90683731540358</v>
+        <v>-20.994143017659859</v>
       </c>
     </row>
     <row r="71" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O71" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>131.44822420859035</v>
+        <v>143.01659064084205</v>
       </c>
       <c r="R71">
-        <v>-12.82434425746715</v>
+        <v>-23.911108657321289</v>
       </c>
     </row>
     <row r="72" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O72" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>144.06475345158557</v>
+        <v>144.14104615068234</v>
       </c>
       <c r="R72">
-        <v>-14.918328674842474</v>
+        <v>-22.380981243555336</v>
       </c>
     </row>
     <row r="73" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O73" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>142.83587016468007</v>
+        <v>146.94281184898847</v>
       </c>
       <c r="R73">
-        <v>-12.686216555715513</v>
+        <v>-35.953929114813228</v>
       </c>
     </row>
     <row r="74" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O74" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>142.40851942403145</v>
+        <v>139.31840264795321</v>
       </c>
       <c r="R74">
-        <v>-18.491878095825161</v>
+        <v>-35.731086944716644</v>
       </c>
     </row>
     <row r="75" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O75" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>145.31671437316541</v>
+        <v>152.8095039798896</v>
       </c>
       <c r="R75">
-        <v>-19.409940321761617</v>
+        <v>-28.248182600001183</v>
       </c>
     </row>
     <row r="76" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O76" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>143.2193142021186</v>
+        <v>148.43143168566914</v>
       </c>
       <c r="R76">
-        <v>-21.577252989404748</v>
+        <v>-29.152576423550379</v>
       </c>
     </row>
     <row r="77" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O77" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>141.13298709337377</v>
+        <v>147.48956461856997</v>
       </c>
       <c r="R77">
-        <v>-22.375086663489547</v>
+        <v>-41.86050859336482</v>
       </c>
     </row>
     <row r="78" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O78" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>138.88894971874203</v>
+        <v>147.97254391558172</v>
       </c>
       <c r="R78">
-        <v>-24.087766437384666</v>
+        <v>-36.522039302338754</v>
       </c>
     </row>
     <row r="79" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O79" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>136.76817822772392</v>
+        <v>132.10100769152496</v>
       </c>
       <c r="R79">
-        <v>-19.38668521985424</v>
+        <v>-25.49357352256672</v>
       </c>
     </row>
     <row r="80" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O80" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>136.4508348496494</v>
+        <v>133.70279525625577</v>
       </c>
       <c r="R80">
-        <v>-21.384730246760789</v>
+        <v>-28.066746287936159</v>
       </c>
     </row>
     <row r="81" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O81" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>127.74686025752874</v>
+        <v>131.34409440196771</v>
       </c>
       <c r="R81">
-        <v>-16.305787203948107</v>
+        <v>-28.04146789637413</v>
       </c>
     </row>
     <row r="82" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O82" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>127.14468786066958</v>
+        <v>130.27817420339892</v>
       </c>
       <c r="R82">
-        <v>-21.316826063663147</v>
+        <v>-30.750489466295512</v>
       </c>
     </row>
     <row r="83" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O83" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>128.03124895889869</v>
+        <v>130.87873099518939</v>
       </c>
       <c r="R83">
-        <v>-19.504849900358565</v>
+        <v>-29.75244409199982</v>
       </c>
     </row>
     <row r="84" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O84" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>124.30097588195656</v>
+        <v>133.94123567877054</v>
       </c>
       <c r="R84">
-        <v>-19.646611890372487</v>
+        <v>-31.549752873691599</v>
       </c>
     </row>
     <row r="85" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O85" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>125.44646700631158</v>
+        <v>136.28091361308438</v>
       </c>
       <c r="R85">
-        <v>-18.034517000819385</v>
+        <v>-30.04854365720664</v>
       </c>
     </row>
     <row r="86" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O86" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>119.8792314384001</v>
+        <v>134.5027026411494</v>
       </c>
       <c r="R86">
-        <v>-26.943751576747506</v>
+        <v>-30.55204904451108</v>
       </c>
     </row>
     <row r="87" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O87" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>123.91849872196477</v>
+        <v>138.74457983050598</v>
       </c>
       <c r="R87">
-        <v>-28.596430984362627</v>
+        <v>-26.873524361102771</v>
       </c>
     </row>
     <row r="88" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O88" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>120.83347096461442</v>
+        <v>136.91940532518902</v>
       </c>
       <c r="R88">
-        <v>-28.749113003071905</v>
+        <v>-28.248428425646203</v>
       </c>
     </row>
     <row r="89" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O89" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P89" t="s">
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>127.45396257591824</v>
+        <v>139.25388984353549</v>
       </c>
       <c r="R89">
-        <v>-29.710182852828943</v>
+        <v>-24.111623182346271</v>
       </c>
     </row>
     <row r="90" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>125.2634274064108</v>
+        <v>135.92252961017942</v>
       </c>
       <c r="R90">
-        <v>-30.48444119537271</v>
+        <v>-24.40588485921278</v>
       </c>
     </row>
     <row r="91" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>124.60722906157319</v>
+        <v>135.89696303129097</v>
       </c>
       <c r="R91">
-        <v>-31.80277872120627</v>
+        <v>-21.914244713938611</v>
       </c>
     </row>
     <row r="92" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>122.14641208564728</v>
+        <v>133.07960193023257</v>
       </c>
       <c r="R92">
-        <v>-30.486367305495254</v>
+        <v>-19.811351599191354</v>
       </c>
     </row>
     <row r="93" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>126.75981019754011</v>
+        <v>131.21829069078203</v>
       </c>
       <c r="R93">
-        <v>-23.110892098770499</v>
+        <v>-21.32990756247144</v>
       </c>
     </row>
     <row r="94" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>125.01398345772546</v>
+        <v>130.92501902101736</v>
       </c>
       <c r="R94">
-        <v>-26.67735817029363</v>
+        <v>-23.251052266326525</v>
       </c>
     </row>
     <row r="95" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>127.5392725342796</v>
+        <v>145.43792160633583</v>
       </c>
       <c r="R95">
-        <v>-26.043555904293484</v>
+        <v>-19.209071955066257</v>
       </c>
     </row>
     <row r="96" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O96" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="P96" t="s">
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>121.1112351491342</v>
+        <v>143.53155140797961</v>
       </c>
       <c r="R96">
-        <v>-24.976935367502929</v>
+        <v>-16.842782017898529</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O97" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="P97" t="s">
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>123.32635134509788</v>
+        <v>133.68164249424419</v>
       </c>
       <c r="R97">
-        <v>-23.526051244043099</v>
+        <v>-16.101517102011233</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O98" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="P98" t="s">
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>121.92904804994386</v>
+        <v>141.61698509211399</v>
       </c>
       <c r="R98">
-        <v>-20.812639760955228</v>
+        <v>-21.232659958612345</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O99" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="P99" t="s">
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>119.16208753086686</v>
+        <v>136.37075790886232</v>
       </c>
       <c r="R99">
-        <v>-21.695504082474919</v>
+        <v>-19.694955700281337</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O100" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="P100" t="s">
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>117.41731439882852</v>
+        <v>139.27208639414761</v>
       </c>
       <c r="R100">
-        <v>-24.068771928108724</v>
+        <v>-18.904569355313825</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O101" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="P101" t="s">
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>149.05199661054391</v>
+        <v>148.87423748201786</v>
       </c>
       <c r="R101">
-        <v>-37.002032630466068</v>
+        <v>-36.165910195321878</v>
       </c>
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O102" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="P102" t="s">
         <v>8</v>
       </c>
       <c r="Q102">
-        <v>148.65352254441521</v>
+        <v>119.13598848396089</v>
       </c>
       <c r="R102">
-        <v>-34.439834706959083</v>
+        <v>-30.796729707503129</v>
       </c>
     </row>
     <row r="103" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O103" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="P103" t="s">
         <v>8</v>
       </c>
       <c r="Q103">
-        <v>145.73081872404185</v>
+        <v>145.58833738514707</v>
       </c>
       <c r="R103">
-        <v>-35.085374523771193</v>
+        <v>-38.353648620663961</v>
       </c>
     </row>
     <row r="104" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O104" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="P104" t="s">
         <v>8</v>
       </c>
       <c r="Q104">
-        <v>147.56216804451495</v>
+        <v>141.56872594051842</v>
       </c>
       <c r="R104">
-        <v>-35.99216254102295</v>
+        <v>-37.886047349671941</v>
       </c>
     </row>
     <row r="105" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O105" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P105" t="s">
         <v>8</v>
       </c>
       <c r="Q105">
-        <v>142.90804330239868</v>
+        <v>117.08968332824684</v>
       </c>
       <c r="R105">
-        <v>-33.141361171375287</v>
+        <v>-23.34813400404289</v>
       </c>
     </row>
     <row r="106" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O106" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="P106" t="s">
         <v>8</v>
       </c>
       <c r="Q106">
-        <v>143.83516136861633</v>
+        <v>116.59754239923603</v>
       </c>
       <c r="R106">
-        <v>-34.872998231421811</v>
+        <v>-24.508876936966072</v>
       </c>
     </row>
     <row r="107" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O107" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="P107" t="s">
         <v>8</v>
       </c>
       <c r="Q107">
-        <v>145.52740655459939</v>
+        <v>115.07187092228614</v>
       </c>
       <c r="R107">
-        <v>-36.621932253037947</v>
+        <v>-24.596020608669654</v>
       </c>
     </row>
     <row r="108" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O108" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="P108" t="s">
         <v>8</v>
       </c>
       <c r="Q108">
-        <v>146.92390427712806</v>
+        <v>151.23547888480226</v>
       </c>
       <c r="R108">
-        <v>-38.141004719968016</v>
+        <v>-24.237718714685045</v>
       </c>
     </row>
     <row r="109" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O109" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P109" t="s">
         <v>8</v>
       </c>
       <c r="Q109">
-        <v>145.30589191019487</v>
+        <v>146.86762072808455</v>
       </c>
       <c r="R109">
-        <v>-38.106686018724361</v>
+        <v>-38.005975900323904</v>
       </c>
     </row>
     <row r="110" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O110" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="P110" t="s">
         <v>8</v>
       </c>
       <c r="Q110">
-        <v>141.9946318567072</v>
+        <v>145.31596139132495</v>
       </c>
       <c r="R110">
-        <v>-37.361011760610033</v>
+        <v>-26.875235100913308</v>
       </c>
     </row>
     <row r="111" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O111" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="P111" t="s">
         <v>8</v>
       </c>
       <c r="Q111">
-        <v>142.82534027744816</v>
+        <v>148.61257540765266</v>
       </c>
       <c r="R111">
-        <v>-38.177452919514529</v>
+        <v>-26.534025398042417</v>
       </c>
     </row>
     <row r="112" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O112" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="P112" t="s">
         <v>8</v>
       </c>
       <c r="Q112">
-        <v>140.4901558842385</v>
+        <v>114.28448585444229</v>
       </c>
       <c r="R112">
-        <v>-35.674441574858221</v>
+        <v>-22.74753318631009</v>
       </c>
     </row>
     <row r="113" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O113" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P113" t="s">
         <v>8</v>
       </c>
       <c r="Q113">
-        <v>140.48912208275175</v>
+        <v>116.35887740209482</v>
       </c>
       <c r="R113">
-        <v>-37.060205851775557</v>
+        <v>-21.641041566438822</v>
       </c>
     </row>
     <row r="114" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O114" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="P114" t="s">
         <v>8</v>
       </c>
       <c r="Q114">
-        <v>145.36174013178348</v>
+        <v>127.54952565439332</v>
       </c>
       <c r="R114">
-        <v>-40.954878234189231</v>
+        <v>-23.272862019631749</v>
       </c>
     </row>
     <row r="115" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O115" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="P115" t="s">
         <v>8</v>
       </c>
       <c r="Q115">
-        <v>147.73975425579624</v>
+        <v>127.01719063542636</v>
       </c>
       <c r="R115">
-        <v>-41.160834609417009</v>
+        <v>-21.623457964519616</v>
       </c>
     </row>
     <row r="116" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
       </c>
       <c r="Q116">
-        <v>147.36591370809563</v>
+        <v>129.60637731166216</v>
       </c>
       <c r="R116">
-        <v>-42.210138412085627</v>
+        <v>-21.552485284497635</v>
       </c>
     </row>
     <row r="117" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
       </c>
       <c r="Q117">
-        <v>122.55812845579398</v>
+        <v>119.59455175647253</v>
       </c>
       <c r="R117">
-        <v>-33.332763044697707</v>
+        <v>-24.876471033320065</v>
       </c>
     </row>
     <row r="118" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
       </c>
       <c r="Q118">
-        <v>120.86799171391893</v>
+        <v>123.7935343157984</v>
       </c>
       <c r="R118">
-        <v>-32.593875240972459</v>
+        <v>-22.661907303492882</v>
       </c>
     </row>
     <row r="119" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
       </c>
       <c r="Q119">
-        <v>116.03100720882161</v>
+        <v>120.82495004703642</v>
       </c>
       <c r="R119">
-        <v>-34.127034311484337</v>
+        <v>-22.694486273853538</v>
       </c>
     </row>
     <row r="120" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
       </c>
       <c r="Q120">
-        <v>118.0751068059126</v>
+        <v>123.29069613160677</v>
       </c>
       <c r="R120">
-        <v>-34.615466066232315</v>
+        <v>-24.801140356990636</v>
       </c>
     </row>
     <row r="121" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
       </c>
       <c r="Q121">
-        <v>116.65659464654038</v>
+        <v>118.08875025296304</v>
       </c>
       <c r="R121">
-        <v>-27.007695799781629</v>
+        <v>-27.37470299236471</v>
       </c>
     </row>
     <row r="122" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
       </c>
       <c r="Q122">
-        <v>115.14238021324108</v>
+        <v>116.48320104154482</v>
       </c>
       <c r="R122">
-        <v>-24.697893127946649</v>
+        <v>-28.851705964151201</v>
       </c>
     </row>
     <row r="123" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
       </c>
       <c r="Q123">
-        <v>115.68722214682816</v>
+        <v>115.73230211115954</v>
       </c>
       <c r="R123">
-        <v>-28.167441697824167</v>
+        <v>-26.91171685213137</v>
       </c>
     </row>
     <row r="124" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
       </c>
       <c r="Q124">
-        <v>115.90421239972798</v>
+        <v>149.1953877079581</v>
       </c>
       <c r="R124">
-        <v>-31.444882640740847</v>
+        <v>-34.626011552010475</v>
       </c>
     </row>
     <row r="125" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
       </c>
       <c r="Q125">
-        <v>118.59104261535464</v>
+        <v>141.24985273725568</v>
       </c>
       <c r="R125">
-        <v>-29.285502942557969</v>
+        <v>-32.348145019885699</v>
       </c>
     </row>
     <row r="126" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
       </c>
       <c r="Q126">
-        <v>118.39673279724994</v>
+        <v>141.72219895580699</v>
       </c>
       <c r="R126">
-        <v>-30.752758698157304</v>
+        <v>-30.839990770085397</v>
       </c>
     </row>
     <row r="127" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
       </c>
       <c r="Q127">
-        <v>150.93934717708817</v>
+        <v>142.48380553442243</v>
       </c>
       <c r="R127">
-        <v>-24.76727518444596</v>
+        <v>-26.901256766800199</v>
       </c>
     </row>
     <row r="128" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
       </c>
       <c r="Q128">
-        <v>148.23171019375965</v>
+        <v>144.47914731976934</v>
       </c>
       <c r="R128">
-        <v>-20.970084429509942</v>
+        <v>-30.074386929609709</v>
       </c>
     </row>
     <row r="129" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
       </c>
       <c r="Q129">
-        <v>147.06350485205559</v>
+        <v>142.16563309949274</v>
       </c>
       <c r="R129">
-        <v>-21.81503719825152</v>
+        <v>-29.138471100616751</v>
       </c>
     </row>
     <row r="130" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
       </c>
       <c r="Q130">
-        <v>151.88900228121577</v>
+        <v>115.58712662224472</v>
       </c>
       <c r="R130">
-        <v>-28.426665025009203</v>
+        <v>-30.038314092521837</v>
       </c>
     </row>
     <row r="131" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
       </c>
       <c r="Q131">
-        <v>149.22438062186285</v>
+        <v>151.70987912757346</v>
       </c>
       <c r="R131">
-        <v>-27.235374901982532</v>
+        <v>-32.162377524327063</v>
       </c>
     </row>
     <row r="132" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
       </c>
       <c r="Q132">
-        <v>147.76330434123716</v>
+        <v>115.99441240315986</v>
       </c>
       <c r="R132">
-        <v>-28.17719003058987</v>
+        <v>-31.925575525228531</v>
       </c>
     </row>
     <row r="133" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
       </c>
       <c r="Q133">
-        <v>149.43559238340944</v>
+        <v>141.26169564851568</v>
       </c>
       <c r="R133">
-        <v>-25.53208894708445</v>
+        <v>-36.601637274283433</v>
       </c>
     </row>
     <row r="134" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
       </c>
       <c r="Q134">
-        <v>146.46677109095083</v>
+        <v>130.44549037437517</v>
       </c>
       <c r="R134">
-        <v>-23.265870692651252</v>
+        <v>-19.148753079902079</v>
       </c>
     </row>
     <row r="135" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O135" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="P135" t="s">
         <v>8</v>
       </c>
       <c r="Q135">
-        <v>146.2530408921524</v>
+        <v>130.21666041483596</v>
       </c>
       <c r="R135">
-        <v>-24.912836419118246</v>
+        <v>-15.336686243625843</v>
       </c>
     </row>
     <row r="136" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O136" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P136" t="s">
         <v>8</v>
       </c>
       <c r="Q136">
-        <v>150.77513759786697</v>
+        <v>119.58806566385246</v>
       </c>
       <c r="R136">
-        <v>-33.927321285914829</v>
+        <v>-20.825706306232721</v>
       </c>
     </row>
     <row r="137" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O137" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="P137" t="s">
         <v>8</v>
       </c>
       <c r="Q137">
-        <v>149.63395959889763</v>
+        <v>123.07722410756404</v>
       </c>
       <c r="R137">
-        <v>-34.446112622440367</v>
+        <v>-19.907342783485745</v>
       </c>
     </row>
     <row r="138" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O138" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="P138" t="s">
         <v>8</v>
       </c>
       <c r="Q138">
-        <v>151.9510333951863</v>
+        <v>126.86620324681024</v>
       </c>
       <c r="R138">
-        <v>-31.610779267089288</v>
+        <v>-16.778364179633666</v>
       </c>
     </row>
     <row r="139" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O139" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P139" t="s">
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>150.64279122684428</v>
+        <v>126.68911386447304</v>
       </c>
       <c r="R139">
-        <v>-30.329307192442041</v>
+        <v>-19.57556420488984</v>
       </c>
     </row>
     <row r="140" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O140" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="P140" t="s">
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>142.69665953395346</v>
+        <v>146.61070950534349</v>
       </c>
       <c r="R140">
-        <v>-28.42615104088356</v>
+        <v>-42.539251485649778</v>
       </c>
     </row>
     <row r="141" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
       </c>
       <c r="Q141">
-        <v>145.17717767511434</v>
+        <v>126.88202236935292</v>
       </c>
       <c r="R141">
-        <v>-28.240292440619939</v>
+        <v>-29.912338692430929</v>
       </c>
     </row>
     <row r="142" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
       </c>
       <c r="Q142">
-        <v>143.59071424731289</v>
+        <v>123.94047174725048</v>
       </c>
       <c r="R142">
-        <v>-25.934310769926011</v>
+        <v>-26.619227583857882</v>
       </c>
     </row>
     <row r="143" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
       </c>
       <c r="Q143">
-        <v>147.73996892366085</v>
+        <v>127.21716462818084</v>
       </c>
       <c r="R143">
-        <v>-30.460324370284951</v>
+        <v>-26.19534615411176</v>
       </c>
     </row>
     <row r="144" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
       </c>
       <c r="Q144">
-        <v>145.08028680507692</v>
+        <v>120.96002955221816</v>
       </c>
       <c r="R144">
-        <v>-33.42596416811471</v>
+        <v>-30.015041377829604</v>
       </c>
     </row>
     <row r="145" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
       </c>
       <c r="Q145">
-        <v>144.10689207891647</v>
+        <v>121.9776632692068</v>
       </c>
       <c r="R145">
-        <v>-31.011320891898983</v>
+        <v>-28.23473524394884</v>
       </c>
     </row>
     <row r="146" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
       </c>
       <c r="Q146">
-        <v>119.9126561006962</v>
+        <v>126.87543483120088</v>
       </c>
       <c r="R146">
-        <v>-18.762930736574628</v>
+        <v>-31.570835856427525</v>
       </c>
     </row>
     <row r="147" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
       </c>
       <c r="Q147">
-        <v>118.04505668609308</v>
+        <v>124.41500527547988</v>
       </c>
       <c r="R147">
-        <v>-18.943711458300104</v>
+        <v>-31.872154827099781</v>
       </c>
     </row>
     <row r="148" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
       </c>
       <c r="Q148">
-        <v>119.47741098585524</v>
+        <v>151.1379657899632</v>
       </c>
       <c r="R148">
-        <v>-17.341576901661309</v>
+        <v>-34.584112229567701</v>
       </c>
     </row>
     <row r="149" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>120.7699066609067</v>
+        <v>116.44753624908248</v>
       </c>
       <c r="R149">
-        <v>-16.701861452529982</v>
+        <v>-34.917150029871202</v>
       </c>
     </row>
     <row r="150" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>120.92507981057096</v>
+        <v>146.66672296307451</v>
       </c>
       <c r="R150">
-        <v>-17.89119788373922</v>
+        <v>-40.272839726974297</v>
       </c>
     </row>
     <row r="151" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>148.32310486365299</v>
+        <v>144.64697355726699</v>
       </c>
       <c r="R151">
-        <v>-38.317649436280313</v>
+        <v>-40.546840571798938</v>
       </c>
     </row>
     <row r="152" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
       </c>
       <c r="Q152">
-        <v>149.91427469508412</v>
+        <v>143.87674213215473</v>
       </c>
       <c r="R152">
-        <v>-37.666954901440938</v>
+        <v>-39.257876116339148</v>
       </c>
     </row>
     <row r="153" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O153" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="P153" t="s">
         <v>8</v>
       </c>
       <c r="Q153">
-        <v>148.2380581815757</v>
+        <v>150.90399697993092</v>
       </c>
       <c r="R153">
-        <v>-42.385662374939223</v>
+        <v>-21.252254703658771</v>
       </c>
     </row>
     <row r="154" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O154" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P154" t="s">
         <v>8</v>
       </c>
       <c r="Q154">
-        <v>145.49022483115897</v>
+        <v>153.37306950018458</v>
       </c>
       <c r="R154">
-        <v>-43.009861490614647</v>
+        <v>-30.859626845395809</v>
       </c>
     </row>
     <row r="155" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
       </c>
       <c r="Q155">
-        <v>141.65592107949502</v>
+        <v>137.75207579058173</v>
       </c>
       <c r="R155">
-        <v>-38.521010458884057</v>
+        <v>-32.743780387632853</v>
       </c>
     </row>
     <row r="156" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O156" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="P156" t="s">
         <v>8</v>
       </c>
       <c r="Q156">
-        <v>144.55763782706819</v>
+        <v>133.82287060397272</v>
       </c>
       <c r="R156">
-        <v>-38.513951467094387</v>
+        <v>-34.227843031724603</v>
       </c>
     </row>
     <row r="157" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O157" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="P157" t="s">
         <v>8</v>
       </c>
       <c r="Q157">
-        <v>144.77326716667514</v>
+        <v>150.32141234786266</v>
       </c>
       <c r="R157">
-        <v>-39.715987878044587</v>
+        <v>-21.199688649197544</v>
       </c>
     </row>
     <row r="158" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O158" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="P158" t="s">
         <v>8</v>
       </c>
       <c r="Q158">
-        <v>147.27289869429097</v>
+        <v>150.81900140649941</v>
       </c>
       <c r="R158">
-        <v>-39.835742995149893</v>
+        <v>-19.943795597851125</v>
       </c>
     </row>
     <row r="159" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O159" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P159" t="s">
         <v>8</v>
       </c>
       <c r="Q159">
-        <v>125.93096074584602</v>
+        <v>153.55763832618015</v>
       </c>
       <c r="R159">
-        <v>-33.361274423793468</v>
+        <v>-25.92492989840304</v>
       </c>
     </row>
     <row r="160" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O160" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="P160" t="s">
         <v>8</v>
       </c>
       <c r="Q160">
-        <v>123.37535402247092</v>
+        <v>151.46867878644642</v>
       </c>
       <c r="R160">
-        <v>-34.303485688836098</v>
+        <v>-21.50731377536102</v>
       </c>
     </row>
     <row r="161" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O161" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P161" t="s">
         <v>8</v>
       </c>
       <c r="Q161">
-        <v>114.7947165340852</v>
+        <v>153.73370306869481</v>
       </c>
       <c r="R161">
-        <v>-32.54438600940842</v>
+        <v>-23.608887736048747</v>
       </c>
     </row>
     <row r="162" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O162" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="P162" t="s">
         <v>8</v>
       </c>
       <c r="Q162">
-        <v>115.63509693996244</v>
+        <v>150.57744483884846</v>
       </c>
       <c r="R162">
-        <v>-34.956218827910511</v>
+        <v>-17.040567652389406</v>
       </c>
     </row>
     <row r="163" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O163" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="P163" t="s">
         <v>8</v>
       </c>
       <c r="Q163">
-        <v>119.9072235311796</v>
+        <v>149.21297177481156</v>
       </c>
       <c r="R163">
-        <v>-34.597269389279965</v>
+        <v>-18.721877322770485</v>
       </c>
     </row>
     <row r="164" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O164" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="P164" t="s">
         <v>8</v>
       </c>
       <c r="Q164">
-        <v>137.78035397071665</v>
+        <v>135.81882012006892</v>
       </c>
       <c r="R164">
-        <v>-32.819241490786624</v>
+        <v>-35.521402273625938</v>
       </c>
     </row>
     <row r="165" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O165" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P165" t="s">
         <v>8</v>
       </c>
       <c r="Q165">
-        <v>137.20967407247699</v>
+        <v>138.0138906141494</v>
       </c>
       <c r="R165">
-        <v>-36.223304540952505</v>
+        <v>-36.635585635401441</v>
       </c>
     </row>
     <row r="166" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O166" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P166" t="s">
         <v>8</v>
       </c>
       <c r="Q166">
-        <v>129.134450023667</v>
+        <v>153.78400128986024</v>
       </c>
       <c r="R166">
-        <v>-32.909253032721082</v>
+        <v>-27.74890644111397</v>
       </c>
     </row>
     <row r="167" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O167" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P167" t="s">
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>132.03627064460872</v>
+        <v>148.55880462471723</v>
       </c>
       <c r="R167">
-        <v>-33.087877243811086</v>
+        <v>-41.33210911071906</v>
       </c>
     </row>
     <row r="168" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O168" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="P168" t="s">
         <v>8</v>
       </c>
       <c r="Q168">
-        <v>133.90646814672945</v>
+        <v>149.25432880621693</v>
       </c>
       <c r="R168">
-        <v>-34.666650757457681</v>
+        <v>-38.046262781033171</v>
       </c>
     </row>
     <row r="169" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O169" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="P169" t="s">
         <v>8</v>
       </c>
       <c r="Q169">
-        <v>133.91848973168982</v>
+        <v>132.28941986584897</v>
       </c>
       <c r="R169">
-        <v>-33.290709632176373</v>
+        <v>-32.63728608022614</v>
       </c>
     </row>
     <row r="170" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O170" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="P170" t="s">
         <v>8</v>
       </c>
       <c r="Q170">
-        <v>113.74486915277508</v>
+        <v>130.63888127420114</v>
       </c>
       <c r="R170">
-        <v>-28.996828120045929</v>
+        <v>-32.982094689407965</v>
       </c>
     </row>
     <row r="171" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O171" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="P171" t="s">
         <v>8</v>
       </c>
       <c r="Q171">
-        <v>112.74359053980096</v>
+        <v>144.31606678591064</v>
       </c>
       <c r="R171">
-        <v>-26.772426753633201</v>
+        <v>-10.389603210951345</v>
       </c>
     </row>
     <row r="172" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O172" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="P172" t="s">
         <v>8</v>
       </c>
       <c r="Q172">
-        <v>112.63415325098336</v>
+        <v>148.5909913276279</v>
       </c>
       <c r="R172">
-        <v>-24.422167043715746</v>
+        <v>-16.784378905659178</v>
       </c>
     </row>
     <row r="173" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O173" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P173" t="s">
         <v>8</v>
       </c>
       <c r="Q173">
-        <v>113.73544067893422</v>
+        <v>138.30721536965922</v>
       </c>
       <c r="R173">
-        <v>-21.706116736523096</v>
+        <v>-14.184024112238506</v>
       </c>
     </row>
     <row r="174" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O174" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="P174" t="s">
         <v>8</v>
       </c>
       <c r="Q174">
-        <v>116.10746995541636</v>
+        <v>135.27984866110239</v>
       </c>
       <c r="R174">
-        <v>-19.480023550066459</v>
+        <v>-10.398499647377401</v>
       </c>
     </row>
     <row r="175" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O175" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="P175" t="s">
         <v>8</v>
       </c>
       <c r="Q175">
-        <v>114.68862040279514</v>
+        <v>140.32179370962868</v>
       </c>
       <c r="R175">
-        <v>-20.711484124597217</v>
+        <v>-12.954950246643154</v>
       </c>
     </row>
     <row r="176" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O176" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="P176" t="s">
         <v>8</v>
       </c>
       <c r="Q176">
-        <v>153.46075007326399</v>
+        <v>150.33067292817168</v>
       </c>
       <c r="R176">
-        <v>-25.64608975222702</v>
+        <v>-37.040409183139161</v>
       </c>
     </row>
     <row r="177" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O177" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P177" t="s">
         <v>8</v>
       </c>
       <c r="Q177">
-        <v>159.20482777269496</v>
+        <v>120.12011991435632</v>
       </c>
       <c r="R177">
-        <v>-31.490532239940517</v>
+        <v>-34.407627927699693</v>
       </c>
     </row>
     <row r="178" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O178" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="P178" t="s">
         <v>8</v>
       </c>
       <c r="Q178">
-        <v>153.68674355709717</v>
+        <v>144.8902831112365</v>
       </c>
       <c r="R178">
-        <v>-27.494239414331563</v>
+        <v>-39.085132333872046</v>
       </c>
     </row>
     <row r="179" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O179" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="P179" t="s">
         <v>8</v>
       </c>
       <c r="Q179">
-        <v>151.35627784832863</v>
+        <v>142.02787957366007</v>
       </c>
       <c r="R179">
-        <v>-34.275360972593546</v>
+        <v>-38.800100646368243</v>
       </c>
     </row>
     <row r="180" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O180" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="P180" t="s">
         <v>8</v>
       </c>
       <c r="Q180">
-        <v>153.55763832618015</v>
+        <v>112.58480671076954</v>
       </c>
       <c r="R180">
-        <v>-29.527372673957174</v>
+        <v>-24.711616537979179</v>
       </c>
     </row>
     <row r="181" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O181" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="P181" t="s">
         <v>8</v>
       </c>
       <c r="Q181">
-        <v>152.90565408954197</v>
+        <v>152.81794203252727</v>
       </c>
       <c r="R181">
-        <v>-32.160506789513327</v>
+        <v>-22.354482597944848</v>
       </c>
     </row>
     <row r="182" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O182" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="P182" t="s">
         <v>8</v>
       </c>
       <c r="Q182">
-        <v>123.6209360771076</v>
+        <v>152.95719415436176</v>
       </c>
       <c r="R182">
-        <v>-12.313250418759196</v>
+        <v>-20.523860877195684</v>
       </c>
     </row>
     <row r="183" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O183" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P183" t="s">
         <v>8</v>
       </c>
       <c r="Q183">
-        <v>127.28982693164365</v>
+        <v>147.80794227266995</v>
       </c>
       <c r="R183">
-        <v>-13.447264969718235</v>
+        <v>-38.121468284809652</v>
       </c>
     </row>
     <row r="184" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O184" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="P184" t="s">
         <v>8</v>
       </c>
       <c r="Q184">
-        <v>137.9274007467076</v>
+        <v>147.20511661161083</v>
       </c>
       <c r="R184">
-        <v>-13.53904439343483</v>
+        <v>-39.111899860277866</v>
       </c>
     </row>
     <row r="185" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O185" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P185" t="s">
         <v>8</v>
       </c>
       <c r="Q185">
-        <v>138.7835300980004</v>
+        <v>116.46522333369435</v>
       </c>
       <c r="R185">
-        <v>-14.99287485410888</v>
+        <v>-19.417223673518691</v>
       </c>
     </row>
     <row r="186" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O186" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="P186" t="s">
         <v>8</v>
       </c>
       <c r="Q186">
-        <v>140.70260155913493</v>
+        <v>113.54021526049658</v>
       </c>
       <c r="R186">
-        <v>-11.977657398671996</v>
+        <v>-22.345487760282055</v>
       </c>
     </row>
     <row r="187" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O187" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="P187" t="s">
         <v>8</v>
       </c>
       <c r="Q187">
-        <v>140.0512616860895</v>
+        <v>113.47630330878668</v>
       </c>
       <c r="R187">
-        <v>-13.649234810616214</v>
+        <v>-27.354177147344291</v>
       </c>
     </row>
     <row r="188" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O188" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="P188" t="s">
         <v>8</v>
       </c>
       <c r="Q188">
-        <v>135.53232690608246</v>
+        <v>112.51630917494138</v>
       </c>
       <c r="R188">
-        <v>-10.058412830277735</v>
+        <v>-26.207109582102465</v>
       </c>
     </row>
     <row r="189" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O189" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P189" t="s">
         <v>8</v>
       </c>
       <c r="Q189">
-        <v>138.02236339770641</v>
+        <v>150.33067292817165</v>
       </c>
       <c r="R189">
-        <v>-11.457551359089519</v>
+        <v>-35.683734291786699</v>
       </c>
     </row>
     <row r="190" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O190" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="P190" t="s">
         <v>8</v>
       </c>
       <c r="Q190">
-        <v>129.80616836492629</v>
+        <v>113.59618016494302</v>
       </c>
       <c r="R190">
-        <v>-10.099829044183595</v>
+        <v>-28.778266365139427</v>
       </c>
     </row>
     <row r="191" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O191" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="P191" t="s">
         <v>8</v>
       </c>
       <c r="Q191">
-        <v>132.27258092622665</v>
+        <v>152.28799997656037</v>
       </c>
       <c r="R191">
-        <v>-10.034977983480973</v>
+        <v>-33.016657902646344</v>
       </c>
     </row>
     <row r="192" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O192" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P192" t="s">
         <v>8</v>
       </c>
       <c r="Q192">
-        <v>152.45277308531408</v>
+        <v>114.82346202946719</v>
       </c>
       <c r="R192">
-        <v>-22.783968088520972</v>
+        <v>-32.513996088608671</v>
       </c>
     </row>
     <row r="193" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O193" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="P193" t="s">
         <v>8</v>
       </c>
       <c r="Q193">
-        <v>152.48347016037607</v>
+        <v>139.84303538464414</v>
       </c>
       <c r="R193">
-        <v>-20.980492993694121</v>
+        <v>-37.165158559530319</v>
       </c>
     </row>
     <row r="194" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O194" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="P194" t="s">
         <v>8</v>
       </c>
       <c r="Q194">
-        <v>144.36177021993478</v>
+        <v>119.67814798329256</v>
       </c>
       <c r="R194">
-        <v>-9.9641044817147968</v>
+        <v>-17.977932221868844</v>
       </c>
     </row>
     <row r="195" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O195" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="P195" t="s">
         <v>8</v>
       </c>
       <c r="Q195">
-        <v>144.12580128857698</v>
+        <v>130.24318545304698</v>
       </c>
       <c r="R195">
-        <v>-12.160973985632396</v>
+        <v>-10.13254267953079</v>
       </c>
     </row>
     <row r="196" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O196" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="P196" t="s">
         <v>8</v>
       </c>
       <c r="Q196">
-        <v>149.93800636445266</v>
+        <v>124.84028618906758</v>
       </c>
       <c r="R196">
-        <v>-16.926232109956484</v>
+        <v>-12.690138373320879</v>
       </c>
     </row>
     <row r="197" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O197" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="P197" t="s">
         <v>8</v>
       </c>
       <c r="Q197">
-        <v>149.09136985948658</v>
+        <v>146.29696618066109</v>
       </c>
       <c r="R197">
-        <v>-19.056413284503343</v>
+        <v>-43.909028252220295</v>
       </c>
     </row>
     <row r="198" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O198" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="P198" t="s">
         <v>8</v>
       </c>
       <c r="Q198">
-        <v>143.90359456668338</v>
+        <v>122.85287314689302</v>
       </c>
       <c r="R198">
-        <v>-16.424523984767728</v>
+        <v>-34.292485898627589</v>
       </c>
     </row>
     <row r="199" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O199" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P199" t="s">
         <v>8</v>
       </c>
       <c r="Q199">
-        <v>143.22470052438001</v>
+        <v>126.61421252675746</v>
       </c>
       <c r="R199">
-        <v>-13.468602452715691</v>
+        <v>-33.282150864166539</v>
       </c>
     </row>
     <row r="200" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O200" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="P200" t="s">
         <v>8</v>
       </c>
       <c r="Q200">
-        <v>143.90529016295486</v>
+        <v>150.4869165841626</v>
       </c>
       <c r="R200">
-        <v>-18.480560456616804</v>
+        <v>-34.568155881156414</v>
       </c>
     </row>
     <row r="201" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O201" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P201" t="s">
         <v>8</v>
       </c>
       <c r="Q201">
-        <v>141.91280510410783</v>
+        <v>145.13667075942735</v>
       </c>
       <c r="R201">
-        <v>-14.267874545971546</v>
+        <v>-36.753271835090963</v>
       </c>
     </row>
     <row r="202" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O202" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P202" t="s">
         <v>8</v>
       </c>
       <c r="Q202">
-        <v>147.94674742269942</v>
+        <v>117.35815311681628</v>
       </c>
       <c r="R202">
-        <v>-20.402760450148971</v>
+        <v>-34.636518230808882</v>
       </c>
     </row>
     <row r="203" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O203" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="P203" t="s">
         <v>8</v>
       </c>
       <c r="Q203">
-        <v>144.07788557941856</v>
+        <v>145.43263864663615</v>
       </c>
       <c r="R203">
-        <v>-21.717575465917388</v>
+        <v>-41.070134274350721</v>
       </c>
     </row>
     <row r="204" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O204" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P204" t="s">
         <v>8</v>
       </c>
       <c r="Q204">
-        <v>145.9443079211926</v>
+        <v>143.60220683880638</v>
       </c>
       <c r="R204">
-        <v>-20.239947228052181</v>
+        <v>-37.539659494375663</v>
       </c>
     </row>
     <row r="205" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O205" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="P205" t="s">
         <v>8</v>
       </c>
       <c r="Q205">
-        <v>147.65166753303404</v>
+        <v>150.1958929235482</v>
       </c>
       <c r="R205">
-        <v>-22.848790085185165</v>
+        <v>-24.594606239715439</v>
       </c>
     </row>
     <row r="206" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O206" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="P206" t="s">
         <v>8</v>
       </c>
       <c r="Q206">
-        <v>142.11939483808513</v>
+        <v>147.12093706215981</v>
       </c>
       <c r="R206">
-        <v>-20.287585477957197</v>
+        <v>-23.934891614524041</v>
       </c>
     </row>
     <row r="207" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O207" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="P207" t="s">
         <v>8</v>
       </c>
       <c r="Q207">
-        <v>142.30082021143733</v>
+        <v>150.9301046692855</v>
       </c>
       <c r="R207">
-        <v>-18.402066295276651</v>
+        <v>-30.52001579209675</v>
       </c>
     </row>
     <row r="208" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O208" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="P208" t="s">
         <v>8</v>
       </c>
       <c r="Q208">
-        <v>139.9406845355177</v>
+        <v>136.29183659962365</v>
       </c>
       <c r="R208">
-        <v>-18.592001825958096</v>
+        <v>-33.217357840283256</v>
       </c>
     </row>
     <row r="209" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O209" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P209" t="s">
         <v>8</v>
       </c>
       <c r="Q209">
-        <v>136.52844938766063</v>
+        <v>137.71882435043975</v>
       </c>
       <c r="R209">
-        <v>-16.923318022496602</v>
+        <v>-32.011051991230055</v>
       </c>
     </row>
     <row r="210" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O210" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="P210" t="s">
         <v>8</v>
       </c>
       <c r="Q210">
-        <v>138.01439622256723</v>
+        <v>139.89087405555921</v>
       </c>
       <c r="R210">
-        <v>-19.947965320150729</v>
+        <v>-33.242416864356407</v>
       </c>
     </row>
     <row r="211" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O211" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P211" t="s">
         <v>8</v>
       </c>
       <c r="Q211">
-        <v>135.46557003772165</v>
+        <v>145.36437526923956</v>
       </c>
       <c r="R211">
-        <v>-18.416233482486358</v>
+        <v>-23.938105777917052</v>
       </c>
     </row>
     <row r="212" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O212" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="P212" t="s">
         <v>8</v>
       </c>
       <c r="Q212">
-        <v>134.79283929397783</v>
+        <v>148.38516785311737</v>
       </c>
       <c r="R212">
-        <v>-20.732600676782639</v>
+        <v>-31.78762838768008</v>
       </c>
     </row>
     <row r="213" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O213" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="P213" t="s">
         <v>8</v>
       </c>
       <c r="Q213">
-        <v>136.52758085947576</v>
+        <v>145.08190486780563</v>
       </c>
       <c r="R213">
-        <v>-22.021539553207361</v>
+        <v>-34.136563287228782</v>
       </c>
     </row>
     <row r="214" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O214" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="P214" t="s">
         <v>8</v>
       </c>
       <c r="Q214">
-        <v>127.98414541606536</v>
+        <v>145.71203930501878</v>
       </c>
       <c r="R214">
-        <v>-20.935762467407532</v>
+        <v>-31.39220732642514</v>
       </c>
     </row>
     <row r="215" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O215" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="P215" t="s">
         <v>8</v>
       </c>
       <c r="Q215">
-        <v>126.75721806702428</v>
+        <v>143.64431413529221</v>
       </c>
       <c r="R215">
-        <v>-19.535728093615841</v>
+        <v>-33.709133190238028</v>
       </c>
     </row>
     <row r="216" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O216" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="P216" t="s">
         <v>8</v>
       </c>
       <c r="Q216">
-        <v>131.0185841389347</v>
+        <v>151.57248940239651</v>
       </c>
       <c r="R216">
-        <v>-20.991416477707151</v>
+        <v>-26.323911406128701</v>
       </c>
     </row>
     <row r="217" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O217" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="P217" t="s">
         <v>8</v>
       </c>
       <c r="Q217">
-        <v>132.36508456813664</v>
+        <v>150.24713680163202</v>
       </c>
       <c r="R217">
-        <v>-18.910342658765423</v>
+        <v>-23.693112920968051</v>
       </c>
     </row>
     <row r="218" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O218" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="P218" t="s">
         <v>8</v>
       </c>
       <c r="Q218">
-        <v>134.77431748659325</v>
+        <v>151.61716576352794</v>
       </c>
       <c r="R218">
-        <v>-15.537965116102958</v>
+        <v>-25.37400675796134</v>
       </c>
     </row>
     <row r="219" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O219" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="P219" t="s">
         <v>8</v>
       </c>
       <c r="Q219">
-        <v>134.41284432791551</v>
+        <v>143.35412326528009</v>
       </c>
       <c r="R219">
-        <v>-12.119621907128884</v>
+        <v>-23.419388107531574</v>
       </c>
     </row>
     <row r="220" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O220" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="P220" t="s">
         <v>8</v>
       </c>
       <c r="Q220">
-        <v>135.69256848725669</v>
+        <v>144.78502894446973</v>
       </c>
       <c r="R220">
-        <v>-13.664146166265898</v>
+        <v>-21.882733173886301</v>
       </c>
     </row>
     <row r="221" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O221" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="P221" t="s">
         <v>8</v>
       </c>
       <c r="Q221">
-        <v>131.62113689763146</v>
+        <v>147.21725198745645</v>
       </c>
       <c r="R221">
-        <v>-12.894653149909704</v>
+        <v>-35.479752937238217</v>
       </c>
     </row>
     <row r="222" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O222" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="P222" t="s">
         <v>8</v>
       </c>
       <c r="Q222">
-        <v>132.48892524469898</v>
+        <v>139.19580294835177</v>
       </c>
       <c r="R222">
-        <v>-13.907083618728224</v>
+        <v>-35.629567001716929</v>
       </c>
     </row>
     <row r="223" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O223" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="P223" t="s">
         <v>8</v>
       </c>
       <c r="Q223">
-        <v>125.8255204059364</v>
+        <v>152.52412221723841</v>
       </c>
       <c r="R223">
-        <v>-17.70421688591648</v>
+        <v>-28.289668493542941</v>
       </c>
     </row>
     <row r="224" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O224" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="P224" t="s">
         <v>8</v>
       </c>
       <c r="Q224">
-        <v>127.53869595671664</v>
+        <v>148.19644471385828</v>
       </c>
       <c r="R224">
-        <v>-15.425735818899312</v>
+        <v>-29.184208941029169</v>
       </c>
     </row>
     <row r="225" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O225" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="P225" t="s">
         <v>8</v>
       </c>
       <c r="Q225">
-        <v>132.08986312355745</v>
+        <v>147.39311396207361</v>
       </c>
       <c r="R225">
-        <v>-16.935964240758963</v>
+        <v>-42.094338889464559</v>
       </c>
     </row>
     <row r="226" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O226" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="P226" t="s">
         <v>8</v>
       </c>
       <c r="Q226">
-        <v>127.9753364052041</v>
+        <v>148.5749039530551</v>
       </c>
       <c r="R226">
-        <v>-17.004321685535825</v>
+        <v>-37.082583790808052</v>
       </c>
     </row>
     <row r="227" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O227" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="P227" t="s">
         <v>8</v>
       </c>
       <c r="Q227">
-        <v>146.86282244839464</v>
+        <v>137.83805940200597</v>
       </c>
       <c r="R227">
-        <v>-37.676684149628869</v>
+        <v>-28.559817952692089</v>
       </c>
     </row>
     <row r="228" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O228" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="P228" t="s">
         <v>8</v>
       </c>
       <c r="Q228">
-        <v>149.04105094255826</v>
+        <v>135.17612341051682</v>
       </c>
       <c r="R228">
-        <v>-36.144059038515685</v>
+        <v>-29.592137880611126</v>
       </c>
     </row>
     <row r="229" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O229" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="P229" t="s">
         <v>8</v>
       </c>
       <c r="Q229">
-        <v>147.20822379338119</v>
+        <v>131.51936175665412</v>
       </c>
       <c r="R229">
-        <v>-42.133338684243697</v>
+        <v>-29.335892876129801</v>
       </c>
     </row>
     <row r="230" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O230" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="P230" t="s">
         <v>8</v>
       </c>
       <c r="Q230">
-        <v>145.87076740617448</v>
+        <v>131.51051079709126</v>
       </c>
       <c r="R230">
-        <v>-38.482407313362081</v>
+        <v>-27.601128760451285</v>
       </c>
     </row>
     <row r="231" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O231" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="P231" t="s">
         <v>8</v>
       </c>
       <c r="Q231">
-        <v>141.59885822344779</v>
+        <v>134.25701691462129</v>
       </c>
       <c r="R231">
-        <v>-37.194161249481041</v>
+        <v>-31.225893165724464</v>
       </c>
     </row>
     <row r="232" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O232" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="P232" t="s">
         <v>8</v>
       </c>
       <c r="Q232">
-        <v>136.47849302130328</v>
+        <v>130.77152772622495</v>
       </c>
       <c r="R232">
-        <v>-32.689973080235788</v>
+        <v>-30.635030423097369</v>
       </c>
     </row>
     <row r="233" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O233" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="P233" t="s">
         <v>8</v>
       </c>
       <c r="Q233">
-        <v>143.02654384684817</v>
+        <v>132.31187419111029</v>
       </c>
       <c r="R233">
-        <v>-32.045131116301349</v>
+        <v>-19.7614568980045</v>
       </c>
     </row>
     <row r="234" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O234" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="P234" t="s">
         <v>8</v>
       </c>
       <c r="Q234">
-        <v>144.49127087303509</v>
+        <v>134.6221744623754</v>
       </c>
       <c r="R234">
-        <v>-34.862419802160197</v>
+        <v>-20.985072115261776</v>
       </c>
     </row>
     <row r="235" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O235" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="P235" t="s">
         <v>8</v>
       </c>
       <c r="Q235">
-        <v>140.56642796401263</v>
+        <v>130.77675686091649</v>
       </c>
       <c r="R235">
-        <v>-33.052401492209839</v>
+        <v>-22.185521896147964</v>
       </c>
     </row>
     <row r="236" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O236" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="P236" t="s">
         <v>8</v>
       </c>
       <c r="Q236">
-        <v>140.00081023529913</v>
+        <v>134.32732174678949</v>
       </c>
       <c r="R236">
-        <v>-31.408285546713287</v>
+        <v>-22.491780738849684</v>
       </c>
     </row>
     <row r="237" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O237" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="P237" t="s">
         <v>8</v>
       </c>
       <c r="Q237">
-        <v>137.08711551887083</v>
+        <v>138.64701561304034</v>
       </c>
       <c r="R237">
-        <v>-31.014904189409062</v>
+        <v>-23.182718054941848</v>
       </c>
     </row>
     <row r="238" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O238" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="P238" t="s">
         <v>8</v>
       </c>
       <c r="Q238">
-        <v>145.51452797003827</v>
+        <v>139.01907042410895</v>
       </c>
       <c r="R238">
-        <v>-24.435784713644757</v>
+        <v>-27.01676446044485</v>
       </c>
     </row>
     <row r="239" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O239" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P239" t="s">
         <v>8</v>
       </c>
       <c r="Q239">
-        <v>140.02638596197502</v>
+        <v>137.84589650192467</v>
       </c>
       <c r="R239">
-        <v>-24.142642750494868</v>
+        <v>-24.564743730374044</v>
       </c>
     </row>
     <row r="240" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O240" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="P240" t="s">
         <v>8</v>
       </c>
       <c r="Q240">
-        <v>141.87331622694285</v>
+        <v>130.63977444697886</v>
       </c>
       <c r="R240">
-        <v>-22.59801335237621</v>
+        <v>-24.119247432589709</v>
       </c>
     </row>
     <row r="241" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O241" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="P241" t="s">
         <v>8</v>
       </c>
       <c r="Q241">
-        <v>134.39885944606516</v>
+        <v>130.93808934217148</v>
       </c>
       <c r="R241">
-        <v>-24.79923061036914</v>
+        <v>-25.857755904197489</v>
       </c>
     </row>
     <row r="242" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O242" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="P242" t="s">
         <v>8</v>
       </c>
       <c r="Q242">
-        <v>137.32322652242817</v>
+        <v>134.39885944606516</v>
       </c>
       <c r="R242">
-        <v>-24.727021000667804</v>
+        <v>-24.79923061036914</v>
       </c>
     </row>
     <row r="243" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O243" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="P243" t="s">
         <v>8</v>
       </c>
       <c r="Q243">
-        <v>143.17631246690607</v>
+        <v>135.35284193128018</v>
       </c>
       <c r="R243">
-        <v>-26.284316493363157</v>
+        <v>-26.633458313858693</v>
       </c>
     </row>
     <row r="244" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O244" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="P244" t="s">
         <v>8</v>
       </c>
       <c r="Q244">
-        <v>141.05568117271642</v>
+        <v>138.92597164638124</v>
       </c>
       <c r="R244">
-        <v>-27.058724077525344</v>
+        <v>-20.49820523250327</v>
       </c>
     </row>
     <row r="245" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O245" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="P245" t="s">
         <v>8</v>
       </c>
       <c r="Q245">
-        <v>131.51442733918063</v>
+        <v>133.79613426251686</v>
       </c>
       <c r="R245">
-        <v>-28.368760408286018</v>
+        <v>-17.741016470746892</v>
       </c>
     </row>
     <row r="246" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O246" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="P246" t="s">
         <v>8</v>
       </c>
       <c r="Q246">
-        <v>134.32283850489063</v>
+        <v>142.30082021143733</v>
       </c>
       <c r="R246">
-        <v>-30.621921725356888</v>
+        <v>-18.402066295276651</v>
       </c>
     </row>
     <row r="247" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O247" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="P247" t="s">
         <v>8</v>
       </c>
       <c r="Q247">
-        <v>130.77152772622495</v>
+        <v>138.93282019553646</v>
       </c>
       <c r="R247">
-        <v>-30.635030423097369</v>
+        <v>-18.420745131426489</v>
       </c>
     </row>
     <row r="248" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O248" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="P248" t="s">
         <v>8</v>
       </c>
       <c r="Q248">
-        <v>140.72984435371333</v>
+        <v>135.17066209997108</v>
       </c>
       <c r="R248">
-        <v>-29.40377609579539</v>
+        <v>-13.663984400146033</v>
       </c>
     </row>
     <row r="249" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O249" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="P249" t="s">
         <v>8</v>
       </c>
       <c r="Q249">
-        <v>134.66612187113373</v>
+        <v>144.18081306008108</v>
       </c>
       <c r="R249">
-        <v>-28.15690116839572</v>
+        <v>-20.229420786672222</v>
       </c>
     </row>
     <row r="250" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O250" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="P250" t="s">
         <v>8</v>
       </c>
       <c r="Q250">
-        <v>136.77228252752337</v>
+        <v>149.05890457083896</v>
       </c>
       <c r="R250">
-        <v>-27.541992457451759</v>
+        <v>-36.214456588804133</v>
       </c>
     </row>
     <row r="251" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O251" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="P251" t="s">
         <v>8</v>
       </c>
       <c r="Q251">
-        <v>149.35779146912768</v>
+        <v>119.13755382787576</v>
       </c>
       <c r="R251">
-        <v>-26.300868571942431</v>
+        <v>-30.848388264297188</v>
       </c>
     </row>
     <row r="252" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O252" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="P252" t="s">
         <v>8</v>
       </c>
       <c r="Q252">
-        <v>148.14237478588089</v>
+        <v>145.58163249489499</v>
       </c>
       <c r="R252">
-        <v>-27.600157486042235</v>
+        <v>-38.380451924359413</v>
       </c>
     </row>
     <row r="253" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O253" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="P253" t="s">
         <v>8</v>
       </c>
       <c r="Q253">
-        <v>152.12642849359025</v>
+        <v>141.5028913601783</v>
       </c>
       <c r="R253">
-        <v>-28.3347891959374</v>
+        <v>-37.829918739943992</v>
       </c>
     </row>
     <row r="254" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O254" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="P254" t="s">
         <v>8</v>
       </c>
       <c r="Q254">
-        <v>153.10456995993425</v>
+        <v>114.27381043138838</v>
       </c>
       <c r="R254">
-        <v>-28.752190756768822</v>
+        <v>-24.339791643388494</v>
       </c>
     </row>
     <row r="255" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O255" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="P255" t="s">
         <v>8</v>
       </c>
       <c r="Q255">
-        <v>150.05391578943551</v>
+        <v>117.34247945346981</v>
       </c>
       <c r="R255">
-        <v>-24.982613757086916</v>
+        <v>-22.660298873087012</v>
       </c>
     </row>
     <row r="256" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O256" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="P256" t="s">
         <v>8</v>
       </c>
       <c r="Q256">
-        <v>151.79277925052281</v>
+        <v>116.29723010890623</v>
       </c>
       <c r="R256">
-        <v>-25.038955284229257</v>
+        <v>-24.548778739246707</v>
       </c>
     </row>
     <row r="257" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O257" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P257" t="s">
         <v>8</v>
       </c>
       <c r="Q257">
-        <v>151.94448277205771</v>
+        <v>151.23547888480226</v>
       </c>
       <c r="R257">
-        <v>-30.648097888639381</v>
+        <v>-24.09724976838157</v>
       </c>
     </row>
     <row r="258" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O258" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="P258" t="s">
         <v>8</v>
       </c>
       <c r="Q258">
-        <v>150.2541462946395</v>
+        <v>146.75055419846774</v>
       </c>
       <c r="R258">
-        <v>-31.530311559255505</v>
+        <v>-38.174584890819979</v>
       </c>
     </row>
     <row r="259" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O259" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="P259" t="s">
         <v>8</v>
       </c>
       <c r="Q259">
-        <v>149.62090042212768</v>
+        <v>148.69110889822107</v>
       </c>
       <c r="R259">
-        <v>-34.29495419383332</v>
+        <v>-26.595631032117534</v>
       </c>
     </row>
     <row r="260" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O260" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="P260" t="s">
         <v>8</v>
       </c>
       <c r="Q260">
-        <v>152.83763455688668</v>
+        <v>145.30043379524335</v>
       </c>
       <c r="R260">
-        <v>-30.889034568147331</v>
+        <v>-26.851379015168551</v>
       </c>
     </row>
     <row r="261" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O261" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="P261" t="s">
         <v>8</v>
       </c>
       <c r="Q261">
-        <v>151.67802522839008</v>
+        <v>114.7799968126468</v>
       </c>
       <c r="R261">
-        <v>-32.897248213926524</v>
+        <v>-22.493300099751107</v>
       </c>
     </row>
     <row r="262" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O262" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="P262" t="s">
         <v>8</v>
       </c>
       <c r="Q262">
-        <v>144.77318477184815</v>
+        <v>117.14188971970221</v>
       </c>
       <c r="R262">
-        <v>-30.102696294151649</v>
+        <v>-21.27831181122556</v>
       </c>
     </row>
     <row r="263" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O263" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="P263" t="s">
         <v>8</v>
       </c>
       <c r="Q263">
-        <v>146.63244669472485</v>
+        <v>126.82413474256852</v>
       </c>
       <c r="R263">
-        <v>-28.772135899285555</v>
+        <v>-21.544050383279892</v>
       </c>
     </row>
     <row r="264" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O264" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="P264" t="s">
         <v>8</v>
       </c>
       <c r="Q264">
-        <v>145.27438207575517</v>
+        <v>127.96303555320348</v>
       </c>
       <c r="R264">
-        <v>-33.717668107285725</v>
+        <v>-22.91061540635657</v>
       </c>
     </row>
     <row r="265" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O265" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="P265" t="s">
         <v>8</v>
       </c>
       <c r="Q265">
-        <v>147.93972516999915</v>
+        <v>125.43810026510718</v>
       </c>
       <c r="R265">
-        <v>-32.762336355038023</v>
+        <v>-23.36259114408892</v>
       </c>
     </row>
     <row r="266" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O266" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="P266" t="s">
         <v>8</v>
       </c>
       <c r="Q266">
-        <v>115.97456492850932</v>
+        <v>122.43915465461684</v>
       </c>
       <c r="R266">
-        <v>-27.306192795280872</v>
+        <v>-22.19879226832656</v>
       </c>
     </row>
     <row r="267" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O267" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="P267" t="s">
         <v>8</v>
       </c>
       <c r="Q267">
-        <v>118.30697028240009</v>
+        <v>120.09507964562351</v>
       </c>
       <c r="R267">
-        <v>-27.961249059143668</v>
+        <v>-22.295755610725131</v>
       </c>
     </row>
     <row r="268" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O268" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="P268" t="s">
         <v>8</v>
       </c>
       <c r="Q268">
-        <v>116.84344906931088</v>
+        <v>123.07418817864048</v>
       </c>
       <c r="R268">
-        <v>-29.109751296776803</v>
+        <v>-24.357617484853719</v>
       </c>
     </row>
     <row r="269" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O269" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="P269" t="s">
         <v>8</v>
       </c>
       <c r="Q269">
-        <v>127.92921064711308</v>
+        <v>119.76529220000766</v>
       </c>
       <c r="R269">
-        <v>-27.965189577949349</v>
+        <v>-25.094212865580069</v>
       </c>
     </row>
     <row r="270" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O270" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="P270" t="s">
         <v>8</v>
       </c>
       <c r="Q270">
-        <v>124.48324861064027</v>
+        <v>114.86283373084184</v>
       </c>
       <c r="R270">
-        <v>-28.350204599948327</v>
+        <v>-26.850317897683912</v>
       </c>
     </row>
     <row r="271" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O271" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="P271" t="s">
         <v>8</v>
       </c>
       <c r="Q271">
-        <v>121.30598072890582</v>
+        <v>117.46314854792784</v>
       </c>
       <c r="R271">
-        <v>-28.309618557173209</v>
+        <v>-29.069482523035592</v>
       </c>
     </row>
     <row r="272" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O272" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="P272" t="s">
         <v>8</v>
       </c>
       <c r="Q272">
-        <v>124.46777334471824</v>
+        <v>117.30938067644048</v>
       </c>
       <c r="R272">
-        <v>-32.105240034383613</v>
+        <v>-27.142611408067889</v>
       </c>
     </row>
     <row r="273" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O273" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="P273" t="s">
         <v>8</v>
       </c>
       <c r="Q273">
-        <v>124.4931229496114</v>
+        <v>149.14914911900263</v>
       </c>
       <c r="R273">
-        <v>-30.717946569059819</v>
+        <v>-34.631126809612212</v>
       </c>
     </row>
     <row r="274" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O274" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="P274" t="s">
         <v>8</v>
       </c>
       <c r="Q274">
-        <v>127.0895269072734</v>
+        <v>140.85809836004995</v>
       </c>
       <c r="R274">
-        <v>-30.529227185974907</v>
+        <v>-30.861063865580281</v>
       </c>
     </row>
     <row r="275" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O275" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="P275" t="s">
         <v>8</v>
       </c>
       <c r="Q275">
-        <v>118.05603838350194</v>
+        <v>142.23046674229096</v>
       </c>
       <c r="R275">
-        <v>-34.353314155008022</v>
+        <v>-32.160947640007599</v>
       </c>
     </row>
     <row r="276" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O276" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="P276" t="s">
         <v>8</v>
       </c>
       <c r="Q276">
-        <v>116.48599270419892</v>
+        <v>142.36723327169233</v>
       </c>
       <c r="R276">
-        <v>-31.735226030591157</v>
+        <v>-26.903893975033345</v>
       </c>
     </row>
     <row r="277" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O277" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="P277" t="s">
         <v>8</v>
       </c>
       <c r="Q277">
-        <v>121.35823120776448</v>
+        <v>140.91642234898802</v>
       </c>
       <c r="R277">
-        <v>-30.231203300821271</v>
+        <v>-28.940424642755492</v>
       </c>
     </row>
     <row r="278" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O278" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="P278" t="s">
         <v>8</v>
       </c>
       <c r="Q278">
-        <v>120.98810738452003</v>
+        <v>143.54246285523544</v>
       </c>
       <c r="R278">
-        <v>-31.912666666511377</v>
+        <v>-29.719049479687857</v>
       </c>
     </row>
     <row r="279" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O279" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="P279" t="s">
         <v>8</v>
       </c>
       <c r="Q279">
-        <v>121.40365316346715</v>
+        <v>115.72489967191386</v>
       </c>
       <c r="R279">
-        <v>-23.38749660972239</v>
+        <v>-30.087420725859118</v>
       </c>
     </row>
     <row r="280" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O280" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="P280" t="s">
         <v>8</v>
       </c>
       <c r="Q280">
-        <v>120.78862262071124</v>
+        <v>151.40868064688263</v>
       </c>
       <c r="R280">
-        <v>-25.85084559145124</v>
+        <v>-32.413854621654295</v>
       </c>
     </row>
     <row r="281" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O281" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="P281" t="s">
         <v>8</v>
       </c>
       <c r="Q281">
-        <v>124.92644854307436</v>
+        <v>116.00387277079756</v>
       </c>
       <c r="R281">
-        <v>-24.488649236868213</v>
+        <v>-31.925669117423599</v>
       </c>
     </row>
     <row r="282" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O282" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="P282" t="s">
         <v>8</v>
       </c>
       <c r="Q282">
-        <v>125.40253143865678</v>
+        <v>141.23511036743511</v>
       </c>
       <c r="R282">
-        <v>-26.39599312341414</v>
+        <v>-36.7528504674559</v>
       </c>
     </row>
     <row r="283" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O283" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="P283" t="s">
         <v>8</v>
       </c>
       <c r="Q283">
-        <v>127.83407424972432</v>
+        <v>123.0900307495962</v>
       </c>
       <c r="R283">
-        <v>-23.326148026767665</v>
+        <v>-18.602592489260651</v>
       </c>
     </row>
     <row r="284" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O284" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="P284" t="s">
         <v>8</v>
       </c>
       <c r="Q284">
-        <v>125.11073457612062</v>
+        <v>122.54308312197736</v>
       </c>
       <c r="R284">
-        <v>-22.060062802137889</v>
+        <v>-20.355566838375449</v>
       </c>
     </row>
     <row r="285" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O285" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="P285" t="s">
         <v>8</v>
       </c>
       <c r="Q285">
-        <v>130.77987585880484</v>
+        <v>128.22766529346336</v>
       </c>
       <c r="R285">
-        <v>-23.6520771510862</v>
+        <v>-19.496163382311977</v>
       </c>
     </row>
     <row r="286" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O286" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P286" t="s">
         <v>8</v>
       </c>
       <c r="Q286">
-        <v>129.76000532797065</v>
+        <v>129.86196084560535</v>
       </c>
       <c r="R286">
-        <v>-25.751442172745637</v>
+        <v>-14.565317050693372</v>
       </c>
     </row>
     <row r="287" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O287" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="P287" t="s">
         <v>8</v>
       </c>
       <c r="Q287">
-        <v>121.19680097154732</v>
+        <v>126.43376235886116</v>
       </c>
       <c r="R287">
-        <v>-20.824241557837841</v>
+        <v>-17.866548200273396</v>
       </c>
     </row>
     <row r="288" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O288" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="P288" t="s">
         <v>8</v>
       </c>
       <c r="Q288">
-        <v>123.82322757098922</v>
+        <v>146.97091687570963</v>
       </c>
       <c r="R288">
-        <v>-17.471436176410265</v>
+        <v>-43.000695831545308</v>
       </c>
     </row>
     <row r="289" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O289" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="P289" t="s">
         <v>8</v>
       </c>
       <c r="Q289">
-        <v>123.74790786027596</v>
+        <v>124.48324861064027</v>
       </c>
       <c r="R289">
-        <v>-19.213785896290247</v>
+        <v>-28.350204599948327</v>
       </c>
     </row>
     <row r="290" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O290" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="P290" t="s">
         <v>8</v>
       </c>
       <c r="Q290">
-        <v>117.42275836968288</v>
+        <v>121.40253377841466</v>
       </c>
       <c r="R290">
-        <v>-21.144003963089126</v>
+        <v>-28.183968446146601</v>
       </c>
     </row>
     <row r="291" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O291" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="P291" t="s">
         <v>8</v>
       </c>
       <c r="Q291">
-        <v>117.89666131220254</v>
+        <v>127.46158804742136</v>
       </c>
       <c r="R291">
-        <v>-23.720298383817479</v>
+        <v>-27.580725512880846</v>
       </c>
     </row>
     <row r="292" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O292" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P292" t="s">
         <v>8</v>
       </c>
       <c r="Q292">
-        <v>116.20239512475231</v>
+        <v>126.0618843650622</v>
       </c>
       <c r="R292">
-        <v>-25.347887721648856</v>
+        <v>-25.58725211244526</v>
       </c>
     </row>
     <row r="293" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O293" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="P293" t="s">
         <v>8</v>
       </c>
       <c r="Q293">
-        <v>115.38939990331832</v>
+        <v>127.65367876736605</v>
       </c>
       <c r="R293">
-        <v>-22.518290090128978</v>
+        <v>-31.392148397151932</v>
       </c>
     </row>
     <row r="294" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O294" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="P294" t="s">
         <v>8</v>
       </c>
       <c r="Q294">
-        <v>114.29262158861788</v>
+        <v>126.50666581107932</v>
       </c>
       <c r="R294">
-        <v>-24.397642917030851</v>
+        <v>-30.359828636142097</v>
+      </c>
+    </row>
+    <row r="295" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O295" t="s">
+        <v>419</v>
+      </c>
+      <c r="P295" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q295">
+        <v>121.15731523216064</v>
+      </c>
+      <c r="R295">
+        <v>-30.892773675948479</v>
+      </c>
+    </row>
+    <row r="296" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O296" t="s">
+        <v>420</v>
+      </c>
+      <c r="P296" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q296">
+        <v>124.45740918984608</v>
+      </c>
+      <c r="R296">
+        <v>-32.109749022654</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05B38BD7-F9F3-4497-AF0D-6937B774A8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6B03ABC-9128-4BE7-AA02-CBEE87E908D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3EBA9A0-17D7-42CD-BE39-5272F0764C25}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AFF512D8-FD25-4372-95E2-293C16BC124D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="419">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -71,228 +71,225 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_AUS42p8S146p2E_AUS</t>
+    <t>e_Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>g_Armidale_AUS-Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>e_BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>g_Armidale_AUS-BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>e_Australind_AUS</t>
+  </si>
+  <si>
+    <t>e_Merredin_AUS</t>
+  </si>
+  <si>
+    <t>g_Australind_AUS-Merredin_AUS</t>
+  </si>
+  <si>
+    <t>e_Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_Horsham_AUS</t>
+  </si>
+  <si>
+    <t>g_Ballarat_AUS-Horsham_AUS</t>
+  </si>
+  <si>
+    <t>e_SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>g_Ballarat_AUS-SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarrone_AUS</t>
+  </si>
+  <si>
+    <t>g_Ballarat_AUS-Tarrone_AUS</t>
+  </si>
+  <si>
+    <t>e_Balranald_AUS</t>
+  </si>
+  <si>
+    <t>g_Balranald_AUS-Ballarat_AUS</t>
+  </si>
+  <si>
+    <t>e_DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>g_Balranald_AUS-DarlingtonPoint_AUS</t>
+  </si>
+  <si>
+    <t>g_Balranald_AUS-Horsham_AUS</t>
+  </si>
+  <si>
+    <t>e_Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>g_Bouldercombe_AUS-CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>e_Calvale_AUS</t>
+  </si>
+  <si>
+    <t>g_Bouldercombe_AUS-Calvale_AUS</t>
+  </si>
+  <si>
+    <t>e_Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>g_Broadsound_AUS-Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>e_BrokenHill_AUS</t>
+  </si>
+  <si>
+    <t>g_BrokenHill_AUS-Balranald_AUS</t>
+  </si>
+  <si>
+    <t>e_Tarong_AUS</t>
+  </si>
+  <si>
+    <t>g_BulliCreek_AUS-Tarong_AUS</t>
+  </si>
+  <si>
+    <t>e_GinGin_AUS</t>
+  </si>
+  <si>
+    <t>g_CalliopeRiver_AUS-GinGin_AUS</t>
+  </si>
+  <si>
+    <t>g_Calvale_AUS-Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>g_Calvale_AUS-CalliopeRiver_AUS</t>
+  </si>
+  <si>
+    <t>g_Calvale_AUS-Tarong_AUS</t>
+  </si>
+  <si>
+    <t>e_Canberra_AUS</t>
+  </si>
+  <si>
+    <t>e_SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>g_Canberra_AUS-SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>e_CentralCoast_AUS</t>
+  </si>
+  <si>
+    <t>g_CentralCoast_AUS-Armidale_AUS</t>
+  </si>
+  <si>
+    <t>e_MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>g_CentralCoast_AUS-MountPiper_AUS</t>
+  </si>
+  <si>
+    <t>e_Chalumbin_AUS</t>
+  </si>
+  <si>
+    <t>e_Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>g_Chalumbin_AUS-Strathmore_AUS</t>
+  </si>
+  <si>
+    <t>e_Wagga_AUS</t>
+  </si>
+  <si>
+    <t>g_DarlingtonPoint_AUS-Wagga_AUS</t>
+  </si>
+  <si>
+    <t>e_Davenport_AUS</t>
+  </si>
+  <si>
+    <t>e_Robertstown_AUS</t>
+  </si>
+  <si>
+    <t>g_Davenport_AUS-Robertstown_AUS</t>
+  </si>
+  <si>
+    <t>g_GinGin_AUS-Tarong_AUS</t>
+  </si>
+  <si>
+    <t>e_Hobart_AUS</t>
   </si>
   <si>
     <t>e_Palmerston_AUS</t>
   </si>
   <si>
-    <t>g_AUS42p8S146p2E_AUS-Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>g_Hobart_AUS-Palmerston_AUS</t>
+  </si>
+  <si>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>g_Karratha_AUS-TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>g_Merredin_AUS-Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>g_Morawa_AUS-Yandin_AUS</t>
+  </si>
+  <si>
+    <t>g_MountPiper_AUS-SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>g_Murray_AUS-SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Nebo_AUS</t>
+  </si>
+  <si>
+    <t>g_Nebo_AUS-Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>g_Nebo_AUS-Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
   </si>
   <si>
     <t>e_Sheffield_AUS</t>
   </si>
   <si>
-    <t>g_AUS42p8S146p2E_AUS-Sheffield_AUS</t>
-  </si>
-  <si>
-    <t>e_Armidale_AUS</t>
-  </si>
-  <si>
-    <t>e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>g_Armidale_AUS-Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>e_BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>g_Armidale_AUS-BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>e_Australind_AUS</t>
-  </si>
-  <si>
-    <t>e_Merredin_AUS</t>
-  </si>
-  <si>
-    <t>g_Australind_AUS-Merredin_AUS</t>
-  </si>
-  <si>
-    <t>e_Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_Horsham_AUS</t>
-  </si>
-  <si>
-    <t>g_Ballarat_AUS-Horsham_AUS</t>
-  </si>
-  <si>
-    <t>e_SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>g_Ballarat_AUS-SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarrone_AUS</t>
-  </si>
-  <si>
-    <t>g_Ballarat_AUS-Tarrone_AUS</t>
-  </si>
-  <si>
-    <t>e_Balranald_AUS</t>
-  </si>
-  <si>
-    <t>g_Balranald_AUS-Ballarat_AUS</t>
-  </si>
-  <si>
-    <t>e_DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>g_Balranald_AUS-DarlingtonPoint_AUS</t>
-  </si>
-  <si>
-    <t>g_Balranald_AUS-Horsham_AUS</t>
-  </si>
-  <si>
-    <t>e_Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>g_Bouldercombe_AUS-CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>e_Calvale_AUS</t>
-  </si>
-  <si>
-    <t>g_Bouldercombe_AUS-Calvale_AUS</t>
-  </si>
-  <si>
-    <t>e_Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>g_Broadsound_AUS-Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>e_BrokenHill_AUS</t>
-  </si>
-  <si>
-    <t>g_BrokenHill_AUS-Balranald_AUS</t>
-  </si>
-  <si>
-    <t>e_Tarong_AUS</t>
-  </si>
-  <si>
-    <t>g_BulliCreek_AUS-Tarong_AUS</t>
-  </si>
-  <si>
-    <t>e_GinGin_AUS</t>
-  </si>
-  <si>
-    <t>g_CalliopeRiver_AUS-GinGin_AUS</t>
-  </si>
-  <si>
-    <t>g_Calvale_AUS-Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>g_Calvale_AUS-CalliopeRiver_AUS</t>
-  </si>
-  <si>
-    <t>g_Calvale_AUS-Tarong_AUS</t>
-  </si>
-  <si>
-    <t>e_Canberra_AUS</t>
-  </si>
-  <si>
-    <t>e_SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>g_Canberra_AUS-SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_CentralCoast_AUS</t>
-  </si>
-  <si>
-    <t>g_CentralCoast_AUS-Armidale_AUS</t>
-  </si>
-  <si>
-    <t>e_MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>g_CentralCoast_AUS-MountPiper_AUS</t>
-  </si>
-  <si>
-    <t>e_Chalumbin_AUS</t>
-  </si>
-  <si>
-    <t>e_Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>g_Chalumbin_AUS-Strathmore_AUS</t>
-  </si>
-  <si>
-    <t>e_Wagga_AUS</t>
-  </si>
-  <si>
-    <t>g_DarlingtonPoint_AUS-Wagga_AUS</t>
-  </si>
-  <si>
-    <t>e_Davenport_AUS</t>
-  </si>
-  <si>
-    <t>e_Robertstown_AUS</t>
-  </si>
-  <si>
-    <t>g_Davenport_AUS-Robertstown_AUS</t>
-  </si>
-  <si>
-    <t>g_GinGin_AUS-Tarong_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>g_Karratha_AUS-TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>g_Merredin_AUS-Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>g_Morawa_AUS-Yandin_AUS</t>
-  </si>
-  <si>
-    <t>g_MountPiper_AUS-SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>g_Murray_AUS-SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Nebo_AUS</t>
-  </si>
-  <si>
-    <t>g_Nebo_AUS-Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>g_Nebo_AUS-Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_OlympicDamWest_AUS</t>
-  </si>
-  <si>
-    <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
-  </si>
-  <si>
     <t>g_Palmerston_AUS-Sheffield_AUS</t>
   </si>
   <si>
@@ -386,12 +383,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -122.0 km- AU149-220;way/174441055-220 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
-    <t>grid link -131.0 km- AU149-220;way/88191017-220 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
     <t>grid link -371.0 km- way/160201298-330;way/172587651-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -465,6 +456,9 @@
   </si>
   <si>
     <t>grid link -100.0 km- way/170709510-275;way/171728751-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -143.0 km- AU146-220;way/174441055-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>grid link -254.0 km- way/337655870-220;way/583492111-220 (thermal x 0.7 N-1)</t>
@@ -1672,7 +1666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BF4525-D81A-4AEB-B1E7-225B3B7ACA9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671C2949-9012-45D1-9FB3-B966B448D2C2}">
   <dimension ref="B3:R296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1681,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -1710,22 +1704,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L4" t="s">
         <v>113</v>
       </c>
-      <c r="L4" t="s">
-        <v>114</v>
-      </c>
       <c r="O4" t="s">
+        <v>169</v>
+      </c>
+      <c r="P4" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q4" t="s">
         <v>171</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>172</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>173</v>
-      </c>
-      <c r="R4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -1754,10 +1748,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
@@ -1795,7 +1789,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s">
         <v>10</v>
@@ -1804,10 +1798,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>146.17591077698933</v>
+        <v>151.71319760744726</v>
       </c>
       <c r="R6">
-        <v>-42.848328268142403</v>
+        <v>-30.532100853424872</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
@@ -1836,7 +1830,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O7" t="s">
         <v>16</v>
@@ -1845,10 +1839,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>151.71319760744726</v>
+        <v>116.2758549871163</v>
       </c>
       <c r="R7">
-        <v>-30.532100853424872</v>
+        <v>-33.318012556546421</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
@@ -1862,34 +1856,34 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P8" t="s">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>116.2758549871163</v>
+        <v>143.92108294719912</v>
       </c>
       <c r="R8">
-        <v>-33.318012556546421</v>
+        <v>-37.567537497399123</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
@@ -1903,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -1918,19 +1912,19 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>143.92108294719912</v>
+        <v>143.5251594037239</v>
       </c>
       <c r="R9">
-        <v>-37.567537497399123</v>
+        <v>-34.775720926588463</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
@@ -1944,22 +1938,22 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
         <v>24</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O10" t="s">
         <v>31</v>
@@ -1968,10 +1962,10 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>143.5251594037239</v>
+        <v>150.48716060704265</v>
       </c>
       <c r="R10">
-        <v>-34.775720926588463</v>
+        <v>-23.537233256213721</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -1985,34 +1979,34 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
         <v>27</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>150.48716060704265</v>
+        <v>152.95633561497641</v>
       </c>
       <c r="R11">
-        <v>-23.537233256213721</v>
+        <v>-27.732264407857119</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -2026,34 +2020,34 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
         <v>29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O12" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>152.95633561497641</v>
+        <v>149.40404924290272</v>
       </c>
       <c r="R12">
-        <v>-27.732264407857119</v>
+        <v>-22.820756210209289</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
@@ -2067,34 +2061,34 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>149.40404924290272</v>
+        <v>141.41917764116005</v>
       </c>
       <c r="R13">
-        <v>-22.820756210209289</v>
+        <v>-31.986353168692315</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.45">
@@ -2111,31 +2105,31 @@
         <v>31</v>
       </c>
       <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
         <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>34</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O14" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>141.41917764116005</v>
+        <v>150.84329384341081</v>
       </c>
       <c r="R14">
-        <v>-31.986353168692315</v>
+        <v>-27.920986820196017</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
@@ -2152,7 +2146,7 @@
         <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
         <v>35</v>
@@ -2164,19 +2158,19 @@
         <v>35</v>
       </c>
       <c r="L15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O15" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>150.84329384341081</v>
+        <v>151.19284847613793</v>
       </c>
       <c r="R15">
-        <v>-27.920986820196017</v>
+        <v>-23.856194719487281</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -2193,31 +2187,31 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" t="s">
         <v>37</v>
-      </c>
-      <c r="G16" t="s">
-        <v>38</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>151.19284847613793</v>
+        <v>150.62709905075124</v>
       </c>
       <c r="R16">
-        <v>-23.856194719487281</v>
+        <v>-24.342461230294287</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -2231,34 +2225,34 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" t="s">
         <v>39</v>
-      </c>
-      <c r="G17" t="s">
-        <v>40</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O17" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>150.62709905075124</v>
+        <v>148.90388563970319</v>
       </c>
       <c r="R17">
-        <v>-24.342461230294287</v>
+        <v>-34.862594637477081</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -2272,34 +2266,34 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" t="s">
         <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" t="s">
-        <v>42</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>148.90388563970319</v>
+        <v>151.49237495717287</v>
       </c>
       <c r="R18">
-        <v>-34.862594637477081</v>
+        <v>-33.052074884026759</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
@@ -2313,34 +2307,34 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
         <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" t="s">
-        <v>44</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>151.49237495717287</v>
+        <v>145.52658139950708</v>
       </c>
       <c r="R19">
-        <v>-33.052074884026759</v>
+        <v>-17.800806029919851</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">
@@ -2354,34 +2348,34 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O20" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>145.52658139950708</v>
+        <v>146.03429268958672</v>
       </c>
       <c r="R20">
-        <v>-17.800806029919851</v>
+        <v>-34.648775935550987</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.45">
@@ -2395,34 +2389,34 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O21" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>146.03429268958672</v>
+        <v>137.8128974128341</v>
       </c>
       <c r="R21">
-        <v>-34.648775935550987</v>
+        <v>-32.536269144315668</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.45">
@@ -2436,34 +2430,34 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O22" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>137.8128974128341</v>
+        <v>151.81952564800682</v>
       </c>
       <c r="R22">
-        <v>-32.536269144315668</v>
+        <v>-24.90133538944163</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2477,34 +2471,34 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O23" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>151.81952564800682</v>
+        <v>146.42885495857578</v>
       </c>
       <c r="R23">
-        <v>-24.90133538944163</v>
+        <v>-38.281663652861432</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2518,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
         <v>51</v>
@@ -2533,19 +2527,19 @@
         <v>51</v>
       </c>
       <c r="L24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O24" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>146.42885495857578</v>
+        <v>146.7152693827272</v>
       </c>
       <c r="R24">
-        <v>-38.281663652861432</v>
+        <v>-42.823952846681991</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2559,25 +2553,25 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>53</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O25" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
@@ -2600,10 +2594,10 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" t="s">
         <v>55</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
       </c>
       <c r="G26" t="s">
         <v>56</v>
@@ -2615,10 +2609,10 @@
         <v>56</v>
       </c>
       <c r="L26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
@@ -2641,7 +2635,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
         <v>57</v>
@@ -2656,10 +2650,10 @@
         <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
@@ -2697,10 +2691,10 @@
         <v>61</v>
       </c>
       <c r="L28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O28" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
@@ -2723,25 +2717,25 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" t="s">
         <v>62</v>
-      </c>
-      <c r="G29" t="s">
-        <v>63</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
@@ -2764,25 +2758,25 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" t="s">
         <v>64</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>65</v>
-      </c>
-      <c r="G30" t="s">
-        <v>66</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O30" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
@@ -2805,25 +2799,25 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P31" t="s">
         <v>8</v>
@@ -2846,7 +2840,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
         <v>69</v>
@@ -2861,10 +2855,10 @@
         <v>70</v>
       </c>
       <c r="L32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
@@ -2887,25 +2881,25 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O33" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
@@ -2928,25 +2922,25 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" t="s">
         <v>74</v>
-      </c>
-      <c r="G34" t="s">
-        <v>75</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O34" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
@@ -2969,10 +2963,10 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
@@ -2984,10 +2978,10 @@
         <v>76</v>
       </c>
       <c r="L35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P35" t="s">
         <v>8</v>
@@ -3013,7 +3007,7 @@
         <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
         <v>78</v>
@@ -3025,10 +3019,10 @@
         <v>78</v>
       </c>
       <c r="L36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
@@ -3051,25 +3045,25 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
         <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
@@ -3092,10 +3086,10 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G38" t="s">
         <v>81</v>
@@ -3107,10 +3101,10 @@
         <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O38" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
@@ -3133,10 +3127,10 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
+        <v>64</v>
+      </c>
+      <c r="F39" t="s">
         <v>82</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
       </c>
       <c r="G39" t="s">
         <v>83</v>
@@ -3148,10 +3142,10 @@
         <v>83</v>
       </c>
       <c r="L39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P39" t="s">
         <v>8</v>
@@ -3174,25 +3168,25 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="P40" t="s">
         <v>8</v>
@@ -3215,25 +3209,25 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O41" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P41" t="s">
         <v>8</v>
@@ -3256,25 +3250,25 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O42" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="P42" t="s">
         <v>8</v>
@@ -3297,10 +3291,10 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G43" t="s">
         <v>90</v>
@@ -3312,10 +3306,10 @@
         <v>90</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P43" t="s">
         <v>8</v>
@@ -3338,10 +3332,10 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s">
         <v>91</v>
@@ -3353,10 +3347,10 @@
         <v>91</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O44" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P44" t="s">
         <v>8</v>
@@ -3379,25 +3373,25 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O45" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
@@ -3420,10 +3414,10 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="G46" t="s">
         <v>95</v>
@@ -3435,10 +3429,10 @@
         <v>95</v>
       </c>
       <c r="L46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
@@ -3461,10 +3455,10 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" t="s">
         <v>93</v>
-      </c>
-      <c r="F47" t="s">
-        <v>27</v>
       </c>
       <c r="G47" t="s">
         <v>96</v>
@@ -3476,10 +3470,10 @@
         <v>96</v>
       </c>
       <c r="L47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P47" t="s">
         <v>8</v>
@@ -3502,10 +3496,10 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s">
         <v>97</v>
@@ -3517,10 +3511,10 @@
         <v>97</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O48" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P48" t="s">
         <v>8</v>
@@ -3543,10 +3537,10 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F49" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G49" t="s">
         <v>98</v>
@@ -3558,10 +3552,10 @@
         <v>98</v>
       </c>
       <c r="L49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P49" t="s">
         <v>8</v>
@@ -3584,10 +3578,10 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F50" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="G50" t="s">
         <v>99</v>
@@ -3599,10 +3593,10 @@
         <v>99</v>
       </c>
       <c r="L50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
@@ -3625,10 +3619,10 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G51" t="s">
         <v>100</v>
@@ -3640,10 +3634,10 @@
         <v>100</v>
       </c>
       <c r="L51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
@@ -3666,25 +3660,25 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="G52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
@@ -3707,25 +3701,25 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O53" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
@@ -3748,34 +3742,34 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="F54" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O54" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>145.74672600476077</v>
+        <v>145.74657208657698</v>
       </c>
       <c r="R54">
-        <v>-41.239472398304343</v>
+        <v>-41.2407776578913</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -3789,10 +3783,10 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s">
         <v>107</v>
@@ -3804,10 +3798,10 @@
         <v>107</v>
       </c>
       <c r="L55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
@@ -3830,10 +3824,10 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="F56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G56" t="s">
         <v>108</v>
@@ -3845,10 +3839,10 @@
         <v>108</v>
       </c>
       <c r="L56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O56" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P56" t="s">
         <v>8</v>
@@ -3871,10 +3865,10 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G57" t="s">
         <v>109</v>
@@ -3886,10 +3880,10 @@
         <v>109</v>
       </c>
       <c r="L57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O57" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P57" t="s">
         <v>8</v>
@@ -3912,10 +3906,10 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="G58" t="s">
         <v>110</v>
@@ -3927,10 +3921,10 @@
         <v>110</v>
       </c>
       <c r="L58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
@@ -3943,35 +3937,8 @@
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>74</v>
-      </c>
-      <c r="F59" t="s">
-        <v>87</v>
-      </c>
-      <c r="G59" t="s">
-        <v>111</v>
-      </c>
-      <c r="H59" t="s">
-        <v>13</v>
-      </c>
-      <c r="K59" t="s">
-        <v>111</v>
-      </c>
-      <c r="L59" t="s">
-        <v>169</v>
-      </c>
       <c r="O59" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
@@ -3985,7 +3952,7 @@
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O60" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
@@ -3999,7 +3966,7 @@
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
@@ -4013,7 +3980,7 @@
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
@@ -4027,7 +3994,7 @@
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
@@ -4041,7 +4008,7 @@
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O64" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
@@ -4055,7 +4022,7 @@
     </row>
     <row r="65" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O65" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
@@ -4069,7 +4036,7 @@
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O66" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
@@ -4083,7 +4050,7 @@
     </row>
     <row r="67" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
@@ -4097,7 +4064,7 @@
     </row>
     <row r="68" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
@@ -4111,7 +4078,7 @@
     </row>
     <row r="69" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
@@ -4125,7 +4092,7 @@
     </row>
     <row r="70" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O70" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
@@ -4139,7 +4106,7 @@
     </row>
     <row r="71" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O71" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
@@ -4153,7 +4120,7 @@
     </row>
     <row r="72" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O72" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
@@ -4167,7 +4134,7 @@
     </row>
     <row r="73" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O73" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
@@ -4181,7 +4148,7 @@
     </row>
     <row r="74" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O74" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
@@ -4195,7 +4162,7 @@
     </row>
     <row r="75" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
@@ -4209,7 +4176,7 @@
     </row>
     <row r="76" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O76" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
@@ -4223,21 +4190,21 @@
     </row>
     <row r="77" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>147.48956461856997</v>
+        <v>147.51971261676547</v>
       </c>
       <c r="R77">
-        <v>-41.86050859336482</v>
+        <v>-41.754650558287658</v>
       </c>
     </row>
     <row r="78" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O78" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
@@ -4251,7 +4218,7 @@
     </row>
     <row r="79" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O79" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
@@ -4265,7 +4232,7 @@
     </row>
     <row r="80" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O80" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
@@ -4279,7 +4246,7 @@
     </row>
     <row r="81" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O81" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
@@ -4293,7 +4260,7 @@
     </row>
     <row r="82" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O82" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
@@ -4307,7 +4274,7 @@
     </row>
     <row r="83" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O83" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
@@ -4321,7 +4288,7 @@
     </row>
     <row r="84" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O84" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
@@ -4335,7 +4302,7 @@
     </row>
     <row r="85" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O85" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
@@ -4349,7 +4316,7 @@
     </row>
     <row r="86" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O86" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
@@ -4363,7 +4330,7 @@
     </row>
     <row r="87" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O87" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
@@ -4377,7 +4344,7 @@
     </row>
     <row r="88" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O88" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
@@ -4391,7 +4358,7 @@
     </row>
     <row r="89" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O89" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P89" t="s">
         <v>8</v>
@@ -4405,7 +4372,7 @@
     </row>
     <row r="90" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
@@ -4419,7 +4386,7 @@
     </row>
     <row r="91" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
@@ -4433,7 +4400,7 @@
     </row>
     <row r="92" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
@@ -4447,7 +4414,7 @@
     </row>
     <row r="93" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
@@ -4461,7 +4428,7 @@
     </row>
     <row r="94" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
@@ -4475,7 +4442,7 @@
     </row>
     <row r="95" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
@@ -4489,7 +4456,7 @@
     </row>
     <row r="96" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O96" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P96" t="s">
         <v>8</v>
@@ -4503,7 +4470,7 @@
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P97" t="s">
         <v>8</v>
@@ -4517,7 +4484,7 @@
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P98" t="s">
         <v>8</v>
@@ -4531,7 +4498,7 @@
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O99" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P99" t="s">
         <v>8</v>
@@ -4545,7 +4512,7 @@
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O100" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P100" t="s">
         <v>8</v>
@@ -4559,7 +4526,7 @@
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O101" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="P101" t="s">
         <v>8</v>
@@ -4573,7 +4540,7 @@
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O102" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P102" t="s">
         <v>8</v>
@@ -4587,7 +4554,7 @@
     </row>
     <row r="103" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O103" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P103" t="s">
         <v>8</v>
@@ -4601,7 +4568,7 @@
     </row>
     <row r="104" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O104" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P104" t="s">
         <v>8</v>
@@ -4615,7 +4582,7 @@
     </row>
     <row r="105" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O105" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P105" t="s">
         <v>8</v>
@@ -4629,7 +4596,7 @@
     </row>
     <row r="106" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O106" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P106" t="s">
         <v>8</v>
@@ -4643,7 +4610,7 @@
     </row>
     <row r="107" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O107" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P107" t="s">
         <v>8</v>
@@ -4657,7 +4624,7 @@
     </row>
     <row r="108" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O108" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P108" t="s">
         <v>8</v>
@@ -4671,7 +4638,7 @@
     </row>
     <row r="109" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O109" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P109" t="s">
         <v>8</v>
@@ -4685,7 +4652,7 @@
     </row>
     <row r="110" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O110" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P110" t="s">
         <v>8</v>
@@ -4699,7 +4666,7 @@
     </row>
     <row r="111" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O111" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P111" t="s">
         <v>8</v>
@@ -4713,7 +4680,7 @@
     </row>
     <row r="112" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O112" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P112" t="s">
         <v>8</v>
@@ -4727,7 +4694,7 @@
     </row>
     <row r="113" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O113" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P113" t="s">
         <v>8</v>
@@ -4741,7 +4708,7 @@
     </row>
     <row r="114" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O114" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P114" t="s">
         <v>8</v>
@@ -4755,7 +4722,7 @@
     </row>
     <row r="115" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O115" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P115" t="s">
         <v>8</v>
@@ -4769,7 +4736,7 @@
     </row>
     <row r="116" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
@@ -4783,7 +4750,7 @@
     </row>
     <row r="117" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
@@ -4797,7 +4764,7 @@
     </row>
     <row r="118" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
@@ -4811,7 +4778,7 @@
     </row>
     <row r="119" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
@@ -4825,7 +4792,7 @@
     </row>
     <row r="120" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
@@ -4839,7 +4806,7 @@
     </row>
     <row r="121" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
@@ -4853,7 +4820,7 @@
     </row>
     <row r="122" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
@@ -4867,7 +4834,7 @@
     </row>
     <row r="123" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
@@ -4881,7 +4848,7 @@
     </row>
     <row r="124" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
@@ -4895,7 +4862,7 @@
     </row>
     <row r="125" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
@@ -4909,7 +4876,7 @@
     </row>
     <row r="126" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
@@ -4923,7 +4890,7 @@
     </row>
     <row r="127" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
@@ -4937,7 +4904,7 @@
     </row>
     <row r="128" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
@@ -4951,7 +4918,7 @@
     </row>
     <row r="129" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
@@ -4965,7 +4932,7 @@
     </row>
     <row r="130" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
@@ -4979,7 +4946,7 @@
     </row>
     <row r="131" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
@@ -4993,7 +4960,7 @@
     </row>
     <row r="132" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
@@ -5007,7 +4974,7 @@
     </row>
     <row r="133" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
@@ -5021,7 +4988,7 @@
     </row>
     <row r="134" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
@@ -5035,7 +5002,7 @@
     </row>
     <row r="135" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O135" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P135" t="s">
         <v>8</v>
@@ -5049,7 +5016,7 @@
     </row>
     <row r="136" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O136" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P136" t="s">
         <v>8</v>
@@ -5063,7 +5030,7 @@
     </row>
     <row r="137" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O137" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P137" t="s">
         <v>8</v>
@@ -5077,7 +5044,7 @@
     </row>
     <row r="138" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O138" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P138" t="s">
         <v>8</v>
@@ -5091,7 +5058,7 @@
     </row>
     <row r="139" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O139" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P139" t="s">
         <v>8</v>
@@ -5105,21 +5072,21 @@
     </row>
     <row r="140" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O140" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P140" t="s">
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>146.61070950534349</v>
+        <v>147.1701068156745</v>
       </c>
       <c r="R140">
-        <v>-42.539251485649778</v>
+        <v>-42.677737589053145</v>
       </c>
     </row>
     <row r="141" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
@@ -5133,7 +5100,7 @@
     </row>
     <row r="142" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
@@ -5147,7 +5114,7 @@
     </row>
     <row r="143" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
@@ -5161,7 +5128,7 @@
     </row>
     <row r="144" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
@@ -5175,7 +5142,7 @@
     </row>
     <row r="145" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
@@ -5189,7 +5156,7 @@
     </row>
     <row r="146" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
@@ -5203,7 +5170,7 @@
     </row>
     <row r="147" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
@@ -5217,7 +5184,7 @@
     </row>
     <row r="148" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
@@ -5231,7 +5198,7 @@
     </row>
     <row r="149" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
@@ -5245,35 +5212,35 @@
     </row>
     <row r="150" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>146.66672296307451</v>
+        <v>144.36113356472447</v>
       </c>
       <c r="R150">
-        <v>-40.272839726974297</v>
+        <v>-41.44005143720814</v>
       </c>
     </row>
     <row r="151" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>144.64697355726699</v>
+        <v>145.97678015008486</v>
       </c>
       <c r="R151">
-        <v>-40.546840571798938</v>
+        <v>-40.254914758185407</v>
       </c>
     </row>
     <row r="152" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
@@ -5287,7 +5254,7 @@
     </row>
     <row r="153" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O153" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P153" t="s">
         <v>8</v>
@@ -5301,7 +5268,7 @@
     </row>
     <row r="154" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O154" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P154" t="s">
         <v>8</v>
@@ -5315,7 +5282,7 @@
     </row>
     <row r="155" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
@@ -5329,7 +5296,7 @@
     </row>
     <row r="156" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O156" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P156" t="s">
         <v>8</v>
@@ -5343,7 +5310,7 @@
     </row>
     <row r="157" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O157" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P157" t="s">
         <v>8</v>
@@ -5357,7 +5324,7 @@
     </row>
     <row r="158" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O158" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P158" t="s">
         <v>8</v>
@@ -5371,7 +5338,7 @@
     </row>
     <row r="159" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O159" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P159" t="s">
         <v>8</v>
@@ -5385,7 +5352,7 @@
     </row>
     <row r="160" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O160" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P160" t="s">
         <v>8</v>
@@ -5399,7 +5366,7 @@
     </row>
     <row r="161" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O161" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P161" t="s">
         <v>8</v>
@@ -5413,7 +5380,7 @@
     </row>
     <row r="162" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O162" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P162" t="s">
         <v>8</v>
@@ -5427,7 +5394,7 @@
     </row>
     <row r="163" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O163" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P163" t="s">
         <v>8</v>
@@ -5441,7 +5408,7 @@
     </row>
     <row r="164" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O164" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P164" t="s">
         <v>8</v>
@@ -5455,7 +5422,7 @@
     </row>
     <row r="165" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O165" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P165" t="s">
         <v>8</v>
@@ -5469,7 +5436,7 @@
     </row>
     <row r="166" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O166" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P166" t="s">
         <v>8</v>
@@ -5483,21 +5450,21 @@
     </row>
     <row r="167" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O167" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P167" t="s">
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>148.55880462471723</v>
+        <v>148.64966281870522</v>
       </c>
       <c r="R167">
-        <v>-41.33210911071906</v>
+        <v>-41.089250164550577</v>
       </c>
     </row>
     <row r="168" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O168" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P168" t="s">
         <v>8</v>
@@ -5511,7 +5478,7 @@
     </row>
     <row r="169" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O169" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P169" t="s">
         <v>8</v>
@@ -5525,7 +5492,7 @@
     </row>
     <row r="170" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O170" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P170" t="s">
         <v>8</v>
@@ -5539,7 +5506,7 @@
     </row>
     <row r="171" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O171" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P171" t="s">
         <v>8</v>
@@ -5553,7 +5520,7 @@
     </row>
     <row r="172" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O172" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P172" t="s">
         <v>8</v>
@@ -5567,7 +5534,7 @@
     </row>
     <row r="173" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O173" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P173" t="s">
         <v>8</v>
@@ -5581,7 +5548,7 @@
     </row>
     <row r="174" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O174" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P174" t="s">
         <v>8</v>
@@ -5595,7 +5562,7 @@
     </row>
     <row r="175" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O175" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P175" t="s">
         <v>8</v>
@@ -5609,7 +5576,7 @@
     </row>
     <row r="176" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O176" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P176" t="s">
         <v>8</v>
@@ -5623,7 +5590,7 @@
     </row>
     <row r="177" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O177" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P177" t="s">
         <v>8</v>
@@ -5637,7 +5604,7 @@
     </row>
     <row r="178" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O178" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P178" t="s">
         <v>8</v>
@@ -5651,7 +5618,7 @@
     </row>
     <row r="179" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O179" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P179" t="s">
         <v>8</v>
@@ -5665,7 +5632,7 @@
     </row>
     <row r="180" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O180" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P180" t="s">
         <v>8</v>
@@ -5679,7 +5646,7 @@
     </row>
     <row r="181" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O181" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P181" t="s">
         <v>8</v>
@@ -5693,7 +5660,7 @@
     </row>
     <row r="182" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O182" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P182" t="s">
         <v>8</v>
@@ -5707,7 +5674,7 @@
     </row>
     <row r="183" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O183" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P183" t="s">
         <v>8</v>
@@ -5721,7 +5688,7 @@
     </row>
     <row r="184" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O184" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P184" t="s">
         <v>8</v>
@@ -5735,7 +5702,7 @@
     </row>
     <row r="185" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O185" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P185" t="s">
         <v>8</v>
@@ -5749,7 +5716,7 @@
     </row>
     <row r="186" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O186" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P186" t="s">
         <v>8</v>
@@ -5763,7 +5730,7 @@
     </row>
     <row r="187" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O187" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P187" t="s">
         <v>8</v>
@@ -5777,7 +5744,7 @@
     </row>
     <row r="188" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O188" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P188" t="s">
         <v>8</v>
@@ -5791,7 +5758,7 @@
     </row>
     <row r="189" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O189" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="P189" t="s">
         <v>8</v>
@@ -5805,7 +5772,7 @@
     </row>
     <row r="190" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O190" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P190" t="s">
         <v>8</v>
@@ -5819,7 +5786,7 @@
     </row>
     <row r="191" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O191" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P191" t="s">
         <v>8</v>
@@ -5833,7 +5800,7 @@
     </row>
     <row r="192" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O192" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P192" t="s">
         <v>8</v>
@@ -5847,7 +5814,7 @@
     </row>
     <row r="193" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O193" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="P193" t="s">
         <v>8</v>
@@ -5861,7 +5828,7 @@
     </row>
     <row r="194" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O194" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P194" t="s">
         <v>8</v>
@@ -5875,7 +5842,7 @@
     </row>
     <row r="195" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O195" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="P195" t="s">
         <v>8</v>
@@ -5889,7 +5856,7 @@
     </row>
     <row r="196" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O196" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P196" t="s">
         <v>8</v>
@@ -5903,21 +5870,21 @@
     </row>
     <row r="197" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O197" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P197" t="s">
         <v>8</v>
       </c>
       <c r="Q197">
-        <v>146.29696618066109</v>
+        <v>147.10370753016318</v>
       </c>
       <c r="R197">
-        <v>-43.909028252220295</v>
+        <v>-43.459445564853546</v>
       </c>
     </row>
     <row r="198" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O198" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P198" t="s">
         <v>8</v>
@@ -5931,7 +5898,7 @@
     </row>
     <row r="199" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O199" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P199" t="s">
         <v>8</v>
@@ -5945,7 +5912,7 @@
     </row>
     <row r="200" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O200" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P200" t="s">
         <v>8</v>
@@ -5959,7 +5926,7 @@
     </row>
     <row r="201" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O201" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P201" t="s">
         <v>8</v>
@@ -5973,7 +5940,7 @@
     </row>
     <row r="202" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O202" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P202" t="s">
         <v>8</v>
@@ -5987,21 +5954,21 @@
     </row>
     <row r="203" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O203" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="P203" t="s">
         <v>8</v>
       </c>
       <c r="Q203">
-        <v>145.43263864663615</v>
+        <v>145.43305512263535</v>
       </c>
       <c r="R203">
-        <v>-41.070134274350721</v>
+        <v>-41.072643681112218</v>
       </c>
     </row>
     <row r="204" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O204" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P204" t="s">
         <v>8</v>
@@ -6015,7 +5982,7 @@
     </row>
     <row r="205" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O205" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P205" t="s">
         <v>8</v>
@@ -6029,7 +5996,7 @@
     </row>
     <row r="206" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O206" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P206" t="s">
         <v>8</v>
@@ -6043,7 +6010,7 @@
     </row>
     <row r="207" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O207" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P207" t="s">
         <v>8</v>
@@ -6057,7 +6024,7 @@
     </row>
     <row r="208" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O208" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P208" t="s">
         <v>8</v>
@@ -6071,7 +6038,7 @@
     </row>
     <row r="209" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O209" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="P209" t="s">
         <v>8</v>
@@ -6085,7 +6052,7 @@
     </row>
     <row r="210" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O210" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P210" t="s">
         <v>8</v>
@@ -6099,7 +6066,7 @@
     </row>
     <row r="211" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O211" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P211" t="s">
         <v>8</v>
@@ -6113,7 +6080,7 @@
     </row>
     <row r="212" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O212" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="P212" t="s">
         <v>8</v>
@@ -6127,7 +6094,7 @@
     </row>
     <row r="213" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O213" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P213" t="s">
         <v>8</v>
@@ -6141,7 +6108,7 @@
     </row>
     <row r="214" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O214" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P214" t="s">
         <v>8</v>
@@ -6155,7 +6122,7 @@
     </row>
     <row r="215" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O215" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P215" t="s">
         <v>8</v>
@@ -6169,7 +6136,7 @@
     </row>
     <row r="216" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O216" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P216" t="s">
         <v>8</v>
@@ -6183,7 +6150,7 @@
     </row>
     <row r="217" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O217" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P217" t="s">
         <v>8</v>
@@ -6197,7 +6164,7 @@
     </row>
     <row r="218" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O218" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P218" t="s">
         <v>8</v>
@@ -6211,7 +6178,7 @@
     </row>
     <row r="219" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O219" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P219" t="s">
         <v>8</v>
@@ -6225,7 +6192,7 @@
     </row>
     <row r="220" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O220" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="P220" t="s">
         <v>8</v>
@@ -6239,7 +6206,7 @@
     </row>
     <row r="221" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O221" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P221" t="s">
         <v>8</v>
@@ -6253,7 +6220,7 @@
     </row>
     <row r="222" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O222" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P222" t="s">
         <v>8</v>
@@ -6267,7 +6234,7 @@
     </row>
     <row r="223" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O223" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="P223" t="s">
         <v>8</v>
@@ -6281,7 +6248,7 @@
     </row>
     <row r="224" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O224" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P224" t="s">
         <v>8</v>
@@ -6295,21 +6262,21 @@
     </row>
     <row r="225" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O225" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="P225" t="s">
         <v>8</v>
       </c>
       <c r="Q225">
-        <v>147.39311396207361</v>
+        <v>147.4317513167116</v>
       </c>
       <c r="R225">
-        <v>-42.094338889464559</v>
+        <v>-41.912687414816389</v>
       </c>
     </row>
     <row r="226" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O226" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P226" t="s">
         <v>8</v>
@@ -6323,7 +6290,7 @@
     </row>
     <row r="227" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O227" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P227" t="s">
         <v>8</v>
@@ -6337,7 +6304,7 @@
     </row>
     <row r="228" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O228" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P228" t="s">
         <v>8</v>
@@ -6351,7 +6318,7 @@
     </row>
     <row r="229" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O229" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="P229" t="s">
         <v>8</v>
@@ -6365,7 +6332,7 @@
     </row>
     <row r="230" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O230" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P230" t="s">
         <v>8</v>
@@ -6379,7 +6346,7 @@
     </row>
     <row r="231" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O231" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="P231" t="s">
         <v>8</v>
@@ -6393,7 +6360,7 @@
     </row>
     <row r="232" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O232" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P232" t="s">
         <v>8</v>
@@ -6407,7 +6374,7 @@
     </row>
     <row r="233" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O233" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P233" t="s">
         <v>8</v>
@@ -6421,7 +6388,7 @@
     </row>
     <row r="234" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O234" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P234" t="s">
         <v>8</v>
@@ -6435,7 +6402,7 @@
     </row>
     <row r="235" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O235" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P235" t="s">
         <v>8</v>
@@ -6449,7 +6416,7 @@
     </row>
     <row r="236" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O236" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P236" t="s">
         <v>8</v>
@@ -6463,7 +6430,7 @@
     </row>
     <row r="237" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O237" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P237" t="s">
         <v>8</v>
@@ -6477,7 +6444,7 @@
     </row>
     <row r="238" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O238" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P238" t="s">
         <v>8</v>
@@ -6491,7 +6458,7 @@
     </row>
     <row r="239" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O239" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P239" t="s">
         <v>8</v>
@@ -6505,7 +6472,7 @@
     </row>
     <row r="240" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O240" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P240" t="s">
         <v>8</v>
@@ -6519,7 +6486,7 @@
     </row>
     <row r="241" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O241" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P241" t="s">
         <v>8</v>
@@ -6533,7 +6500,7 @@
     </row>
     <row r="242" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O242" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="P242" t="s">
         <v>8</v>
@@ -6547,7 +6514,7 @@
     </row>
     <row r="243" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O243" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P243" t="s">
         <v>8</v>
@@ -6561,7 +6528,7 @@
     </row>
     <row r="244" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O244" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P244" t="s">
         <v>8</v>
@@ -6575,7 +6542,7 @@
     </row>
     <row r="245" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O245" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P245" t="s">
         <v>8</v>
@@ -6589,7 +6556,7 @@
     </row>
     <row r="246" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O246" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P246" t="s">
         <v>8</v>
@@ -6603,7 +6570,7 @@
     </row>
     <row r="247" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O247" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P247" t="s">
         <v>8</v>
@@ -6617,7 +6584,7 @@
     </row>
     <row r="248" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O248" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P248" t="s">
         <v>8</v>
@@ -6631,7 +6598,7 @@
     </row>
     <row r="249" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O249" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P249" t="s">
         <v>8</v>
@@ -6645,7 +6612,7 @@
     </row>
     <row r="250" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O250" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P250" t="s">
         <v>8</v>
@@ -6659,7 +6626,7 @@
     </row>
     <row r="251" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O251" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="P251" t="s">
         <v>8</v>
@@ -6673,7 +6640,7 @@
     </row>
     <row r="252" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O252" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P252" t="s">
         <v>8</v>
@@ -6687,7 +6654,7 @@
     </row>
     <row r="253" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O253" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P253" t="s">
         <v>8</v>
@@ -6701,7 +6668,7 @@
     </row>
     <row r="254" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O254" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P254" t="s">
         <v>8</v>
@@ -6715,7 +6682,7 @@
     </row>
     <row r="255" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O255" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P255" t="s">
         <v>8</v>
@@ -6729,7 +6696,7 @@
     </row>
     <row r="256" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O256" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="P256" t="s">
         <v>8</v>
@@ -6743,7 +6710,7 @@
     </row>
     <row r="257" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O257" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P257" t="s">
         <v>8</v>
@@ -6757,7 +6724,7 @@
     </row>
     <row r="258" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O258" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P258" t="s">
         <v>8</v>
@@ -6771,7 +6738,7 @@
     </row>
     <row r="259" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O259" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P259" t="s">
         <v>8</v>
@@ -6785,7 +6752,7 @@
     </row>
     <row r="260" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O260" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P260" t="s">
         <v>8</v>
@@ -6799,7 +6766,7 @@
     </row>
     <row r="261" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O261" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P261" t="s">
         <v>8</v>
@@ -6813,7 +6780,7 @@
     </row>
     <row r="262" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O262" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P262" t="s">
         <v>8</v>
@@ -6827,7 +6794,7 @@
     </row>
     <row r="263" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O263" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="P263" t="s">
         <v>8</v>
@@ -6841,7 +6808,7 @@
     </row>
     <row r="264" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O264" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P264" t="s">
         <v>8</v>
@@ -6855,7 +6822,7 @@
     </row>
     <row r="265" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O265" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P265" t="s">
         <v>8</v>
@@ -6869,7 +6836,7 @@
     </row>
     <row r="266" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O266" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P266" t="s">
         <v>8</v>
@@ -6883,7 +6850,7 @@
     </row>
     <row r="267" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O267" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="P267" t="s">
         <v>8</v>
@@ -6897,7 +6864,7 @@
     </row>
     <row r="268" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O268" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P268" t="s">
         <v>8</v>
@@ -6911,7 +6878,7 @@
     </row>
     <row r="269" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O269" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P269" t="s">
         <v>8</v>
@@ -6925,7 +6892,7 @@
     </row>
     <row r="270" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O270" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P270" t="s">
         <v>8</v>
@@ -6939,7 +6906,7 @@
     </row>
     <row r="271" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O271" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="P271" t="s">
         <v>8</v>
@@ -6953,7 +6920,7 @@
     </row>
     <row r="272" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O272" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P272" t="s">
         <v>8</v>
@@ -6967,7 +6934,7 @@
     </row>
     <row r="273" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O273" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P273" t="s">
         <v>8</v>
@@ -6981,7 +6948,7 @@
     </row>
     <row r="274" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O274" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P274" t="s">
         <v>8</v>
@@ -6995,7 +6962,7 @@
     </row>
     <row r="275" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O275" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P275" t="s">
         <v>8</v>
@@ -7009,7 +6976,7 @@
     </row>
     <row r="276" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O276" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P276" t="s">
         <v>8</v>
@@ -7023,7 +6990,7 @@
     </row>
     <row r="277" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O277" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P277" t="s">
         <v>8</v>
@@ -7037,7 +7004,7 @@
     </row>
     <row r="278" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O278" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P278" t="s">
         <v>8</v>
@@ -7051,7 +7018,7 @@
     </row>
     <row r="279" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O279" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P279" t="s">
         <v>8</v>
@@ -7065,7 +7032,7 @@
     </row>
     <row r="280" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O280" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P280" t="s">
         <v>8</v>
@@ -7079,7 +7046,7 @@
     </row>
     <row r="281" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O281" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P281" t="s">
         <v>8</v>
@@ -7093,7 +7060,7 @@
     </row>
     <row r="282" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O282" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P282" t="s">
         <v>8</v>
@@ -7107,7 +7074,7 @@
     </row>
     <row r="283" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O283" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P283" t="s">
         <v>8</v>
@@ -7121,7 +7088,7 @@
     </row>
     <row r="284" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O284" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P284" t="s">
         <v>8</v>
@@ -7135,7 +7102,7 @@
     </row>
     <row r="285" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O285" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="P285" t="s">
         <v>8</v>
@@ -7149,7 +7116,7 @@
     </row>
     <row r="286" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O286" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P286" t="s">
         <v>8</v>
@@ -7163,7 +7130,7 @@
     </row>
     <row r="287" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O287" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P287" t="s">
         <v>8</v>
@@ -7177,21 +7144,21 @@
     </row>
     <row r="288" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O288" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P288" t="s">
         <v>8</v>
       </c>
       <c r="Q288">
-        <v>146.97091687570963</v>
+        <v>147.23477366457425</v>
       </c>
       <c r="R288">
-        <v>-43.000695831545308</v>
+        <v>-42.735045094737728</v>
       </c>
     </row>
     <row r="289" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O289" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P289" t="s">
         <v>8</v>
@@ -7205,7 +7172,7 @@
     </row>
     <row r="290" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O290" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P290" t="s">
         <v>8</v>
@@ -7219,7 +7186,7 @@
     </row>
     <row r="291" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O291" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P291" t="s">
         <v>8</v>
@@ -7233,7 +7200,7 @@
     </row>
     <row r="292" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O292" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P292" t="s">
         <v>8</v>
@@ -7247,7 +7214,7 @@
     </row>
     <row r="293" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O293" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="P293" t="s">
         <v>8</v>
@@ -7261,7 +7228,7 @@
     </row>
     <row r="294" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O294" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P294" t="s">
         <v>8</v>
@@ -7275,7 +7242,7 @@
     </row>
     <row r="295" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O295" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P295" t="s">
         <v>8</v>
@@ -7289,7 +7256,7 @@
     </row>
     <row r="296" spans="15:18" x14ac:dyDescent="0.45">
       <c r="O296" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P296" t="s">
         <v>8</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6B03ABC-9128-4BE7-AA02-CBEE87E908D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14C7DC14-6377-45DA-B6CE-F1CE517B9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AFF512D8-FD25-4372-95E2-293C16BC124D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D415FEC-CA3D-4C17-9B43-A7C217D7D3B9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="637">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -74,19 +74,19 @@
     <t>e_Armidale_AUS</t>
   </si>
   <si>
-    <t>e_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>g_Armidale_AUS-Brisbane_AUS</t>
+    <t>e_BulliCreek_AUS</t>
+  </si>
+  <si>
+    <t>g_Armidale_AUS-BulliCreek_AUS</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_BulliCreek_AUS</t>
-  </si>
-  <si>
-    <t>g_Armidale_AUS-BulliCreek_AUS</t>
+    <t>e_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>g_Armidale_AUS-Ipswich_AUS</t>
   </si>
   <si>
     <t>e_Australind_AUS</t>
@@ -230,61 +230,61 @@
     <t>g_GinGin_AUS-Tarong_AUS</t>
   </si>
   <si>
-    <t>e_Hobart_AUS</t>
+    <t>e_Karratha_AUS</t>
+  </si>
+  <si>
+    <t>e_TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>g_Karratha_AUS-TomPriceMine_AUS</t>
+  </si>
+  <si>
+    <t>e_Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>g_Merredin_AUS-Kalgoorlie_AUS</t>
+  </si>
+  <si>
+    <t>e_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>e_Yandin_AUS</t>
+  </si>
+  <si>
+    <t>g_Morawa_AUS-Yandin_AUS</t>
+  </si>
+  <si>
+    <t>g_MountPiper_AUS-SydneyWest_AUS</t>
+  </si>
+  <si>
+    <t>e_Murray_AUS</t>
+  </si>
+  <si>
+    <t>g_Murray_AUS-SouthMorang_AUS</t>
+  </si>
+  <si>
+    <t>e_Nebo_AUS</t>
+  </si>
+  <si>
+    <t>g_Nebo_AUS-Bouldercombe_AUS</t>
+  </si>
+  <si>
+    <t>g_Nebo_AUS-Broadsound_AUS</t>
+  </si>
+  <si>
+    <t>e_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
   </si>
   <si>
     <t>e_Palmerston_AUS</t>
   </si>
   <si>
-    <t>g_Hobart_AUS-Palmerston_AUS</t>
-  </si>
-  <si>
-    <t>e_Karratha_AUS</t>
-  </si>
-  <si>
-    <t>e_TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>g_Karratha_AUS-TomPriceMine_AUS</t>
-  </si>
-  <si>
-    <t>e_Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>g_Merredin_AUS-Kalgoorlie_AUS</t>
-  </si>
-  <si>
-    <t>e_Morawa_AUS</t>
-  </si>
-  <si>
-    <t>e_Yandin_AUS</t>
-  </si>
-  <si>
-    <t>g_Morawa_AUS-Yandin_AUS</t>
-  </si>
-  <si>
-    <t>g_MountPiper_AUS-SydneyWest_AUS</t>
-  </si>
-  <si>
-    <t>e_Murray_AUS</t>
-  </si>
-  <si>
-    <t>g_Murray_AUS-SouthMorang_AUS</t>
-  </si>
-  <si>
-    <t>e_Nebo_AUS</t>
-  </si>
-  <si>
-    <t>g_Nebo_AUS-Bouldercombe_AUS</t>
-  </si>
-  <si>
-    <t>g_Nebo_AUS-Broadsound_AUS</t>
-  </si>
-  <si>
-    <t>e_OlympicDamWest_AUS</t>
-  </si>
-  <si>
-    <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
+    <t>e_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>g_Palmerston_AUS-Kingston_AUS</t>
   </si>
   <si>
     <t>e_Sheffield_AUS</t>
@@ -338,12 +338,12 @@
     <t>g_SydneyWest_AUS-CentralCoast_AUS</t>
   </si>
   <si>
-    <t>g_Tarong_AUS-Brisbane_AUS</t>
-  </si>
-  <si>
     <t>g_Tarong_AUS-BulliCreek_AUS</t>
   </si>
   <si>
+    <t>g_Tarong_AUS-Ipswich_AUS</t>
+  </si>
+  <si>
     <t>e_WandoanSouth_AUS</t>
   </si>
   <si>
@@ -383,12 +383,12 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -371.0 km- way/160201298-330;way/172587651-275 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
     <t>grid link -90.0 km- way/160201298-330;way/172887193-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -371.0 km- way/160201298-330;way/170832455-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -238.0 km- way/223939702-220;way/87853100-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -458,9 +458,6 @@
     <t>grid link -100.0 km- way/170709510-275;way/171728751-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>grid link -143.0 km- AU146-220;way/174441055-220 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
     <t>grid link -254.0 km- way/337655870-220;way/583492111-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -485,6 +482,9 @@
     <t>grid link -123.0 km- way/164764363-275;way/185835127-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -78.0 km- AU147-220;way/174441055-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -87.0 km- way/174441055-220;way/88191017-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -518,12 +518,12 @@
     <t>grid link -407.0 km- AU73-330;way/925410265-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>grid link -126.0 km- way/170709510-275;way/172587651-275 (thermal x 0.7 N-1)</t>
-  </si>
-  <si>
     <t>grid link -109.0 km- way/170709510-275;way/172887193-330 (thermal x 0.7 N-1)</t>
   </si>
   <si>
+    <t>grid link -126.0 km- way/170709510-275;way/170832455-275 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
     <t>grid link -41.0 km- way/170709510-275;way/550221344-275 (thermal x 0.7 N-1)</t>
   </si>
   <si>
@@ -560,453 +560,903 @@
     <t>lat</t>
   </si>
   <si>
+    <t>shape</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_001</t>
   </si>
   <si>
+    <t>POLYGON ((150.033862 -34.377801, 150.033862 -33.928141, 150.033862 -33.478481, 150.83494 -33.478481, 151.636018 -33.478481, 151.636018 -33.928141, 151.636018 -34.377801, 151.636018 -34.827461, 150.83494 -34.827461, 150.83494 -35.277121, 150.033862 -35.277121, 150.033862 -34.827461, 150.033862 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_002</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -36.626102, 144.426317 -36.176442, 144.426317 -35.726781, 145.227395 -35.726781, 145.227395 -36.176442, 146.028473 -36.176442, 146.028473 -36.626102, 146.028473 -37.075762, 146.028473 -37.525422, 145.227395 -37.525422, 145.227395 -37.975082, 144.426317 -37.975082, 144.426317 -37.525422, 144.426317 -37.075762, 144.426317 -36.626102))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_003</t>
   </si>
   <si>
+    <t>POLYGON ((114.786437 -34.377801, 114.786437 -33.928141, 114.786437 -33.478481, 115.587515 -33.478481, 115.587515 -33.02882, 115.587515 -32.57916, 116.388593 -32.57916, 117.189671 -32.57916, 117.990749 -32.57916, 117.990749 -33.02882, 117.990749 -33.478481, 118.791827 -33.478481, 118.791827 -33.928141, 118.791827 -34.377801, 119.592904 -34.377801, 119.592904 -34.827461, 118.791827 -34.827461, 118.791827 -35.277121, 117.990749 -35.277121, 117.189671 -35.277121, 116.388593 -35.277121, 116.388593 -34.827461, 115.587515 -34.827461, 115.587515 -34.377801, 114.786437 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_004</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((146.028473 -42.022024, 146.028473 -42.471684, 145.227395 -42.471684, 145.227395 -42.022024, 146.028473 -42.022024)), ((146.829551 -42.022024, 146.028473 -42.022024, 146.028473 -41.572364, 145.227395 -41.572364, 144.426317 -41.572364, 144.426317 -41.122704, 144.426317 -40.673043, 145.227395 -40.673043, 146.028473 -40.673043, 146.028473 -41.122704, 146.829551 -41.122704, 146.829551 -41.572364, 146.829551 -42.022024)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_005</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((144.426317 -39.773723, 143.625239 -39.773723, 143.625239 -39.324063, 144.426317 -39.324063, 144.426317 -39.773723)), ((143.625239 -38.874403, 143.625239 -38.424743, 142.824162 -38.424743, 142.824162 -37.975082, 142.824162 -37.525422, 142.824162 -37.075762, 143.625239 -37.075762, 143.625239 -36.626102, 143.625239 -36.176442, 144.426317 -36.176442, 144.426317 -36.626102, 144.426317 -37.075762, 144.426317 -37.525422, 144.426317 -37.975082, 144.426317 -38.424743, 144.426317 -38.874403, 143.625239 -38.874403)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_006</t>
   </si>
   <si>
+    <t>POLYGON ((150.83494 -25.384597, 150.033862 -25.384597, 150.033862 -24.934937, 149.232784 -24.934937, 149.232784 -24.485277, 149.232784 -24.035617, 150.033862 -24.035617, 150.83494 -24.035617, 150.83494 -24.485277, 150.83494 -24.934937, 150.83494 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_007</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -23.585957, 146.829551 -23.585957, 146.829551 -23.136296, 147.630629 -23.136296, 147.630629 -22.686636, 148.431706 -22.686636, 148.431706 -22.236976, 149.232784 -22.236976, 149.232784 -21.787316, 150.033862 -21.787316, 150.033862 -22.236976, 150.033862 -22.686636, 150.033862 -23.136296, 150.033862 -23.585957, 149.232784 -23.585957, 149.232784 -24.035617, 149.232784 -24.485277, 148.431706 -24.485277, 147.630629 -24.485277, 147.630629 -24.934937, 146.829551 -24.934937, 146.028473 -24.934937, 145.227395 -24.934937, 145.227395 -24.485277, 146.028473 -24.485277, 146.028473 -24.035617, 146.028473 -23.585957))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_008</t>
   </si>
   <si>
+    <t>POLYGON ((150.033862 -31.67984, 150.033862 -31.23018, 149.232784 -31.23018, 149.232784 -30.780519, 148.431706 -30.780519, 148.431706 -30.330859, 148.431706 -29.881199, 149.232784 -29.881199, 150.033862 -29.881199, 150.033862 -29.431539, 150.83494 -29.431539, 151.636018 -29.431539, 151.636018 -28.981879, 152.437096 -28.981879, 152.437096 -29.431539, 153.238173 -29.431539, 154.039251 -29.431539, 154.039251 -29.881199, 153.238173 -29.881199, 153.238173 -30.330859, 153.238173 -30.780519, 153.238173 -31.23018, 153.238173 -31.67984, 152.437096 -31.67984, 151.636018 -31.67984, 150.83494 -31.67984, 150.033862 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_009</t>
   </si>
   <si>
+    <t>POLYGON ((134.012305 -33.928141, 134.012305 -33.478481, 134.012305 -33.02882, 134.813383 -33.02882, 134.813383 -32.57916, 135.614461 -32.57916, 136.415539 -32.57916, 136.415539 -33.02882, 136.415539 -33.478481, 137.216617 -33.478481, 137.216617 -33.928141, 137.216617 -34.377801, 136.415539 -34.377801, 135.614461 -34.377801, 135.614461 -34.827461, 134.813383 -34.827461, 134.813383 -34.377801, 134.813383 -33.928141, 134.012305 -33.928141))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_010</t>
   </si>
   <si>
+    <t>POLYGON ((137.216617 -33.478481, 136.415539 -33.478481, 136.415539 -33.02882, 136.415539 -32.57916, 135.614461 -32.57916, 135.614461 -32.1295, 136.415539 -32.1295, 136.415539 -31.67984, 137.216617 -31.67984, 137.216617 -31.23018, 138.017695 -31.23018, 138.017695 -30.780519, 138.818772 -30.780519, 139.61985 -30.780519, 139.61985 -31.23018, 139.61985 -31.67984, 139.61985 -32.1295, 139.61985 -32.57916, 138.818772 -32.57916, 138.818772 -33.02882, 138.818772 -33.478481, 138.017695 -33.478481, 138.017695 -33.928141, 137.216617 -33.928141, 137.216617 -33.478481))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_011</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -33.928141, 138.017695 -33.928141, 138.017695 -33.478481, 138.818772 -33.478481, 138.818772 -33.02882, 138.818772 -32.57916, 139.61985 -32.57916, 140.420928 -32.57916, 140.420928 -33.02882, 140.420928 -33.478481, 141.222006 -33.478481, 141.222006 -33.928141, 141.222006 -34.377801, 141.222006 -34.827461, 141.222006 -35.277121, 140.420928 -35.277121, 140.420928 -34.827461, 139.61985 -34.827461, 139.61985 -34.377801, 138.818772 -34.377801, 138.818772 -33.928141))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_012</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -24.485277, 144.426317 -24.035617, 144.426317 -23.585957, 145.227395 -23.585957, 145.227395 -23.136296, 146.028473 -23.136296, 146.028473 -22.686636, 146.829551 -22.686636, 146.829551 -22.236976, 146.829551 -21.787316, 147.630629 -21.787316, 147.630629 -21.337656, 148.431706 -21.337656, 148.431706 -20.887995, 148.431706 -20.438335, 149.232784 -20.438335, 149.232784 -20.887995, 150.033862 -20.887995, 150.033862 -21.337656, 150.033862 -21.787316, 149.232784 -21.787316, 149.232784 -22.236976, 148.431706 -22.236976, 148.431706 -22.686636, 147.630629 -22.686636, 147.630629 -23.136296, 146.829551 -23.136296, 146.829551 -23.585957, 146.028473 -23.585957, 146.028473 -24.035617, 146.028473 -24.485277, 145.227395 -24.485277, 145.227395 -24.934937, 144.426317 -24.934937, 144.426317 -25.384597, 143.625239 -25.384597, 142.824162 -25.384597, 142.824162 -24.934937, 143.625239 -24.934937, 143.625239 -24.485277, 144.426317 -24.485277))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_013</t>
   </si>
   <si>
+    <t>POLYGON ((147.630629 -32.1295, 147.630629 -31.67984, 146.829551 -31.67984, 146.829551 -31.23018, 146.829551 -30.780519, 146.829551 -30.330859, 147.630629 -30.330859, 148.431706 -30.330859, 148.431706 -30.780519, 149.232784 -30.780519, 149.232784 -31.23018, 150.033862 -31.23018, 150.033862 -31.67984, 150.83494 -31.67984, 150.83494 -32.1295, 150.83494 -32.57916, 150.83494 -33.02882, 150.83494 -33.478481, 150.033862 -33.478481, 150.033862 -33.928141, 150.033862 -34.377801, 149.232784 -34.377801, 149.232784 -33.928141, 149.232784 -33.478481, 148.431706 -33.478481, 148.431706 -33.02882, 147.630629 -33.02882, 147.630629 -32.57916, 147.630629 -32.1295))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_014</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -33.478481, 146.028473 -33.02882, 145.227395 -33.02882, 144.426317 -33.02882, 144.426317 -32.57916, 144.426317 -32.1295, 144.426317 -31.67984, 144.426317 -31.23018, 145.227395 -31.23018, 145.227395 -30.780519, 145.227395 -30.330859, 145.227395 -29.881199, 146.028473 -29.881199, 146.829551 -29.881199, 146.829551 -30.330859, 146.829551 -30.780519, 146.829551 -31.23018, 146.829551 -31.67984, 147.630629 -31.67984, 147.630629 -32.1295, 147.630629 -32.57916, 147.630629 -33.02882, 147.630629 -33.478481, 146.829551 -33.478481, 146.028473 -33.478481))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_015</t>
   </si>
   <si>
+    <t>POLYGON ((145.227395 -35.726781, 144.426317 -35.726781, 144.426317 -35.277121, 144.426317 -34.827461, 144.426317 -34.377801, 144.426317 -33.928141, 144.426317 -33.478481, 144.426317 -33.02882, 145.227395 -33.02882, 146.028473 -33.02882, 146.028473 -33.478481, 146.829551 -33.478481, 146.829551 -33.928141, 146.829551 -34.377801, 146.829551 -34.827461, 146.829551 -35.277121, 146.829551 -35.726781, 146.028473 -35.726781, 146.028473 -36.176442, 145.227395 -36.176442, 145.227395 -35.726781))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_016</t>
   </si>
   <si>
+    <t>POLYGON ((142.023084 -34.827461, 141.222006 -34.827461, 141.222006 -34.377801, 141.222006 -33.928141, 142.023084 -33.928141, 142.023084 -33.478481, 142.824162 -33.478481, 142.824162 -33.02882, 143.625239 -33.02882, 143.625239 -32.57916, 143.625239 -32.1295, 144.426317 -32.1295, 144.426317 -32.57916, 144.426317 -33.02882, 144.426317 -33.478481, 144.426317 -33.928141, 144.426317 -34.377801, 144.426317 -34.827461, 144.426317 -35.277121, 144.426317 -35.726781, 144.426317 -36.176442, 143.625239 -36.176442, 142.824162 -36.176442, 142.824162 -35.726781, 142.824162 -35.277121, 142.023084 -35.277121, 142.023084 -34.827461))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_017</t>
   </si>
   <si>
+    <t>POLYGON ((151.636018 -27.632898, 151.636018 -27.183238, 150.83494 -27.183238, 150.83494 -26.733578, 150.83494 -26.283918, 150.83494 -25.834257, 151.636018 -25.834257, 152.437096 -25.834257, 153.238173 -25.834257, 153.238173 -26.283918, 153.238173 -26.733578, 152.437096 -26.733578, 152.437096 -27.183238, 152.437096 -27.632898, 151.636018 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_018</t>
   </si>
   <si>
+    <t>POLYGON ((151.636018 -28.532219, 151.636018 -28.082558, 151.636018 -27.632898, 152.437096 -27.632898, 152.437096 -27.183238, 152.437096 -26.733578, 153.238173 -26.733578, 154.039251 -26.733578, 154.039251 -27.183238, 154.039251 -27.632898, 154.039251 -28.082558, 154.039251 -28.532219, 154.039251 -28.981879, 154.039251 -29.431539, 153.238173 -29.431539, 152.437096 -29.431539, 152.437096 -28.981879, 151.636018 -28.981879, 151.636018 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_019</t>
   </si>
   <si>
+    <t>POLYGON ((150.033862 -23.585957, 150.033862 -23.136296, 150.033862 -22.686636, 150.033862 -22.236976, 150.83494 -22.236976, 150.83494 -22.686636, 150.83494 -23.136296, 150.83494 -23.585957, 150.83494 -24.035617, 150.033862 -24.035617, 149.232784 -24.035617, 149.232784 -23.585957, 150.033862 -23.585957))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_020</t>
   </si>
   <si>
+    <t>POLYGON ((150.83494 -24.485277, 151.636018 -24.485277, 151.636018 -24.035617, 152.437096 -24.035617, 152.437096 -24.485277, 153.238173 -24.485277, 154.039251 -24.485277, 154.039251 -24.934937, 154.039251 -25.384597, 153.238173 -25.384597, 153.238173 -25.834257, 152.437096 -25.834257, 151.636018 -25.834257, 150.83494 -25.834257, 150.83494 -25.384597, 150.83494 -24.934937, 150.83494 -24.485277))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_021</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -22.236976, 145.227395 -22.236976, 145.227395 -21.787316, 145.227395 -21.337656, 145.227395 -20.887995, 145.227395 -20.438335, 145.227395 -19.988675, 146.028473 -19.988675, 146.028473 -19.539015, 146.829551 -19.539015, 146.829551 -19.089355, 147.630629 -19.089355, 147.630629 -19.539015, 148.431706 -19.539015, 148.431706 -19.988675, 149.232784 -19.988675, 149.232784 -20.438335, 148.431706 -20.438335, 148.431706 -20.887995, 148.431706 -21.337656, 147.630629 -21.337656, 147.630629 -21.787316, 146.829551 -21.787316, 146.829551 -22.236976, 146.829551 -22.686636, 146.028473 -22.686636, 146.028473 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_022</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -24.035617, 141.222006 -23.585957, 141.222006 -23.136296, 142.023084 -23.136296, 142.023084 -22.686636, 142.824162 -22.686636, 142.824162 -23.136296, 143.625239 -23.136296, 144.426317 -23.136296, 144.426317 -23.585957, 144.426317 -24.035617, 144.426317 -24.485277, 143.625239 -24.485277, 143.625239 -24.934937, 142.824162 -24.934937, 142.023084 -24.934937, 142.023084 -24.485277, 141.222006 -24.485277, 141.222006 -24.035617))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_023</t>
   </si>
   <si>
+    <t>POLYGON ((145.227395 -23.585957, 144.426317 -23.585957, 144.426317 -23.136296, 143.625239 -23.136296, 142.824162 -23.136296, 142.824162 -22.686636, 142.824162 -22.236976, 142.824162 -21.787316, 143.625239 -21.787316, 143.625239 -21.337656, 144.426317 -21.337656, 144.426317 -20.887995, 145.227395 -20.887995, 145.227395 -21.337656, 145.227395 -21.787316, 145.227395 -22.236976, 146.028473 -22.236976, 146.028473 -22.686636, 146.028473 -23.136296, 145.227395 -23.136296, 145.227395 -23.585957))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_024</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -35.726781, 146.829551 -35.277121, 146.829551 -34.827461, 146.829551 -34.377801, 146.829551 -33.928141, 146.829551 -33.478481, 147.630629 -33.478481, 147.630629 -33.928141, 147.630629 -34.377801, 148.431706 -34.377801, 148.431706 -34.827461, 148.431706 -35.277121, 147.630629 -35.277121, 147.630629 -35.726781, 147.630629 -36.176442, 146.829551 -36.176442, 146.829551 -36.626102, 146.028473 -36.626102, 146.028473 -36.176442, 146.028473 -35.726781, 146.829551 -35.726781))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_025</t>
   </si>
   <si>
+    <t>POLYGON ((136.415539 -35.726781, 136.415539 -35.277121, 135.614461 -35.277121, 135.614461 -34.827461, 135.614461 -34.377801, 136.415539 -34.377801, 136.415539 -34.827461, 137.216617 -34.827461, 137.216617 -34.377801, 137.216617 -33.928141, 138.017695 -33.928141, 138.818772 -33.928141, 138.818772 -34.377801, 139.61985 -34.377801, 139.61985 -34.827461, 140.420928 -34.827461, 140.420928 -35.277121, 140.420928 -35.726781, 140.420928 -36.176442, 140.420928 -36.626102, 139.61985 -36.626102, 139.61985 -36.176442, 138.818772 -36.176442, 138.017695 -36.176442, 137.216617 -36.176442, 136.415539 -36.176442, 136.415539 -35.726781))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_026</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -30.330859, 146.829551 -29.881199, 146.028473 -29.881199, 146.028473 -29.431539, 146.829551 -29.431539, 146.829551 -28.981879, 147.630629 -28.981879, 147.630629 -28.532219, 148.431706 -28.532219, 148.431706 -28.082558, 149.232784 -28.082558, 149.232784 -27.632898, 150.033862 -27.632898, 150.033862 -27.183238, 150.83494 -27.183238, 151.636018 -27.183238, 151.636018 -27.632898, 151.636018 -28.082558, 151.636018 -28.532219, 151.636018 -28.981879, 151.636018 -29.431539, 150.83494 -29.431539, 150.033862 -29.431539, 150.033862 -29.881199, 149.232784 -29.881199, 148.431706 -29.881199, 148.431706 -30.330859, 147.630629 -30.330859, 146.829551 -30.330859))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_027</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((146.829551 -41.572364, 146.829551 -41.122704, 146.829551 -40.673043, 147.630629 -40.673043, 148.431706 -40.673043, 148.431706 -41.122704, 148.431706 -41.572364, 148.431706 -42.022024, 147.630629 -42.022024, 147.630629 -42.471684, 146.829551 -42.471684, 146.028473 -42.471684, 146.028473 -42.022024, 146.829551 -42.022024, 146.829551 -41.572364)), ((147.630629 -40.223383, 147.630629 -39.773723, 148.431706 -39.773723, 148.431706 -40.223383, 147.630629 -40.223383)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_028</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -37.075762, 146.829551 -36.626102, 146.829551 -36.176442, 147.630629 -36.176442, 147.630629 -35.726781, 148.431706 -35.726781, 148.431706 -36.176442, 148.431706 -36.626102, 149.232784 -36.626102, 149.232784 -37.075762, 150.033862 -37.075762, 150.033862 -37.525422, 150.033862 -37.975082, 149.232784 -37.975082, 148.431706 -37.975082, 147.630629 -37.975082, 147.630629 -37.525422, 147.630629 -37.075762, 146.829551 -37.075762))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_029</t>
   </si>
   <si>
+    <t>POLYGON ((131.609072 -26.283918, 130.807994 -26.283918, 130.006916 -26.283918, 129.205838 -26.283918, 129.205838 -25.834257, 129.205838 -25.384597, 129.205838 -24.934937, 129.205838 -24.485277, 129.205838 -24.035617, 130.006916 -24.035617, 130.807994 -24.035617, 130.807994 -24.485277, 131.609072 -24.485277, 132.41015 -24.485277, 133.211228 -24.485277, 133.211228 -24.934937, 134.012305 -24.934937, 134.012305 -25.384597, 134.813383 -25.384597, 134.813383 -25.834257, 134.813383 -26.283918, 134.813383 -26.733578, 134.012305 -26.733578, 133.211228 -26.733578, 132.41015 -26.733578, 131.609072 -26.733578, 131.609072 -26.283918))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_030</t>
   </si>
   <si>
+    <t>POLYGON ((132.41015 -28.082558, 132.41015 -27.632898, 131.609072 -27.632898, 131.609072 -27.183238, 131.609072 -26.733578, 132.41015 -26.733578, 133.211228 -26.733578, 134.012305 -26.733578, 134.012305 -27.183238, 134.012305 -27.632898, 134.813383 -27.632898, 134.813383 -28.082558, 135.614461 -28.082558, 135.614461 -28.532219, 135.614461 -28.981879, 134.813383 -28.981879, 134.813383 -29.431539, 134.012305 -29.431539, 133.211228 -29.431539, 133.211228 -28.981879, 133.211228 -28.532219, 133.211228 -28.082558, 132.41015 -28.082558))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_031</t>
   </si>
   <si>
+    <t>POLYGON ((130.006916 -28.082558, 129.205838 -28.082558, 129.205838 -27.632898, 129.205838 -27.183238, 129.205838 -26.733578, 129.205838 -26.283918, 130.006916 -26.283918, 130.807994 -26.283918, 131.609072 -26.283918, 131.609072 -26.733578, 131.609072 -27.183238, 131.609072 -27.632898, 132.41015 -27.632898, 132.41015 -28.082558, 133.211228 -28.082558, 133.211228 -28.532219, 133.211228 -28.981879, 133.211228 -29.431539, 133.211228 -29.881199, 132.41015 -29.881199, 132.41015 -29.431539, 131.609072 -29.431539, 130.807994 -29.431539, 130.807994 -28.981879, 130.807994 -28.532219, 130.006916 -28.532219, 130.006916 -28.082558))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_032</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -30.330859, 129.205838 -29.881199, 130.006916 -29.881199, 130.807994 -29.881199, 130.807994 -30.330859, 130.807994 -30.780519, 131.609072 -30.780519, 131.609072 -31.23018, 132.41015 -31.23018, 132.41015 -31.67984, 132.41015 -32.1295, 131.609072 -32.1295, 131.609072 -31.67984, 130.807994 -31.67984, 130.006916 -31.67984, 129.205838 -31.67984, 129.205838 -31.23018, 129.205838 -30.780519, 129.205838 -30.330859))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_033</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -28.532219, 129.205838 -28.082558, 130.006916 -28.082558, 130.006916 -28.532219, 130.807994 -28.532219, 130.807994 -28.981879, 130.807994 -29.431539, 131.609072 -29.431539, 132.41015 -29.431539, 132.41015 -29.881199, 132.41015 -30.330859, 132.41015 -30.780519, 132.41015 -31.23018, 131.609072 -31.23018, 131.609072 -30.780519, 130.807994 -30.780519, 130.807994 -30.330859, 130.807994 -29.881199, 130.006916 -29.881199, 129.205838 -29.881199, 129.205838 -29.431539, 129.205838 -28.981879, 129.205838 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_034</t>
   </si>
   <si>
+    <t>POLYGON ((132.41015 -31.67984, 132.41015 -31.23018, 132.41015 -30.780519, 133.211228 -30.780519, 133.211228 -31.23018, 134.012305 -31.23018, 134.813383 -31.23018, 134.813383 -31.67984, 135.614461 -31.67984, 135.614461 -32.1295, 135.614461 -32.57916, 134.813383 -32.57916, 134.813383 -33.02882, 134.012305 -33.02882, 134.012305 -32.57916, 133.211228 -32.57916, 133.211228 -32.1295, 132.41015 -32.1295, 132.41015 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_035</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -29.881199, 134.813383 -29.431539, 134.813383 -28.981879, 135.614461 -28.981879, 136.415539 -28.981879, 136.415539 -29.431539, 137.216617 -29.431539, 137.216617 -29.881199, 137.216617 -30.330859, 138.017695 -30.330859, 138.017695 -30.780519, 138.017695 -31.23018, 137.216617 -31.23018, 136.415539 -31.23018, 136.415539 -30.780519, 135.614461 -30.780519, 135.614461 -30.330859, 135.614461 -29.881199, 134.813383 -29.881199))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_036</t>
   </si>
   <si>
+    <t>POLYGON ((134.012305 -31.23018, 133.211228 -31.23018, 133.211228 -30.780519, 132.41015 -30.780519, 132.41015 -30.330859, 132.41015 -29.881199, 133.211228 -29.881199, 133.211228 -29.431539, 134.012305 -29.431539, 134.813383 -29.431539, 134.813383 -29.881199, 135.614461 -29.881199, 135.614461 -30.330859, 135.614461 -30.780519, 136.415539 -30.780519, 136.415539 -31.23018, 137.216617 -31.23018, 137.216617 -31.67984, 136.415539 -31.67984, 136.415539 -32.1295, 135.614461 -32.1295, 135.614461 -31.67984, 134.813383 -31.67984, 134.813383 -31.23018, 134.012305 -31.23018))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_037</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -28.532219, 138.818772 -28.082558, 138.818772 -27.632898, 138.017695 -27.632898, 137.216617 -27.632898, 137.216617 -27.183238, 137.216617 -26.733578, 137.216617 -26.283918, 137.216617 -25.834257, 137.216617 -25.384597, 138.017695 -25.384597, 138.818772 -25.384597, 138.818772 -25.834257, 139.61985 -25.834257, 139.61985 -26.283918, 140.420928 -26.283918, 140.420928 -26.733578, 140.420928 -27.183238, 140.420928 -27.632898, 140.420928 -28.082558, 140.420928 -28.532219, 139.61985 -28.532219, 138.818772 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_038</t>
   </si>
   <si>
+    <t>POLYGON ((137.216617 -29.881199, 137.216617 -29.431539, 136.415539 -29.431539, 136.415539 -28.981879, 135.614461 -28.981879, 135.614461 -28.532219, 135.614461 -28.082558, 134.813383 -28.082558, 134.813383 -27.632898, 134.012305 -27.632898, 134.012305 -27.183238, 134.012305 -26.733578, 134.813383 -26.733578, 134.813383 -26.283918, 135.614461 -26.283918, 135.614461 -26.733578, 136.415539 -26.733578, 137.216617 -26.733578, 137.216617 -27.183238, 137.216617 -27.632898, 138.017695 -27.632898, 138.818772 -27.632898, 138.818772 -28.082558, 138.818772 -28.532219, 139.61985 -28.532219, 139.61985 -28.981879, 139.61985 -29.431539, 139.61985 -29.881199, 139.61985 -30.330859, 139.61985 -30.780519, 138.818772 -30.780519, 138.017695 -30.780519, 138.017695 -30.330859, 137.216617 -30.330859, 137.216617 -29.881199))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_039</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -24.035617, 138.017695 -24.035617, 138.017695 -23.585957, 137.216617 -23.585957, 137.216617 -23.136296, 137.216617 -22.686636, 137.216617 -22.236976, 138.017695 -22.236976, 138.818772 -22.236976, 138.818772 -22.686636, 139.61985 -22.686636, 139.61985 -23.136296, 140.420928 -23.136296, 140.420928 -23.585957, 140.420928 -24.035617, 141.222006 -24.035617, 141.222006 -24.485277, 141.222006 -24.934937, 141.222006 -25.384597, 141.222006 -25.834257, 141.222006 -26.283918, 140.420928 -26.283918, 139.61985 -26.283918, 139.61985 -25.834257, 138.818772 -25.834257, 138.818772 -25.384597, 138.818772 -24.934937, 138.818772 -24.485277, 138.818772 -24.035617))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_040</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -25.834257, 134.813383 -25.384597, 134.012305 -25.384597, 134.012305 -24.934937, 133.211228 -24.934937, 133.211228 -24.485277, 133.211228 -24.035617, 133.211228 -23.585957, 133.211228 -23.136296, 133.211228 -22.686636, 133.211228 -22.236976, 133.211228 -21.787316, 134.012305 -21.787316, 134.012305 -22.236976, 134.813383 -22.236976, 135.614461 -22.236976, 135.614461 -22.686636, 136.415539 -22.686636, 136.415539 -23.136296, 137.216617 -23.136296, 137.216617 -23.585957, 138.017695 -23.585957, 138.017695 -24.035617, 138.818772 -24.035617, 138.818772 -24.485277, 138.818772 -24.934937, 138.818772 -25.384597, 138.017695 -25.384597, 137.216617 -25.384597, 137.216617 -25.834257, 137.216617 -26.283918, 137.216617 -26.733578, 136.415539 -26.733578, 135.614461 -26.733578, 135.614461 -26.283918, 134.813383 -26.283918, 134.813383 -25.834257))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_041</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -22.236976, 134.012305 -22.236976, 134.012305 -21.787316, 133.211228 -21.787316, 133.211228 -21.337656, 133.211228 -20.887995, 134.012305 -20.887995, 134.813383 -20.887995, 135.614461 -20.887995, 135.614461 -21.337656, 136.415539 -21.337656, 137.216617 -21.337656, 137.216617 -21.787316, 138.017695 -21.787316, 138.017695 -22.236976, 137.216617 -22.236976, 137.216617 -22.686636, 137.216617 -23.136296, 136.415539 -23.136296, 136.415539 -22.686636, 135.614461 -22.686636, 135.614461 -22.236976, 134.813383 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_042</t>
   </si>
   <si>
+    <t>POLYGON ((130.807994 -20.438335, 130.807994 -19.988675, 130.807994 -19.539015, 130.807994 -19.089355, 131.609072 -19.089355, 131.609072 -18.639695, 131.609072 -18.190034, 131.609072 -17.740374, 132.41015 -17.740374, 132.41015 -18.190034, 133.211228 -18.190034, 133.211228 -18.639695, 133.211228 -19.089355, 134.012305 -19.089355, 134.012305 -19.539015, 134.813383 -19.539015, 134.813383 -19.988675, 135.614461 -19.988675, 135.614461 -20.438335, 136.415539 -20.438335, 136.415539 -20.887995, 136.415539 -21.337656, 135.614461 -21.337656, 135.614461 -20.887995, 134.813383 -20.887995, 134.012305 -20.887995, 133.211228 -20.887995, 133.211228 -21.337656, 132.41015 -21.337656, 132.41015 -20.887995, 131.609072 -20.887995, 131.609072 -20.438335, 130.807994 -20.438335))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_043</t>
   </si>
   <si>
+    <t>POLYGON ((130.006916 -20.887995, 130.006916 -20.438335, 130.807994 -20.438335, 131.609072 -20.438335, 131.609072 -20.887995, 132.41015 -20.887995, 132.41015 -21.337656, 133.211228 -21.337656, 133.211228 -21.787316, 133.211228 -22.236976, 132.41015 -22.236976, 131.609072 -22.236976, 130.807994 -22.236976, 130.006916 -22.236976, 130.006916 -21.787316, 130.006916 -21.337656, 130.006916 -20.887995))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_044</t>
   </si>
   <si>
+    <t>POLYGON ((130.807994 -24.035617, 130.006916 -24.035617, 129.205838 -24.035617, 129.205838 -23.585957, 129.205838 -23.136296, 129.205838 -22.686636, 129.205838 -22.236976, 130.006916 -22.236976, 130.807994 -22.236976, 131.609072 -22.236976, 132.41015 -22.236976, 133.211228 -22.236976, 133.211228 -22.686636, 133.211228 -23.136296, 133.211228 -23.585957, 133.211228 -24.035617, 133.211228 -24.485277, 132.41015 -24.485277, 131.609072 -24.485277, 130.807994 -24.485277, 130.807994 -24.035617))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_045</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -19.988675, 144.426317 -19.539015, 144.426317 -19.089355, 144.426317 -18.639695, 144.426317 -18.190034, 144.426317 -17.740374, 145.227395 -17.740374, 145.227395 -17.290714, 145.227395 -16.841054, 146.028473 -16.841054, 146.028473 -17.290714, 146.829551 -17.290714, 146.829551 -17.740374, 146.829551 -18.190034, 146.829551 -18.639695, 146.829551 -19.089355, 146.829551 -19.539015, 146.028473 -19.539015, 146.028473 -19.988675, 145.227395 -19.988675, 144.426317 -19.988675))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_046</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((141.222006 -15.492073, 141.222006 -15.042413, 141.222006 -14.592753, 141.222006 -14.143093, 141.222006 -13.693433, 141.222006 -13.243772, 141.222006 -12.794112, 141.222006 -12.344452, 142.023084 -12.344452, 142.023084 -11.894792, 142.023084 -11.445132, 142.023084 -10.995471, 142.023084 -10.545811, 142.023084 -10.096151, 142.824162 -10.096151, 142.824162 -10.545811, 142.824162 -10.995471, 142.824162 -11.445132, 142.824162 -11.894792, 143.625239 -11.894792, 143.625239 -12.344452, 143.625239 -12.794112, 143.625239 -13.243772, 143.625239 -13.693433, 143.625239 -14.143093, 144.426317 -14.143093, 145.227395 -14.143093, 145.227395 -14.592753, 146.028473 -14.592753, 146.028473 -15.042413, 146.028473 -15.492073, 146.028473 -15.941733, 146.028473 -16.391394, 146.028473 -16.841054, 145.227395 -16.841054, 145.227395 -17.290714, 145.227395 -17.740374, 144.426317 -17.740374, 144.426317 -18.190034, 143.625239 -18.190034, 143.625239 -17.740374, 142.824162 -17.740374, 142.824162 -17.290714, 142.023084 -17.290714, 142.023084 -16.841054, 142.023084 -16.391394, 141.222006 -16.391394, 141.222006 -15.941733, 141.222006 -15.492073), (142.023084 -14.592753, 142.824162 -14.592753, 142.824162 -14.143093, 142.023084 -14.143093, 142.023084 -14.592753), (144.426317 -15.941733, 144.426317 -16.391394, 145.227395 -16.391394, 145.227395 -15.941733, 144.426317 -15.941733)), ((141.222006 -16.391394, 141.222006 -16.841054, 140.420928 -16.841054, 140.420928 -16.391394, 141.222006 -16.391394)), ((134.813383 -11.445132, 134.813383 -11.894792, 134.012305 -11.894792, 134.012305 -11.445132, 134.813383 -11.445132)), ((142.023084 -9.196831, 142.824162 -9.196831, 142.824162 -9.646491, 142.023084 -9.646491, 141.222006 -9.646491, 141.222006 -9.196831, 142.023084 -9.196831)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_047</t>
   </si>
   <si>
+    <t>POLYGON ((131.609072 -16.391394, 131.609072 -15.941733, 131.609072 -15.492073, 131.609072 -15.042413, 131.609072 -14.592753, 131.609072 -14.143093, 131.609072 -13.693433, 131.609072 -13.243772, 131.609072 -12.794112, 131.609072 -12.344452, 131.609072 -11.894792, 132.41015 -11.894792, 132.41015 -11.445132, 132.41015 -10.995471, 133.211228 -10.995471, 133.211228 -11.445132, 134.012305 -11.445132, 134.012305 -11.894792, 134.813383 -11.894792, 135.614461 -11.894792, 135.614461 -11.445132, 136.415539 -11.445132, 136.415539 -10.995471, 137.216617 -10.995471, 137.216617 -11.445132, 137.216617 -11.894792, 137.216617 -12.344452, 137.216617 -12.794112, 137.216617 -13.243772, 136.415539 -13.243772, 136.415539 -13.693433, 137.216617 -13.693433, 137.216617 -14.143093, 137.216617 -14.592753, 136.415539 -14.592753, 135.614461 -14.592753, 135.614461 -15.042413, 136.415539 -15.042413, 136.415539 -15.492073, 135.614461 -15.492073, 134.813383 -15.492073, 134.813383 -15.941733, 134.813383 -16.391394, 134.813383 -16.841054, 135.614461 -16.841054, 135.614461 -17.290714, 135.614461 -17.740374, 134.813383 -17.740374, 134.012305 -17.740374, 133.211228 -17.740374, 133.211228 -17.290714, 132.41015 -17.290714, 131.609072 -17.290714, 131.609072 -16.841054, 131.609072 -16.391394))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_048</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -22.686636, 138.818772 -22.236976, 139.61985 -22.236976, 139.61985 -21.787316, 139.61985 -21.337656, 138.818772 -21.337656, 138.818772 -20.887995, 138.818772 -20.438335, 138.818772 -19.988675, 139.61985 -19.988675, 139.61985 -20.438335, 140.420928 -20.438335, 141.222006 -20.438335, 141.222006 -19.988675, 141.222006 -19.539015, 142.023084 -19.539015, 142.023084 -19.089355, 142.023084 -18.639695, 141.222006 -18.639695, 141.222006 -18.190034, 141.222006 -17.740374, 141.222006 -17.290714, 141.222006 -16.841054, 141.222006 -16.391394, 142.023084 -16.391394, 142.023084 -16.841054, 142.023084 -17.290714, 142.824162 -17.290714, 142.824162 -17.740374, 143.625239 -17.740374, 143.625239 -18.190034, 144.426317 -18.190034, 144.426317 -18.639695, 144.426317 -19.089355, 144.426317 -19.539015, 144.426317 -19.988675, 145.227395 -19.988675, 145.227395 -20.438335, 145.227395 -20.887995, 144.426317 -20.887995, 144.426317 -21.337656, 143.625239 -21.337656, 143.625239 -21.787316, 142.824162 -21.787316, 142.824162 -22.236976, 142.824162 -22.686636, 142.023084 -22.686636, 142.023084 -23.136296, 141.222006 -23.136296, 141.222006 -23.585957, 141.222006 -24.035617, 140.420928 -24.035617, 140.420928 -23.585957, 140.420928 -23.136296, 139.61985 -23.136296, 139.61985 -22.686636, 138.818772 -22.686636))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_049</t>
   </si>
   <si>
+    <t>POLYGON ((134.012305 -19.539015, 134.012305 -19.089355, 133.211228 -19.089355, 133.211228 -18.639695, 133.211228 -18.190034, 132.41015 -18.190034, 132.41015 -17.740374, 131.609072 -17.740374, 131.609072 -17.290714, 132.41015 -17.290714, 133.211228 -17.290714, 133.211228 -17.740374, 134.012305 -17.740374, 134.813383 -17.740374, 135.614461 -17.740374, 135.614461 -18.190034, 136.415539 -18.190034, 136.415539 -18.639695, 137.216617 -18.639695, 137.216617 -19.089355, 138.017695 -19.089355, 138.818772 -19.089355, 138.818772 -19.539015, 138.818772 -19.988675, 138.818772 -20.438335, 138.818772 -20.887995, 138.818772 -21.337656, 139.61985 -21.337656, 139.61985 -21.787316, 139.61985 -22.236976, 138.818772 -22.236976, 138.017695 -22.236976, 138.017695 -21.787316, 137.216617 -21.787316, 137.216617 -21.337656, 136.415539 -21.337656, 136.415539 -20.887995, 136.415539 -20.438335, 135.614461 -20.438335, 135.614461 -19.988675, 134.813383 -19.988675, 134.813383 -19.539015, 134.012305 -19.539015))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_050</t>
   </si>
   <si>
+    <t>POLYGON ((135.614461 -17.740374, 135.614461 -17.290714, 135.614461 -16.841054, 134.813383 -16.841054, 134.813383 -16.391394, 134.813383 -15.941733, 134.813383 -15.492073, 135.614461 -15.492073, 136.415539 -15.492073, 137.216617 -15.492073, 137.216617 -15.941733, 138.017695 -15.941733, 138.017695 -16.391394, 138.818772 -16.391394, 138.818772 -16.841054, 139.61985 -16.841054, 139.61985 -17.290714, 140.420928 -17.290714, 140.420928 -16.841054, 141.222006 -16.841054, 141.222006 -17.290714, 141.222006 -17.740374, 141.222006 -18.190034, 141.222006 -18.639695, 142.023084 -18.639695, 142.023084 -19.089355, 142.023084 -19.539015, 141.222006 -19.539015, 141.222006 -19.988675, 141.222006 -20.438335, 140.420928 -20.438335, 139.61985 -20.438335, 139.61985 -19.988675, 138.818772 -19.988675, 138.818772 -19.539015, 138.818772 -19.089355, 138.017695 -19.089355, 137.216617 -19.089355, 137.216617 -18.639695, 136.415539 -18.639695, 136.415539 -18.190034, 135.614461 -18.190034, 135.614461 -17.740374))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_051</t>
   </si>
   <si>
+    <t>POLYGON ((149.232784 -37.075762, 149.232784 -36.626102, 148.431706 -36.626102, 148.431706 -36.176442, 148.431706 -35.726781, 147.630629 -35.726781, 147.630629 -35.277121, 148.431706 -35.277121, 149.232784 -35.277121, 149.232784 -35.726781, 150.033862 -35.726781, 150.033862 -36.176442, 150.83494 -36.176442, 150.83494 -36.626102, 150.033862 -36.626102, 150.033862 -37.075762, 149.232784 -37.075762))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_052</t>
   </si>
   <si>
+    <t>POLYGON ((118.791827 -34.377801, 118.791827 -33.928141, 118.791827 -33.478481, 117.990749 -33.478481, 117.990749 -33.02882, 117.990749 -32.57916, 117.189671 -32.57916, 117.189671 -32.1295, 117.189671 -31.67984, 117.189671 -31.23018, 117.189671 -30.780519, 117.189671 -30.330859, 117.990749 -30.330859, 117.990749 -29.881199, 118.791827 -29.881199, 118.791827 -29.431539, 119.592904 -29.431539, 119.592904 -29.881199, 119.592904 -30.330859, 119.592904 -30.780519, 119.592904 -31.23018, 119.592904 -31.67984, 120.393982 -31.67984, 120.393982 -32.1295, 120.393982 -32.57916, 120.393982 -33.02882, 120.393982 -33.478481, 120.393982 -33.928141, 120.393982 -34.377801, 119.592904 -34.377801, 118.791827 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_053</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((144.426317 -39.773723, 144.426317 -40.223383, 143.625239 -40.223383, 143.625239 -39.773723, 144.426317 -39.773723)), ((146.028473 -38.874403, 145.227395 -38.874403, 144.426317 -38.874403, 144.426317 -38.424743, 144.426317 -37.975082, 145.227395 -37.975082, 145.227395 -37.525422, 146.028473 -37.525422, 146.028473 -37.975082, 146.028473 -38.424743, 146.028473 -38.874403)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_054</t>
   </si>
   <si>
+    <t>POLYGON ((143.625239 -38.874403, 142.824162 -38.874403, 142.023084 -38.874403, 142.023084 -38.424743, 141.222006 -38.424743, 140.420928 -38.424743, 140.420928 -37.975082, 139.61985 -37.975082, 139.61985 -37.525422, 139.61985 -37.075762, 140.420928 -37.075762, 140.420928 -37.525422, 141.222006 -37.525422, 142.023084 -37.525422, 142.824162 -37.525422, 142.824162 -37.975082, 142.824162 -38.424743, 143.625239 -38.424743, 143.625239 -38.874403))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_055</t>
   </si>
   <si>
+    <t>POLYGON ((115.587515 -23.136296, 115.587515 -22.686636, 115.587515 -22.236976, 116.388593 -22.236976, 116.388593 -21.787316, 117.189671 -21.787316, 117.990749 -21.787316, 117.990749 -22.236976, 117.990749 -22.686636, 117.990749 -23.136296, 117.990749 -23.585957, 117.990749 -24.035617, 117.990749 -24.485277, 117.189671 -24.485277, 117.189671 -24.035617, 116.388593 -24.035617, 116.388593 -23.585957, 116.388593 -23.136296, 115.587515 -23.136296))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_056</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((116.388593 -25.834257, 116.388593 -25.384597, 116.388593 -24.934937, 116.388593 -24.485277, 116.388593 -24.035617, 117.189671 -24.035617, 117.189671 -24.485277, 117.990749 -24.485277, 117.990749 -24.934937, 117.990749 -25.384597, 117.990749 -25.834257, 117.189671 -25.834257, 116.388593 -25.834257)), ((114.786437 -23.136296, 114.786437 -22.686636, 115.587515 -22.686636, 115.587515 -23.136296, 116.388593 -23.136296, 116.388593 -23.585957, 116.388593 -24.035617, 115.587515 -24.035617, 115.587515 -23.585957, 114.786437 -23.585957, 114.786437 -23.136296)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_057</t>
   </si>
   <si>
+    <t>POLYGON ((113.184282 -25.384597, 113.184282 -24.934937, 113.184282 -24.485277, 113.184282 -24.035617, 113.184282 -23.585957, 113.98536 -23.585957, 113.98536 -23.136296, 114.786437 -23.136296, 114.786437 -23.585957, 115.587515 -23.585957, 115.587515 -24.035617, 116.388593 -24.035617, 116.388593 -24.485277, 116.388593 -24.934937, 116.388593 -25.384597, 116.388593 -25.834257, 115.587515 -25.834257, 114.786437 -25.834257, 114.786437 -25.384597, 113.98536 -25.384597, 113.184282 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_058</t>
   </si>
   <si>
+    <t>POLYGON ((150.83494 -24.035617, 150.83494 -23.585957, 150.83494 -23.136296, 151.636018 -23.136296, 151.636018 -23.585957, 151.636018 -24.035617, 151.636018 -24.485277, 150.83494 -24.485277, 150.83494 -24.035617))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_059</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -38.424743, 146.028473 -37.975082, 146.028473 -37.525422, 146.028473 -37.075762, 146.028473 -36.626102, 146.829551 -36.626102, 146.829551 -37.075762, 147.630629 -37.075762, 147.630629 -37.525422, 147.630629 -37.975082, 148.431706 -37.975082, 148.431706 -38.424743, 147.630629 -38.424743, 147.630629 -38.874403, 146.829551 -38.874403, 146.829551 -39.324063, 146.028473 -39.324063, 145.227395 -39.324063, 145.227395 -38.874403, 146.028473 -38.874403, 146.028473 -38.424743))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_060</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -27.183238, 144.426317 -26.733578, 143.625239 -26.733578, 143.625239 -26.283918, 143.625239 -25.834257, 142.824162 -25.834257, 142.824162 -25.384597, 143.625239 -25.384597, 144.426317 -25.384597, 144.426317 -24.934937, 145.227395 -24.934937, 146.028473 -24.934937, 146.829551 -24.934937, 146.829551 -25.384597, 146.829551 -25.834257, 146.829551 -26.283918, 146.829551 -26.733578, 146.829551 -27.183238, 146.829551 -27.632898, 146.829551 -28.082558, 147.630629 -28.082558, 147.630629 -28.532219, 147.630629 -28.981879, 146.829551 -28.981879, 146.829551 -29.431539, 146.028473 -29.431539, 146.028473 -28.981879, 145.227395 -28.981879, 145.227395 -28.532219, 145.227395 -28.082558, 144.426317 -28.082558, 144.426317 -27.632898, 144.426317 -27.183238))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_061</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -28.082558, 146.829551 -27.632898, 146.829551 -27.183238, 146.829551 -26.733578, 146.829551 -26.283918, 146.829551 -25.834257, 146.829551 -25.384597, 146.829551 -24.934937, 147.630629 -24.934937, 147.630629 -24.485277, 148.431706 -24.485277, 149.232784 -24.485277, 149.232784 -24.934937, 150.033862 -24.934937, 150.033862 -25.384597, 150.83494 -25.384597, 150.83494 -25.834257, 150.83494 -26.283918, 150.83494 -26.733578, 150.83494 -27.183238, 150.033862 -27.183238, 150.033862 -27.632898, 149.232784 -27.632898, 149.232784 -28.082558, 148.431706 -28.082558, 148.431706 -28.532219, 147.630629 -28.532219, 147.630629 -28.082558, 146.829551 -28.082558))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_062</t>
   </si>
   <si>
+    <t>POLYGON ((113.184282 -22.686636, 113.184282 -22.236976, 113.184282 -21.787316, 113.98536 -21.787316, 114.786437 -21.787316, 114.786437 -22.236976, 114.786437 -22.686636, 114.786437 -23.136296, 113.98536 -23.136296, 113.98536 -23.585957, 113.184282 -23.585957, 113.184282 -23.136296, 113.184282 -22.686636))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_063</t>
   </si>
   <si>
+    <t>POLYGON ((114.786437 -21.337656, 115.587515 -21.337656, 115.587515 -20.887995, 114.786437 -20.887995, 114.786437 -20.438335, 115.587515 -20.438335, 116.388593 -20.438335, 117.189671 -20.438335, 117.990749 -20.438335, 117.990749 -20.887995, 117.990749 -21.337656, 117.990749 -21.787316, 117.189671 -21.787316, 116.388593 -21.787316, 116.388593 -22.236976, 115.587515 -22.236976, 115.587515 -22.686636, 114.786437 -22.686636, 114.786437 -22.236976, 114.786437 -21.787316, 114.786437 -21.337656))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_064</t>
   </si>
   <si>
+    <t>POLYGON ((126.001527 -24.485277, 126.001527 -24.035617, 126.001527 -23.585957, 126.001527 -23.136296, 126.001527 -22.686636, 126.001527 -22.236976, 126.802605 -22.236976, 126.802605 -22.686636, 127.603683 -22.686636, 127.603683 -22.236976, 128.404761 -22.236976, 129.205838 -22.236976, 129.205838 -22.686636, 129.205838 -23.136296, 129.205838 -23.585957, 129.205838 -24.035617, 128.404761 -24.035617, 127.603683 -24.035617, 127.603683 -24.485277, 126.802605 -24.485277, 126.001527 -24.485277))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_065</t>
   </si>
   <si>
+    <t>POLYGON ((126.802605 -22.236976, 126.001527 -22.236976, 125.200449 -22.236976, 125.200449 -21.787316, 124.399371 -21.787316, 124.399371 -21.337656, 125.200449 -21.337656, 125.200449 -20.887995, 126.001527 -20.887995, 126.802605 -20.887995, 127.603683 -20.887995, 128.404761 -20.887995, 129.205838 -20.887995, 129.205838 -21.337656, 129.205838 -21.787316, 129.205838 -22.236976, 128.404761 -22.236976, 127.603683 -22.236976, 127.603683 -22.686636, 126.802605 -22.686636, 126.802605 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_066</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -21.787316, 129.205838 -21.337656, 129.205838 -20.887995, 130.006916 -20.887995, 130.006916 -21.337656, 130.006916 -21.787316, 130.006916 -22.236976, 129.205838 -22.236976, 129.205838 -21.787316))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_067</t>
   </si>
   <si>
+    <t>POLYGON ((117.990749 -25.834257, 117.990749 -25.384597, 117.990749 -24.934937, 117.990749 -24.485277, 117.990749 -24.035617, 117.990749 -23.585957, 117.990749 -23.136296, 117.990749 -22.686636, 117.990749 -22.236976, 118.791827 -22.236976, 118.791827 -22.686636, 118.791827 -23.136296, 119.592904 -23.136296, 120.393982 -23.136296, 120.393982 -23.585957, 121.19506 -23.585957, 121.19506 -24.035617, 121.19506 -24.485277, 121.19506 -24.934937, 121.19506 -25.384597, 121.19506 -25.834257, 121.996138 -25.834257, 121.996138 -26.283918, 121.19506 -26.283918, 121.19506 -26.733578, 120.393982 -26.733578, 119.592904 -26.733578, 119.592904 -26.283918, 118.791827 -26.283918, 117.990749 -26.283918, 117.990749 -25.834257))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_068</t>
   </si>
   <si>
+    <t>POLYGON ((121.996138 -22.686636, 121.996138 -22.236976, 121.19506 -22.236976, 121.19506 -21.787316, 121.19506 -21.337656, 121.996138 -21.337656, 122.797216 -21.337656, 123.598294 -21.337656, 124.399371 -21.337656, 124.399371 -21.787316, 125.200449 -21.787316, 125.200449 -22.236976, 126.001527 -22.236976, 126.001527 -22.686636, 126.001527 -23.136296, 126.001527 -23.585957, 126.001527 -24.035617, 125.200449 -24.035617, 124.399371 -24.035617, 123.598294 -24.035617, 122.797216 -24.035617, 122.797216 -23.585957, 122.797216 -23.136296, 121.996138 -23.136296, 121.996138 -22.686636))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_069</t>
   </si>
   <si>
+    <t>POLYGON ((120.393982 -23.136296, 119.592904 -23.136296, 118.791827 -23.136296, 118.791827 -22.686636, 118.791827 -22.236976, 117.990749 -22.236976, 117.990749 -21.787316, 118.791827 -21.787316, 119.592904 -21.787316, 119.592904 -21.337656, 120.393982 -21.337656, 121.19506 -21.337656, 121.19506 -21.787316, 121.19506 -22.236976, 121.996138 -22.236976, 121.996138 -22.686636, 121.996138 -23.136296, 122.797216 -23.136296, 122.797216 -23.585957, 122.797216 -24.035617, 121.996138 -24.035617, 121.19506 -24.035617, 121.19506 -23.585957, 120.393982 -23.585957, 120.393982 -23.136296))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_070</t>
   </si>
   <si>
+    <t>POLYGON ((121.19506 -25.384597, 121.19506 -24.934937, 121.19506 -24.485277, 121.19506 -24.035617, 121.996138 -24.035617, 122.797216 -24.035617, 123.598294 -24.035617, 124.399371 -24.035617, 125.200449 -24.035617, 126.001527 -24.035617, 126.001527 -24.485277, 126.001527 -24.934937, 125.200449 -24.934937, 125.200449 -25.384597, 124.399371 -25.384597, 123.598294 -25.384597, 123.598294 -25.834257, 122.797216 -25.834257, 121.996138 -25.834257, 121.19506 -25.834257, 121.19506 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_071</t>
   </si>
   <si>
+    <t>POLYGON ((117.189671 -28.532219, 117.189671 -28.082558, 117.189671 -27.632898, 117.189671 -27.183238, 117.189671 -26.733578, 116.388593 -26.733578, 116.388593 -26.283918, 116.388593 -25.834257, 117.189671 -25.834257, 117.990749 -25.834257, 117.990749 -26.283918, 118.791827 -26.283918, 119.592904 -26.283918, 119.592904 -26.733578, 120.393982 -26.733578, 120.393982 -27.183238, 119.592904 -27.183238, 119.592904 -27.632898, 119.592904 -28.082558, 119.592904 -28.532219, 119.592904 -28.981879, 119.592904 -29.431539, 118.791827 -29.431539, 118.791827 -29.881199, 117.990749 -29.881199, 117.990749 -29.431539, 117.189671 -29.431539, 117.189671 -28.981879, 117.189671 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_072</t>
   </si>
   <si>
+    <t>POLYGON ((114.786437 -28.981879, 114.786437 -28.532219, 113.98536 -28.532219, 113.98536 -28.082558, 113.98536 -27.632898, 114.786437 -27.632898, 115.587515 -27.632898, 115.587515 -28.082558, 115.587515 -28.532219, 116.388593 -28.532219, 117.189671 -28.532219, 117.189671 -28.981879, 117.189671 -29.431539, 117.990749 -29.431539, 117.990749 -29.881199, 117.990749 -30.330859, 117.189671 -30.330859, 116.388593 -30.330859, 116.388593 -29.881199, 115.587515 -29.881199, 115.587515 -29.431539, 114.786437 -29.431539, 114.786437 -28.981879))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_073</t>
   </si>
   <si>
+    <t>POLYGON ((113.98536 -27.632898, 113.98536 -27.183238, 113.184282 -27.183238, 113.184282 -26.733578, 113.184282 -26.283918, 113.184282 -25.834257, 113.184282 -25.384597, 113.98536 -25.384597, 114.786437 -25.384597, 114.786437 -25.834257, 115.587515 -25.834257, 116.388593 -25.834257, 116.388593 -26.283918, 116.388593 -26.733578, 117.189671 -26.733578, 117.189671 -27.183238, 117.189671 -27.632898, 117.189671 -28.082558, 117.189671 -28.532219, 116.388593 -28.532219, 115.587515 -28.532219, 115.587515 -28.082558, 115.587515 -27.632898, 114.786437 -27.632898, 113.98536 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_074</t>
   </si>
   <si>
+    <t>POLYGON ((147.630629 -34.377801, 147.630629 -33.928141, 147.630629 -33.478481, 147.630629 -33.02882, 148.431706 -33.02882, 148.431706 -33.478481, 149.232784 -33.478481, 149.232784 -33.928141, 149.232784 -34.377801, 150.033862 -34.377801, 150.033862 -34.827461, 150.033862 -35.277121, 150.83494 -35.277121, 150.83494 -35.726781, 150.83494 -36.176442, 150.033862 -36.176442, 150.033862 -35.726781, 149.232784 -35.726781, 149.232784 -35.277121, 148.431706 -35.277121, 148.431706 -34.827461, 148.431706 -34.377801, 147.630629 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_075</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -33.928141, 141.222006 -33.478481, 140.420928 -33.478481, 140.420928 -33.02882, 140.420928 -32.57916, 139.61985 -32.57916, 139.61985 -32.1295, 139.61985 -31.67984, 139.61985 -31.23018, 140.420928 -31.23018, 141.222006 -31.23018, 141.222006 -31.67984, 141.222006 -32.1295, 142.023084 -32.1295, 142.824162 -32.1295, 143.625239 -32.1295, 143.625239 -32.57916, 143.625239 -33.02882, 142.824162 -33.02882, 142.824162 -33.478481, 142.023084 -33.478481, 142.023084 -33.928141, 141.222006 -33.928141))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_076</t>
   </si>
   <si>
+    <t>POLYGON ((139.61985 -31.23018, 139.61985 -30.780519, 139.61985 -30.330859, 139.61985 -29.881199, 139.61985 -29.431539, 139.61985 -28.981879, 140.420928 -28.981879, 140.420928 -29.431539, 141.222006 -29.431539, 141.222006 -29.881199, 142.023084 -29.881199, 142.023084 -30.330859, 142.824162 -30.330859, 142.824162 -30.780519, 143.625239 -30.780519, 143.625239 -31.23018, 144.426317 -31.23018, 144.426317 -31.67984, 144.426317 -32.1295, 143.625239 -32.1295, 142.824162 -32.1295, 142.023084 -32.1295, 141.222006 -32.1295, 141.222006 -31.67984, 141.222006 -31.23018, 140.420928 -31.23018, 139.61985 -31.23018))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_077</t>
   </si>
   <si>
+    <t>POLYGON ((140.420928 -27.632898, 140.420928 -27.183238, 140.420928 -26.733578, 140.420928 -26.283918, 141.222006 -26.283918, 141.222006 -25.834257, 141.222006 -25.384597, 141.222006 -24.934937, 141.222006 -24.485277, 142.023084 -24.485277, 142.023084 -24.934937, 142.824162 -24.934937, 142.824162 -25.384597, 142.824162 -25.834257, 143.625239 -25.834257, 143.625239 -26.283918, 143.625239 -26.733578, 144.426317 -26.733578, 144.426317 -27.183238, 144.426317 -27.632898, 144.426317 -28.082558, 145.227395 -28.082558, 145.227395 -28.532219, 145.227395 -28.981879, 144.426317 -28.981879, 143.625239 -28.981879, 143.625239 -28.532219, 143.625239 -28.082558, 142.824162 -28.082558, 142.824162 -28.532219, 142.023084 -28.532219, 142.023084 -28.082558, 141.222006 -28.082558, 141.222006 -27.632898, 140.420928 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_078</t>
   </si>
   <si>
+    <t>POLYGON ((143.625239 -29.881199, 143.625239 -29.431539, 143.625239 -28.981879, 144.426317 -28.981879, 145.227395 -28.981879, 146.028473 -28.981879, 146.028473 -29.431539, 146.028473 -29.881199, 145.227395 -29.881199, 145.227395 -30.330859, 145.227395 -30.780519, 145.227395 -31.23018, 144.426317 -31.23018, 143.625239 -31.23018, 143.625239 -30.780519, 143.625239 -30.330859, 143.625239 -29.881199))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_079</t>
   </si>
   <si>
+    <t>POLYGON ((142.023084 -30.330859, 142.023084 -29.881199, 141.222006 -29.881199, 141.222006 -29.431539, 140.420928 -29.431539, 140.420928 -28.981879, 139.61985 -28.981879, 139.61985 -28.532219, 140.420928 -28.532219, 140.420928 -28.082558, 140.420928 -27.632898, 141.222006 -27.632898, 141.222006 -28.082558, 142.023084 -28.082558, 142.023084 -28.532219, 142.824162 -28.532219, 142.824162 -28.082558, 143.625239 -28.082558, 143.625239 -28.532219, 143.625239 -28.981879, 143.625239 -29.431539, 143.625239 -29.881199, 143.625239 -30.330859, 143.625239 -30.780519, 142.824162 -30.780519, 142.824162 -30.330859, 142.023084 -30.330859))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_080</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((114.786437 -30.330859, 114.786437 -29.881199, 114.786437 -29.431539, 115.587515 -29.431539, 115.587515 -29.881199, 116.388593 -29.881199, 116.388593 -30.330859, 117.189671 -30.330859, 117.189671 -30.780519, 117.189671 -31.23018, 116.388593 -31.23018, 115.587515 -31.23018, 115.587515 -31.67984, 114.786437 -31.67984, 114.786437 -31.23018, 114.786437 -30.780519, 114.786437 -30.330859)), ((113.98536 -28.981879, 113.98536 -28.532219, 114.786437 -28.532219, 114.786437 -28.981879, 113.98536 -28.981879)), ((113.184282 -28.532219, 113.184282 -28.082558, 113.98536 -28.082558, 113.98536 -28.532219, 113.184282 -28.532219)))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_081</t>
   </si>
   <si>
+    <t>POLYGON ((151.636018 -33.478481, 150.83494 -33.478481, 150.83494 -33.02882, 150.83494 -32.57916, 150.83494 -32.1295, 150.83494 -31.67984, 151.636018 -31.67984, 152.437096 -31.67984, 153.238173 -31.67984, 153.238173 -32.1295, 153.238173 -32.57916, 152.437096 -32.57916, 152.437096 -33.02882, 152.437096 -33.478481, 151.636018 -33.478481))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_082</t>
   </si>
   <si>
+    <t>POLYGON ((115.587515 -31.67984, 115.587515 -31.23018, 116.388593 -31.23018, 117.189671 -31.23018, 117.189671 -31.67984, 117.189671 -32.1295, 117.189671 -32.57916, 116.388593 -32.57916, 115.587515 -32.57916, 115.587515 -32.1295, 115.587515 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_083</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -37.525422, 140.420928 -37.525422, 140.420928 -37.075762, 139.61985 -37.075762, 139.61985 -36.626102, 140.420928 -36.626102, 140.420928 -36.176442, 140.420928 -35.726781, 140.420928 -35.277121, 141.222006 -35.277121, 141.222006 -34.827461, 142.023084 -34.827461, 142.023084 -35.277121, 142.824162 -35.277121, 142.824162 -35.726781, 142.023084 -35.726781, 142.023084 -36.176442, 142.824162 -36.176442, 143.625239 -36.176442, 143.625239 -36.626102, 143.625239 -37.075762, 142.824162 -37.075762, 142.824162 -37.525422, 142.023084 -37.525422, 141.222006 -37.525422))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_084</t>
   </si>
   <si>
+    <t>POLYGON ((148.431706 -43.371005, 147.630629 -43.371005, 146.829551 -43.371005, 146.829551 -42.921344, 146.028473 -42.921344, 146.028473 -42.471684, 146.829551 -42.471684, 147.630629 -42.471684, 147.630629 -42.022024, 148.431706 -42.022024, 148.431706 -42.471684, 148.431706 -42.921344, 148.431706 -43.371005))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_085</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -19.089355, 129.205838 -18.639695, 129.205838 -18.190034, 129.205838 -17.740374, 129.205838 -17.290714, 129.205838 -16.841054, 130.006916 -16.841054, 130.807994 -16.841054, 131.609072 -16.841054, 131.609072 -17.290714, 131.609072 -17.740374, 131.609072 -18.190034, 131.609072 -18.639695, 131.609072 -19.089355, 130.807994 -19.089355, 130.807994 -19.539015, 130.807994 -19.988675, 130.807994 -20.438335, 130.006916 -20.438335, 130.006916 -20.887995, 129.205838 -20.887995, 129.205838 -20.438335, 129.205838 -19.988675, 129.205838 -19.539015, 129.205838 -19.089355))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_086</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -16.391394, 129.205838 -15.941733, 129.205838 -15.492073, 129.205838 -15.042413, 129.205838 -14.592753, 129.205838 -14.143093, 129.205838 -13.693433, 129.205838 -13.243772, 130.006916 -13.243772, 130.006916 -12.794112, 130.006916 -12.344452, 130.807994 -12.344452, 130.807994 -11.894792, 130.006916 -11.894792, 130.006916 -11.445132, 130.006916 -10.995471, 130.807994 -10.995471, 131.609072 -10.995471, 131.609072 -11.445132, 131.609072 -11.894792, 131.609072 -12.344452, 131.609072 -12.794112, 131.609072 -13.243772, 131.609072 -13.693433, 131.609072 -14.143093, 131.609072 -14.592753, 131.609072 -15.042413, 131.609072 -15.492073, 131.609072 -15.941733, 131.609072 -16.391394, 131.609072 -16.841054, 130.807994 -16.841054, 130.006916 -16.841054, 129.205838 -16.841054, 129.205838 -16.391394))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_087</t>
   </si>
   <si>
+    <t>POLYGON ((117.990749 -21.787316, 117.990749 -21.337656, 117.990749 -20.887995, 117.990749 -20.438335, 117.990749 -19.988675, 118.791827 -19.988675, 118.791827 -19.539015, 119.592904 -19.539015, 120.393982 -19.539015, 120.393982 -19.988675, 121.19506 -19.988675, 121.19506 -20.438335, 121.19506 -20.887995, 121.19506 -21.337656, 120.393982 -21.337656, 119.592904 -21.337656, 119.592904 -21.787316, 118.791827 -21.787316, 117.990749 -21.787316))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_088</t>
   </si>
   <si>
+    <t>POLYGON ((121.19506 -20.887995, 121.19506 -20.438335, 121.19506 -19.988675, 120.393982 -19.988675, 120.393982 -19.539015, 120.393982 -19.089355, 121.19506 -19.089355, 121.19506 -18.639695, 121.19506 -18.190034, 121.996138 -18.190034, 121.996138 -17.740374, 122.797216 -17.740374, 123.598294 -17.740374, 123.598294 -18.190034, 124.399371 -18.190034, 124.399371 -18.639695, 124.399371 -19.089355, 124.399371 -19.539015, 124.399371 -19.988675, 124.399371 -20.438335, 125.200449 -20.438335, 125.200449 -20.887995, 125.200449 -21.337656, 124.399371 -21.337656, 123.598294 -21.337656, 122.797216 -21.337656, 121.996138 -21.337656, 121.19506 -21.337656, 121.19506 -20.887995))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_089</t>
   </si>
   <si>
+    <t>POLYGON ((125.200449 -17.290714, 125.200449 -16.841054, 124.399371 -16.841054, 124.399371 -16.391394, 124.399371 -15.941733, 124.399371 -15.492073, 124.399371 -15.042413, 125.200449 -15.042413, 125.200449 -14.592753, 124.399371 -14.592753, 124.399371 -14.143093, 125.200449 -14.143093, 126.001527 -14.143093, 126.001527 -13.693433, 126.802605 -13.693433, 127.603683 -13.693433, 127.603683 -14.143093, 128.404761 -14.143093, 128.404761 -14.592753, 129.205838 -14.592753, 129.205838 -15.042413, 129.205838 -15.492073, 129.205838 -15.941733, 129.205838 -16.391394, 129.205838 -16.841054, 129.205838 -17.290714, 128.404761 -17.290714, 127.603683 -17.290714, 127.603683 -17.740374, 126.802605 -17.740374, 126.001527 -17.740374, 125.200449 -17.740374, 125.200449 -17.290714))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_090</t>
   </si>
   <si>
+    <t>POLYGON ((124.399371 -18.190034, 123.598294 -18.190034, 123.598294 -17.740374, 122.797216 -17.740374, 121.996138 -17.740374, 121.996138 -17.290714, 121.996138 -16.841054, 121.996138 -16.391394, 122.797216 -16.391394, 122.797216 -15.941733, 123.598294 -15.941733, 124.399371 -15.941733, 124.399371 -16.391394, 124.399371 -16.841054, 125.200449 -16.841054, 125.200449 -17.290714, 125.200449 -17.740374, 126.001527 -17.740374, 126.802605 -17.740374, 127.603683 -17.740374, 127.603683 -17.290714, 128.404761 -17.290714, 129.205838 -17.290714, 129.205838 -17.740374, 129.205838 -18.190034, 129.205838 -18.639695, 129.205838 -19.089355, 129.205838 -19.539015, 129.205838 -19.988675, 129.205838 -20.438335, 129.205838 -20.887995, 128.404761 -20.887995, 127.603683 -20.887995, 126.802605 -20.887995, 126.001527 -20.887995, 125.200449 -20.887995, 125.200449 -20.438335, 124.399371 -20.438335, 124.399371 -19.988675, 124.399371 -19.539015, 124.399371 -19.089355, 124.399371 -18.639695, 124.399371 -18.190034))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_091</t>
   </si>
   <si>
+    <t>POLYGON ((123.598294 -30.330859, 123.598294 -29.881199, 123.598294 -29.431539, 124.399371 -29.431539, 125.200449 -29.431539, 125.200449 -28.981879, 125.200449 -28.532219, 125.200449 -28.082558, 126.001527 -28.082558, 126.802605 -28.082558, 127.603683 -28.082558, 128.404761 -28.082558, 128.404761 -28.532219, 129.205838 -28.532219, 129.205838 -28.981879, 129.205838 -29.431539, 129.205838 -29.881199, 129.205838 -30.330859, 129.205838 -30.780519, 129.205838 -31.23018, 128.404761 -31.23018, 127.603683 -31.23018, 126.802605 -31.23018, 126.001527 -31.23018, 125.200449 -31.23018, 124.399371 -31.23018, 123.598294 -31.23018, 123.598294 -30.780519, 123.598294 -30.330859))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_092</t>
   </si>
   <si>
+    <t>POLYGON ((123.598294 -27.632898, 122.797216 -27.632898, 122.797216 -27.183238, 122.797216 -26.733578, 121.996138 -26.733578, 121.996138 -26.283918, 121.996138 -25.834257, 122.797216 -25.834257, 123.598294 -25.834257, 123.598294 -25.384597, 124.399371 -25.384597, 125.200449 -25.384597, 125.200449 -25.834257, 125.200449 -26.283918, 125.200449 -26.733578, 125.200449 -27.183238, 125.200449 -27.632898, 125.200449 -28.082558, 124.399371 -28.082558, 123.598294 -28.082558, 123.598294 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_093</t>
   </si>
   <si>
+    <t>POLYGON ((125.200449 -27.632898, 125.200449 -27.183238, 125.200449 -26.733578, 125.200449 -26.283918, 125.200449 -25.834257, 125.200449 -25.384597, 125.200449 -24.934937, 126.001527 -24.934937, 126.001527 -24.485277, 126.802605 -24.485277, 127.603683 -24.485277, 127.603683 -24.035617, 128.404761 -24.035617, 129.205838 -24.035617, 129.205838 -24.485277, 129.205838 -24.934937, 129.205838 -25.384597, 129.205838 -25.834257, 129.205838 -26.283918, 129.205838 -26.733578, 129.205838 -27.183238, 129.205838 -27.632898, 129.205838 -28.082558, 129.205838 -28.532219, 128.404761 -28.532219, 128.404761 -28.082558, 127.603683 -28.082558, 126.802605 -28.082558, 126.001527 -28.082558, 125.200449 -28.082558, 125.200449 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_094</t>
   </si>
   <si>
+    <t>POLYGON ((119.592904 -31.67984, 119.592904 -31.23018, 119.592904 -30.780519, 119.592904 -30.330859, 119.592904 -29.881199, 119.592904 -29.431539, 119.592904 -28.981879, 120.393982 -28.981879, 120.393982 -29.431539, 121.19506 -29.431539, 121.19506 -29.881199, 121.996138 -29.881199, 122.797216 -29.881199, 122.797216 -30.330859, 123.598294 -30.330859, 123.598294 -30.780519, 123.598294 -31.23018, 122.797216 -31.23018, 122.797216 -31.67984, 121.996138 -31.67984, 121.19506 -31.67984, 120.393982 -31.67984, 119.592904 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_095</t>
   </si>
   <si>
+    <t>POLYGON ((121.19506 -29.881199, 121.19506 -29.431539, 120.393982 -29.431539, 120.393982 -28.981879, 119.592904 -28.981879, 119.592904 -28.532219, 119.592904 -28.082558, 119.592904 -27.632898, 119.592904 -27.183238, 120.393982 -27.183238, 120.393982 -26.733578, 121.19506 -26.733578, 121.19506 -26.283918, 121.996138 -26.283918, 121.996138 -26.733578, 122.797216 -26.733578, 122.797216 -27.183238, 122.797216 -27.632898, 123.598294 -27.632898, 123.598294 -28.082558, 124.399371 -28.082558, 125.200449 -28.082558, 125.200449 -28.532219, 125.200449 -28.981879, 125.200449 -29.431539, 124.399371 -29.431539, 123.598294 -29.431539, 123.598294 -29.881199, 123.598294 -30.330859, 122.797216 -30.330859, 122.797216 -29.881199, 121.996138 -29.881199, 121.19506 -29.881199))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_096</t>
   </si>
   <si>
+    <t>POLYGON ((127.603683 -32.57916, 126.802605 -32.57916, 126.001527 -32.57916, 125.200449 -32.57916, 125.200449 -32.1295, 125.200449 -31.67984, 125.200449 -31.23018, 126.001527 -31.23018, 126.802605 -31.23018, 127.603683 -31.23018, 128.404761 -31.23018, 129.205838 -31.23018, 129.205838 -31.67984, 129.205838 -32.1295, 128.404761 -32.1295, 127.603683 -32.1295, 127.603683 -32.57916))</t>
+  </si>
+  <si>
     <t>elc_spv_AUS_097</t>
   </si>
   <si>
+    <t>POLYGON ((122.797216 -34.377801, 121.996138 -34.377801, 121.996138 -33.928141, 121.19506 -33.928141, 120.393982 -33.928141, 120.393982 -33.478481, 120.393982 -33.02882, 120.393982 -32.57916, 120.393982 -32.1295, 120.393982 -31.67984, 121.19506 -31.67984, 121.996138 -31.67984, 122.797216 -31.67984, 122.797216 -31.23018, 123.598294 -31.23018, 124.399371 -31.23018, 125.200449 -31.23018, 125.200449 -31.67984, 125.200449 -32.1295, 125.200449 -32.57916, 125.200449 -33.02882, 124.399371 -33.02882, 124.399371 -33.478481, 124.399371 -33.928141, 123.598294 -33.928141, 123.598294 -34.377801, 122.797216 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_001</t>
   </si>
   <si>
+    <t>POLYGON ((150.734044 -35.147761, 150.734044 -34.698101, 150.734044 -34.248441, 150.734044 -33.798781, 150.734044 -33.349121, 151.540785 -33.349121, 151.540785 -33.798781, 151.540785 -34.248441, 152.347526 -34.248441, 152.347526 -34.698101, 151.540785 -34.698101, 151.540785 -35.147761, 151.540785 -35.597422, 151.540785 -36.047082, 150.734044 -36.047082, 150.734044 -35.597422, 150.734044 -35.147761))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_002</t>
   </si>
   <si>
+    <t>POLYGON ((119.271131 -35.597422, 118.46439 -35.597422, 117.657648 -35.597422, 117.657648 -35.147761, 116.850907 -35.147761, 116.850907 -34.698101, 117.657648 -34.698101, 118.46439 -34.698101, 118.46439 -34.248441, 119.271131 -34.248441, 119.271131 -34.698101, 119.271131 -35.147761, 119.271131 -35.597422))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_003</t>
   </si>
   <si>
+    <t>POLYGON ((113.623942 -34.698101, 113.623942 -34.248441, 113.623942 -33.798781, 113.623942 -33.349121, 114.430683 -33.349121, 115.237424 -33.349121, 115.237424 -33.798781, 115.237424 -34.248441, 116.044166 -34.248441, 116.044166 -34.698101, 116.850907 -34.698101, 116.850907 -35.147761, 117.657648 -35.147761, 117.657648 -35.597422, 116.850907 -35.597422, 116.044166 -35.597422, 115.237424 -35.597422, 114.430683 -35.597422, 114.430683 -35.147761, 113.623942 -35.147761, 113.623942 -34.698101))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_004</t>
   </si>
   <si>
+    <t>POLYGON ((145.893596 -41.443004, 145.893596 -40.993344, 145.086854 -40.993344, 145.086854 -40.543684, 145.086854 -40.094023, 145.086854 -39.644363, 145.893596 -39.644363, 146.700337 -39.644363, 147.507078 -39.644363, 147.507078 -40.094023, 147.507078 -40.543684, 147.507078 -40.993344, 146.700337 -40.993344, 146.700337 -41.443004, 145.893596 -41.443004))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_005</t>
   </si>
   <si>
+    <t>POLYGON ((144.280113 -41.892664, 144.280113 -41.443004, 143.473371 -41.443004, 143.473371 -40.993344, 143.473371 -40.543684, 143.473371 -40.094023, 144.280113 -40.094023, 145.086854 -40.094023, 145.086854 -40.543684, 145.086854 -40.993344, 145.086854 -41.443004, 145.086854 -41.892664, 145.893596 -41.892664, 145.893596 -42.342324, 145.893596 -42.791984, 145.086854 -42.791984, 145.086854 -43.241645, 144.280113 -43.241645, 144.280113 -42.791984, 144.280113 -42.342324, 144.280113 -41.892664))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_006</t>
   </si>
   <si>
+    <t>POLYGON ((143.473371 -39.194703, 143.473371 -38.745043, 143.473371 -38.295383, 144.280113 -38.295383, 144.280113 -38.745043, 144.280113 -39.194703, 144.280113 -39.644363, 144.280113 -40.094023, 143.473371 -40.094023, 143.473371 -39.644363, 143.473371 -39.194703))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_007</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((149.927302 -22.107616, 149.927302 -21.657956, 150.734044 -21.657956, 150.734044 -22.107616, 150.734044 -22.557276, 149.927302 -22.557276, 149.927302 -22.107616)), ((151.540785 -20.758636, 151.540785 -21.208296, 150.734044 -21.208296, 150.734044 -20.758636, 151.540785 -20.758636)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_008</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((153.154268 -31.10082, 153.154268 -30.65116, 153.154268 -30.201499, 153.154268 -29.751839, 153.154268 -29.302179, 153.961009 -29.302179, 153.961009 -29.751839, 153.961009 -30.201499, 153.961009 -30.65116, 153.961009 -31.10082, 153.961009 -31.55048, 153.961009 -32.00014, 153.154268 -32.00014, 152.347526 -32.00014, 152.347526 -31.55048, 153.154268 -31.55048, 153.154268 -31.10082)), ((159.608198 -32.00014, 158.801457 -32.00014, 158.801457 -31.55048, 159.608198 -31.55048, 159.608198 -32.00014)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_009</t>
   </si>
   <si>
+    <t>POLYGON ((137.826182 -32.89946, 137.019441 -32.89946, 137.019441 -32.4498, 137.826182 -32.4498, 138.632923 -32.4498, 138.632923 -32.89946, 138.632923 -33.349121, 137.826182 -33.349121, 137.826182 -32.89946))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_010</t>
   </si>
   <si>
+    <t>POLYGON ((133.792475 -35.147761, 132.985734 -35.147761, 132.178993 -35.147761, 132.178993 -34.698101, 131.372251 -34.698101, 131.372251 -34.248441, 132.178993 -34.248441, 132.178993 -33.798781, 132.985734 -33.798781, 132.985734 -33.349121, 133.792475 -33.349121, 133.792475 -32.89946, 134.599217 -32.89946, 135.405958 -32.89946, 135.405958 -33.349121, 135.405958 -33.798781, 135.405958 -34.248441, 135.405958 -34.698101, 135.405958 -35.147761, 134.599217 -35.147761, 133.792475 -35.147761))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_011</t>
   </si>
   <si>
+    <t>POLYGON ((149.927302 -21.208296, 149.120561 -21.208296, 149.120561 -20.758636, 149.927302 -20.758636, 150.734044 -20.758636, 150.734044 -21.208296, 150.734044 -21.657956, 149.927302 -21.657956, 149.927302 -21.208296))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_012</t>
   </si>
   <si>
+    <t>POLYGON ((149.120561 -20.758636, 149.120561 -20.308975, 149.120561 -19.859315, 149.927302 -19.859315, 149.927302 -19.409655, 150.734044 -19.409655, 150.734044 -18.959995, 151.540785 -18.959995, 151.540785 -19.409655, 152.347526 -19.409655, 152.347526 -19.859315, 152.347526 -20.308975, 151.540785 -20.308975, 151.540785 -20.758636, 150.734044 -20.758636, 149.927302 -20.758636, 149.120561 -20.758636))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_013</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((153.154268 -27.503538, 153.154268 -27.053878, 153.154268 -26.604218, 153.154268 -26.154558, 153.154268 -25.704898, 153.961009 -25.704898, 154.76775 -25.704898, 154.76775 -25.255237, 155.574492 -25.255237, 155.574492 -25.704898, 155.574492 -26.154558, 154.76775 -26.154558, 154.76775 -26.604218, 153.961009 -26.604218, 153.961009 -27.053878, 154.76775 -27.053878, 155.574492 -27.053878, 155.574492 -27.503538, 156.381233 -27.503538, 156.381233 -27.953198, 156.381233 -28.402859, 156.381233 -28.852519, 155.574492 -28.852519, 154.76775 -28.852519, 153.961009 -28.852519, 153.961009 -29.302179, 153.154268 -29.302179, 153.154268 -28.852519, 153.154268 -28.402859, 153.154268 -27.953198, 153.154268 -27.503538)), ((158.801457 -31.10082, 159.608198 -31.10082, 159.608198 -31.55048, 158.801457 -31.55048, 158.801457 -31.10082)), ((158.801457 -29.751839, 159.608198 -29.751839, 159.608198 -30.201499, 158.801457 -30.201499, 158.801457 -29.751839)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_014</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((150.734044 -22.107616, 150.734044 -21.657956, 150.734044 -21.208296, 151.540785 -21.208296, 151.540785 -21.657956, 151.540785 -22.107616, 151.540785 -22.557276, 151.540785 -23.006936, 150.734044 -23.006936, 150.734044 -22.557276, 150.734044 -22.107616)), ((152.347526 -20.308975, 152.347526 -20.758636, 152.347526 -21.208296, 151.540785 -21.208296, 151.540785 -20.758636, 151.540785 -20.308975, 152.347526 -20.308975)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_015</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((152.347526 -24.355917, 152.347526 -23.906257, 152.347526 -23.456597, 153.154268 -23.456597, 153.154268 -23.006936, 153.961009 -23.006936, 153.961009 -22.557276, 154.76775 -22.557276, 154.76775 -23.006936, 155.574492 -23.006936, 156.381233 -23.006936, 156.381233 -23.456597, 155.574492 -23.456597, 154.76775 -23.456597, 154.76775 -23.906257, 153.961009 -23.906257, 153.961009 -24.355917, 153.961009 -24.805577, 153.961009 -25.255237, 153.961009 -25.704898, 153.154268 -25.704898, 153.154268 -25.255237, 153.154268 -24.805577, 152.347526 -24.805577, 152.347526 -24.355917)), ((155.574492 -24.805577, 155.574492 -25.255237, 154.76775 -25.255237, 154.76775 -24.805577, 154.76775 -24.355917, 155.574492 -24.355917, 155.574492 -24.805577)), ((156.381233 -21.657956, 156.381233 -21.208296, 157.187974 -21.208296, 157.994716 -21.208296, 157.994716 -21.657956, 157.187974 -21.657956, 157.187974 -22.107616, 156.381233 -22.107616, 156.381233 -22.557276, 155.574492 -22.557276, 154.76775 -22.557276, 154.76775 -22.107616, 155.574492 -22.107616, 155.574492 -21.657956, 156.381233 -21.657956)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_016</t>
   </si>
   <si>
+    <t>POLYGON ((150.734044 -18.060674, 150.734044 -17.611014, 149.927302 -17.611014, 149.120561 -17.611014, 149.120561 -17.161354, 149.120561 -16.711694, 149.927302 -16.711694, 149.927302 -16.262034, 150.734044 -16.262034, 150.734044 -15.812374, 151.540785 -15.812374, 152.347526 -15.812374, 152.347526 -16.262034, 152.347526 -16.711694, 152.347526 -17.161354, 152.347526 -17.611014, 152.347526 -18.060674, 151.540785 -18.060674, 150.734044 -18.060674))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_017</t>
   </si>
   <si>
+    <t>POLYGON ((147.507078 -19.409655, 147.507078 -18.959995, 147.507078 -18.510335, 147.507078 -18.060674, 148.31382 -18.060674, 148.31382 -17.611014, 149.120561 -17.611014, 149.927302 -17.611014, 150.734044 -17.611014, 150.734044 -18.060674, 150.734044 -18.510335, 151.540785 -18.510335, 151.540785 -18.959995, 150.734044 -18.959995, 150.734044 -19.409655, 149.927302 -19.409655, 149.927302 -19.859315, 149.120561 -19.859315, 149.120561 -20.308975, 149.120561 -20.758636, 148.31382 -20.758636, 148.31382 -20.308975, 148.31382 -19.859315, 147.507078 -19.859315, 147.507078 -19.409655))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_018</t>
   </si>
   <si>
+    <t>POLYGON ((134.599217 -36.047082, 134.599217 -35.597422, 133.792475 -35.597422, 133.792475 -35.147761, 134.599217 -35.147761, 135.405958 -35.147761, 135.405958 -34.698101, 136.212699 -34.698101, 137.019441 -34.698101, 137.019441 -35.147761, 137.019441 -35.597422, 137.019441 -36.047082, 136.212699 -36.047082, 136.212699 -36.496742, 136.212699 -36.946402, 135.405958 -36.946402, 135.405958 -36.496742, 135.405958 -36.047082, 134.599217 -36.047082))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_019</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((137.826182 -37.396062, 137.019441 -37.396062, 137.019441 -36.946402, 136.212699 -36.946402, 136.212699 -36.496742, 136.212699 -36.047082, 137.019441 -36.047082, 137.019441 -35.597422, 137.826182 -35.597422, 138.632923 -35.597422, 139.439665 -35.597422, 140.246406 -35.597422, 140.246406 -36.047082, 139.439665 -36.047082, 139.439665 -36.496742, 140.246406 -36.496742, 140.246406 -36.946402, 139.439665 -36.946402, 139.439665 -37.396062, 139.439665 -37.845722, 138.632923 -37.845722, 138.632923 -37.396062, 137.826182 -37.396062)), ((137.826182 -33.798781, 138.632923 -33.798781, 138.632923 -34.248441, 137.826182 -34.248441, 137.826182 -33.798781)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_020</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((148.31382 -42.342324, 147.507078 -42.342324, 147.507078 -41.892664, 148.31382 -41.892664, 148.31382 -42.342324)), ((148.31382 -41.892664, 148.31382 -41.443004, 148.31382 -40.993344, 147.507078 -40.993344, 147.507078 -40.543684, 147.507078 -40.094023, 147.507078 -39.644363, 148.31382 -39.644363, 149.120561 -39.644363, 149.120561 -40.094023, 149.120561 -40.543684, 149.120561 -40.993344, 149.120561 -41.443004, 149.120561 -41.892664, 148.31382 -41.892664)), ((147.507078 -41.443004, 146.700337 -41.443004, 146.700337 -40.993344, 147.507078 -40.993344, 147.507078 -41.443004)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_021</t>
   </si>
   <si>
+    <t>POLYGON ((148.31382 -38.295383, 148.31382 -37.845722, 148.31382 -37.396062, 149.120561 -37.396062, 149.927302 -37.396062, 149.927302 -37.845722, 150.734044 -37.845722, 150.734044 -38.295383, 149.927302 -38.295383, 149.927302 -38.745043, 149.120561 -38.745043, 149.120561 -38.295383, 148.31382 -38.295383))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_022</t>
   </si>
   <si>
+    <t>POLYGON ((132.985734 -33.798781, 132.178993 -33.798781, 132.178993 -33.349121, 132.178993 -32.89946, 132.178993 -32.4498, 131.372251 -32.4498, 130.56551 -32.4498, 130.56551 -32.00014, 129.758769 -32.00014, 129.758769 -31.55048, 130.56551 -31.55048, 131.372251 -31.55048, 132.178993 -31.55048, 132.178993 -32.00014, 132.985734 -32.00014, 133.792475 -32.00014, 133.792475 -32.4498, 134.599217 -32.4498, 134.599217 -32.89946, 133.792475 -32.89946, 133.792475 -33.349121, 132.985734 -33.349121, 132.985734 -33.798781))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_023</t>
   </si>
   <si>
+    <t>POLYGON ((128.952027 -33.798781, 128.952027 -33.349121, 128.952027 -32.89946, 128.952027 -32.4498, 128.952027 -32.00014, 128.952027 -31.55048, 129.758769 -31.55048, 129.758769 -32.00014, 130.56551 -32.00014, 130.56551 -32.4498, 131.372251 -32.4498, 132.178993 -32.4498, 132.178993 -32.89946, 132.178993 -33.349121, 132.178993 -33.798781, 132.178993 -34.248441, 131.372251 -34.248441, 130.56551 -34.248441, 130.56551 -33.798781, 129.758769 -33.798781, 128.952027 -33.798781))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_024</t>
   </si>
   <si>
+    <t>POLYGON ((143.473371 -12.215092, 142.66663 -12.215092, 142.66663 -11.765432, 142.66663 -11.315772, 143.473371 -11.315772, 143.473371 -10.866112, 143.473371 -10.416451, 142.66663 -10.416451, 142.66663 -9.966791, 142.66663 -9.517131, 142.66663 -9.067471, 143.473371 -9.067471, 144.280113 -9.067471, 144.280113 -9.517131, 145.086854 -9.517131, 145.086854 -9.966791, 145.893596 -9.966791, 145.893596 -10.416451, 145.893596 -10.866112, 145.086854 -10.866112, 144.280113 -10.866112, 144.280113 -11.315772, 144.280113 -11.765432, 144.280113 -12.215092, 144.280113 -12.664752, 144.280113 -13.114412, 144.280113 -13.564073, 145.086854 -13.564073, 145.086854 -14.013733, 145.893596 -14.013733, 145.893596 -13.564073, 146.700337 -13.564073, 147.507078 -13.564073, 147.507078 -14.013733, 147.507078 -14.463393, 146.700337 -14.463393, 145.893596 -14.463393, 145.893596 -14.913053, 145.086854 -14.913053, 145.086854 -14.463393, 144.280113 -14.463393, 144.280113 -14.013733, 143.473371 -14.013733, 143.473371 -13.564073, 143.473371 -13.114412, 143.473371 -12.664752, 143.473371 -12.215092))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_025</t>
   </si>
   <si>
+    <t>POLYGON ((145.893596 -17.161354, 145.893596 -16.711694, 145.893596 -16.262034, 145.086854 -16.262034, 145.086854 -15.812374, 145.086854 -15.362713, 145.086854 -14.913053, 145.893596 -14.913053, 145.893596 -15.362713, 145.893596 -15.812374, 146.700337 -15.812374, 146.700337 -15.362713, 147.507078 -15.362713, 148.31382 -15.362713, 148.31382 -14.913053, 149.120561 -14.913053, 149.120561 -15.362713, 149.927302 -15.362713, 150.734044 -15.362713, 150.734044 -15.812374, 150.734044 -16.262034, 149.927302 -16.262034, 149.927302 -16.711694, 149.120561 -16.711694, 149.120561 -17.161354, 149.120561 -17.611014, 148.31382 -17.611014, 148.31382 -18.060674, 147.507078 -18.060674, 147.507078 -18.510335, 147.507078 -18.959995, 146.700337 -18.959995, 146.700337 -18.510335, 146.700337 -18.060674, 145.893596 -18.060674, 145.893596 -17.611014, 145.893596 -17.161354), (146.700337 -16.262034, 147.507078 -16.262034, 147.507078 -15.812374, 146.700337 -15.812374, 146.700337 -16.262034))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_026</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((137.826182 -15.362713, 137.019441 -15.362713, 137.019441 -14.913053, 137.019441 -14.463393, 137.019441 -14.013733, 136.212699 -14.013733, 136.212699 -13.564073, 137.019441 -13.564073, 137.019441 -13.114412, 137.019441 -12.664752, 137.826182 -12.664752, 138.632923 -12.664752, 138.632923 -13.114412, 138.632923 -13.564073, 139.439665 -13.564073, 139.439665 -14.013733, 139.439665 -14.463393, 139.439665 -14.913053, 140.246406 -14.913053, 140.246406 -15.362713, 140.246406 -15.812374, 139.439665 -15.812374, 138.632923 -15.812374, 137.826182 -15.812374, 137.826182 -15.362713)), ((140.246406 -17.161354, 140.246406 -16.711694, 141.053147 -16.711694, 141.053147 -17.161354, 140.246406 -17.161354)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_027</t>
   </si>
   <si>
+    <t>POLYGON ((131.372251 -10.866112, 131.372251 -10.416451, 131.372251 -9.966791, 131.372251 -9.517131, 131.372251 -9.067471, 132.178993 -9.067471, 132.985734 -9.067471, 133.792475 -9.067471, 134.599217 -9.067471, 135.405958 -9.067471, 136.212699 -9.067471, 137.019441 -9.067471, 137.019441 -9.517131, 137.826182 -9.517131, 137.826182 -9.966791, 138.632923 -9.966791, 139.439665 -9.966791, 139.439665 -10.416451, 140.246406 -10.416451, 140.246406 -10.866112, 140.246406 -11.315772, 140.246406 -11.765432, 139.439665 -11.765432, 138.632923 -11.765432, 138.632923 -12.215092, 138.632923 -12.664752, 137.826182 -12.664752, 137.019441 -12.664752, 137.019441 -12.215092, 136.212699 -12.215092, 135.405958 -12.215092, 135.405958 -11.765432, 136.212699 -11.765432, 136.212699 -11.315772, 135.405958 -11.315772, 134.599217 -11.315772, 133.792475 -11.315772, 132.985734 -11.315772, 132.178993 -11.315772, 131.372251 -11.315772, 131.372251 -10.866112), (138.632923 -10.416451, 138.632923 -10.866112, 138.632923 -11.315772, 139.439665 -11.315772, 139.439665 -10.866112, 139.439665 -10.416451, 138.632923 -10.416451))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_028</t>
   </si>
   <si>
+    <t>POLYGON ((139.439665 -14.013733, 139.439665 -13.564073, 138.632923 -13.564073, 138.632923 -13.114412, 138.632923 -12.664752, 138.632923 -12.215092, 138.632923 -11.765432, 139.439665 -11.765432, 140.246406 -11.765432, 140.246406 -11.315772, 140.246406 -10.866112, 140.246406 -10.416451, 141.053147 -10.416451, 141.053147 -10.866112, 141.053147 -11.315772, 141.859889 -11.315772, 141.859889 -11.765432, 141.859889 -12.215092, 141.859889 -12.664752, 141.859889 -13.114412, 141.053147 -13.114412, 141.053147 -13.564073, 141.053147 -14.013733, 141.053147 -14.463393, 141.053147 -14.913053, 141.053147 -15.362713, 140.246406 -15.362713, 140.246406 -14.913053, 139.439665 -14.913053, 139.439665 -14.463393, 139.439665 -14.013733))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_029</t>
   </si>
   <si>
+    <t>POLYGON ((149.927302 -36.946402, 149.927302 -36.496742, 149.927302 -36.047082, 150.734044 -36.047082, 150.734044 -36.496742, 150.734044 -36.946402, 150.734044 -37.396062, 150.734044 -37.845722, 149.927302 -37.845722, 149.927302 -37.396062, 149.927302 -36.946402))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_030</t>
   </si>
   <si>
+    <t>POLYGON ((119.271131 -34.248441, 119.271131 -33.798781, 120.077872 -33.798781, 120.884614 -33.798781, 120.884614 -34.248441, 120.884614 -34.698101, 120.077872 -34.698101, 120.077872 -35.147761, 119.271131 -35.147761, 119.271131 -34.698101, 119.271131 -34.248441))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_031</t>
   </si>
   <si>
+    <t>POLYGON ((144.280113 -39.194703, 144.280113 -38.745043, 144.280113 -38.295383, 145.086854 -38.295383, 145.893596 -38.295383, 145.893596 -38.745043, 145.893596 -39.194703, 145.086854 -39.194703, 145.086854 -39.644363, 145.086854 -40.094023, 144.280113 -40.094023, 144.280113 -39.644363, 144.280113 -39.194703))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_032</t>
   </si>
   <si>
+    <t>POLYGON ((141.859889 -39.644363, 141.859889 -39.194703, 141.053147 -39.194703, 141.053147 -38.745043, 140.246406 -38.745043, 140.246406 -38.295383, 139.439665 -38.295383, 139.439665 -37.845722, 139.439665 -37.396062, 140.246406 -37.396062, 140.246406 -37.845722, 141.053147 -37.845722, 141.859889 -37.845722, 141.859889 -38.295383, 142.66663 -38.295383, 143.473371 -38.295383, 143.473371 -38.745043, 143.473371 -39.194703, 143.473371 -39.644363, 143.473371 -40.094023, 143.473371 -40.543684, 143.473371 -40.993344, 142.66663 -40.993344, 142.66663 -40.543684, 142.66663 -40.094023, 142.66663 -39.644363, 141.859889 -39.644363))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_033</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((112.010459 -24.805577, 112.010459 -24.355917, 112.8172 -24.355917, 112.8172 -23.906257, 113.623942 -23.906257, 113.623942 -24.355917, 113.623942 -24.805577, 113.623942 -25.255237, 112.8172 -25.255237, 112.010459 -25.255237, 111.203717 -25.255237, 111.203717 -24.805577, 112.010459 -24.805577)), ((114.430683 -23.906257, 113.623942 -23.906257, 113.623942 -23.456597, 114.430683 -23.456597, 114.430683 -23.906257)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_034</t>
   </si>
   <si>
+    <t>POLYGON ((151.540785 -22.557276, 151.540785 -22.107616, 151.540785 -21.657956, 151.540785 -21.208296, 152.347526 -21.208296, 153.154268 -21.208296, 153.961009 -21.208296, 154.76775 -21.208296, 154.76775 -21.657956, 154.76775 -22.107616, 154.76775 -22.557276, 153.961009 -22.557276, 153.961009 -23.006936, 153.154268 -23.006936, 153.154268 -23.456597, 152.347526 -23.456597, 152.347526 -23.906257, 151.540785 -23.906257, 150.734044 -23.906257, 150.734044 -23.456597, 151.540785 -23.456597, 151.540785 -23.006936, 151.540785 -22.557276))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_035</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((154.76775 -21.208296, 153.961009 -21.208296, 153.154268 -21.208296, 152.347526 -21.208296, 152.347526 -20.758636, 152.347526 -20.308975, 152.347526 -19.859315, 152.347526 -19.409655, 153.154268 -19.409655, 153.154268 -19.859315, 153.961009 -19.859315, 153.961009 -20.308975, 154.76775 -20.308975, 154.76775 -20.758636, 154.76775 -21.208296)), ((157.187974 -20.758636, 157.187974 -21.208296, 156.381233 -21.208296, 156.381233 -21.657956, 155.574492 -21.657956, 155.574492 -21.208296, 155.574492 -20.758636, 156.381233 -20.758636, 157.187974 -20.758636)), ((155.574492 -17.611014, 155.574492 -18.060674, 155.574492 -18.510335, 155.574492 -18.959995, 154.76775 -18.959995, 154.76775 -18.510335, 154.76775 -18.060674, 154.76775 -17.611014, 155.574492 -17.611014)), ((155.574492 -17.611014, 155.574492 -17.161354, 156.381233 -17.161354, 156.381233 -17.611014, 155.574492 -17.611014)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_036</t>
   </si>
   <si>
+    <t>POLYGON ((146.700337 -38.295383, 146.700337 -37.845722, 147.507078 -37.845722, 148.31382 -37.845722, 148.31382 -38.295383, 147.507078 -38.295383, 147.507078 -38.745043, 146.700337 -38.745043, 145.893596 -38.745043, 145.893596 -38.295383, 146.700337 -38.295383))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_037</t>
   </si>
   <si>
+    <t>POLYGON ((145.893596 -38.745043, 146.700337 -38.745043, 147.507078 -38.745043, 147.507078 -38.295383, 148.31382 -38.295383, 149.120561 -38.295383, 149.120561 -38.745043, 149.120561 -39.194703, 149.120561 -39.644363, 148.31382 -39.644363, 147.507078 -39.644363, 146.700337 -39.644363, 145.893596 -39.644363, 145.086854 -39.644363, 145.086854 -39.194703, 145.893596 -39.194703, 145.893596 -38.745043))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_038</t>
   </si>
   <si>
+    <t>POLYGON ((116.044166 -21.208296, 115.237424 -21.208296, 115.237424 -20.758636, 115.237424 -20.308975, 114.430683 -20.308975, 114.430683 -19.859315, 114.430683 -19.409655, 115.237424 -19.409655, 115.237424 -18.959995, 115.237424 -18.510335, 116.044166 -18.510335, 116.850907 -18.510335, 117.657648 -18.510335, 117.657648 -18.959995, 117.657648 -19.409655, 117.657648 -19.859315, 117.657648 -20.308975, 116.850907 -20.308975, 116.044166 -20.308975, 116.044166 -20.758636, 116.850907 -20.758636, 116.850907 -21.208296, 116.044166 -21.208296))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_039</t>
   </si>
   <si>
+    <t>POLYGON ((112.010459 -23.456597, 112.010459 -23.006936, 112.8172 -23.006936, 112.8172 -22.557276, 112.8172 -22.107616, 112.8172 -21.657956, 113.623942 -21.657956, 113.623942 -21.208296, 112.8172 -21.208296, 112.010459 -21.208296, 112.010459 -20.758636, 112.010459 -20.308975, 112.8172 -20.308975, 112.8172 -19.859315, 113.623942 -19.859315, 114.430683 -19.859315, 114.430683 -20.308975, 115.237424 -20.308975, 115.237424 -20.758636, 115.237424 -21.208296, 115.237424 -21.657956, 115.237424 -22.107616, 114.430683 -22.107616, 114.430683 -22.557276, 114.430683 -23.006936, 114.430683 -23.456597, 113.623942 -23.456597, 113.623942 -23.906257, 112.8172 -23.906257, 112.8172 -24.355917, 112.010459 -24.355917, 112.010459 -24.805577, 111.203717 -24.805577, 111.203717 -24.355917, 111.203717 -23.906257, 112.010459 -23.906257, 112.010459 -23.456597))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_040</t>
   </si>
   <si>
+    <t>POLYGON ((113.623942 -27.503538, 112.8172 -27.503538, 112.8172 -27.053878, 113.623942 -27.053878, 114.430683 -27.053878, 114.430683 -27.503538, 114.430683 -27.953198, 114.430683 -28.402859, 113.623942 -28.402859, 113.623942 -27.953198, 113.623942 -27.503538))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_041</t>
   </si>
   <si>
+    <t>POLYGON ((111.203717 -26.154558, 111.203717 -25.704898, 111.203717 -25.255237, 112.010459 -25.255237, 112.8172 -25.255237, 113.623942 -25.255237, 113.623942 -25.704898, 113.623942 -26.154558, 114.430683 -26.154558, 114.430683 -26.604218, 114.430683 -27.053878, 113.623942 -27.053878, 112.8172 -27.053878, 112.010459 -27.053878, 112.010459 -26.604218, 111.203717 -26.604218, 111.203717 -26.154558))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_042</t>
   </si>
   <si>
+    <t>POLYGON ((149.927302 -35.597422, 149.927302 -35.147761, 150.734044 -35.147761, 150.734044 -35.597422, 150.734044 -36.047082, 149.927302 -36.047082, 149.927302 -35.597422))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_043</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((113.623942 -30.65116, 113.623942 -30.201499, 113.623942 -29.751839, 113.623942 -29.302179, 112.8172 -29.302179, 112.8172 -28.852519, 112.8172 -28.402859, 112.010459 -28.402859, 112.010459 -27.953198, 112.010459 -27.503538, 112.010459 -27.053878, 112.8172 -27.053878, 112.8172 -27.503538, 113.623942 -27.503538, 113.623942 -27.953198, 113.623942 -28.402859, 114.430683 -28.402859, 114.430683 -28.852519, 115.237424 -28.852519, 115.237424 -29.302179, 115.237424 -29.751839, 115.237424 -30.201499, 115.237424 -30.65116, 115.237424 -31.10082, 116.044166 -31.10082, 116.044166 -31.55048, 115.237424 -31.55048, 114.430683 -31.55048, 114.430683 -31.10082, 114.430683 -30.65116, 113.623942 -30.65116)), ((111.203717 -26.604218, 112.010459 -26.604218, 112.010459 -27.053878, 111.203717 -27.053878, 111.203717 -26.604218)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_044</t>
   </si>
   <si>
+    <t>POLYGON ((151.540785 -32.89946, 151.540785 -32.4498, 152.347526 -32.4498, 152.347526 -32.00014, 153.154268 -32.00014, 153.961009 -32.00014, 153.961009 -32.4498, 153.154268 -32.4498, 153.154268 -32.89946, 153.154268 -33.349121, 152.347526 -33.349121, 152.347526 -33.798781, 152.347526 -34.248441, 151.540785 -34.248441, 151.540785 -33.798781, 151.540785 -33.349121, 151.540785 -32.89946))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_045</t>
   </si>
   <si>
+    <t>POLYGON ((114.430683 -33.349121, 113.623942 -33.349121, 113.623942 -32.89946, 113.623942 -32.4498, 114.430683 -32.4498, 114.430683 -32.00014, 114.430683 -31.55048, 115.237424 -31.55048, 116.044166 -31.55048, 116.044166 -32.00014, 116.044166 -32.4498, 116.044166 -32.89946, 115.237424 -32.89946, 115.237424 -33.349121, 114.430683 -33.349121))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_046</t>
   </si>
   <si>
+    <t>POLYGON ((139.439665 -37.396062, 139.439665 -36.946402, 140.246406 -36.946402, 140.246406 -37.396062, 139.439665 -37.396062))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_047</t>
   </si>
   <si>
+    <t>POLYGON ((146.700337 -44.590625, 145.893596 -44.590625, 145.893596 -44.140965, 145.086854 -44.140965, 145.086854 -43.691305, 145.086854 -43.241645, 145.086854 -42.791984, 145.893596 -42.791984, 145.893596 -43.241645, 146.700337 -43.241645, 146.700337 -42.791984, 147.507078 -42.791984, 147.507078 -42.342324, 148.31382 -42.342324, 148.31382 -41.892664, 149.120561 -41.892664, 149.120561 -42.342324, 149.120561 -42.791984, 149.120561 -43.241645, 148.31382 -43.241645, 148.31382 -43.691305, 148.31382 -44.140965, 147.507078 -44.140965, 147.507078 -44.590625, 146.700337 -44.590625))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_048</t>
   </si>
   <si>
+    <t>POLYGON ((116.850907 -18.510335, 116.850907 -18.060674, 117.657648 -18.060674, 117.657648 -17.611014, 117.657648 -17.161354, 118.46439 -17.161354, 118.46439 -16.711694, 118.46439 -16.262034, 119.271131 -16.262034, 120.077872 -16.262034, 120.884614 -16.262034, 121.691355 -16.262034, 122.498096 -16.262034, 122.498096 -16.711694, 121.691355 -16.711694, 121.691355 -17.161354, 122.498096 -17.161354, 122.498096 -17.611014, 122.498096 -18.060674, 122.498096 -18.510335, 121.691355 -18.510335, 121.691355 -18.959995, 120.884614 -18.959995, 120.884614 -19.409655, 120.077872 -19.409655, 120.077872 -19.859315, 119.271131 -19.859315, 118.46439 -19.859315, 118.46439 -20.308975, 117.657648 -20.308975, 117.657648 -19.859315, 117.657648 -19.409655, 117.657648 -18.959995, 117.657648 -18.510335, 116.850907 -18.510335))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_049</t>
   </si>
   <si>
+    <t>POLYGON ((129.758769 -10.866112, 128.952027 -10.866112, 128.952027 -10.416451, 128.145286 -10.416451, 128.145286 -9.966791, 128.952027 -9.966791, 128.952027 -9.517131, 129.758769 -9.517131, 130.56551 -9.517131, 131.372251 -9.517131, 131.372251 -9.966791, 131.372251 -10.416451, 131.372251 -10.866112, 131.372251 -11.315772, 130.56551 -11.315772, 130.56551 -10.866112, 129.758769 -10.866112))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_050</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((121.691355 -13.564073, 120.884614 -13.564073, 120.884614 -13.114412, 121.691355 -13.114412, 121.691355 -13.564073)), ((122.498096 -13.114412, 121.691355 -13.114412, 121.691355 -12.664752, 122.498096 -12.664752, 122.498096 -12.215092, 122.498096 -11.765432, 123.304838 -11.765432, 124.111579 -11.765432, 124.91832 -11.765432, 124.91832 -12.215092, 124.91832 -12.664752, 124.111579 -12.664752, 123.304838 -12.664752, 123.304838 -13.114412, 122.498096 -13.114412)), ((128.952027 -14.463393, 128.145286 -14.463393, 128.145286 -14.013733, 128.952027 -14.013733, 128.952027 -14.463393)), ((127.338544 -14.013733, 127.338544 -13.564073, 126.531803 -13.564073, 125.725062 -13.564073, 125.725062 -13.114412, 126.531803 -13.114412, 127.338544 -13.114412, 128.145286 -13.114412, 128.145286 -13.564073, 128.145286 -14.013733, 127.338544 -14.013733)))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_051</t>
   </si>
   <si>
+    <t>POLYGON ((122.498096 -35.147761, 121.691355 -35.147761, 121.691355 -34.698101, 120.884614 -34.698101, 120.884614 -34.248441, 120.884614 -33.798781, 121.691355 -33.798781, 122.498096 -33.798781, 123.304838 -33.798781, 123.304838 -33.349121, 124.111579 -33.349121, 124.111579 -33.798781, 124.91832 -33.798781, 124.91832 -34.248441, 124.91832 -34.698101, 124.111579 -34.698101, 124.111579 -35.147761, 123.304838 -35.147761, 122.498096 -35.147761))</t>
+  </si>
+  <si>
     <t>elc_wof_AUS_052</t>
   </si>
   <si>
+    <t>POLYGON ((124.91832 -34.248441, 124.91832 -33.798781, 124.111579 -33.798781, 124.111579 -33.349121, 124.111579 -32.89946, 124.91832 -32.89946, 124.91832 -32.4498, 125.725062 -32.4498, 126.531803 -32.4498, 127.338544 -32.4498, 128.145286 -32.4498, 128.952027 -32.4498, 128.952027 -32.89946, 128.952027 -33.349121, 128.952027 -33.798781, 128.145286 -33.798781, 127.338544 -33.798781, 127.338544 -34.248441, 126.531803 -34.248441, 125.725062 -34.248441, 124.91832 -34.248441))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_001</t>
   </si>
   <si>
@@ -1019,6 +1469,9 @@
     <t>elc_won_AUS_004</t>
   </si>
   <si>
+    <t>POLYGON ((145.227395 -42.471684, 145.227395 -42.022024, 144.426317 -42.022024, 144.426317 -41.572364, 144.426317 -41.122704, 144.426317 -40.673043, 144.426317 -40.223383, 145.227395 -40.223383, 145.227395 -40.673043, 146.028473 -40.673043, 146.829551 -40.673043, 146.829551 -41.122704, 146.829551 -41.572364, 146.829551 -42.022024, 146.028473 -42.022024, 146.028473 -42.471684, 145.227395 -42.471684))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_005</t>
   </si>
   <si>
@@ -1034,9 +1487,15 @@
     <t>elc_won_AUS_009</t>
   </si>
   <si>
+    <t>POLYGON ((135.614461 -34.377801, 135.614461 -34.827461, 134.813383 -34.827461, 134.813383 -34.377801, 134.813383 -33.928141, 134.012305 -33.928141, 134.012305 -33.478481, 134.012305 -33.02882, 134.813383 -33.02882, 134.813383 -32.57916, 135.614461 -32.57916, 136.415539 -32.57916, 136.415539 -33.02882, 137.216617 -33.02882, 138.017695 -33.02882, 138.017695 -33.478481, 138.017695 -33.928141, 137.216617 -33.928141, 137.216617 -34.377801, 136.415539 -34.377801, 135.614461 -34.377801))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_010</t>
   </si>
   <si>
+    <t>POLYGON ((138.017695 -33.478481, 138.017695 -33.02882, 137.216617 -33.02882, 136.415539 -33.02882, 136.415539 -32.57916, 135.614461 -32.57916, 135.614461 -32.1295, 136.415539 -32.1295, 136.415539 -31.67984, 137.216617 -31.67984, 137.216617 -31.23018, 138.017695 -31.23018, 138.017695 -30.780519, 138.818772 -30.780519, 139.61985 -30.780519, 139.61985 -31.23018, 139.61985 -31.67984, 139.61985 -32.1295, 139.61985 -32.57916, 138.818772 -32.57916, 138.818772 -33.02882, 138.818772 -33.478481, 138.017695 -33.478481))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_011</t>
   </si>
   <si>
@@ -1049,9 +1508,15 @@
     <t>elc_won_AUS_014</t>
   </si>
   <si>
+    <t>POLYGON ((145.227395 -35.726781, 144.426317 -35.726781, 144.426317 -35.277121, 144.426317 -34.827461, 144.426317 -34.377801, 144.426317 -33.928141, 144.426317 -33.478481, 144.426317 -33.02882, 144.426317 -32.57916, 145.227395 -32.57916, 145.227395 -33.02882, 145.227395 -33.478481, 146.028473 -33.478481, 146.028473 -33.928141, 146.829551 -33.928141, 146.829551 -34.377801, 146.829551 -34.827461, 146.829551 -35.277121, 146.829551 -35.726781, 146.028473 -35.726781, 146.028473 -36.176442, 145.227395 -36.176442, 145.227395 -35.726781))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_015</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -33.928141, 146.028473 -33.478481, 145.227395 -33.478481, 145.227395 -33.02882, 145.227395 -32.57916, 144.426317 -32.57916, 144.426317 -32.1295, 144.426317 -31.67984, 144.426317 -31.23018, 145.227395 -31.23018, 145.227395 -30.780519, 145.227395 -30.330859, 145.227395 -29.881199, 146.028473 -29.881199, 146.829551 -29.881199, 146.829551 -30.330859, 146.829551 -30.780519, 146.829551 -31.23018, 146.829551 -31.67984, 147.630629 -31.67984, 147.630629 -32.1295, 147.630629 -32.57916, 147.630629 -33.02882, 147.630629 -33.478481, 146.829551 -33.478481, 146.829551 -33.928141, 146.028473 -33.928141))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_016</t>
   </si>
   <si>
@@ -1070,9 +1535,15 @@
     <t>elc_won_AUS_021</t>
   </si>
   <si>
+    <t>POLYGON ((142.023084 -24.934937, 142.023084 -24.485277, 141.222006 -24.485277, 141.222006 -24.035617, 141.222006 -23.585957, 141.222006 -23.136296, 142.023084 -23.136296, 142.023084 -22.686636, 142.824162 -22.686636, 142.824162 -22.236976, 142.824162 -21.787316, 143.625239 -21.787316, 143.625239 -22.236976, 143.625239 -22.686636, 144.426317 -22.686636, 145.227395 -22.686636, 145.227395 -23.136296, 145.227395 -23.585957, 144.426317 -23.585957, 144.426317 -24.035617, 144.426317 -24.485277, 143.625239 -24.485277, 143.625239 -24.934937, 142.824162 -24.934937, 142.023084 -24.934937))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_022</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -22.686636, 143.625239 -22.686636, 143.625239 -22.236976, 143.625239 -21.787316, 143.625239 -21.337656, 144.426317 -21.337656, 144.426317 -20.887995, 145.227395 -20.887995, 145.227395 -20.438335, 145.227395 -19.988675, 146.028473 -19.988675, 146.028473 -19.539015, 146.829551 -19.539015, 146.829551 -19.089355, 147.630629 -19.089355, 147.630629 -19.539015, 148.431706 -19.539015, 148.431706 -19.988675, 149.232784 -19.988675, 149.232784 -20.438335, 148.431706 -20.438335, 148.431706 -20.887995, 148.431706 -21.337656, 147.630629 -21.337656, 147.630629 -21.787316, 146.829551 -21.787316, 146.829551 -22.236976, 146.829551 -22.686636, 146.028473 -22.686636, 146.028473 -23.136296, 145.227395 -23.136296, 145.227395 -22.686636, 144.426317 -22.686636))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_023</t>
   </si>
   <si>
@@ -1085,78 +1556,153 @@
     <t>elc_won_AUS_026</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -41.572364, 146.829551 -41.122704, 146.829551 -40.673043, 147.630629 -40.673043, 147.630629 -40.223383, 147.630629 -39.773723, 148.431706 -39.773723, 148.431706 -40.223383, 148.431706 -40.673043, 148.431706 -41.122704, 148.431706 -41.572364, 148.431706 -42.022024, 147.630629 -42.022024, 147.630629 -42.471684, 146.829551 -42.471684, 146.028473 -42.471684, 146.028473 -42.022024, 146.829551 -42.022024, 146.829551 -41.572364))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_027</t>
   </si>
   <si>
+    <t>POLYGON ((146.829551 -37.075762, 146.829551 -36.626102, 147.630629 -36.626102, 147.630629 -36.176442, 147.630629 -35.726781, 148.431706 -35.726781, 148.431706 -36.176442, 148.431706 -36.626102, 149.232784 -36.626102, 149.232784 -37.075762, 150.033862 -37.075762, 150.033862 -37.525422, 150.033862 -37.975082, 149.232784 -37.975082, 148.431706 -37.975082, 147.630629 -37.975082, 147.630629 -37.525422, 147.630629 -37.075762, 146.829551 -37.075762))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_028</t>
   </si>
   <si>
+    <t>POLYGON ((135.614461 -28.532219, 135.614461 -28.082558, 135.614461 -27.632898, 135.614461 -27.183238, 136.415539 -27.183238, 136.415539 -27.632898, 137.216617 -27.632898, 137.216617 -27.183238, 137.216617 -26.733578, 138.017695 -26.733578, 138.017695 -27.183238, 138.818772 -27.183238, 138.818772 -27.632898, 138.818772 -28.082558, 138.818772 -28.532219, 139.61985 -28.532219, 139.61985 -28.981879, 139.61985 -29.431539, 139.61985 -29.881199, 139.61985 -30.330859, 139.61985 -30.780519, 138.818772 -30.780519, 138.017695 -30.780519, 138.017695 -30.330859, 138.017695 -29.881199, 137.216617 -29.881199, 136.415539 -29.881199, 136.415539 -29.431539, 136.415539 -28.981879, 136.415539 -28.532219, 135.614461 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_029</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -31.23018, 134.813383 -30.780519, 134.813383 -30.330859, 134.012305 -30.330859, 133.211228 -30.330859, 133.211228 -29.881199, 133.211228 -29.431539, 133.211228 -28.981879, 133.211228 -28.532219, 133.211228 -28.082558, 133.211228 -27.632898, 133.211228 -27.183238, 134.012305 -27.183238, 134.012305 -27.632898, 134.813383 -27.632898, 134.813383 -28.082558, 135.614461 -28.082558, 135.614461 -28.532219, 136.415539 -28.532219, 136.415539 -28.981879, 136.415539 -29.431539, 136.415539 -29.881199, 137.216617 -29.881199, 138.017695 -29.881199, 138.017695 -30.330859, 138.017695 -30.780519, 138.017695 -31.23018, 137.216617 -31.23018, 137.216617 -31.67984, 136.415539 -31.67984, 136.415539 -32.1295, 135.614461 -32.1295, 135.614461 -31.67984, 135.614461 -31.23018, 134.813383 -31.23018))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_030</t>
   </si>
   <si>
+    <t>POLYGON ((130.807994 -29.431539, 130.006916 -29.431539, 129.205838 -29.431539, 129.205838 -28.981879, 129.205838 -28.532219, 130.006916 -28.532219, 130.807994 -28.532219, 130.807994 -28.082558, 131.609072 -28.082558, 131.609072 -28.532219, 132.41015 -28.532219, 132.41015 -28.981879, 133.211228 -28.981879, 133.211228 -29.431539, 133.211228 -29.881199, 133.211228 -30.330859, 133.211228 -30.780519, 132.41015 -30.780519, 132.41015 -30.330859, 131.609072 -30.330859, 131.609072 -29.881199, 130.807994 -29.881199, 130.807994 -29.431539))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_031</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -28.532219, 129.205838 -28.082558, 129.205838 -27.632898, 129.205838 -27.183238, 129.205838 -26.733578, 130.006916 -26.733578, 130.807994 -26.733578, 131.609072 -26.733578, 131.609072 -26.283918, 132.41015 -26.283918, 133.211228 -26.283918, 133.211228 -26.733578, 133.211228 -27.183238, 133.211228 -27.632898, 133.211228 -28.082558, 133.211228 -28.532219, 133.211228 -28.981879, 132.41015 -28.981879, 132.41015 -28.532219, 131.609072 -28.532219, 131.609072 -28.082558, 130.807994 -28.082558, 130.807994 -28.532219, 130.006916 -28.532219, 129.205838 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_032</t>
   </si>
   <si>
+    <t>POLYGON ((133.211228 -32.1295, 132.41015 -32.1295, 132.41015 -31.67984, 133.211228 -31.67984, 133.211228 -31.23018, 133.211228 -30.780519, 133.211228 -30.330859, 134.012305 -30.330859, 134.813383 -30.330859, 134.813383 -30.780519, 134.813383 -31.23018, 135.614461 -31.23018, 135.614461 -31.67984, 135.614461 -32.1295, 135.614461 -32.57916, 134.813383 -32.57916, 134.813383 -33.02882, 134.012305 -33.02882, 134.012305 -32.57916, 133.211228 -32.57916, 133.211228 -32.1295))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_033</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -31.67984, 129.205838 -31.23018, 129.205838 -30.780519, 129.205838 -30.330859, 129.205838 -29.881199, 129.205838 -29.431539, 130.006916 -29.431539, 130.807994 -29.431539, 130.807994 -29.881199, 131.609072 -29.881199, 131.609072 -30.330859, 132.41015 -30.330859, 132.41015 -30.780519, 133.211228 -30.780519, 133.211228 -31.23018, 133.211228 -31.67984, 132.41015 -31.67984, 132.41015 -32.1295, 131.609072 -32.1295, 131.609072 -31.67984, 130.807994 -31.67984, 130.006916 -31.67984, 129.205838 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_034</t>
   </si>
   <si>
+    <t>POLYGON ((130.807994 -21.337656, 130.006916 -21.337656, 130.006916 -20.887995, 130.006916 -20.438335, 130.807994 -20.438335, 130.807994 -19.988675, 130.807994 -19.539015, 130.807994 -19.089355, 131.609072 -19.089355, 131.609072 -18.639695, 131.609072 -18.190034, 131.609072 -17.740374, 132.41015 -17.740374, 132.41015 -18.190034, 133.211228 -18.190034, 133.211228 -18.639695, 133.211228 -19.089355, 134.012305 -19.089355, 134.012305 -19.539015, 134.813383 -19.539015, 134.813383 -19.988675, 134.813383 -20.438335, 134.012305 -20.438335, 133.211228 -20.438335, 133.211228 -19.988675, 132.41015 -19.988675, 132.41015 -20.438335, 132.41015 -20.887995, 132.41015 -21.337656, 131.609072 -21.337656, 130.807994 -21.337656))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_035</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -21.787316, 134.012305 -21.787316, 133.211228 -21.787316, 133.211228 -22.236976, 132.41015 -22.236976, 132.41015 -21.787316, 132.41015 -21.337656, 132.41015 -20.887995, 132.41015 -20.438335, 132.41015 -19.988675, 133.211228 -19.988675, 133.211228 -20.438335, 134.012305 -20.438335, 134.813383 -20.438335, 134.813383 -19.988675, 135.614461 -19.988675, 135.614461 -20.438335, 136.415539 -20.438335, 136.415539 -20.887995, 136.415539 -21.337656, 137.216617 -21.337656, 137.216617 -21.787316, 136.415539 -21.787316, 135.614461 -21.787316, 135.614461 -21.337656, 134.813383 -21.337656, 134.813383 -21.787316))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_036</t>
   </si>
   <si>
+    <t>POLYGON ((130.006916 -22.236976, 130.006916 -21.787316, 130.006916 -21.337656, 130.807994 -21.337656, 131.609072 -21.337656, 132.41015 -21.337656, 132.41015 -21.787316, 132.41015 -22.236976, 131.609072 -22.236976, 131.609072 -22.686636, 131.609072 -23.136296, 130.807994 -23.136296, 130.006916 -23.136296, 129.205838 -23.136296, 129.205838 -22.686636, 129.205838 -22.236976, 130.006916 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_037</t>
   </si>
   <si>
+    <t>POLYGON ((133.211228 -23.585957, 132.41015 -23.585957, 131.609072 -23.585957, 131.609072 -23.136296, 131.609072 -22.686636, 131.609072 -22.236976, 132.41015 -22.236976, 133.211228 -22.236976, 133.211228 -21.787316, 134.012305 -21.787316, 134.813383 -21.787316, 134.813383 -21.337656, 135.614461 -21.337656, 135.614461 -21.787316, 136.415539 -21.787316, 136.415539 -22.236976, 136.415539 -22.686636, 135.614461 -22.686636, 135.614461 -23.136296, 134.813383 -23.136296, 134.012305 -23.136296, 134.012305 -23.585957, 133.211228 -23.585957))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_038</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -24.485277, 138.818772 -24.035617, 138.818772 -23.585957, 138.017695 -23.585957, 138.017695 -23.136296, 137.216617 -23.136296, 137.216617 -22.686636, 136.415539 -22.686636, 136.415539 -22.236976, 136.415539 -21.787316, 137.216617 -21.787316, 138.017695 -21.787316, 138.017695 -22.236976, 138.818772 -22.236976, 138.818772 -22.686636, 139.61985 -22.686636, 139.61985 -23.136296, 140.420928 -23.136296, 140.420928 -23.585957, 140.420928 -24.035617, 141.222006 -24.035617, 141.222006 -24.485277, 141.222006 -24.934937, 140.420928 -24.934937, 140.420928 -24.485277, 139.61985 -24.485277, 138.818772 -24.485277))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_039</t>
   </si>
   <si>
+    <t>POLYGON ((138.818772 -28.532219, 138.818772 -28.082558, 138.818772 -27.632898, 138.818772 -27.183238, 138.017695 -27.183238, 138.017695 -26.733578, 137.216617 -26.733578, 137.216617 -26.283918, 137.216617 -25.834257, 138.017695 -25.834257, 138.818772 -25.834257, 139.61985 -25.834257, 139.61985 -26.283918, 140.420928 -26.283918, 140.420928 -26.733578, 140.420928 -27.183238, 140.420928 -27.632898, 140.420928 -28.082558, 140.420928 -28.532219, 139.61985 -28.532219, 138.818772 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_040</t>
   </si>
   <si>
+    <t>POLYGON ((136.415539 -25.384597, 136.415539 -24.934937, 135.614461 -24.934937, 135.614461 -24.485277, 135.614461 -24.035617, 135.614461 -23.585957, 134.813383 -23.585957, 134.813383 -23.136296, 135.614461 -23.136296, 135.614461 -22.686636, 136.415539 -22.686636, 137.216617 -22.686636, 137.216617 -23.136296, 138.017695 -23.136296, 138.017695 -23.585957, 138.818772 -23.585957, 138.818772 -24.035617, 138.818772 -24.485277, 139.61985 -24.485277, 140.420928 -24.485277, 140.420928 -24.934937, 141.222006 -24.934937, 141.222006 -25.384597, 141.222006 -25.834257, 141.222006 -26.283918, 140.420928 -26.283918, 139.61985 -26.283918, 139.61985 -25.834257, 138.818772 -25.834257, 138.017695 -25.834257, 137.216617 -25.834257, 136.415539 -25.834257, 136.415539 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_041</t>
   </si>
   <si>
+    <t>POLYGON ((130.807994 -25.384597, 130.807994 -24.934937, 130.006916 -24.934937, 129.205838 -24.934937, 129.205838 -24.485277, 129.205838 -24.035617, 129.205838 -23.585957, 129.205838 -23.136296, 130.006916 -23.136296, 130.807994 -23.136296, 131.609072 -23.136296, 131.609072 -23.585957, 132.41015 -23.585957, 132.41015 -24.035617, 132.41015 -24.485277, 132.41015 -24.934937, 132.41015 -25.384597, 131.609072 -25.384597, 130.807994 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_042</t>
   </si>
   <si>
+    <t>POLYGON ((129.205838 -25.384597, 129.205838 -24.934937, 130.006916 -24.934937, 130.807994 -24.934937, 130.807994 -25.384597, 131.609072 -25.384597, 132.41015 -25.384597, 133.211228 -25.384597, 133.211228 -25.834257, 133.211228 -26.283918, 132.41015 -26.283918, 131.609072 -26.283918, 131.609072 -26.733578, 130.807994 -26.733578, 130.006916 -26.733578, 129.205838 -26.733578, 129.205838 -26.283918, 129.205838 -25.834257, 129.205838 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_043</t>
   </si>
   <si>
+    <t>POLYGON ((133.211228 -25.384597, 132.41015 -25.384597, 132.41015 -24.934937, 132.41015 -24.485277, 132.41015 -24.035617, 132.41015 -23.585957, 133.211228 -23.585957, 134.012305 -23.585957, 134.012305 -23.136296, 134.813383 -23.136296, 134.813383 -23.585957, 135.614461 -23.585957, 135.614461 -24.035617, 135.614461 -24.485277, 135.614461 -24.934937, 136.415539 -24.934937, 136.415539 -25.384597, 136.415539 -25.834257, 135.614461 -25.834257, 135.614461 -25.384597, 134.813383 -25.384597, 134.012305 -25.384597, 134.012305 -25.834257, 133.211228 -25.834257, 133.211228 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_044</t>
   </si>
   <si>
+    <t>POLYGON ((134.813383 -27.632898, 134.012305 -27.632898, 134.012305 -27.183238, 133.211228 -27.183238, 133.211228 -26.733578, 133.211228 -26.283918, 133.211228 -25.834257, 134.012305 -25.834257, 134.012305 -25.384597, 134.813383 -25.384597, 135.614461 -25.384597, 135.614461 -25.834257, 136.415539 -25.834257, 137.216617 -25.834257, 137.216617 -26.283918, 137.216617 -26.733578, 137.216617 -27.183238, 137.216617 -27.632898, 136.415539 -27.632898, 136.415539 -27.183238, 135.614461 -27.183238, 135.614461 -27.632898, 135.614461 -28.082558, 134.813383 -28.082558, 134.813383 -27.632898))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_045</t>
   </si>
   <si>
+    <t>POLYGON ((137.216617 -21.337656, 136.415539 -21.337656, 136.415539 -20.887995, 136.415539 -20.438335, 135.614461 -20.438335, 135.614461 -19.988675, 134.813383 -19.988675, 134.813383 -19.539015, 134.012305 -19.539015, 134.012305 -19.089355, 133.211228 -19.089355, 133.211228 -18.639695, 133.211228 -18.190034, 134.012305 -18.190034, 134.813383 -18.190034, 135.614461 -18.190034, 136.415539 -18.190034, 137.216617 -18.190034, 137.216617 -18.639695, 138.017695 -18.639695, 138.017695 -19.089355, 138.818772 -19.089355, 139.61985 -19.089355, 140.420928 -19.089355, 141.222006 -19.089355, 141.222006 -18.639695, 141.222006 -18.190034, 142.023084 -18.190034, 142.023084 -18.639695, 142.023084 -19.089355, 142.824162 -19.089355, 143.625239 -19.089355, 143.625239 -19.539015, 143.625239 -19.988675, 143.625239 -20.438335, 143.625239 -20.887995, 143.625239 -21.337656, 143.625239 -21.787316, 142.824162 -21.787316, 142.824162 -22.236976, 142.824162 -22.686636, 142.023084 -22.686636, 142.023084 -23.136296, 141.222006 -23.136296, 141.222006 -23.585957, 141.222006 -24.035617, 140.420928 -24.035617, 140.420928 -23.585957, 140.420928 -23.136296, 139.61985 -23.136296, 139.61985 -22.686636, 138.818772 -22.686636, 138.818772 -22.236976, 138.017695 -22.236976, 138.017695 -21.787316, 137.216617 -21.787316, 137.216617 -21.337656))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_046</t>
   </si>
   <si>
+    <t>POLYGON ((132.41015 -18.190034, 132.41015 -17.740374, 131.609072 -17.740374, 131.609072 -17.290714, 131.609072 -16.841054, 131.609072 -16.391394, 131.609072 -15.941733, 131.609072 -15.492073, 131.609072 -15.042413, 131.609072 -14.592753, 131.609072 -14.143093, 132.41015 -14.143093, 133.211228 -14.143093, 133.211228 -14.592753, 133.211228 -15.042413, 134.012305 -15.042413, 134.813383 -15.042413, 134.813383 -15.492073, 135.614461 -15.492073, 135.614461 -15.941733, 135.614461 -16.391394, 134.813383 -16.391394, 134.813383 -16.841054, 134.813383 -17.290714, 135.614461 -17.290714, 135.614461 -17.740374, 136.415539 -17.740374, 136.415539 -18.190034, 135.614461 -18.190034, 134.813383 -18.190034, 134.012305 -18.190034, 133.211228 -18.190034, 132.41015 -18.190034))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_047</t>
   </si>
   <si>
+    <t>POLYGON ((140.420928 -17.290714, 140.420928 -16.841054, 140.420928 -16.391394, 141.222006 -16.391394, 141.222006 -15.941733, 141.222006 -15.492073, 141.222006 -15.042413, 142.023084 -15.042413, 142.023084 -15.492073, 142.023084 -15.941733, 142.023084 -16.391394, 142.023084 -16.841054, 142.824162 -16.841054, 142.824162 -17.290714, 142.824162 -17.740374, 142.824162 -18.190034, 142.824162 -18.639695, 142.824162 -19.089355, 142.023084 -19.089355, 142.023084 -18.639695, 142.023084 -18.190034, 141.222006 -18.190034, 141.222006 -17.740374, 140.420928 -17.740374, 140.420928 -17.290714))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_048</t>
   </si>
   <si>
+    <t>POLYGON ((138.017695 -18.639695, 137.216617 -18.639695, 137.216617 -18.190034, 136.415539 -18.190034, 136.415539 -17.740374, 135.614461 -17.740374, 135.614461 -17.290714, 134.813383 -17.290714, 134.813383 -16.841054, 134.813383 -16.391394, 135.614461 -16.391394, 135.614461 -15.941733, 136.415539 -15.941733, 136.415539 -16.391394, 137.216617 -16.391394, 137.216617 -15.941733, 138.017695 -15.941733, 138.017695 -16.391394, 138.818772 -16.391394, 138.818772 -16.841054, 139.61985 -16.841054, 139.61985 -17.290714, 140.420928 -17.290714, 140.420928 -17.740374, 141.222006 -17.740374, 141.222006 -18.190034, 141.222006 -18.639695, 141.222006 -19.089355, 140.420928 -19.089355, 139.61985 -19.089355, 138.818772 -19.089355, 138.017695 -19.089355, 138.017695 -18.639695))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_049</t>
   </si>
   <si>
+    <t>POLYGON ((131.609072 -13.693433, 131.609072 -13.243772, 131.609072 -12.794112, 131.609072 -12.344452, 131.609072 -11.894792, 132.41015 -11.894792, 132.41015 -11.445132, 132.41015 -10.995471, 133.211228 -10.995471, 133.211228 -11.445132, 134.012305 -11.445132, 134.813383 -11.445132, 134.813383 -11.894792, 135.614461 -11.894792, 135.614461 -11.445132, 136.415539 -11.445132, 136.415539 -10.995471, 137.216617 -10.995471, 137.216617 -11.445132, 137.216617 -11.894792, 137.216617 -12.344452, 137.216617 -12.794112, 137.216617 -13.243772, 136.415539 -13.243772, 136.415539 -13.693433, 137.216617 -13.693433, 137.216617 -14.143093, 137.216617 -14.592753, 136.415539 -14.592753, 135.614461 -14.592753, 135.614461 -15.042413, 136.415539 -15.042413, 136.415539 -15.492073, 137.216617 -15.492073, 137.216617 -15.941733, 137.216617 -16.391394, 136.415539 -16.391394, 136.415539 -15.941733, 135.614461 -15.941733, 135.614461 -15.492073, 134.813383 -15.492073, 134.813383 -15.042413, 134.012305 -15.042413, 133.211228 -15.042413, 133.211228 -14.592753, 133.211228 -14.143093, 132.41015 -14.143093, 131.609072 -14.143093, 131.609072 -13.693433))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_050</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((143.625239 -16.841054, 143.625239 -16.391394, 143.625239 -15.941733, 143.625239 -15.492073, 142.824162 -15.492073, 142.824162 -15.941733, 142.824162 -16.391394, 142.023084 -16.391394, 142.023084 -15.941733, 142.023084 -15.492073, 142.023084 -15.042413, 141.222006 -15.042413, 141.222006 -14.592753, 141.222006 -14.143093, 141.222006 -13.693433, 141.222006 -13.243772, 141.222006 -12.794112, 141.222006 -12.344452, 142.023084 -12.344452, 142.023084 -11.894792, 142.023084 -11.445132, 142.023084 -10.995471, 142.023084 -10.545811, 142.023084 -10.096151, 142.824162 -10.096151, 142.824162 -10.545811, 142.824162 -10.995471, 142.824162 -11.445132, 142.824162 -11.894792, 143.625239 -11.894792, 143.625239 -12.344452, 143.625239 -12.794112, 143.625239 -13.243772, 143.625239 -13.693433, 143.625239 -14.143093, 144.426317 -14.143093, 145.227395 -14.143093, 145.227395 -14.592753, 146.028473 -14.592753, 146.028473 -15.042413, 146.028473 -15.492073, 145.227395 -15.492073, 145.227395 -15.941733, 146.028473 -15.941733, 146.028473 -16.391394, 146.028473 -16.841054, 146.028473 -17.290714, 146.028473 -17.740374, 146.028473 -18.190034, 146.028473 -18.639695, 146.829551 -18.639695, 146.829551 -19.089355, 146.829551 -19.539015, 146.028473 -19.539015, 146.028473 -19.988675, 145.227395 -19.988675, 145.227395 -20.438335, 145.227395 -20.887995, 144.426317 -20.887995, 144.426317 -21.337656, 143.625239 -21.337656, 143.625239 -20.887995, 143.625239 -20.438335, 143.625239 -19.988675, 143.625239 -19.539015, 143.625239 -19.089355, 142.824162 -19.089355, 142.824162 -18.639695, 142.824162 -18.190034, 142.824162 -17.740374, 142.824162 -17.290714, 142.824162 -16.841054, 143.625239 -16.841054), (142.023084 -14.143093, 142.023084 -14.592753, 142.824162 -14.592753, 142.824162 -14.143093, 142.023084 -14.143093)), ((141.222006 -9.646491, 141.222006 -9.196831, 142.023084 -9.196831, 142.824162 -9.196831, 142.824162 -9.646491, 142.023084 -9.646491, 141.222006 -9.646491)))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_051</t>
   </si>
   <si>
@@ -1172,78 +1718,147 @@
     <t>elc_won_AUS_055</t>
   </si>
   <si>
+    <t>POLYGON ((113.98536 -25.384597, 113.184282 -25.384597, 113.184282 -24.934937, 113.184282 -24.485277, 113.184282 -24.035617, 113.184282 -23.585957, 113.98536 -23.585957, 113.98536 -23.136296, 114.786437 -23.136296, 114.786437 -23.585957, 114.786437 -24.035617, 114.786437 -24.485277, 114.786437 -24.934937, 114.786437 -25.384597, 113.98536 -25.384597))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_056</t>
   </si>
   <si>
+    <t>POLYGON ((116.388593 -22.236976, 116.388593 -21.787316, 117.189671 -21.787316, 117.990749 -21.787316, 117.990749 -22.236976, 117.990749 -22.686636, 117.990749 -23.136296, 117.189671 -23.136296, 116.388593 -23.136296, 116.388593 -22.686636, 116.388593 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_057</t>
   </si>
   <si>
+    <t>POLYGON ((114.786437 -24.035617, 114.786437 -23.585957, 114.786437 -23.136296, 114.786437 -22.686636, 115.587515 -22.686636, 115.587515 -22.236976, 116.388593 -22.236976, 116.388593 -22.686636, 116.388593 -23.136296, 117.189671 -23.136296, 117.990749 -23.136296, 117.990749 -23.585957, 117.990749 -24.035617, 117.990749 -24.485277, 117.990749 -24.934937, 117.990749 -25.384597, 117.990749 -25.834257, 117.189671 -25.834257, 116.388593 -25.834257, 115.587515 -25.834257, 114.786437 -25.834257, 114.786437 -25.384597, 114.786437 -24.934937, 114.786437 -24.485277, 114.786437 -24.035617))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_058</t>
   </si>
   <si>
     <t>elc_won_AUS_059</t>
   </si>
   <si>
+    <t>POLYGON ((146.028473 -38.424743, 146.028473 -37.975082, 146.028473 -37.525422, 146.028473 -37.075762, 146.028473 -36.626102, 146.829551 -36.626102, 146.829551 -37.075762, 147.630629 -37.075762, 147.630629 -37.525422, 147.630629 -37.975082, 148.431706 -37.975082, 148.431706 -38.424743, 147.630629 -38.424743, 147.630629 -38.874403, 147.630629 -39.324063, 147.630629 -39.773723, 146.829551 -39.773723, 146.829551 -39.324063, 146.028473 -39.324063, 145.227395 -39.324063, 145.227395 -38.874403, 146.028473 -38.874403, 146.028473 -38.424743))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_060</t>
   </si>
   <si>
+    <t>POLYGON ((148.431706 -28.532219, 147.630629 -28.532219, 147.630629 -28.082558, 147.630629 -27.632898, 146.829551 -27.632898, 146.829551 -27.183238, 146.829551 -26.733578, 146.829551 -26.283918, 146.829551 -25.834257, 146.829551 -25.384597, 146.829551 -24.934937, 147.630629 -24.934937, 147.630629 -24.485277, 148.431706 -24.485277, 149.232784 -24.485277, 149.232784 -24.934937, 150.033862 -24.934937, 150.033862 -25.384597, 150.83494 -25.384597, 150.83494 -25.834257, 150.83494 -26.283918, 150.83494 -26.733578, 150.83494 -27.183238, 150.033862 -27.183238, 150.033862 -27.632898, 149.232784 -27.632898, 149.232784 -28.082558, 148.431706 -28.082558, 148.431706 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_061</t>
   </si>
   <si>
+    <t>POLYGON ((144.426317 -27.183238, 144.426317 -26.733578, 143.625239 -26.733578, 143.625239 -26.283918, 143.625239 -25.834257, 142.824162 -25.834257, 142.824162 -25.384597, 143.625239 -25.384597, 144.426317 -25.384597, 144.426317 -24.934937, 145.227395 -24.934937, 146.028473 -24.934937, 146.829551 -24.934937, 146.829551 -25.384597, 146.829551 -25.834257, 146.829551 -26.283918, 146.829551 -26.733578, 146.829551 -27.183238, 146.829551 -27.632898, 147.630629 -27.632898, 147.630629 -28.082558, 147.630629 -28.532219, 147.630629 -28.981879, 146.829551 -28.981879, 146.829551 -29.431539, 146.028473 -29.431539, 146.028473 -28.981879, 145.227395 -28.981879, 145.227395 -28.532219, 145.227395 -28.082558, 144.426317 -28.082558, 144.426317 -27.632898, 144.426317 -27.183238))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_062</t>
   </si>
   <si>
+    <t>POLYGON ((113.184282 -22.236976, 113.184282 -21.787316, 113.98536 -21.787316, 113.98536 -21.337656, 114.786437 -21.337656, 115.587515 -21.337656, 115.587515 -21.787316, 116.388593 -21.787316, 116.388593 -22.236976, 115.587515 -22.236976, 115.587515 -22.686636, 114.786437 -22.686636, 114.786437 -23.136296, 113.98536 -23.136296, 113.98536 -23.585957, 113.184282 -23.585957, 113.184282 -23.136296, 113.184282 -22.686636, 113.184282 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_063</t>
   </si>
   <si>
+    <t>POLYGON ((115.587515 -21.787316, 115.587515 -21.337656, 115.587515 -20.887995, 114.786437 -20.887995, 114.786437 -20.438335, 115.587515 -20.438335, 116.388593 -20.438335, 117.189671 -20.438335, 117.990749 -20.438335, 117.990749 -20.887995, 117.990749 -21.337656, 117.990749 -21.787316, 117.189671 -21.787316, 116.388593 -21.787316, 115.587515 -21.787316))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_064</t>
   </si>
   <si>
+    <t>POLYGON ((126.001527 -22.236976, 125.200449 -22.236976, 124.399371 -22.236976, 123.598294 -22.236976, 123.598294 -21.787316, 123.598294 -21.337656, 124.399371 -21.337656, 125.200449 -21.337656, 125.200449 -20.887995, 126.001527 -20.887995, 126.802605 -20.887995, 127.603683 -20.887995, 128.404761 -20.887995, 129.205838 -20.887995, 130.006916 -20.887995, 130.006916 -21.337656, 130.006916 -21.787316, 130.006916 -22.236976, 129.205838 -22.236976, 129.205838 -21.787316, 128.404761 -21.787316, 127.603683 -21.787316, 126.802605 -21.787316, 126.802605 -22.236976, 126.001527 -22.236976))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_065</t>
   </si>
   <si>
+    <t>POLYGON ((126.802605 -22.686636, 126.802605 -22.236976, 126.802605 -21.787316, 127.603683 -21.787316, 128.404761 -21.787316, 129.205838 -21.787316, 129.205838 -22.236976, 129.205838 -22.686636, 129.205838 -23.136296, 129.205838 -23.585957, 129.205838 -24.035617, 128.404761 -24.035617, 127.603683 -24.035617, 126.802605 -24.035617, 126.802605 -23.585957, 126.802605 -23.136296, 126.802605 -22.686636))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_066</t>
   </si>
   <si>
+    <t>POLYGON ((126.001527 -24.934937, 125.200449 -24.934937, 125.200449 -24.485277, 125.200449 -24.035617, 125.200449 -23.585957, 124.399371 -23.585957, 123.598294 -23.585957, 123.598294 -23.136296, 123.598294 -22.686636, 123.598294 -22.236976, 124.399371 -22.236976, 125.200449 -22.236976, 126.001527 -22.236976, 126.802605 -22.236976, 126.802605 -22.686636, 126.802605 -23.136296, 126.802605 -23.585957, 126.802605 -24.035617, 127.603683 -24.035617, 127.603683 -24.485277, 126.802605 -24.485277, 126.001527 -24.485277, 126.001527 -24.934937))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_067</t>
   </si>
   <si>
+    <t>POLYGON ((121.19506 -21.787316, 121.19506 -21.337656, 121.996138 -21.337656, 122.797216 -21.337656, 123.598294 -21.337656, 123.598294 -21.787316, 123.598294 -22.236976, 123.598294 -22.686636, 123.598294 -23.136296, 122.797216 -23.136296, 121.996138 -23.136296, 121.19506 -23.136296, 121.19506 -22.686636, 121.19506 -22.236976, 121.19506 -21.787316))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_068</t>
   </si>
   <si>
+    <t>POLYGON ((119.592904 -23.585957, 119.592904 -23.136296, 118.791827 -23.136296, 117.990749 -23.136296, 117.990749 -22.686636, 117.990749 -22.236976, 117.990749 -21.787316, 118.791827 -21.787316, 119.592904 -21.787316, 119.592904 -21.337656, 120.393982 -21.337656, 121.19506 -21.337656, 121.19506 -21.787316, 121.19506 -22.236976, 121.19506 -22.686636, 121.19506 -23.136296, 120.393982 -23.136296, 120.393982 -23.585957, 119.592904 -23.585957))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_069</t>
   </si>
   <si>
+    <t>POLYGON ((122.797216 -25.834257, 122.797216 -25.384597, 121.996138 -25.384597, 121.19506 -25.384597, 121.19506 -24.934937, 121.19506 -24.485277, 121.19506 -24.035617, 120.393982 -24.035617, 120.393982 -23.585957, 120.393982 -23.136296, 121.19506 -23.136296, 121.996138 -23.136296, 122.797216 -23.136296, 123.598294 -23.136296, 123.598294 -23.585957, 124.399371 -23.585957, 125.200449 -23.585957, 125.200449 -24.035617, 125.200449 -24.485277, 125.200449 -24.934937, 125.200449 -25.384597, 124.399371 -25.384597, 123.598294 -25.384597, 123.598294 -25.834257, 122.797216 -25.834257))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_070</t>
   </si>
   <si>
+    <t>POLYGON ((119.592904 -26.733578, 119.592904 -26.283918, 118.791827 -26.283918, 117.990749 -26.283918, 117.990749 -25.834257, 117.990749 -25.384597, 117.990749 -24.934937, 117.990749 -24.485277, 117.990749 -24.035617, 117.990749 -23.585957, 117.990749 -23.136296, 118.791827 -23.136296, 119.592904 -23.136296, 119.592904 -23.585957, 120.393982 -23.585957, 120.393982 -24.035617, 121.19506 -24.035617, 121.19506 -24.485277, 121.19506 -24.934937, 121.19506 -25.384597, 121.996138 -25.384597, 122.797216 -25.384597, 122.797216 -25.834257, 121.996138 -25.834257, 121.996138 -26.283918, 121.19506 -26.283918, 121.19506 -26.733578, 120.393982 -26.733578, 119.592904 -26.733578))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_071</t>
   </si>
   <si>
+    <t>POLYGON ((113.184282 -27.183238, 113.184282 -26.733578, 113.184282 -26.283918, 113.184282 -25.834257, 113.184282 -25.384597, 113.98536 -25.384597, 114.786437 -25.384597, 114.786437 -25.834257, 114.786437 -26.283918, 114.786437 -26.733578, 114.786437 -27.183238, 115.587515 -27.183238, 115.587515 -27.632898, 116.388593 -27.632898, 116.388593 -28.082558, 116.388593 -28.532219, 115.587515 -28.532219, 114.786437 -28.532219, 113.98536 -28.532219, 113.98536 -28.082558, 113.98536 -27.632898, 113.98536 -27.183238, 113.184282 -27.183238))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_072</t>
   </si>
   <si>
+    <t>POLYGON ((115.587515 -29.431539, 114.786437 -29.431539, 114.786437 -28.981879, 114.786437 -28.532219, 115.587515 -28.532219, 116.388593 -28.532219, 117.189671 -28.532219, 117.990749 -28.532219, 117.990749 -28.981879, 118.791827 -28.981879, 118.791827 -29.431539, 118.791827 -29.881199, 117.990749 -29.881199, 117.990749 -30.330859, 117.189671 -30.330859, 116.388593 -30.330859, 116.388593 -29.881199, 115.587515 -29.881199, 115.587515 -29.431539))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_073</t>
   </si>
   <si>
+    <t>POLYGON ((116.388593 -28.082558, 116.388593 -27.632898, 115.587515 -27.632898, 115.587515 -27.183238, 114.786437 -27.183238, 114.786437 -26.733578, 114.786437 -26.283918, 114.786437 -25.834257, 115.587515 -25.834257, 116.388593 -25.834257, 117.189671 -25.834257, 117.990749 -25.834257, 117.990749 -26.283918, 118.791827 -26.283918, 119.592904 -26.283918, 119.592904 -26.733578, 120.393982 -26.733578, 120.393982 -27.183238, 119.592904 -27.183238, 119.592904 -27.632898, 119.592904 -28.082558, 119.592904 -28.532219, 119.592904 -28.981879, 119.592904 -29.431539, 118.791827 -29.431539, 118.791827 -28.981879, 117.990749 -28.981879, 117.990749 -28.532219, 117.189671 -28.532219, 116.388593 -28.532219, 116.388593 -28.082558))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_074</t>
   </si>
   <si>
     <t>elc_won_AUS_075</t>
   </si>
   <si>
+    <t>POLYGON ((139.61985 -32.1295, 139.61985 -31.67984, 139.61985 -31.23018, 139.61985 -30.780519, 139.61985 -30.330859, 139.61985 -29.881199, 139.61985 -29.431539, 140.420928 -29.431539, 140.420928 -29.881199, 141.222006 -29.881199, 142.023084 -29.881199, 142.023084 -30.330859, 142.023084 -30.780519, 142.824162 -30.780519, 142.824162 -31.23018, 142.023084 -31.23018, 142.023084 -31.67984, 141.222006 -31.67984, 141.222006 -32.1295, 140.420928 -32.1295, 139.61985 -32.1295))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_076</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -33.478481, 140.420928 -33.478481, 140.420928 -33.02882, 140.420928 -32.57916, 139.61985 -32.57916, 139.61985 -32.1295, 140.420928 -32.1295, 141.222006 -32.1295, 141.222006 -31.67984, 142.023084 -31.67984, 142.023084 -31.23018, 142.824162 -31.23018, 142.824162 -30.780519, 143.625239 -30.780519, 143.625239 -31.23018, 144.426317 -31.23018, 144.426317 -31.67984, 144.426317 -32.1295, 143.625239 -32.1295, 143.625239 -32.57916, 143.625239 -33.02882, 142.824162 -33.02882, 142.824162 -33.478481, 142.023084 -33.478481, 142.023084 -33.928141, 141.222006 -33.928141, 141.222006 -33.478481))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_077</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -28.082558, 140.420928 -28.082558, 140.420928 -27.632898, 140.420928 -27.183238, 140.420928 -26.733578, 140.420928 -26.283918, 141.222006 -26.283918, 141.222006 -25.834257, 141.222006 -25.384597, 141.222006 -24.934937, 141.222006 -24.485277, 142.023084 -24.485277, 142.023084 -24.934937, 142.824162 -24.934937, 142.824162 -25.384597, 142.824162 -25.834257, 143.625239 -25.834257, 143.625239 -26.283918, 143.625239 -26.733578, 144.426317 -26.733578, 144.426317 -27.183238, 144.426317 -27.632898, 144.426317 -28.082558, 144.426317 -28.532219, 144.426317 -28.981879, 143.625239 -28.981879, 143.625239 -28.532219, 142.824162 -28.532219, 142.824162 -28.082558, 142.023084 -28.082558, 141.222006 -28.082558))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_078</t>
   </si>
   <si>
+    <t>POLYGON ((141.222006 -29.881199, 140.420928 -29.881199, 140.420928 -29.431539, 139.61985 -29.431539, 139.61985 -28.981879, 139.61985 -28.532219, 140.420928 -28.532219, 140.420928 -28.082558, 141.222006 -28.082558, 142.023084 -28.082558, 142.023084 -28.532219, 142.023084 -28.981879, 142.023084 -29.431539, 142.023084 -29.881199, 141.222006 -29.881199))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_079</t>
   </si>
   <si>
+    <t>POLYGON ((143.625239 -30.780519, 142.824162 -30.780519, 142.023084 -30.780519, 142.023084 -30.330859, 142.023084 -29.881199, 142.023084 -29.431539, 142.023084 -28.981879, 142.023084 -28.532219, 142.023084 -28.082558, 142.824162 -28.082558, 142.824162 -28.532219, 143.625239 -28.532219, 143.625239 -28.981879, 144.426317 -28.981879, 144.426317 -28.532219, 144.426317 -28.082558, 145.227395 -28.082558, 145.227395 -28.532219, 145.227395 -28.981879, 146.028473 -28.981879, 146.028473 -29.431539, 146.028473 -29.881199, 145.227395 -29.881199, 145.227395 -30.330859, 145.227395 -30.780519, 145.227395 -31.23018, 144.426317 -31.23018, 143.625239 -31.23018, 143.625239 -30.780519))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_080</t>
   </si>
   <si>
@@ -1262,40 +1877,79 @@
     <t>elc_won_AUS_085</t>
   </si>
   <si>
+    <t>POLYGON ((121.996138 -18.190034, 121.996138 -17.740374, 121.996138 -17.290714, 121.996138 -16.841054, 121.996138 -16.391394, 122.797216 -16.391394, 122.797216 -15.941733, 123.598294 -15.941733, 123.598294 -16.391394, 123.598294 -16.841054, 124.399371 -16.841054, 124.399371 -17.290714, 125.200449 -17.290714, 125.200449 -17.740374, 125.200449 -18.190034, 125.200449 -18.639695, 124.399371 -18.639695, 123.598294 -18.639695, 123.598294 -19.089355, 122.797216 -19.089355, 121.996138 -19.089355, 121.996138 -19.539015, 121.19506 -19.539015, 121.19506 -19.089355, 121.19506 -18.639695, 121.19506 -18.190034, 121.996138 -18.190034))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_086</t>
   </si>
   <si>
+    <t>POLYGON ((117.990749 -21.337656, 117.990749 -20.887995, 117.990749 -20.438335, 117.990749 -19.988675, 118.791827 -19.988675, 118.791827 -19.539015, 119.592904 -19.539015, 120.393982 -19.539015, 120.393982 -19.089355, 121.19506 -19.089355, 121.19506 -19.539015, 121.996138 -19.539015, 121.996138 -19.089355, 122.797216 -19.089355, 123.598294 -19.089355, 123.598294 -18.639695, 124.399371 -18.639695, 125.200449 -18.639695, 125.200449 -19.089355, 125.200449 -19.539015, 125.200449 -19.988675, 126.001527 -19.988675, 126.001527 -20.438335, 126.802605 -20.438335, 126.802605 -20.887995, 126.001527 -20.887995, 125.200449 -20.887995, 125.200449 -21.337656, 124.399371 -21.337656, 123.598294 -21.337656, 122.797216 -21.337656, 121.996138 -21.337656, 121.19506 -21.337656, 120.393982 -21.337656, 119.592904 -21.337656, 119.592904 -21.787316, 118.791827 -21.787316, 117.990749 -21.787316, 117.990749 -21.337656))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_087</t>
   </si>
   <si>
+    <t>POLYGON ((126.802605 -20.438335, 126.001527 -20.438335, 126.001527 -19.988675, 125.200449 -19.988675, 125.200449 -19.539015, 125.200449 -19.089355, 125.200449 -18.639695, 125.200449 -18.190034, 126.001527 -18.190034, 126.001527 -18.639695, 126.802605 -18.639695, 126.802605 -18.190034, 126.802605 -17.740374, 127.603683 -17.740374, 128.404761 -17.740374, 129.205838 -17.740374, 129.205838 -17.290714, 129.205838 -16.841054, 129.205838 -16.391394, 129.205838 -15.941733, 129.205838 -15.492073, 130.006916 -15.492073, 130.006916 -15.042413, 130.807994 -15.042413, 130.807994 -15.492073, 131.609072 -15.492073, 131.609072 -15.941733, 131.609072 -16.391394, 131.609072 -16.841054, 131.609072 -17.290714, 131.609072 -17.740374, 131.609072 -18.190034, 131.609072 -18.639695, 131.609072 -19.089355, 130.807994 -19.089355, 130.807994 -19.539015, 130.807994 -19.988675, 130.807994 -20.438335, 130.006916 -20.438335, 130.006916 -20.887995, 129.205838 -20.887995, 128.404761 -20.887995, 127.603683 -20.887995, 126.802605 -20.887995, 126.802605 -20.438335))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_088</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((125.200449 -14.592753, 125.200449 -14.143093, 126.001527 -14.143093, 126.001527 -13.693433, 126.802605 -13.693433, 126.802605 -14.143093, 126.802605 -14.592753, 126.001527 -14.592753, 126.001527 -15.042413, 125.200449 -15.042413, 125.200449 -14.592753)), ((130.006916 -15.042413, 130.006916 -14.592753, 130.006916 -14.143093, 130.006916 -13.693433, 129.205838 -13.693433, 129.205838 -13.243772, 130.006916 -13.243772, 130.006916 -12.794112, 130.807994 -12.794112, 130.807994 -12.344452, 130.807994 -11.894792, 131.609072 -11.894792, 131.609072 -12.344452, 131.609072 -12.794112, 131.609072 -13.243772, 131.609072 -13.693433, 131.609072 -14.143093, 131.609072 -14.592753, 131.609072 -15.042413, 131.609072 -15.492073, 130.807994 -15.492073, 130.807994 -15.042413, 130.006916 -15.042413)), ((130.006916 -10.995471, 130.807994 -10.995471, 130.807994 -11.445132, 130.006916 -11.445132, 130.006916 -10.995471)))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_089</t>
   </si>
   <si>
+    <t>POLYGON ((125.200449 -18.190034, 125.200449 -17.740374, 125.200449 -17.290714, 124.399371 -17.290714, 124.399371 -16.841054, 124.399371 -16.391394, 125.200449 -16.391394, 125.200449 -15.941733, 124.399371 -15.941733, 124.399371 -15.492073, 125.200449 -15.492073, 125.200449 -15.042413, 126.001527 -15.042413, 126.001527 -14.592753, 126.802605 -14.592753, 126.802605 -14.143093, 126.802605 -13.693433, 127.603683 -13.693433, 127.603683 -14.143093, 128.404761 -14.143093, 128.404761 -14.592753, 129.205838 -14.592753, 130.006916 -14.592753, 130.006916 -15.042413, 130.006916 -15.492073, 129.205838 -15.492073, 129.205838 -15.941733, 129.205838 -16.391394, 129.205838 -16.841054, 129.205838 -17.290714, 129.205838 -17.740374, 128.404761 -17.740374, 127.603683 -17.740374, 126.802605 -17.740374, 126.802605 -18.190034, 126.802605 -18.639695, 126.001527 -18.639695, 126.001527 -18.190034, 125.200449 -18.190034))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_090</t>
   </si>
   <si>
+    <t>POLYGON ((122.797216 -28.532219, 122.797216 -28.082558, 122.797216 -27.632898, 122.797216 -27.183238, 123.598294 -27.183238, 124.399371 -27.183238, 125.200449 -27.183238, 125.200449 -27.632898, 126.001527 -27.632898, 126.001527 -28.082558, 126.802605 -28.082558, 126.802605 -28.532219, 126.001527 -28.532219, 126.001527 -28.981879, 125.200449 -28.981879, 125.200449 -29.431539, 125.200449 -29.881199, 124.399371 -29.881199, 123.598294 -29.881199, 123.598294 -29.431539, 123.598294 -28.981879, 122.797216 -28.981879, 122.797216 -28.532219))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_091</t>
   </si>
   <si>
+    <t>POLYGON ((121.19506 -30.780519, 121.19506 -30.330859, 121.19506 -29.881199, 120.393982 -29.881199, 119.592904 -29.881199, 119.592904 -29.431539, 119.592904 -28.981879, 119.592904 -28.532219, 119.592904 -28.082558, 119.592904 -27.632898, 119.592904 -27.183238, 120.393982 -27.183238, 120.393982 -26.733578, 121.19506 -26.733578, 121.19506 -26.283918, 121.996138 -26.283918, 121.996138 -26.733578, 122.797216 -26.733578, 123.598294 -26.733578, 123.598294 -27.183238, 122.797216 -27.183238, 122.797216 -27.632898, 122.797216 -28.082558, 122.797216 -28.532219, 122.797216 -28.981879, 123.598294 -28.981879, 123.598294 -29.431539, 123.598294 -29.881199, 122.797216 -29.881199, 122.797216 -30.330859, 122.797216 -30.780519, 121.996138 -30.780519, 121.19506 -30.780519))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_092</t>
   </si>
   <si>
+    <t>POLYGON ((127.603683 -29.431539, 127.603683 -28.981879, 126.802605 -28.981879, 126.001527 -28.981879, 126.001527 -28.532219, 126.802605 -28.532219, 126.802605 -28.082558, 126.001527 -28.082558, 126.001527 -27.632898, 125.200449 -27.632898, 125.200449 -27.183238, 125.200449 -26.733578, 125.200449 -26.283918, 126.001527 -26.283918, 126.802605 -26.283918, 127.603683 -26.283918, 127.603683 -25.834257, 128.404761 -25.834257, 129.205838 -25.834257, 129.205838 -26.283918, 129.205838 -26.733578, 129.205838 -27.183238, 129.205838 -27.632898, 129.205838 -28.082558, 129.205838 -28.532219, 129.205838 -28.981879, 129.205838 -29.431539, 128.404761 -29.431539, 127.603683 -29.431539))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_093</t>
   </si>
   <si>
+    <t>POLYGON ((123.598294 -27.183238, 123.598294 -26.733578, 122.797216 -26.733578, 121.996138 -26.733578, 121.996138 -26.283918, 121.996138 -25.834257, 122.797216 -25.834257, 123.598294 -25.834257, 123.598294 -25.384597, 124.399371 -25.384597, 125.200449 -25.384597, 125.200449 -24.934937, 126.001527 -24.934937, 126.001527 -24.485277, 126.802605 -24.485277, 127.603683 -24.485277, 127.603683 -24.035617, 128.404761 -24.035617, 129.205838 -24.035617, 129.205838 -24.485277, 129.205838 -24.934937, 129.205838 -25.384597, 129.205838 -25.834257, 128.404761 -25.834257, 127.603683 -25.834257, 127.603683 -26.283918, 126.802605 -26.283918, 126.001527 -26.283918, 125.200449 -26.283918, 125.200449 -26.733578, 125.200449 -27.183238, 124.399371 -27.183238, 123.598294 -27.183238))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_094</t>
   </si>
   <si>
+    <t>POLYGON ((126.802605 -32.57916, 126.001527 -32.57916, 125.200449 -32.57916, 125.200449 -32.1295, 125.200449 -31.67984, 126.001527 -31.67984, 126.802605 -31.67984, 126.802605 -31.23018, 127.603683 -31.23018, 127.603683 -30.780519, 128.404761 -30.780519, 129.205838 -30.780519, 129.205838 -31.23018, 129.205838 -31.67984, 129.205838 -32.1295, 128.404761 -32.1295, 127.603683 -32.1295, 127.603683 -32.57916, 126.802605 -32.57916))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_095</t>
   </si>
   <si>
+    <t>POLYGON ((126.001527 -31.67984, 125.200449 -31.67984, 124.399371 -31.67984, 123.598294 -31.67984, 123.598294 -31.23018, 123.598294 -30.780519, 122.797216 -30.780519, 122.797216 -30.330859, 122.797216 -29.881199, 123.598294 -29.881199, 124.399371 -29.881199, 125.200449 -29.881199, 125.200449 -29.431539, 125.200449 -28.981879, 126.001527 -28.981879, 126.802605 -28.981879, 127.603683 -28.981879, 127.603683 -29.431539, 128.404761 -29.431539, 129.205838 -29.431539, 129.205838 -29.881199, 129.205838 -30.330859, 129.205838 -30.780519, 128.404761 -30.780519, 127.603683 -30.780519, 127.603683 -31.23018, 126.802605 -31.23018, 126.802605 -31.67984, 126.001527 -31.67984))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_096</t>
   </si>
   <si>
+    <t>POLYGON ((119.592904 -31.23018, 119.592904 -30.780519, 119.592904 -30.330859, 119.592904 -29.881199, 120.393982 -29.881199, 121.19506 -29.881199, 121.19506 -30.330859, 121.19506 -30.780519, 121.996138 -30.780519, 122.797216 -30.780519, 123.598294 -30.780519, 123.598294 -31.23018, 123.598294 -31.67984, 122.797216 -31.67984, 122.797216 -32.1295, 122.797216 -32.57916, 121.996138 -32.57916, 121.19506 -32.57916, 120.393982 -32.57916, 120.393982 -32.1295, 120.393982 -31.67984, 119.592904 -31.67984, 119.592904 -31.23018))</t>
+  </si>
+  <si>
     <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>POLYGON ((121.996138 -34.377801, 121.996138 -33.928141, 121.19506 -33.928141, 120.393982 -33.928141, 120.393982 -33.478481, 120.393982 -33.02882, 120.393982 -32.57916, 121.19506 -32.57916, 121.996138 -32.57916, 122.797216 -32.57916, 122.797216 -32.1295, 122.797216 -31.67984, 123.598294 -31.67984, 124.399371 -31.67984, 125.200449 -31.67984, 125.200449 -32.1295, 125.200449 -32.57916, 125.200449 -33.02882, 124.399371 -33.02882, 124.399371 -33.478481, 124.399371 -33.928141, 123.598294 -33.928141, 123.598294 -34.377801, 122.797216 -34.377801, 121.996138 -34.377801))</t>
   </si>
 </sst>
 </file>
@@ -1666,11 +2320,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671C2949-9012-45D1-9FB3-B966B448D2C2}">
-  <dimension ref="B3:R296"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841604C-4D8C-4334-811B-5CBD2666A8F7}">
+  <dimension ref="B3:S296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1681,7 +2335,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1721,8 +2375,11 @@
       <c r="R4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +2420,7 @@
         <v>-22.86294518145154</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +2461,7 @@
         <v>-30.532100853424872</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1845,7 +2502,7 @@
         <v>-33.318012556546421</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +2543,7 @@
         <v>-37.567537497399123</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -1927,7 +2584,7 @@
         <v>-34.775720926588463</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1968,7 +2625,7 @@
         <v>-23.537233256213721</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1997,19 +2654,19 @@
         <v>120</v>
       </c>
       <c r="O11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>152.95633561497641</v>
+        <v>149.40404924290272</v>
       </c>
       <c r="R11">
-        <v>-27.732264407857119</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-22.820756210209289</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -2038,19 +2695,19 @@
         <v>121</v>
       </c>
       <c r="O12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>149.40404924290272</v>
+        <v>141.41917764116005</v>
       </c>
       <c r="R12">
-        <v>-22.820756210209289</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-31.986353168692315</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -2079,19 +2736,19 @@
         <v>122</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>141.41917764116005</v>
+        <v>150.84329384341081</v>
       </c>
       <c r="R13">
-        <v>-31.986353168692315</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-27.920986820196017</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -2120,19 +2777,19 @@
         <v>123</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>150.84329384341081</v>
+        <v>151.19284847613793</v>
       </c>
       <c r="R14">
-        <v>-27.920986820196017</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-23.856194719487281</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -2161,19 +2818,19 @@
         <v>124</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>151.19284847613793</v>
+        <v>150.62709905075124</v>
       </c>
       <c r="R15">
-        <v>-23.856194719487281</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-24.342461230294287</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -2202,16 +2859,16 @@
         <v>125</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>150.62709905075124</v>
+        <v>148.90388563970319</v>
       </c>
       <c r="R16">
-        <v>-24.342461230294287</v>
+        <v>-34.862594637477081</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -2243,16 +2900,16 @@
         <v>126</v>
       </c>
       <c r="O17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>148.90388563970319</v>
+        <v>151.49237495717287</v>
       </c>
       <c r="R17">
-        <v>-34.862594637477081</v>
+        <v>-33.052074884026759</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -2266,7 +2923,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -2284,16 +2941,16 @@
         <v>127</v>
       </c>
       <c r="O18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>151.49237495717287</v>
+        <v>145.52658139950708</v>
       </c>
       <c r="R18">
-        <v>-33.052074884026759</v>
+        <v>-17.800806029919851</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
@@ -2325,16 +2982,16 @@
         <v>128</v>
       </c>
       <c r="O19" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>145.52658139950708</v>
+        <v>146.03429268958672</v>
       </c>
       <c r="R19">
-        <v>-17.800806029919851</v>
+        <v>-34.648775935550987</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">
@@ -2366,16 +3023,16 @@
         <v>129</v>
       </c>
       <c r="O20" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>146.03429268958672</v>
+        <v>137.8128974128341</v>
       </c>
       <c r="R20">
-        <v>-34.648775935550987</v>
+        <v>-32.536269144315668</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.45">
@@ -2407,16 +3064,16 @@
         <v>130</v>
       </c>
       <c r="O21" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>137.8128974128341</v>
+        <v>151.81952564800682</v>
       </c>
       <c r="R21">
-        <v>-32.536269144315668</v>
+        <v>-24.90133538944163</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.45">
@@ -2448,16 +3105,16 @@
         <v>131</v>
       </c>
       <c r="O22" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>151.81952564800682</v>
+        <v>146.42885495857578</v>
       </c>
       <c r="R22">
-        <v>-24.90133538944163</v>
+        <v>-38.281663652861432</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2489,16 +3146,16 @@
         <v>132</v>
       </c>
       <c r="O23" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>146.42885495857578</v>
+        <v>142.28083100000038</v>
       </c>
       <c r="R23">
-        <v>-38.281663652861432</v>
+        <v>-36.721698083045936</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2530,16 +3187,16 @@
         <v>133</v>
       </c>
       <c r="O24" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>146.7152693827272</v>
+        <v>152.78594479220749</v>
       </c>
       <c r="R24">
-        <v>-42.823952846681991</v>
+        <v>-27.541324760522063</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2571,16 +3228,16 @@
         <v>134</v>
       </c>
       <c r="O25" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>142.28083100000038</v>
+        <v>121.42358390000004</v>
       </c>
       <c r="R25">
-        <v>-36.721698083045936</v>
+        <v>-30.781882477049411</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
@@ -2612,16 +3269,16 @@
         <v>135</v>
       </c>
       <c r="O26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>121.42358390000004</v>
+        <v>116.74275233957847</v>
       </c>
       <c r="R26">
-        <v>-30.781882477049411</v>
+        <v>-20.762601878195927</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -2653,16 +3310,16 @@
         <v>136</v>
       </c>
       <c r="O27" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>116.74275233957847</v>
+        <v>147.20840569999993</v>
       </c>
       <c r="R27">
-        <v>-20.762601878195927</v>
+        <v>-42.829905988893763</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
@@ -2735,7 +3392,7 @@
         <v>138</v>
       </c>
       <c r="O29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
@@ -2799,25 +3456,25 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
         <v>66</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>67</v>
-      </c>
-      <c r="G31" t="s">
-        <v>68</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L31" t="s">
         <v>140</v>
       </c>
       <c r="O31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P31" t="s">
         <v>8</v>
@@ -2840,7 +3497,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s">
         <v>69</v>
@@ -2858,7 +3515,7 @@
         <v>141</v>
       </c>
       <c r="O32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
@@ -2881,25 +3538,25 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" t="s">
         <v>71</v>
-      </c>
-      <c r="F33" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" t="s">
-        <v>73</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L33" t="s">
         <v>142</v>
       </c>
       <c r="O33" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
@@ -2922,25 +3579,25 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L34" t="s">
         <v>143</v>
       </c>
       <c r="O34" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
@@ -2963,19 +3620,19 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
         <v>75</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" t="s">
-        <v>76</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L35" t="s">
         <v>144</v>
@@ -3004,19 +3661,19 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L36" t="s">
         <v>145</v>
@@ -3048,16 +3705,16 @@
         <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L37" t="s">
         <v>146</v>
@@ -3086,10 +3743,10 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" t="s">
         <v>80</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
       </c>
       <c r="G38" t="s">
         <v>81</v>
@@ -3127,7 +3784,7 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
         <v>82</v>
@@ -3253,7 +3910,7 @@
         <v>88</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G42" t="s">
         <v>89</v>
@@ -3432,7 +4089,7 @@
         <v>155</v>
       </c>
       <c r="O46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
@@ -3499,7 +4156,7 @@
         <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
         <v>97</v>
@@ -3526,7 +4183,7 @@
         <v>-35.200406760019412</v>
       </c>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -3567,7 +4224,7 @@
         <v>-26.268566355497121</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>8</v>
       </c>
@@ -3596,7 +4253,7 @@
         <v>159</v>
       </c>
       <c r="O50" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
@@ -3608,7 +4265,7 @@
         <v>-30.767640414252401</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -3637,7 +4294,7 @@
         <v>160</v>
       </c>
       <c r="O51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
@@ -3648,8 +4305,11 @@
       <c r="R51">
         <v>-34.147467956805272</v>
       </c>
-    </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S51" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -3678,7 +4338,7 @@
         <v>161</v>
       </c>
       <c r="O52" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
@@ -3689,8 +4349,11 @@
       <c r="R52">
         <v>-36.83533638167507</v>
       </c>
-    </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S52" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>8</v>
       </c>
@@ -3701,7 +4364,7 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F53" t="s">
         <v>103</v>
@@ -3719,7 +4382,7 @@
         <v>162</v>
       </c>
       <c r="O53" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
@@ -3730,8 +4393,11 @@
       <c r="R53">
         <v>-34.633289924628762</v>
       </c>
-    </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>8</v>
       </c>
@@ -3760,7 +4426,7 @@
         <v>163</v>
       </c>
       <c r="O54" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
@@ -3771,8 +4437,11 @@
       <c r="R54">
         <v>-41.2407776578913</v>
       </c>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>8</v>
       </c>
@@ -3786,7 +4455,7 @@
         <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G55" t="s">
         <v>107</v>
@@ -3801,7 +4470,7 @@
         <v>164</v>
       </c>
       <c r="O55" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
@@ -3812,8 +4481,11 @@
       <c r="R55">
         <v>-37.465189354544776</v>
       </c>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>8</v>
       </c>
@@ -3827,7 +4499,7 @@
         <v>57</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G56" t="s">
         <v>108</v>
@@ -3842,7 +4514,7 @@
         <v>165</v>
       </c>
       <c r="O56" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P56" t="s">
         <v>8</v>
@@ -3853,8 +4525,11 @@
       <c r="R56">
         <v>-24.58894897576948</v>
       </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S56" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>8</v>
       </c>
@@ -3883,7 +4558,7 @@
         <v>166</v>
       </c>
       <c r="O57" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="P57" t="s">
         <v>8</v>
@@ -3894,8 +4569,11 @@
       <c r="R57">
         <v>-23.8370612107902</v>
       </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>8</v>
       </c>
@@ -3906,7 +4584,7 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F58" t="s">
         <v>86</v>
@@ -3924,21 +4602,24 @@
         <v>167</v>
       </c>
       <c r="O58" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>150.70172534099848</v>
+        <v>150.70502233548291</v>
       </c>
       <c r="R58">
-        <v>-30.507071736111641</v>
-      </c>
-    </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.45">
+        <v>-30.506116756678612</v>
+      </c>
+      <c r="S58" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O59" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
@@ -3949,10 +4630,13 @@
       <c r="R59">
         <v>-33.218506405773972</v>
       </c>
-    </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S59" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O60" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
@@ -3963,10 +4647,13 @@
       <c r="R60">
         <v>-31.939913984234508</v>
       </c>
-    </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O61" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
@@ -3977,10 +4664,13 @@
       <c r="R61">
         <v>-33.257596019081056</v>
       </c>
-    </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S61" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O62" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
@@ -3991,10 +4681,13 @@
       <c r="R62">
         <v>-23.758848518091867</v>
       </c>
-    </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S62" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O63" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
@@ -4005,10 +4698,13 @@
       <c r="R63">
         <v>-31.648362130602383</v>
       </c>
-    </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S63" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.45">
       <c r="O64" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
@@ -4019,10 +4715,13 @@
       <c r="R64">
         <v>-31.400551816060769</v>
       </c>
-    </row>
-    <row r="65" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S64" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O65" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
@@ -4033,10 +4732,13 @@
       <c r="R65">
         <v>-34.137093062271134</v>
       </c>
-    </row>
-    <row r="66" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S65" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="66" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O66" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
@@ -4047,10 +4749,13 @@
       <c r="R66">
         <v>-33.62388010001915</v>
       </c>
-    </row>
-    <row r="67" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S66" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="67" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O67" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
@@ -4061,122 +4766,149 @@
       <c r="R67">
         <v>-26.369630010973268</v>
       </c>
-    </row>
-    <row r="68" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S67" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="68" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O68" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
+        <v>152.80647923996878</v>
+      </c>
+      <c r="R68">
+        <v>-28.24304589666794</v>
+      </c>
+      <c r="S68" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="69" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>210</v>
+      </c>
+      <c r="P69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q69">
         <v>150.15732905181272</v>
       </c>
-      <c r="R68">
+      <c r="R69">
         <v>-23.706875486581438</v>
       </c>
-    </row>
-    <row r="69" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O69" t="s">
-        <v>191</v>
-      </c>
-      <c r="P69" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q69">
+      <c r="S69" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>212</v>
+      </c>
+      <c r="P70" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q70">
         <v>151.4718066142166</v>
       </c>
-      <c r="R69">
+      <c r="R70">
         <v>-25.411178903352639</v>
       </c>
-    </row>
-    <row r="70" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O70" t="s">
-        <v>192</v>
-      </c>
-      <c r="P70" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q70">
+      <c r="S70" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="71" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>214</v>
+      </c>
+      <c r="P71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q71">
         <v>146.43171849829355</v>
       </c>
-      <c r="R70">
+      <c r="R71">
         <v>-20.994143017659859</v>
       </c>
-    </row>
-    <row r="71" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O71" t="s">
-        <v>193</v>
-      </c>
-      <c r="P71" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q71">
+      <c r="S71" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="72" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>216</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72">
         <v>143.01659064084205</v>
       </c>
-      <c r="R71">
+      <c r="R72">
         <v>-23.911108657321289</v>
       </c>
-    </row>
-    <row r="72" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O72" t="s">
-        <v>194</v>
-      </c>
-      <c r="P72" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72">
+      <c r="S72" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>218</v>
+      </c>
+      <c r="P73" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73">
         <v>144.14104615068234</v>
       </c>
-      <c r="R72">
+      <c r="R73">
         <v>-22.380981243555336</v>
       </c>
-    </row>
-    <row r="73" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O73" t="s">
-        <v>195</v>
-      </c>
-      <c r="P73" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q73">
+      <c r="S73" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="74" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
+        <v>220</v>
+      </c>
+      <c r="P74" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q74">
         <v>146.94281184898847</v>
       </c>
-      <c r="R73">
+      <c r="R74">
         <v>-35.953929114813228</v>
       </c>
-    </row>
-    <row r="74" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O74" t="s">
-        <v>196</v>
-      </c>
-      <c r="P74" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q74">
+      <c r="S74" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="75" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>222</v>
+      </c>
+      <c r="P75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q75">
         <v>139.31840264795321</v>
       </c>
-      <c r="R74">
+      <c r="R75">
         <v>-35.731086944716644</v>
       </c>
-    </row>
-    <row r="75" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O75" t="s">
-        <v>197</v>
-      </c>
-      <c r="P75" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q75">
-        <v>152.8095039798896</v>
-      </c>
-      <c r="R75">
-        <v>-28.248182600001183</v>
-      </c>
-    </row>
-    <row r="76" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S75" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O76" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
@@ -4187,24 +4919,30 @@
       <c r="R76">
         <v>-29.152576423550379</v>
       </c>
-    </row>
-    <row r="77" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S76" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O77" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>147.51971261676547</v>
+        <v>147.48606991865145</v>
       </c>
       <c r="R77">
-        <v>-41.754650558287658</v>
-      </c>
-    </row>
-    <row r="78" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-41.740655806615202</v>
+      </c>
+      <c r="S77" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O78" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
@@ -4215,10 +4953,13 @@
       <c r="R78">
         <v>-36.522039302338754</v>
       </c>
-    </row>
-    <row r="79" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S78" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O79" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
@@ -4229,10 +4970,13 @@
       <c r="R79">
         <v>-25.49357352256672</v>
       </c>
-    </row>
-    <row r="80" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S79" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="80" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O80" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
@@ -4243,10 +4987,13 @@
       <c r="R80">
         <v>-28.066746287936159</v>
       </c>
-    </row>
-    <row r="81" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S80" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="81" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O81" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
@@ -4257,10 +5004,13 @@
       <c r="R81">
         <v>-28.04146789637413</v>
       </c>
-    </row>
-    <row r="82" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S81" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O82" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
@@ -4271,10 +5021,13 @@
       <c r="R82">
         <v>-30.750489466295512</v>
       </c>
-    </row>
-    <row r="83" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S82" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="83" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O83" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
@@ -4285,10 +5038,13 @@
       <c r="R83">
         <v>-29.75244409199982</v>
       </c>
-    </row>
-    <row r="84" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S83" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O84" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
@@ -4299,10 +5055,13 @@
       <c r="R84">
         <v>-31.549752873691599</v>
       </c>
-    </row>
-    <row r="85" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S84" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O85" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
@@ -4313,10 +5072,13 @@
       <c r="R85">
         <v>-30.04854365720664</v>
       </c>
-    </row>
-    <row r="86" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S85" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O86" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
@@ -4327,10 +5089,13 @@
       <c r="R86">
         <v>-30.55204904451108</v>
       </c>
-    </row>
-    <row r="87" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S86" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O87" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
@@ -4341,10 +5106,13 @@
       <c r="R87">
         <v>-26.873524361102771</v>
       </c>
-    </row>
-    <row r="88" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S87" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O88" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
@@ -4355,10 +5123,13 @@
       <c r="R88">
         <v>-28.248428425646203</v>
       </c>
-    </row>
-    <row r="89" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S88" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="89" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O89" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="P89" t="s">
         <v>8</v>
@@ -4369,10 +5140,13 @@
       <c r="R89">
         <v>-24.111623182346271</v>
       </c>
-    </row>
-    <row r="90" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S89" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="90" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
@@ -4383,10 +5157,13 @@
       <c r="R90">
         <v>-24.40588485921278</v>
       </c>
-    </row>
-    <row r="91" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S90" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="91" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
@@ -4397,10 +5174,13 @@
       <c r="R91">
         <v>-21.914244713938611</v>
       </c>
-    </row>
-    <row r="92" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S91" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
@@ -4411,10 +5191,13 @@
       <c r="R92">
         <v>-19.811351599191354</v>
       </c>
-    </row>
-    <row r="93" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S92" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="93" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
@@ -4425,10 +5208,13 @@
       <c r="R93">
         <v>-21.32990756247144</v>
       </c>
-    </row>
-    <row r="94" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S93" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
@@ -4439,10 +5225,13 @@
       <c r="R94">
         <v>-23.251052266326525</v>
       </c>
-    </row>
-    <row r="95" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S94" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="95" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>217</v>
+        <v>262</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
@@ -4453,10 +5242,13 @@
       <c r="R95">
         <v>-19.209071955066257</v>
       </c>
-    </row>
-    <row r="96" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S95" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="96" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O96" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="P96" t="s">
         <v>8</v>
@@ -4467,10 +5259,13 @@
       <c r="R96">
         <v>-16.842782017898529</v>
       </c>
-    </row>
-    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S96" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O97" t="s">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="P97" t="s">
         <v>8</v>
@@ -4481,10 +5276,13 @@
       <c r="R97">
         <v>-16.101517102011233</v>
       </c>
-    </row>
-    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S97" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="98" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O98" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="P98" t="s">
         <v>8</v>
@@ -4495,10 +5293,13 @@
       <c r="R98">
         <v>-21.232659958612345</v>
       </c>
-    </row>
-    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O99" t="s">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="P99" t="s">
         <v>8</v>
@@ -4509,10 +5310,13 @@
       <c r="R99">
         <v>-19.694955700281337</v>
       </c>
-    </row>
-    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S99" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="100" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O100" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="P100" t="s">
         <v>8</v>
@@ -4523,10 +5327,13 @@
       <c r="R100">
         <v>-18.904569355313825</v>
       </c>
-    </row>
-    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S100" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O101" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="P101" t="s">
         <v>8</v>
@@ -4537,10 +5344,13 @@
       <c r="R101">
         <v>-36.165910195321878</v>
       </c>
-    </row>
-    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S101" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="102" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O102" t="s">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="P102" t="s">
         <v>8</v>
@@ -4551,10 +5361,13 @@
       <c r="R102">
         <v>-30.796729707503129</v>
       </c>
-    </row>
-    <row r="103" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S102" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="103" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O103" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="P103" t="s">
         <v>8</v>
@@ -4565,10 +5378,13 @@
       <c r="R103">
         <v>-38.353648620663961</v>
       </c>
-    </row>
-    <row r="104" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S103" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="104" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O104" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="P104" t="s">
         <v>8</v>
@@ -4579,10 +5395,13 @@
       <c r="R104">
         <v>-37.886047349671941</v>
       </c>
-    </row>
-    <row r="105" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S104" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="105" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O105" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="P105" t="s">
         <v>8</v>
@@ -4593,10 +5412,13 @@
       <c r="R105">
         <v>-23.34813400404289</v>
       </c>
-    </row>
-    <row r="106" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S105" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="106" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O106" t="s">
-        <v>228</v>
+        <v>284</v>
       </c>
       <c r="P106" t="s">
         <v>8</v>
@@ -4607,10 +5429,13 @@
       <c r="R106">
         <v>-24.508876936966072</v>
       </c>
-    </row>
-    <row r="107" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S106" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="107" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O107" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="P107" t="s">
         <v>8</v>
@@ -4621,10 +5446,13 @@
       <c r="R107">
         <v>-24.596020608669654</v>
       </c>
-    </row>
-    <row r="108" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S107" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="108" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O108" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="P108" t="s">
         <v>8</v>
@@ -4635,10 +5463,13 @@
       <c r="R108">
         <v>-24.237718714685045</v>
       </c>
-    </row>
-    <row r="109" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S108" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="109" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O109" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="P109" t="s">
         <v>8</v>
@@ -4649,10 +5480,13 @@
       <c r="R109">
         <v>-38.005975900323904</v>
       </c>
-    </row>
-    <row r="110" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S109" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="110" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O110" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="P110" t="s">
         <v>8</v>
@@ -4663,10 +5497,13 @@
       <c r="R110">
         <v>-26.875235100913308</v>
       </c>
-    </row>
-    <row r="111" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S110" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="111" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O111" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="P111" t="s">
         <v>8</v>
@@ -4677,10 +5514,13 @@
       <c r="R111">
         <v>-26.534025398042417</v>
       </c>
-    </row>
-    <row r="112" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S111" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="112" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O112" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="P112" t="s">
         <v>8</v>
@@ -4691,10 +5531,13 @@
       <c r="R112">
         <v>-22.74753318631009</v>
       </c>
-    </row>
-    <row r="113" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S112" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O113" t="s">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="P113" t="s">
         <v>8</v>
@@ -4705,10 +5548,13 @@
       <c r="R113">
         <v>-21.641041566438822</v>
       </c>
-    </row>
-    <row r="114" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S113" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="114" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O114" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="P114" t="s">
         <v>8</v>
@@ -4719,10 +5565,13 @@
       <c r="R114">
         <v>-23.272862019631749</v>
       </c>
-    </row>
-    <row r="115" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S114" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="115" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O115" t="s">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="P115" t="s">
         <v>8</v>
@@ -4733,10 +5582,13 @@
       <c r="R115">
         <v>-21.623457964519616</v>
       </c>
-    </row>
-    <row r="116" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S115" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="116" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
@@ -4747,10 +5599,13 @@
       <c r="R116">
         <v>-21.552485284497635</v>
       </c>
-    </row>
-    <row r="117" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S116" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="117" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
@@ -4761,10 +5616,13 @@
       <c r="R117">
         <v>-24.876471033320065</v>
       </c>
-    </row>
-    <row r="118" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S117" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="118" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
@@ -4775,10 +5633,13 @@
       <c r="R118">
         <v>-22.661907303492882</v>
       </c>
-    </row>
-    <row r="119" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S118" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="119" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
@@ -4789,10 +5650,13 @@
       <c r="R119">
         <v>-22.694486273853538</v>
       </c>
-    </row>
-    <row r="120" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S119" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="120" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>242</v>
+        <v>312</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
@@ -4803,10 +5667,13 @@
       <c r="R120">
         <v>-24.801140356990636</v>
       </c>
-    </row>
-    <row r="121" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S120" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="121" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>243</v>
+        <v>314</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
@@ -4817,10 +5684,13 @@
       <c r="R121">
         <v>-27.37470299236471</v>
       </c>
-    </row>
-    <row r="122" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S121" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="122" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
@@ -4831,10 +5701,13 @@
       <c r="R122">
         <v>-28.851705964151201</v>
       </c>
-    </row>
-    <row r="123" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S122" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="123" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>245</v>
+        <v>318</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
@@ -4845,10 +5718,13 @@
       <c r="R123">
         <v>-26.91171685213137</v>
       </c>
-    </row>
-    <row r="124" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S123" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="124" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>246</v>
+        <v>320</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
@@ -4859,10 +5735,13 @@
       <c r="R124">
         <v>-34.626011552010475</v>
       </c>
-    </row>
-    <row r="125" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S124" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="125" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
@@ -4873,10 +5752,13 @@
       <c r="R125">
         <v>-32.348145019885699</v>
       </c>
-    </row>
-    <row r="126" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S125" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="126" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>248</v>
+        <v>324</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
@@ -4887,10 +5769,13 @@
       <c r="R126">
         <v>-30.839990770085397</v>
       </c>
-    </row>
-    <row r="127" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S126" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="127" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
@@ -4901,10 +5786,13 @@
       <c r="R127">
         <v>-26.901256766800199</v>
       </c>
-    </row>
-    <row r="128" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S127" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="128" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>250</v>
+        <v>328</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
@@ -4915,10 +5803,13 @@
       <c r="R128">
         <v>-30.074386929609709</v>
       </c>
-    </row>
-    <row r="129" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S128" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="129" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
@@ -4929,10 +5820,13 @@
       <c r="R129">
         <v>-29.138471100616751</v>
       </c>
-    </row>
-    <row r="130" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S129" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="130" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
@@ -4943,10 +5837,13 @@
       <c r="R130">
         <v>-30.038314092521837</v>
       </c>
-    </row>
-    <row r="131" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S130" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="131" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
@@ -4957,10 +5854,13 @@
       <c r="R131">
         <v>-32.162377524327063</v>
       </c>
-    </row>
-    <row r="132" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S131" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="132" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>254</v>
+        <v>336</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
@@ -4971,10 +5871,13 @@
       <c r="R132">
         <v>-31.925575525228531</v>
       </c>
-    </row>
-    <row r="133" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S132" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="133" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
@@ -4985,108 +5888,132 @@
       <c r="R133">
         <v>-36.601637274283433</v>
       </c>
-    </row>
-    <row r="134" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S133" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="134" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
       </c>
       <c r="Q134">
+        <v>147.41425715594278</v>
+      </c>
+      <c r="R134">
+        <v>-42.609106537819358</v>
+      </c>
+      <c r="S134" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="135" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O135" t="s">
+        <v>342</v>
+      </c>
+      <c r="P135" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q135">
         <v>130.44549037437517</v>
       </c>
-      <c r="R134">
+      <c r="R135">
         <v>-19.148753079902079</v>
       </c>
-    </row>
-    <row r="135" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O135" t="s">
-        <v>257</v>
-      </c>
-      <c r="P135" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q135">
+      <c r="S135" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="136" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O136" t="s">
+        <v>344</v>
+      </c>
+      <c r="P136" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q136">
         <v>130.21666041483596</v>
       </c>
-      <c r="R135">
+      <c r="R136">
         <v>-15.336686243625843</v>
       </c>
-    </row>
-    <row r="136" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O136" t="s">
-        <v>258</v>
-      </c>
-      <c r="P136" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q136">
+      <c r="S136" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="137" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O137" t="s">
+        <v>346</v>
+      </c>
+      <c r="P137" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q137">
         <v>119.58806566385246</v>
       </c>
-      <c r="R136">
+      <c r="R137">
         <v>-20.825706306232721</v>
       </c>
-    </row>
-    <row r="137" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O137" t="s">
-        <v>259</v>
-      </c>
-      <c r="P137" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q137">
+      <c r="S137" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="138" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O138" t="s">
+        <v>348</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q138">
         <v>123.07722410756404</v>
       </c>
-      <c r="R137">
+      <c r="R138">
         <v>-19.907342783485745</v>
       </c>
-    </row>
-    <row r="138" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O138" t="s">
-        <v>260</v>
-      </c>
-      <c r="P138" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q138">
+      <c r="S138" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="139" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O139" t="s">
+        <v>350</v>
+      </c>
+      <c r="P139" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q139">
         <v>126.86620324681024</v>
       </c>
-      <c r="R138">
+      <c r="R139">
         <v>-16.778364179633666</v>
       </c>
-    </row>
-    <row r="139" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O139" t="s">
-        <v>261</v>
-      </c>
-      <c r="P139" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q139">
+      <c r="S139" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="140" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O140" t="s">
+        <v>352</v>
+      </c>
+      <c r="P140" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q140">
         <v>126.68911386447304</v>
       </c>
-      <c r="R139">
+      <c r="R140">
         <v>-19.57556420488984</v>
       </c>
-    </row>
-    <row r="140" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O140" t="s">
-        <v>262</v>
-      </c>
-      <c r="P140" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q140">
-        <v>147.1701068156745</v>
-      </c>
-      <c r="R140">
-        <v>-42.677737589053145</v>
-      </c>
-    </row>
-    <row r="141" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S140" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="141" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
@@ -5097,10 +6024,13 @@
       <c r="R141">
         <v>-29.912338692430929</v>
       </c>
-    </row>
-    <row r="142" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S141" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="142" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
@@ -5111,10 +6041,13 @@
       <c r="R142">
         <v>-26.619227583857882</v>
       </c>
-    </row>
-    <row r="143" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S142" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="143" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>265</v>
+        <v>358</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
@@ -5125,10 +6058,13 @@
       <c r="R143">
         <v>-26.19534615411176</v>
       </c>
-    </row>
-    <row r="144" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S143" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="144" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
@@ -5139,10 +6075,13 @@
       <c r="R144">
         <v>-30.015041377829604</v>
       </c>
-    </row>
-    <row r="145" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S144" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="145" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
@@ -5153,10 +6092,13 @@
       <c r="R145">
         <v>-28.23473524394884</v>
       </c>
-    </row>
-    <row r="146" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S145" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="146" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>268</v>
+        <v>364</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
@@ -5167,10 +6109,13 @@
       <c r="R146">
         <v>-31.570835856427525</v>
       </c>
-    </row>
-    <row r="147" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S146" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="147" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>269</v>
+        <v>366</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
@@ -5181,10 +6126,13 @@
       <c r="R147">
         <v>-31.872154827099781</v>
       </c>
-    </row>
-    <row r="148" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S147" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="148" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>270</v>
+        <v>368</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
@@ -5195,276 +6143,336 @@
       <c r="R148">
         <v>-34.584112229567701</v>
       </c>
-    </row>
-    <row r="149" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S148" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="149" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>271</v>
+        <v>370</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>116.44753624908248</v>
+        <v>118.5085945386015</v>
       </c>
       <c r="R149">
-        <v>-34.917150029871202</v>
-      </c>
-    </row>
-    <row r="150" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-35.070026612914461</v>
+      </c>
+      <c r="S149" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="150" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>272</v>
+        <v>372</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>144.36113356472447</v>
+        <v>115.45951859019976</v>
       </c>
       <c r="R150">
-        <v>-41.44005143720814</v>
-      </c>
-    </row>
-    <row r="151" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-34.743596006842388</v>
+      </c>
+      <c r="S150" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="151" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>273</v>
+        <v>374</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>145.97678015008486</v>
+        <v>146.38887677493818</v>
       </c>
       <c r="R151">
-        <v>-40.254914758185407</v>
-      </c>
-    </row>
-    <row r="152" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-40.224745480761946</v>
+      </c>
+      <c r="S151" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="152" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>274</v>
+        <v>376</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
       </c>
       <c r="Q152">
+        <v>144.35963098272583</v>
+      </c>
+      <c r="R152">
+        <v>-41.062297982110003</v>
+      </c>
+      <c r="S152" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="153" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O153" t="s">
+        <v>378</v>
+      </c>
+      <c r="P153" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q153">
         <v>143.87674213215473</v>
       </c>
-      <c r="R152">
+      <c r="R153">
         <v>-39.257876116339148</v>
       </c>
-    </row>
-    <row r="153" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O153" t="s">
-        <v>275</v>
-      </c>
-      <c r="P153" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q153">
+      <c r="S153" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O154" t="s">
+        <v>380</v>
+      </c>
+      <c r="P154" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q154">
         <v>150.90399697993092</v>
       </c>
-      <c r="R153">
+      <c r="R154">
         <v>-21.252254703658771</v>
       </c>
-    </row>
-    <row r="154" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O154" t="s">
-        <v>276</v>
-      </c>
-      <c r="P154" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q154">
-        <v>153.37306950018458</v>
-      </c>
-      <c r="R154">
-        <v>-30.859626845395809</v>
-      </c>
-    </row>
-    <row r="155" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S154" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="155" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>277</v>
+        <v>382</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
       </c>
       <c r="Q155">
+        <v>153.6896898968202</v>
+      </c>
+      <c r="R155">
+        <v>-30.56757638507419</v>
+      </c>
+      <c r="S155" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="156" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O156" t="s">
+        <v>384</v>
+      </c>
+      <c r="P156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q156">
         <v>137.75207579058173</v>
       </c>
-      <c r="R155">
+      <c r="R156">
         <v>-32.743780387632853</v>
       </c>
-    </row>
-    <row r="156" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O156" t="s">
-        <v>278</v>
-      </c>
-      <c r="P156" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q156">
+      <c r="S156" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="157" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O157" t="s">
+        <v>386</v>
+      </c>
+      <c r="P157" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q157">
         <v>133.82287060397272</v>
       </c>
-      <c r="R156">
+      <c r="R157">
         <v>-34.227843031724603</v>
       </c>
-    </row>
-    <row r="157" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O157" t="s">
-        <v>279</v>
-      </c>
-      <c r="P157" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q157">
+      <c r="S157" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="158" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O158" t="s">
+        <v>388</v>
+      </c>
+      <c r="P158" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q158">
         <v>150.32141234786266</v>
       </c>
-      <c r="R157">
+      <c r="R158">
         <v>-21.199688649197544</v>
       </c>
-    </row>
-    <row r="158" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O158" t="s">
-        <v>280</v>
-      </c>
-      <c r="P158" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q158">
+      <c r="S158" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="159" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O159" t="s">
+        <v>390</v>
+      </c>
+      <c r="P159" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q159">
         <v>150.81900140649941</v>
       </c>
-      <c r="R158">
+      <c r="R159">
         <v>-19.943795597851125</v>
       </c>
-    </row>
-    <row r="159" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O159" t="s">
-        <v>281</v>
-      </c>
-      <c r="P159" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q159">
-        <v>153.55763832618015</v>
-      </c>
-      <c r="R159">
-        <v>-25.92492989840304</v>
-      </c>
-    </row>
-    <row r="160" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S159" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="160" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O160" t="s">
-        <v>282</v>
+        <v>392</v>
       </c>
       <c r="P160" t="s">
         <v>8</v>
       </c>
       <c r="Q160">
+        <v>153.65346669501773</v>
+      </c>
+      <c r="R160">
+        <v>-27.062670728927419</v>
+      </c>
+      <c r="S160" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="161" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O161" t="s">
+        <v>394</v>
+      </c>
+      <c r="P161" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q161">
         <v>151.46867878644642</v>
       </c>
-      <c r="R160">
+      <c r="R161">
         <v>-21.50731377536102</v>
       </c>
-    </row>
-    <row r="161" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O161" t="s">
-        <v>283</v>
-      </c>
-      <c r="P161" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q161">
+      <c r="S161" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O162" t="s">
+        <v>396</v>
+      </c>
+      <c r="P162" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q162">
         <v>153.73370306869481</v>
       </c>
-      <c r="R161">
+      <c r="R162">
         <v>-23.608887736048747</v>
       </c>
-    </row>
-    <row r="162" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O162" t="s">
-        <v>284</v>
-      </c>
-      <c r="P162" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q162">
+      <c r="S162" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="163" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O163" t="s">
+        <v>398</v>
+      </c>
+      <c r="P163" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q163">
         <v>150.57744483884846</v>
       </c>
-      <c r="R162">
+      <c r="R163">
         <v>-17.040567652389406</v>
       </c>
-    </row>
-    <row r="163" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O163" t="s">
-        <v>285</v>
-      </c>
-      <c r="P163" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q163">
+      <c r="S163" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="164" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O164" t="s">
+        <v>400</v>
+      </c>
+      <c r="P164" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q164">
         <v>149.21297177481156</v>
       </c>
-      <c r="R163">
+      <c r="R164">
         <v>-18.721877322770485</v>
       </c>
-    </row>
-    <row r="164" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O164" t="s">
-        <v>286</v>
-      </c>
-      <c r="P164" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q164">
+      <c r="S164" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="165" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O165" t="s">
+        <v>402</v>
+      </c>
+      <c r="P165" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q165">
         <v>135.81882012006892</v>
       </c>
-      <c r="R164">
+      <c r="R165">
         <v>-35.521402273625938</v>
       </c>
-    </row>
-    <row r="165" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O165" t="s">
-        <v>287</v>
-      </c>
-      <c r="P165" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q165">
+      <c r="S165" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="166" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O166" t="s">
+        <v>404</v>
+      </c>
+      <c r="P166" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q166">
         <v>138.0138906141494</v>
       </c>
-      <c r="R165">
+      <c r="R166">
         <v>-36.635585635401441</v>
       </c>
-    </row>
-    <row r="166" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O166" t="s">
-        <v>288</v>
-      </c>
-      <c r="P166" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q166">
-        <v>153.78400128986024</v>
-      </c>
-      <c r="R166">
-        <v>-27.74890644111397</v>
-      </c>
-    </row>
-    <row r="167" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S166" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="167" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O167" t="s">
-        <v>289</v>
+        <v>406</v>
       </c>
       <c r="P167" t="s">
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>148.64966281870522</v>
+        <v>148.68640459473278</v>
       </c>
       <c r="R167">
-        <v>-41.089250164550577</v>
-      </c>
-    </row>
-    <row r="168" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-40.739731140552188</v>
+      </c>
+      <c r="S167" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="168" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O168" t="s">
-        <v>290</v>
+        <v>408</v>
       </c>
       <c r="P168" t="s">
         <v>8</v>
@@ -5475,10 +6483,13 @@
       <c r="R168">
         <v>-38.046262781033171</v>
       </c>
-    </row>
-    <row r="169" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S168" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="169" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O169" t="s">
-        <v>291</v>
+        <v>410</v>
       </c>
       <c r="P169" t="s">
         <v>8</v>
@@ -5489,10 +6500,13 @@
       <c r="R169">
         <v>-32.63728608022614</v>
       </c>
-    </row>
-    <row r="170" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S169" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="170" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O170" t="s">
-        <v>292</v>
+        <v>412</v>
       </c>
       <c r="P170" t="s">
         <v>8</v>
@@ -5503,10 +6517,13 @@
       <c r="R170">
         <v>-32.982094689407965</v>
       </c>
-    </row>
-    <row r="171" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S170" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="171" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O171" t="s">
-        <v>293</v>
+        <v>414</v>
       </c>
       <c r="P171" t="s">
         <v>8</v>
@@ -5517,10 +6534,13 @@
       <c r="R171">
         <v>-10.389603210951345</v>
       </c>
-    </row>
-    <row r="172" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S171" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="172" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O172" t="s">
-        <v>294</v>
+        <v>416</v>
       </c>
       <c r="P172" t="s">
         <v>8</v>
@@ -5531,10 +6551,13 @@
       <c r="R172">
         <v>-16.784378905659178</v>
       </c>
-    </row>
-    <row r="173" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S172" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="173" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O173" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="P173" t="s">
         <v>8</v>
@@ -5545,10 +6568,13 @@
       <c r="R173">
         <v>-14.184024112238506</v>
       </c>
-    </row>
-    <row r="174" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S173" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="174" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O174" t="s">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="P174" t="s">
         <v>8</v>
@@ -5559,10 +6585,13 @@
       <c r="R174">
         <v>-10.398499647377401</v>
       </c>
-    </row>
-    <row r="175" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S174" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="175" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O175" t="s">
-        <v>297</v>
+        <v>422</v>
       </c>
       <c r="P175" t="s">
         <v>8</v>
@@ -5573,10 +6602,13 @@
       <c r="R175">
         <v>-12.954950246643154</v>
       </c>
-    </row>
-    <row r="176" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S175" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="176" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O176" t="s">
-        <v>298</v>
+        <v>424</v>
       </c>
       <c r="P176" t="s">
         <v>8</v>
@@ -5587,10 +6619,13 @@
       <c r="R176">
         <v>-37.040409183139161</v>
       </c>
-    </row>
-    <row r="177" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S176" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="177" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O177" t="s">
-        <v>299</v>
+        <v>426</v>
       </c>
       <c r="P177" t="s">
         <v>8</v>
@@ -5601,10 +6636,13 @@
       <c r="R177">
         <v>-34.407627927699693</v>
       </c>
-    </row>
-    <row r="178" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S177" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="178" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O178" t="s">
-        <v>300</v>
+        <v>428</v>
       </c>
       <c r="P178" t="s">
         <v>8</v>
@@ -5615,10 +6653,13 @@
       <c r="R178">
         <v>-39.085132333872046</v>
       </c>
-    </row>
-    <row r="179" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S178" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="179" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O179" t="s">
-        <v>301</v>
+        <v>430</v>
       </c>
       <c r="P179" t="s">
         <v>8</v>
@@ -5629,10 +6670,13 @@
       <c r="R179">
         <v>-38.800100646368243</v>
       </c>
-    </row>
-    <row r="180" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S179" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="180" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O180" t="s">
-        <v>302</v>
+        <v>432</v>
       </c>
       <c r="P180" t="s">
         <v>8</v>
@@ -5643,10 +6687,13 @@
       <c r="R180">
         <v>-24.711616537979179</v>
       </c>
-    </row>
-    <row r="181" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S180" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="181" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O181" t="s">
-        <v>303</v>
+        <v>434</v>
       </c>
       <c r="P181" t="s">
         <v>8</v>
@@ -5657,10 +6704,13 @@
       <c r="R181">
         <v>-22.354482597944848</v>
       </c>
-    </row>
-    <row r="182" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S181" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="182" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O182" t="s">
-        <v>304</v>
+        <v>436</v>
       </c>
       <c r="P182" t="s">
         <v>8</v>
@@ -5671,10 +6721,13 @@
       <c r="R182">
         <v>-20.523860877195684</v>
       </c>
-    </row>
-    <row r="183" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S182" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="183" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O183" t="s">
-        <v>305</v>
+        <v>438</v>
       </c>
       <c r="P183" t="s">
         <v>8</v>
@@ -5685,10 +6738,13 @@
       <c r="R183">
         <v>-38.121468284809652</v>
       </c>
-    </row>
-    <row r="184" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S183" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="184" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O184" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
       <c r="P184" t="s">
         <v>8</v>
@@ -5699,10 +6755,13 @@
       <c r="R184">
         <v>-39.111899860277866</v>
       </c>
-    </row>
-    <row r="185" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S184" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="185" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O185" t="s">
-        <v>307</v>
+        <v>442</v>
       </c>
       <c r="P185" t="s">
         <v>8</v>
@@ -5713,10 +6772,13 @@
       <c r="R185">
         <v>-19.417223673518691</v>
       </c>
-    </row>
-    <row r="186" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S185" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="186" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O186" t="s">
-        <v>308</v>
+        <v>444</v>
       </c>
       <c r="P186" t="s">
         <v>8</v>
@@ -5727,10 +6789,13 @@
       <c r="R186">
         <v>-22.345487760282055</v>
       </c>
-    </row>
-    <row r="187" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S186" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="187" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O187" t="s">
-        <v>309</v>
+        <v>446</v>
       </c>
       <c r="P187" t="s">
         <v>8</v>
@@ -5741,10 +6806,13 @@
       <c r="R187">
         <v>-27.354177147344291</v>
       </c>
-    </row>
-    <row r="188" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S187" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="188" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O188" t="s">
-        <v>310</v>
+        <v>448</v>
       </c>
       <c r="P188" t="s">
         <v>8</v>
@@ -5755,10 +6823,13 @@
       <c r="R188">
         <v>-26.207109582102465</v>
       </c>
-    </row>
-    <row r="189" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S188" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="189" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O189" t="s">
-        <v>311</v>
+        <v>450</v>
       </c>
       <c r="P189" t="s">
         <v>8</v>
@@ -5769,10 +6840,13 @@
       <c r="R189">
         <v>-35.683734291786699</v>
       </c>
-    </row>
-    <row r="190" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S189" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="190" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O190" t="s">
-        <v>312</v>
+        <v>452</v>
       </c>
       <c r="P190" t="s">
         <v>8</v>
@@ -5783,10 +6857,13 @@
       <c r="R190">
         <v>-28.778266365139427</v>
       </c>
-    </row>
-    <row r="191" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S190" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="191" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O191" t="s">
-        <v>313</v>
+        <v>454</v>
       </c>
       <c r="P191" t="s">
         <v>8</v>
@@ -5797,10 +6874,13 @@
       <c r="R191">
         <v>-33.016657902646344</v>
       </c>
-    </row>
-    <row r="192" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S191" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="192" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O192" t="s">
-        <v>314</v>
+        <v>456</v>
       </c>
       <c r="P192" t="s">
         <v>8</v>
@@ -5811,10 +6891,13 @@
       <c r="R192">
         <v>-32.513996088608671</v>
       </c>
-    </row>
-    <row r="193" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S192" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="193" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O193" t="s">
-        <v>315</v>
+        <v>458</v>
       </c>
       <c r="P193" t="s">
         <v>8</v>
@@ -5825,66 +6908,81 @@
       <c r="R193">
         <v>-37.165158559530319</v>
       </c>
-    </row>
-    <row r="194" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S193" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="194" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O194" t="s">
-        <v>316</v>
+        <v>460</v>
       </c>
       <c r="P194" t="s">
         <v>8</v>
       </c>
       <c r="Q194">
+        <v>147.06278669756466</v>
+      </c>
+      <c r="R194">
+        <v>-43.476483100222218</v>
+      </c>
+      <c r="S194" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="195" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O195" t="s">
+        <v>462</v>
+      </c>
+      <c r="P195" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q195">
         <v>119.67814798329256</v>
       </c>
-      <c r="R194">
+      <c r="R195">
         <v>-17.977932221868844</v>
       </c>
-    </row>
-    <row r="195" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O195" t="s">
-        <v>317</v>
-      </c>
-      <c r="P195" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q195">
+      <c r="S195" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="196" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O196" t="s">
+        <v>464</v>
+      </c>
+      <c r="P196" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q196">
         <v>130.24318545304698</v>
       </c>
-      <c r="R195">
+      <c r="R196">
         <v>-10.13254267953079</v>
       </c>
-    </row>
-    <row r="196" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O196" t="s">
-        <v>318</v>
-      </c>
-      <c r="P196" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q196">
+      <c r="S196" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="197" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O197" t="s">
+        <v>466</v>
+      </c>
+      <c r="P197" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q197">
         <v>124.84028618906758</v>
       </c>
-      <c r="R196">
+      <c r="R197">
         <v>-12.690138373320879</v>
       </c>
-    </row>
-    <row r="197" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O197" t="s">
-        <v>319</v>
-      </c>
-      <c r="P197" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q197">
-        <v>147.10370753016318</v>
-      </c>
-      <c r="R197">
-        <v>-43.459445564853546</v>
-      </c>
-    </row>
-    <row r="198" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S197" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="198" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O198" t="s">
-        <v>320</v>
+        <v>468</v>
       </c>
       <c r="P198" t="s">
         <v>8</v>
@@ -5895,10 +6993,13 @@
       <c r="R198">
         <v>-34.292485898627589</v>
       </c>
-    </row>
-    <row r="199" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S198" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="199" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O199" t="s">
-        <v>321</v>
+        <v>470</v>
       </c>
       <c r="P199" t="s">
         <v>8</v>
@@ -5909,10 +7010,13 @@
       <c r="R199">
         <v>-33.282150864166539</v>
       </c>
-    </row>
-    <row r="200" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S199" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="200" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O200" t="s">
-        <v>322</v>
+        <v>472</v>
       </c>
       <c r="P200" t="s">
         <v>8</v>
@@ -5923,10 +7027,13 @@
       <c r="R200">
         <v>-34.568155881156414</v>
       </c>
-    </row>
-    <row r="201" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S200" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="201" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O201" t="s">
-        <v>323</v>
+        <v>473</v>
       </c>
       <c r="P201" t="s">
         <v>8</v>
@@ -5937,10 +7044,13 @@
       <c r="R201">
         <v>-36.753271835090963</v>
       </c>
-    </row>
-    <row r="202" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S201" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="202" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O202" t="s">
-        <v>324</v>
+        <v>474</v>
       </c>
       <c r="P202" t="s">
         <v>8</v>
@@ -5951,10 +7061,13 @@
       <c r="R202">
         <v>-34.636518230808882</v>
       </c>
-    </row>
-    <row r="203" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S202" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="203" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O203" t="s">
-        <v>325</v>
+        <v>475</v>
       </c>
       <c r="P203" t="s">
         <v>8</v>
@@ -5965,10 +7078,13 @@
       <c r="R203">
         <v>-41.072643681112218</v>
       </c>
-    </row>
-    <row r="204" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S203" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="204" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O204" t="s">
-        <v>326</v>
+        <v>477</v>
       </c>
       <c r="P204" t="s">
         <v>8</v>
@@ -5979,10 +7095,13 @@
       <c r="R204">
         <v>-37.539659494375663</v>
       </c>
-    </row>
-    <row r="205" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S204" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="205" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O205" t="s">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="P205" t="s">
         <v>8</v>
@@ -5993,10 +7112,13 @@
       <c r="R205">
         <v>-24.594606239715439</v>
       </c>
-    </row>
-    <row r="206" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S205" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="206" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O206" t="s">
-        <v>328</v>
+        <v>479</v>
       </c>
       <c r="P206" t="s">
         <v>8</v>
@@ -6007,24 +7129,30 @@
       <c r="R206">
         <v>-23.934891614524041</v>
       </c>
-    </row>
-    <row r="207" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S206" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="207" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O207" t="s">
-        <v>329</v>
+        <v>480</v>
       </c>
       <c r="P207" t="s">
         <v>8</v>
       </c>
       <c r="Q207">
-        <v>150.9301046692855</v>
+        <v>150.93476814193207</v>
       </c>
       <c r="R207">
-        <v>-30.52001579209675</v>
-      </c>
-    </row>
-    <row r="208" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-30.518528831413143</v>
+      </c>
+      <c r="S207" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="208" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O208" t="s">
-        <v>330</v>
+        <v>481</v>
       </c>
       <c r="P208" t="s">
         <v>8</v>
@@ -6035,10 +7163,13 @@
       <c r="R208">
         <v>-33.217357840283256</v>
       </c>
-    </row>
-    <row r="209" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S208" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="209" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O209" t="s">
-        <v>331</v>
+        <v>483</v>
       </c>
       <c r="P209" t="s">
         <v>8</v>
@@ -6049,10 +7180,13 @@
       <c r="R209">
         <v>-32.011051991230055</v>
       </c>
-    </row>
-    <row r="210" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S209" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="210" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O210" t="s">
-        <v>332</v>
+        <v>485</v>
       </c>
       <c r="P210" t="s">
         <v>8</v>
@@ -6063,10 +7197,13 @@
       <c r="R210">
         <v>-33.242416864356407</v>
       </c>
-    </row>
-    <row r="211" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S210" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="211" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O211" t="s">
-        <v>333</v>
+        <v>486</v>
       </c>
       <c r="P211" t="s">
         <v>8</v>
@@ -6077,10 +7214,13 @@
       <c r="R211">
         <v>-23.938105777917052</v>
       </c>
-    </row>
-    <row r="212" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S211" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="212" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O212" t="s">
-        <v>334</v>
+        <v>487</v>
       </c>
       <c r="P212" t="s">
         <v>8</v>
@@ -6091,10 +7231,13 @@
       <c r="R212">
         <v>-31.78762838768008</v>
       </c>
-    </row>
-    <row r="213" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S212" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="213" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O213" t="s">
-        <v>335</v>
+        <v>488</v>
       </c>
       <c r="P213" t="s">
         <v>8</v>
@@ -6105,10 +7248,13 @@
       <c r="R213">
         <v>-34.136563287228782</v>
       </c>
-    </row>
-    <row r="214" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S213" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="214" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O214" t="s">
-        <v>336</v>
+        <v>490</v>
       </c>
       <c r="P214" t="s">
         <v>8</v>
@@ -6119,10 +7265,13 @@
       <c r="R214">
         <v>-31.39220732642514</v>
       </c>
-    </row>
-    <row r="215" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S214" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="215" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O215" t="s">
-        <v>337</v>
+        <v>492</v>
       </c>
       <c r="P215" t="s">
         <v>8</v>
@@ -6133,10 +7282,13 @@
       <c r="R215">
         <v>-33.709133190238028</v>
       </c>
-    </row>
-    <row r="216" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S215" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="216" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O216" t="s">
-        <v>338</v>
+        <v>493</v>
       </c>
       <c r="P216" t="s">
         <v>8</v>
@@ -6147,108 +7299,132 @@
       <c r="R216">
         <v>-26.323911406128701</v>
       </c>
-    </row>
-    <row r="217" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S216" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="217" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O217" t="s">
-        <v>339</v>
+        <v>494</v>
       </c>
       <c r="P217" t="s">
         <v>8</v>
       </c>
       <c r="Q217">
+        <v>152.51317424828557</v>
+      </c>
+      <c r="R217">
+        <v>-28.276244191915151</v>
+      </c>
+      <c r="S217" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="218" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O218" t="s">
+        <v>495</v>
+      </c>
+      <c r="P218" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q218">
         <v>150.24713680163202</v>
       </c>
-      <c r="R217">
+      <c r="R218">
         <v>-23.693112920968051</v>
       </c>
-    </row>
-    <row r="218" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O218" t="s">
-        <v>340</v>
-      </c>
-      <c r="P218" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q218">
+      <c r="S218" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="219" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O219" t="s">
+        <v>496</v>
+      </c>
+      <c r="P219" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q219">
         <v>151.61716576352794</v>
       </c>
-      <c r="R218">
+      <c r="R219">
         <v>-25.37400675796134</v>
       </c>
-    </row>
-    <row r="219" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O219" t="s">
-        <v>341</v>
-      </c>
-      <c r="P219" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q219">
+      <c r="S219" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="220" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O220" t="s">
+        <v>497</v>
+      </c>
+      <c r="P220" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q220">
         <v>143.35412326528009</v>
       </c>
-      <c r="R219">
+      <c r="R220">
         <v>-23.419388107531574</v>
       </c>
-    </row>
-    <row r="220" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O220" t="s">
-        <v>342</v>
-      </c>
-      <c r="P220" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q220">
+      <c r="S220" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="221" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O221" t="s">
+        <v>499</v>
+      </c>
+      <c r="P221" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q221">
         <v>144.78502894446973</v>
       </c>
-      <c r="R220">
+      <c r="R221">
         <v>-21.882733173886301</v>
       </c>
-    </row>
-    <row r="221" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O221" t="s">
-        <v>343</v>
-      </c>
-      <c r="P221" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q221">
+      <c r="S221" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="222" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O222" t="s">
+        <v>501</v>
+      </c>
+      <c r="P222" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q222">
         <v>147.21725198745645</v>
       </c>
-      <c r="R221">
+      <c r="R222">
         <v>-35.479752937238217</v>
       </c>
-    </row>
-    <row r="222" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O222" t="s">
-        <v>344</v>
-      </c>
-      <c r="P222" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q222">
+      <c r="S222" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O223" t="s">
+        <v>502</v>
+      </c>
+      <c r="P223" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q223">
         <v>139.19580294835177</v>
       </c>
-      <c r="R222">
+      <c r="R223">
         <v>-35.629567001716929</v>
       </c>
-    </row>
-    <row r="223" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O223" t="s">
-        <v>345</v>
-      </c>
-      <c r="P223" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q223">
-        <v>152.52412221723841</v>
-      </c>
-      <c r="R223">
-        <v>-28.289668493542941</v>
-      </c>
-    </row>
-    <row r="224" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S223" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O224" t="s">
-        <v>346</v>
+        <v>503</v>
       </c>
       <c r="P224" t="s">
         <v>8</v>
@@ -6259,24 +7435,30 @@
       <c r="R224">
         <v>-29.184208941029169</v>
       </c>
-    </row>
-    <row r="225" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S224" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="225" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O225" t="s">
-        <v>347</v>
+        <v>504</v>
       </c>
       <c r="P225" t="s">
         <v>8</v>
       </c>
       <c r="Q225">
-        <v>147.4317513167116</v>
+        <v>147.40204885581329</v>
       </c>
       <c r="R225">
-        <v>-41.912687414816389</v>
-      </c>
-    </row>
-    <row r="226" spans="15:18" x14ac:dyDescent="0.45">
+        <v>-41.896128682730868</v>
+      </c>
+      <c r="S225" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="226" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O226" t="s">
-        <v>348</v>
+        <v>506</v>
       </c>
       <c r="P226" t="s">
         <v>8</v>
@@ -6287,10 +7469,13 @@
       <c r="R226">
         <v>-37.082583790808052</v>
       </c>
-    </row>
-    <row r="227" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S226" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="227" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O227" t="s">
-        <v>349</v>
+        <v>508</v>
       </c>
       <c r="P227" t="s">
         <v>8</v>
@@ -6301,10 +7486,13 @@
       <c r="R227">
         <v>-28.559817952692089</v>
       </c>
-    </row>
-    <row r="228" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S227" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="228" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O228" t="s">
-        <v>350</v>
+        <v>510</v>
       </c>
       <c r="P228" t="s">
         <v>8</v>
@@ -6315,10 +7503,13 @@
       <c r="R228">
         <v>-29.592137880611126</v>
       </c>
-    </row>
-    <row r="229" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S228" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="229" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O229" t="s">
-        <v>351</v>
+        <v>512</v>
       </c>
       <c r="P229" t="s">
         <v>8</v>
@@ -6329,10 +7520,13 @@
       <c r="R229">
         <v>-29.335892876129801</v>
       </c>
-    </row>
-    <row r="230" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S229" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="230" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O230" t="s">
-        <v>352</v>
+        <v>514</v>
       </c>
       <c r="P230" t="s">
         <v>8</v>
@@ -6343,10 +7537,13 @@
       <c r="R230">
         <v>-27.601128760451285</v>
       </c>
-    </row>
-    <row r="231" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S230" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="231" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O231" t="s">
-        <v>353</v>
+        <v>516</v>
       </c>
       <c r="P231" t="s">
         <v>8</v>
@@ -6357,10 +7554,13 @@
       <c r="R231">
         <v>-31.225893165724464</v>
       </c>
-    </row>
-    <row r="232" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S231" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="232" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O232" t="s">
-        <v>354</v>
+        <v>518</v>
       </c>
       <c r="P232" t="s">
         <v>8</v>
@@ -6371,10 +7571,13 @@
       <c r="R232">
         <v>-30.635030423097369</v>
       </c>
-    </row>
-    <row r="233" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S232" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="233" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O233" t="s">
-        <v>355</v>
+        <v>520</v>
       </c>
       <c r="P233" t="s">
         <v>8</v>
@@ -6385,10 +7588,13 @@
       <c r="R233">
         <v>-19.7614568980045</v>
       </c>
-    </row>
-    <row r="234" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S233" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="234" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O234" t="s">
-        <v>356</v>
+        <v>522</v>
       </c>
       <c r="P234" t="s">
         <v>8</v>
@@ -6399,10 +7605,13 @@
       <c r="R234">
         <v>-20.985072115261776</v>
       </c>
-    </row>
-    <row r="235" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S234" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="235" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O235" t="s">
-        <v>357</v>
+        <v>524</v>
       </c>
       <c r="P235" t="s">
         <v>8</v>
@@ -6413,10 +7622,13 @@
       <c r="R235">
         <v>-22.185521896147964</v>
       </c>
-    </row>
-    <row r="236" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S235" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="236" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O236" t="s">
-        <v>358</v>
+        <v>526</v>
       </c>
       <c r="P236" t="s">
         <v>8</v>
@@ -6427,10 +7639,13 @@
       <c r="R236">
         <v>-22.491780738849684</v>
       </c>
-    </row>
-    <row r="237" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S236" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="237" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O237" t="s">
-        <v>359</v>
+        <v>528</v>
       </c>
       <c r="P237" t="s">
         <v>8</v>
@@ -6441,10 +7656,13 @@
       <c r="R237">
         <v>-23.182718054941848</v>
       </c>
-    </row>
-    <row r="238" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S237" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="238" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O238" t="s">
-        <v>360</v>
+        <v>530</v>
       </c>
       <c r="P238" t="s">
         <v>8</v>
@@ -6455,10 +7673,13 @@
       <c r="R238">
         <v>-27.01676446044485</v>
       </c>
-    </row>
-    <row r="239" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S238" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="239" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O239" t="s">
-        <v>361</v>
+        <v>532</v>
       </c>
       <c r="P239" t="s">
         <v>8</v>
@@ -6469,10 +7690,13 @@
       <c r="R239">
         <v>-24.564743730374044</v>
       </c>
-    </row>
-    <row r="240" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S239" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="240" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O240" t="s">
-        <v>362</v>
+        <v>534</v>
       </c>
       <c r="P240" t="s">
         <v>8</v>
@@ -6483,10 +7707,13 @@
       <c r="R240">
         <v>-24.119247432589709</v>
       </c>
-    </row>
-    <row r="241" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S240" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="241" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O241" t="s">
-        <v>363</v>
+        <v>536</v>
       </c>
       <c r="P241" t="s">
         <v>8</v>
@@ -6497,10 +7724,13 @@
       <c r="R241">
         <v>-25.857755904197489</v>
       </c>
-    </row>
-    <row r="242" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S241" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="242" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O242" t="s">
-        <v>364</v>
+        <v>538</v>
       </c>
       <c r="P242" t="s">
         <v>8</v>
@@ -6511,10 +7741,13 @@
       <c r="R242">
         <v>-24.79923061036914</v>
       </c>
-    </row>
-    <row r="243" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S242" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="243" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O243" t="s">
-        <v>365</v>
+        <v>540</v>
       </c>
       <c r="P243" t="s">
         <v>8</v>
@@ -6525,10 +7758,13 @@
       <c r="R243">
         <v>-26.633458313858693</v>
       </c>
-    </row>
-    <row r="244" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S243" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="244" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O244" t="s">
-        <v>366</v>
+        <v>542</v>
       </c>
       <c r="P244" t="s">
         <v>8</v>
@@ -6539,10 +7775,13 @@
       <c r="R244">
         <v>-20.49820523250327</v>
       </c>
-    </row>
-    <row r="245" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S244" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="245" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O245" t="s">
-        <v>367</v>
+        <v>544</v>
       </c>
       <c r="P245" t="s">
         <v>8</v>
@@ -6553,10 +7792,13 @@
       <c r="R245">
         <v>-17.741016470746892</v>
       </c>
-    </row>
-    <row r="246" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S245" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="246" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O246" t="s">
-        <v>368</v>
+        <v>546</v>
       </c>
       <c r="P246" t="s">
         <v>8</v>
@@ -6567,10 +7809,13 @@
       <c r="R246">
         <v>-18.402066295276651</v>
       </c>
-    </row>
-    <row r="247" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S246" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="247" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O247" t="s">
-        <v>369</v>
+        <v>548</v>
       </c>
       <c r="P247" t="s">
         <v>8</v>
@@ -6581,10 +7826,13 @@
       <c r="R247">
         <v>-18.420745131426489</v>
       </c>
-    </row>
-    <row r="248" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S247" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="248" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O248" t="s">
-        <v>370</v>
+        <v>550</v>
       </c>
       <c r="P248" t="s">
         <v>8</v>
@@ -6595,10 +7843,13 @@
       <c r="R248">
         <v>-13.663984400146033</v>
       </c>
-    </row>
-    <row r="249" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S248" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="249" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O249" t="s">
-        <v>371</v>
+        <v>552</v>
       </c>
       <c r="P249" t="s">
         <v>8</v>
@@ -6609,10 +7860,13 @@
       <c r="R249">
         <v>-20.229420786672222</v>
       </c>
-    </row>
-    <row r="250" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S249" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="250" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O250" t="s">
-        <v>372</v>
+        <v>554</v>
       </c>
       <c r="P250" t="s">
         <v>8</v>
@@ -6623,10 +7877,13 @@
       <c r="R250">
         <v>-36.214456588804133</v>
       </c>
-    </row>
-    <row r="251" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S250" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="251" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O251" t="s">
-        <v>373</v>
+        <v>555</v>
       </c>
       <c r="P251" t="s">
         <v>8</v>
@@ -6637,10 +7894,13 @@
       <c r="R251">
         <v>-30.848388264297188</v>
       </c>
-    </row>
-    <row r="252" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S251" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="252" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O252" t="s">
-        <v>374</v>
+        <v>556</v>
       </c>
       <c r="P252" t="s">
         <v>8</v>
@@ -6651,10 +7911,13 @@
       <c r="R252">
         <v>-38.380451924359413</v>
       </c>
-    </row>
-    <row r="253" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S252" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="253" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O253" t="s">
-        <v>375</v>
+        <v>557</v>
       </c>
       <c r="P253" t="s">
         <v>8</v>
@@ -6665,10 +7928,13 @@
       <c r="R253">
         <v>-37.829918739943992</v>
       </c>
-    </row>
-    <row r="254" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S253" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="254" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O254" t="s">
-        <v>376</v>
+        <v>558</v>
       </c>
       <c r="P254" t="s">
         <v>8</v>
@@ -6679,10 +7945,13 @@
       <c r="R254">
         <v>-24.339791643388494</v>
       </c>
-    </row>
-    <row r="255" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S254" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="255" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O255" t="s">
-        <v>377</v>
+        <v>560</v>
       </c>
       <c r="P255" t="s">
         <v>8</v>
@@ -6693,10 +7962,13 @@
       <c r="R255">
         <v>-22.660298873087012</v>
       </c>
-    </row>
-    <row r="256" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S255" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="256" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O256" t="s">
-        <v>378</v>
+        <v>562</v>
       </c>
       <c r="P256" t="s">
         <v>8</v>
@@ -6707,10 +7979,13 @@
       <c r="R256">
         <v>-24.548778739246707</v>
       </c>
-    </row>
-    <row r="257" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S256" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="257" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O257" t="s">
-        <v>379</v>
+        <v>564</v>
       </c>
       <c r="P257" t="s">
         <v>8</v>
@@ -6721,10 +7996,13 @@
       <c r="R257">
         <v>-24.09724976838157</v>
       </c>
-    </row>
-    <row r="258" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S257" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="258" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O258" t="s">
-        <v>380</v>
+        <v>565</v>
       </c>
       <c r="P258" t="s">
         <v>8</v>
@@ -6735,10 +8013,13 @@
       <c r="R258">
         <v>-38.174584890819979</v>
       </c>
-    </row>
-    <row r="259" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S258" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="259" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O259" t="s">
-        <v>381</v>
+        <v>567</v>
       </c>
       <c r="P259" t="s">
         <v>8</v>
@@ -6749,10 +8030,13 @@
       <c r="R259">
         <v>-26.595631032117534</v>
       </c>
-    </row>
-    <row r="260" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S259" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="260" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O260" t="s">
-        <v>382</v>
+        <v>569</v>
       </c>
       <c r="P260" t="s">
         <v>8</v>
@@ -6763,10 +8047,13 @@
       <c r="R260">
         <v>-26.851379015168551</v>
       </c>
-    </row>
-    <row r="261" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S260" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="261" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O261" t="s">
-        <v>383</v>
+        <v>571</v>
       </c>
       <c r="P261" t="s">
         <v>8</v>
@@ -6777,10 +8064,13 @@
       <c r="R261">
         <v>-22.493300099751107</v>
       </c>
-    </row>
-    <row r="262" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S261" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="262" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O262" t="s">
-        <v>384</v>
+        <v>573</v>
       </c>
       <c r="P262" t="s">
         <v>8</v>
@@ -6791,10 +8081,13 @@
       <c r="R262">
         <v>-21.27831181122556</v>
       </c>
-    </row>
-    <row r="263" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S262" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="263" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O263" t="s">
-        <v>385</v>
+        <v>575</v>
       </c>
       <c r="P263" t="s">
         <v>8</v>
@@ -6805,10 +8098,13 @@
       <c r="R263">
         <v>-21.544050383279892</v>
       </c>
-    </row>
-    <row r="264" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S263" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="264" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O264" t="s">
-        <v>386</v>
+        <v>577</v>
       </c>
       <c r="P264" t="s">
         <v>8</v>
@@ -6819,10 +8115,13 @@
       <c r="R264">
         <v>-22.91061540635657</v>
       </c>
-    </row>
-    <row r="265" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S264" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="265" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O265" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
       <c r="P265" t="s">
         <v>8</v>
@@ -6833,10 +8132,13 @@
       <c r="R265">
         <v>-23.36259114408892</v>
       </c>
-    </row>
-    <row r="266" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S265" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="266" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O266" t="s">
-        <v>388</v>
+        <v>581</v>
       </c>
       <c r="P266" t="s">
         <v>8</v>
@@ -6847,10 +8149,13 @@
       <c r="R266">
         <v>-22.19879226832656</v>
       </c>
-    </row>
-    <row r="267" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S266" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="267" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O267" t="s">
-        <v>389</v>
+        <v>583</v>
       </c>
       <c r="P267" t="s">
         <v>8</v>
@@ -6861,10 +8166,13 @@
       <c r="R267">
         <v>-22.295755610725131</v>
       </c>
-    </row>
-    <row r="268" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S267" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="268" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O268" t="s">
-        <v>390</v>
+        <v>585</v>
       </c>
       <c r="P268" t="s">
         <v>8</v>
@@ -6875,10 +8183,13 @@
       <c r="R268">
         <v>-24.357617484853719</v>
       </c>
-    </row>
-    <row r="269" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S268" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="269" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O269" t="s">
-        <v>391</v>
+        <v>587</v>
       </c>
       <c r="P269" t="s">
         <v>8</v>
@@ -6889,10 +8200,13 @@
       <c r="R269">
         <v>-25.094212865580069</v>
       </c>
-    </row>
-    <row r="270" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S269" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="270" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O270" t="s">
-        <v>392</v>
+        <v>589</v>
       </c>
       <c r="P270" t="s">
         <v>8</v>
@@ -6903,10 +8217,13 @@
       <c r="R270">
         <v>-26.850317897683912</v>
       </c>
-    </row>
-    <row r="271" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S270" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="271" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O271" t="s">
-        <v>393</v>
+        <v>591</v>
       </c>
       <c r="P271" t="s">
         <v>8</v>
@@ -6917,10 +8234,13 @@
       <c r="R271">
         <v>-29.069482523035592</v>
       </c>
-    </row>
-    <row r="272" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S271" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="272" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O272" t="s">
-        <v>394</v>
+        <v>593</v>
       </c>
       <c r="P272" t="s">
         <v>8</v>
@@ -6931,10 +8251,13 @@
       <c r="R272">
         <v>-27.142611408067889</v>
       </c>
-    </row>
-    <row r="273" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S272" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="273" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O273" t="s">
-        <v>395</v>
+        <v>595</v>
       </c>
       <c r="P273" t="s">
         <v>8</v>
@@ -6945,10 +8268,13 @@
       <c r="R273">
         <v>-34.631126809612212</v>
       </c>
-    </row>
-    <row r="274" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S273" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="274" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O274" t="s">
-        <v>396</v>
+        <v>596</v>
       </c>
       <c r="P274" t="s">
         <v>8</v>
@@ -6959,10 +8285,13 @@
       <c r="R274">
         <v>-30.861063865580281</v>
       </c>
-    </row>
-    <row r="275" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S274" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="275" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O275" t="s">
-        <v>397</v>
+        <v>598</v>
       </c>
       <c r="P275" t="s">
         <v>8</v>
@@ -6973,10 +8302,13 @@
       <c r="R275">
         <v>-32.160947640007599</v>
       </c>
-    </row>
-    <row r="276" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S275" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="276" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O276" t="s">
-        <v>398</v>
+        <v>600</v>
       </c>
       <c r="P276" t="s">
         <v>8</v>
@@ -6987,10 +8319,13 @@
       <c r="R276">
         <v>-26.903893975033345</v>
       </c>
-    </row>
-    <row r="277" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S276" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="277" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O277" t="s">
-        <v>399</v>
+        <v>602</v>
       </c>
       <c r="P277" t="s">
         <v>8</v>
@@ -7001,10 +8336,13 @@
       <c r="R277">
         <v>-28.940424642755492</v>
       </c>
-    </row>
-    <row r="278" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S277" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="278" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O278" t="s">
-        <v>400</v>
+        <v>604</v>
       </c>
       <c r="P278" t="s">
         <v>8</v>
@@ -7015,10 +8353,13 @@
       <c r="R278">
         <v>-29.719049479687857</v>
       </c>
-    </row>
-    <row r="279" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S278" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="279" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O279" t="s">
-        <v>401</v>
+        <v>606</v>
       </c>
       <c r="P279" t="s">
         <v>8</v>
@@ -7029,10 +8370,13 @@
       <c r="R279">
         <v>-30.087420725859118</v>
       </c>
-    </row>
-    <row r="280" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S279" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="280" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O280" t="s">
-        <v>402</v>
+        <v>607</v>
       </c>
       <c r="P280" t="s">
         <v>8</v>
@@ -7043,10 +8387,13 @@
       <c r="R280">
         <v>-32.413854621654295</v>
       </c>
-    </row>
-    <row r="281" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S280" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="281" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O281" t="s">
-        <v>403</v>
+        <v>608</v>
       </c>
       <c r="P281" t="s">
         <v>8</v>
@@ -7057,10 +8404,13 @@
       <c r="R281">
         <v>-31.925669117423599</v>
       </c>
-    </row>
-    <row r="282" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S281" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="282" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O282" t="s">
-        <v>404</v>
+        <v>609</v>
       </c>
       <c r="P282" t="s">
         <v>8</v>
@@ -7071,94 +8421,115 @@
       <c r="R282">
         <v>-36.7528504674559</v>
       </c>
-    </row>
-    <row r="283" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S282" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="283" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O283" t="s">
-        <v>405</v>
+        <v>610</v>
       </c>
       <c r="P283" t="s">
         <v>8</v>
       </c>
       <c r="Q283">
+        <v>147.33244449422352</v>
+      </c>
+      <c r="R283">
+        <v>-42.675172685233107</v>
+      </c>
+      <c r="S283" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="284" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O284" t="s">
+        <v>611</v>
+      </c>
+      <c r="P284" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q284">
         <v>123.0900307495962</v>
       </c>
-      <c r="R283">
+      <c r="R284">
         <v>-18.602592489260651</v>
       </c>
-    </row>
-    <row r="284" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O284" t="s">
-        <v>406</v>
-      </c>
-      <c r="P284" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q284">
+      <c r="S284" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="285" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O285" t="s">
+        <v>613</v>
+      </c>
+      <c r="P285" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q285">
         <v>122.54308312197736</v>
       </c>
-      <c r="R284">
+      <c r="R285">
         <v>-20.355566838375449</v>
       </c>
-    </row>
-    <row r="285" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O285" t="s">
-        <v>407</v>
-      </c>
-      <c r="P285" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q285">
+      <c r="S285" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="286" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O286" t="s">
+        <v>615</v>
+      </c>
+      <c r="P286" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q286">
         <v>128.22766529346336</v>
       </c>
-      <c r="R285">
+      <c r="R286">
         <v>-19.496163382311977</v>
       </c>
-    </row>
-    <row r="286" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O286" t="s">
-        <v>408</v>
-      </c>
-      <c r="P286" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q286">
+      <c r="S286" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="287" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O287" t="s">
+        <v>617</v>
+      </c>
+      <c r="P287" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q287">
         <v>129.86196084560535</v>
       </c>
-      <c r="R286">
+      <c r="R287">
         <v>-14.565317050693372</v>
       </c>
-    </row>
-    <row r="287" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O287" t="s">
-        <v>409</v>
-      </c>
-      <c r="P287" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q287">
+      <c r="S287" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="288" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O288" t="s">
+        <v>619</v>
+      </c>
+      <c r="P288" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q288">
         <v>126.43376235886116</v>
       </c>
-      <c r="R287">
+      <c r="R288">
         <v>-17.866548200273396</v>
       </c>
-    </row>
-    <row r="288" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O288" t="s">
-        <v>410</v>
-      </c>
-      <c r="P288" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q288">
-        <v>147.23477366457425</v>
-      </c>
-      <c r="R288">
-        <v>-42.735045094737728</v>
-      </c>
-    </row>
-    <row r="289" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S288" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="289" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O289" t="s">
-        <v>411</v>
+        <v>621</v>
       </c>
       <c r="P289" t="s">
         <v>8</v>
@@ -7169,10 +8540,13 @@
       <c r="R289">
         <v>-28.350204599948327</v>
       </c>
-    </row>
-    <row r="290" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S289" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="290" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O290" t="s">
-        <v>412</v>
+        <v>623</v>
       </c>
       <c r="P290" t="s">
         <v>8</v>
@@ -7183,10 +8557,13 @@
       <c r="R290">
         <v>-28.183968446146601</v>
       </c>
-    </row>
-    <row r="291" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S290" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="291" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O291" t="s">
-        <v>413</v>
+        <v>625</v>
       </c>
       <c r="P291" t="s">
         <v>8</v>
@@ -7197,10 +8574,13 @@
       <c r="R291">
         <v>-27.580725512880846</v>
       </c>
-    </row>
-    <row r="292" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S291" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="292" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O292" t="s">
-        <v>414</v>
+        <v>627</v>
       </c>
       <c r="P292" t="s">
         <v>8</v>
@@ -7211,10 +8591,13 @@
       <c r="R292">
         <v>-25.58725211244526</v>
       </c>
-    </row>
-    <row r="293" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S292" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="293" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O293" t="s">
-        <v>415</v>
+        <v>629</v>
       </c>
       <c r="P293" t="s">
         <v>8</v>
@@ -7225,10 +8608,13 @@
       <c r="R293">
         <v>-31.392148397151932</v>
       </c>
-    </row>
-    <row r="294" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S293" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="294" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O294" t="s">
-        <v>416</v>
+        <v>631</v>
       </c>
       <c r="P294" t="s">
         <v>8</v>
@@ -7239,10 +8625,13 @@
       <c r="R294">
         <v>-30.359828636142097</v>
       </c>
-    </row>
-    <row r="295" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S294" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="295" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O295" t="s">
-        <v>417</v>
+        <v>633</v>
       </c>
       <c r="P295" t="s">
         <v>8</v>
@@ -7253,10 +8642,13 @@
       <c r="R295">
         <v>-30.892773675948479</v>
       </c>
-    </row>
-    <row r="296" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="S295" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="296" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O296" t="s">
-        <v>418</v>
+        <v>635</v>
       </c>
       <c r="P296" t="s">
         <v>8</v>
@@ -7266,6 +8658,9 @@
       </c>
       <c r="R296">
         <v>-32.109749022654</v>
+      </c>
+      <c r="S296" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14C7DC14-6377-45DA-B6CE-F1CE517B9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E9ED02-BDD3-461F-8562-AF392F2EA455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9D415FEC-CA3D-4C17-9B43-A7C217D7D3B9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7373C368-0149-4D5B-A333-3B30F3CFED23}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2320,7 +2320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841604C-4D8C-4334-811B-5CBD2666A8F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F89059-430C-46C9-B31C-0012B55579DF}">
   <dimension ref="B3:S296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E9ED02-BDD3-461F-8562-AF392F2EA455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8DE43B1-FB12-4E6E-9DA2-7CC35BEE1287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7373C368-0149-4D5B-A333-3B30F3CFED23}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{483137F1-6D34-4934-B657-66012C34E83B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2320,7 +2320,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F89059-430C-46C9-B31C-0012B55579DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EAF44D8-937F-4CF2-A091-D2602F8EA24F}">
   <dimension ref="B3:S296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
